--- a/public/data/Russian_Daily_Word.xlsx
+++ b/public/data/Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348E57C6-9D3E-4A80-97AF-160B2084287A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32FB89B-B479-4D50-AC53-D056DAFC431B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1728">
   <si>
     <t>Topic</t>
   </si>
@@ -4864,12 +4864,6 @@
     <t>🛋️</t>
   </si>
   <si>
-    <t>🟫</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🥭  </t>
-  </si>
-  <si>
     <t>🌶️</t>
   </si>
   <si>
@@ -4933,9 +4927,6 @@
     <t>🌃</t>
   </si>
   <si>
-    <t>🕒</t>
-  </si>
-  <si>
     <t>📅</t>
   </si>
   <si>
@@ -5050,12 +5041,6 @@
     <t>💰</t>
   </si>
   <si>
-    <t>💢</t>
-  </si>
-  <si>
-    <t>🔓</t>
-  </si>
-  <si>
     <t>🔒</t>
   </si>
   <si>
@@ -5095,15 +5080,6 @@
     <t>📍</t>
   </si>
   <si>
-    <t>👈</t>
-  </si>
-  <si>
-    <t>👉</t>
-  </si>
-  <si>
-    <t>😡</t>
-  </si>
-  <si>
     <t>🌟</t>
   </si>
   <si>
@@ -5140,9 +5116,6 @@
     <t>🐐</t>
   </si>
   <si>
-    <t>✨</t>
-  </si>
-  <si>
     <t>🐔</t>
   </si>
   <si>
@@ -5465,6 +5438,36 @@
   </si>
   <si>
     <t>Russian</t>
+  </si>
+  <si>
+    <t>⬜🟪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍢  </t>
+  </si>
+  <si>
+    <t>🧊🥶</t>
+  </si>
+  <si>
+    <t>🕛🌛</t>
+  </si>
+  <si>
+    <t>⌚</t>
+  </si>
+  <si>
+    <t>👉👈</t>
+  </si>
+  <si>
+    <t>👎</t>
+  </si>
+  <si>
+    <t>🫣</t>
+  </si>
+  <si>
+    <t>🤬</t>
+  </si>
+  <si>
+    <t>🔓🔑</t>
   </si>
 </sst>
 </file>
@@ -5863,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1726</v>
+        <v>1717</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1469</v>
@@ -6907,7 +6910,7 @@
         <v>234</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1526</v>
+        <v>1718</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>235</v>
@@ -6953,7 +6956,7 @@
         <v>244</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1527</v>
+        <v>1719</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>245</v>
@@ -7114,7 +7117,7 @@
         <v>279</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>280</v>
@@ -7137,7 +7140,7 @@
         <v>284</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>285</v>
@@ -7275,7 +7278,7 @@
         <v>314</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>315</v>
@@ -7298,7 +7301,7 @@
         <v>319</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>320</v>
@@ -7318,10 +7321,10 @@
         <v>323</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>324</v>
@@ -7344,7 +7347,7 @@
         <v>328</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>2</v>
@@ -7367,7 +7370,7 @@
         <v>332</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>333</v>
@@ -7390,7 +7393,7 @@
         <v>337</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>338</v>
@@ -7413,7 +7416,7 @@
         <v>342</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>343</v>
@@ -7482,7 +7485,7 @@
         <v>357</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>358</v>
@@ -7505,7 +7508,7 @@
         <v>362</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1554</v>
+        <v>1720</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>363</v>
@@ -7528,7 +7531,7 @@
         <v>367</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>368</v>
@@ -7551,7 +7554,7 @@
         <v>372</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>373</v>
@@ -7574,7 +7577,7 @@
         <v>377</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>378</v>
@@ -7597,7 +7600,7 @@
         <v>382</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>383</v>
@@ -7620,7 +7623,7 @@
         <v>387</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>388</v>
@@ -7643,7 +7646,7 @@
         <v>392</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>393</v>
@@ -7689,7 +7692,7 @@
         <v>402</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>403</v>
@@ -7712,7 +7715,7 @@
         <v>407</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>408</v>
@@ -7735,7 +7738,7 @@
         <v>412</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>413</v>
@@ -7804,7 +7807,7 @@
         <v>427</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>1</v>
@@ -7827,7 +7830,7 @@
         <v>431</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>432</v>
@@ -7850,7 +7853,7 @@
         <v>436</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>437</v>
@@ -7873,7 +7876,7 @@
         <v>441</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>442</v>
@@ -7896,7 +7899,7 @@
         <v>446</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1549</v>
+        <v>1721</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>447</v>
@@ -7919,7 +7922,7 @@
         <v>451</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1550</v>
+        <v>1722</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>452</v>
@@ -7942,7 +7945,7 @@
         <v>456</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>457</v>
@@ -7965,7 +7968,7 @@
         <v>461</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>462</v>
@@ -7988,7 +7991,7 @@
         <v>466</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>467</v>
@@ -8011,7 +8014,7 @@
         <v>471</v>
       </c>
       <c r="E94" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>472</v>
@@ -8034,7 +8037,7 @@
         <v>476</v>
       </c>
       <c r="E95" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>477</v>
@@ -8057,7 +8060,7 @@
         <v>481</v>
       </c>
       <c r="E96" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>482</v>
@@ -8080,7 +8083,7 @@
         <v>486</v>
       </c>
       <c r="E97" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>487</v>
@@ -8103,7 +8106,7 @@
         <v>491</v>
       </c>
       <c r="E98" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>492</v>
@@ -8126,7 +8129,7 @@
         <v>496</v>
       </c>
       <c r="E99" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>497</v>
@@ -8149,7 +8152,7 @@
         <v>501</v>
       </c>
       <c r="E100" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>502</v>
@@ -8172,7 +8175,7 @@
         <v>506</v>
       </c>
       <c r="E101" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>507</v>
@@ -8195,7 +8198,7 @@
         <v>511</v>
       </c>
       <c r="E102" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>512</v>
@@ -8218,7 +8221,7 @@
         <v>516</v>
       </c>
       <c r="E103" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>517</v>
@@ -8241,7 +8244,7 @@
         <v>521</v>
       </c>
       <c r="E104" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>522</v>
@@ -8264,7 +8267,7 @@
         <v>526</v>
       </c>
       <c r="E105" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>527</v>
@@ -8287,7 +8290,7 @@
         <v>531</v>
       </c>
       <c r="E106" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>532</v>
@@ -8310,7 +8313,7 @@
         <v>536</v>
       </c>
       <c r="E107" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>537</v>
@@ -8333,7 +8336,7 @@
         <v>541</v>
       </c>
       <c r="E108" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>542</v>
@@ -8356,7 +8359,7 @@
         <v>546</v>
       </c>
       <c r="E109" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>547</v>
@@ -8379,7 +8382,7 @@
         <v>551</v>
       </c>
       <c r="E110" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>552</v>
@@ -8402,7 +8405,7 @@
         <v>556</v>
       </c>
       <c r="E111" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>13</v>
@@ -8425,7 +8428,7 @@
         <v>560</v>
       </c>
       <c r="E112" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>561</v>
@@ -8448,7 +8451,7 @@
         <v>565</v>
       </c>
       <c r="E113" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>566</v>
@@ -8471,7 +8474,7 @@
         <v>570</v>
       </c>
       <c r="E114" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>571</v>
@@ -8494,7 +8497,7 @@
         <v>575</v>
       </c>
       <c r="E115" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>15</v>
@@ -8517,7 +8520,7 @@
         <v>579</v>
       </c>
       <c r="E116" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>580</v>
@@ -8540,7 +8543,7 @@
         <v>584</v>
       </c>
       <c r="E117" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>309</v>
@@ -8586,7 +8589,7 @@
         <v>593</v>
       </c>
       <c r="E119" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>594</v>
@@ -8609,7 +8612,7 @@
         <v>598</v>
       </c>
       <c r="E120" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>9</v>
@@ -8632,7 +8635,7 @@
         <v>602</v>
       </c>
       <c r="E121" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>603</v>
@@ -8655,7 +8658,7 @@
         <v>607</v>
       </c>
       <c r="E122" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>608</v>
@@ -8678,7 +8681,7 @@
         <v>612</v>
       </c>
       <c r="E123" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>613</v>
@@ -8701,7 +8704,7 @@
         <v>617</v>
       </c>
       <c r="E124" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>618</v>
@@ -8724,7 +8727,7 @@
         <v>622</v>
       </c>
       <c r="E125" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>12</v>
@@ -8747,7 +8750,7 @@
         <v>626</v>
       </c>
       <c r="E126" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>627</v>
@@ -8793,7 +8796,7 @@
         <v>636</v>
       </c>
       <c r="E128" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>637</v>
@@ -8816,7 +8819,7 @@
         <v>641</v>
       </c>
       <c r="E129" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>642</v>
@@ -8839,7 +8842,7 @@
         <v>646</v>
       </c>
       <c r="E130" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>647</v>
@@ -8862,7 +8865,7 @@
         <v>651</v>
       </c>
       <c r="E131" t="s">
-        <v>1588</v>
+        <v>1726</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>652</v>
@@ -8885,7 +8888,7 @@
         <v>656</v>
       </c>
       <c r="E132" t="s">
-        <v>1589</v>
+        <v>1727</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>319</v>
@@ -8908,7 +8911,7 @@
         <v>660</v>
       </c>
       <c r="E133" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>661</v>
@@ -8931,7 +8934,7 @@
         <v>665</v>
       </c>
       <c r="E134" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>666</v>
@@ -8954,7 +8957,7 @@
         <v>670</v>
       </c>
       <c r="E135" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>671</v>
@@ -8977,7 +8980,7 @@
         <v>675</v>
       </c>
       <c r="E136" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>676</v>
@@ -9000,7 +9003,7 @@
         <v>680</v>
       </c>
       <c r="E137" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>681</v>
@@ -9023,7 +9026,7 @@
         <v>685</v>
       </c>
       <c r="E138" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>686</v>
@@ -9046,7 +9049,7 @@
         <v>690</v>
       </c>
       <c r="E139" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>691</v>
@@ -9069,7 +9072,7 @@
         <v>695</v>
       </c>
       <c r="E140" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>696</v>
@@ -9092,7 +9095,7 @@
         <v>700</v>
       </c>
       <c r="E141" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>701</v>
@@ -9115,7 +9118,7 @@
         <v>705</v>
       </c>
       <c r="E142" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>706</v>
@@ -9138,7 +9141,7 @@
         <v>710</v>
       </c>
       <c r="E143" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>711</v>
@@ -9161,7 +9164,7 @@
         <v>715</v>
       </c>
       <c r="E144" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>716</v>
@@ -9184,7 +9187,7 @@
         <v>720</v>
       </c>
       <c r="E145" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>721</v>
@@ -9207,7 +9210,7 @@
         <v>725</v>
       </c>
       <c r="E146" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>726</v>
@@ -9230,7 +9233,7 @@
         <v>730</v>
       </c>
       <c r="E147" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>731</v>
@@ -9253,7 +9256,7 @@
         <v>735</v>
       </c>
       <c r="E148" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>736</v>
@@ -9276,7 +9279,7 @@
         <v>740</v>
       </c>
       <c r="E149" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>741</v>
@@ -9299,7 +9302,7 @@
         <v>300</v>
       </c>
       <c r="E150" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>745</v>
@@ -9322,7 +9325,7 @@
         <v>749</v>
       </c>
       <c r="E151" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>4</v>
@@ -9345,7 +9348,7 @@
         <v>753</v>
       </c>
       <c r="E152" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>754</v>
@@ -9368,7 +9371,7 @@
         <v>758</v>
       </c>
       <c r="E153" t="s">
-        <v>1603</v>
+        <v>1723</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>759</v>
@@ -9391,7 +9394,7 @@
         <v>763</v>
       </c>
       <c r="E154" t="s">
-        <v>1604</v>
+        <v>1724</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>764</v>
@@ -9414,7 +9417,7 @@
         <v>768</v>
       </c>
       <c r="E155" t="s">
-        <v>1618</v>
+        <v>1598</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>769</v>
@@ -9437,7 +9440,7 @@
         <v>773</v>
       </c>
       <c r="E156" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>774</v>
@@ -9460,7 +9463,7 @@
         <v>778</v>
       </c>
       <c r="E157" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>779</v>
@@ -9483,7 +9486,7 @@
         <v>783</v>
       </c>
       <c r="E158" t="s">
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>784</v>
@@ -9506,7 +9509,7 @@
         <v>788</v>
       </c>
       <c r="E159" t="s">
-        <v>1608</v>
+        <v>1574</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>789</v>
@@ -9529,7 +9532,7 @@
         <v>793</v>
       </c>
       <c r="E160" t="s">
-        <v>1609</v>
+        <v>1602</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>794</v>
@@ -9552,7 +9555,7 @@
         <v>798</v>
       </c>
       <c r="E161" t="s">
-        <v>1577</v>
+        <v>1725</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>799</v>
@@ -9575,7 +9578,7 @@
         <v>803</v>
       </c>
       <c r="E162" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>804</v>
@@ -9598,7 +9601,7 @@
         <v>808</v>
       </c>
       <c r="E163" t="s">
-        <v>1611</v>
+        <v>1603</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>809</v>
@@ -9621,7 +9624,7 @@
         <v>813</v>
       </c>
       <c r="E164" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>814</v>
@@ -9644,7 +9647,7 @@
         <v>818</v>
       </c>
       <c r="E165" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>819</v>
@@ -9667,7 +9670,7 @@
         <v>823</v>
       </c>
       <c r="E166" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>824</v>
@@ -9690,7 +9693,7 @@
         <v>828</v>
       </c>
       <c r="E167" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>829</v>
@@ -9713,7 +9716,7 @@
         <v>833</v>
       </c>
       <c r="E168" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>834</v>
@@ -9736,7 +9739,7 @@
         <v>838</v>
       </c>
       <c r="E169" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>839</v>
@@ -9759,7 +9762,7 @@
         <v>843</v>
       </c>
       <c r="E170" t="s">
-        <v>1619</v>
+        <v>1610</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>844</v>
@@ -9782,7 +9785,7 @@
         <v>848</v>
       </c>
       <c r="E171" t="s">
-        <v>1620</v>
+        <v>1611</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>849</v>
@@ -9805,7 +9808,7 @@
         <v>853</v>
       </c>
       <c r="E172" t="s">
-        <v>1621</v>
+        <v>1612</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>854</v>
@@ -9828,7 +9831,7 @@
         <v>858</v>
       </c>
       <c r="E173" t="s">
-        <v>1622</v>
+        <v>1613</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>859</v>
@@ -9851,7 +9854,7 @@
         <v>863</v>
       </c>
       <c r="E174" t="s">
-        <v>1623</v>
+        <v>1614</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>864</v>
@@ -9874,7 +9877,7 @@
         <v>868</v>
       </c>
       <c r="E175" t="s">
-        <v>1624</v>
+        <v>1615</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>869</v>
@@ -9897,7 +9900,7 @@
         <v>873</v>
       </c>
       <c r="E176" t="s">
-        <v>1625</v>
+        <v>1616</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>874</v>
@@ -9920,7 +9923,7 @@
         <v>878</v>
       </c>
       <c r="E177" t="s">
-        <v>1626</v>
+        <v>1617</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>879</v>
@@ -9943,7 +9946,7 @@
         <v>883</v>
       </c>
       <c r="E178" t="s">
-        <v>1627</v>
+        <v>1618</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>884</v>
@@ -9966,7 +9969,7 @@
         <v>888</v>
       </c>
       <c r="E179" t="s">
-        <v>1628</v>
+        <v>1619</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>889</v>
@@ -9989,7 +9992,7 @@
         <v>893</v>
       </c>
       <c r="E180" t="s">
-        <v>1629</v>
+        <v>1620</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>894</v>
@@ -10012,7 +10015,7 @@
         <v>898</v>
       </c>
       <c r="E181" t="s">
-        <v>1630</v>
+        <v>1621</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>899</v>
@@ -10035,7 +10038,7 @@
         <v>903</v>
       </c>
       <c r="E182" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>904</v>
@@ -10058,7 +10061,7 @@
         <v>908</v>
       </c>
       <c r="E183" t="s">
-        <v>1632</v>
+        <v>1623</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>909</v>
@@ -10081,7 +10084,7 @@
         <v>913</v>
       </c>
       <c r="E184" t="s">
-        <v>1633</v>
+        <v>1624</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>914</v>
@@ -10104,7 +10107,7 @@
         <v>918</v>
       </c>
       <c r="E185" t="s">
-        <v>1634</v>
+        <v>1625</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>919</v>
@@ -10127,7 +10130,7 @@
         <v>923</v>
       </c>
       <c r="E186" t="s">
-        <v>1635</v>
+        <v>1626</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>924</v>
@@ -10150,7 +10153,7 @@
         <v>928</v>
       </c>
       <c r="E187" t="s">
-        <v>1636</v>
+        <v>1627</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>929</v>
@@ -10173,7 +10176,7 @@
         <v>933</v>
       </c>
       <c r="E188" t="s">
-        <v>1637</v>
+        <v>1628</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>934</v>
@@ -10196,7 +10199,7 @@
         <v>938</v>
       </c>
       <c r="E189" t="s">
-        <v>1638</v>
+        <v>1629</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>939</v>
@@ -10219,7 +10222,7 @@
         <v>943</v>
       </c>
       <c r="E190" t="s">
-        <v>1639</v>
+        <v>1630</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>944</v>
@@ -10242,7 +10245,7 @@
         <v>948</v>
       </c>
       <c r="E191" t="s">
-        <v>1640</v>
+        <v>1631</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>949</v>
@@ -10265,7 +10268,7 @@
         <v>953</v>
       </c>
       <c r="E192" t="s">
-        <v>1641</v>
+        <v>1632</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>132</v>
@@ -10288,7 +10291,7 @@
         <v>957</v>
       </c>
       <c r="E193" t="s">
-        <v>1642</v>
+        <v>1633</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>958</v>
@@ -10311,7 +10314,7 @@
         <v>962</v>
       </c>
       <c r="E194" t="s">
-        <v>1643</v>
+        <v>1634</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>963</v>
@@ -10334,7 +10337,7 @@
         <v>967</v>
       </c>
       <c r="E195" t="s">
-        <v>1644</v>
+        <v>1635</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>968</v>
@@ -10357,7 +10360,7 @@
         <v>972</v>
       </c>
       <c r="E196" t="s">
-        <v>1645</v>
+        <v>1636</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>973</v>
@@ -10380,7 +10383,7 @@
         <v>977</v>
       </c>
       <c r="E197" t="s">
-        <v>1646</v>
+        <v>1637</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>978</v>
@@ -10403,7 +10406,7 @@
         <v>982</v>
       </c>
       <c r="E198" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>983</v>
@@ -10426,7 +10429,7 @@
         <v>987</v>
       </c>
       <c r="E199" t="s">
-        <v>1647</v>
+        <v>1638</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>988</v>
@@ -10449,7 +10452,7 @@
         <v>992</v>
       </c>
       <c r="E200" t="s">
-        <v>1648</v>
+        <v>1639</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>993</v>
@@ -10472,7 +10475,7 @@
         <v>997</v>
       </c>
       <c r="E201" t="s">
-        <v>1649</v>
+        <v>1640</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>998</v>
@@ -10495,7 +10498,7 @@
         <v>1002</v>
       </c>
       <c r="E202" t="s">
-        <v>1624</v>
+        <v>1615</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>1003</v>
@@ -10518,7 +10521,7 @@
         <v>1007</v>
       </c>
       <c r="E203" t="s">
-        <v>1650</v>
+        <v>1641</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>1008</v>
@@ -10541,7 +10544,7 @@
         <v>1012</v>
       </c>
       <c r="E204" t="s">
-        <v>1651</v>
+        <v>1642</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>1013</v>
@@ -10564,7 +10567,7 @@
         <v>1017</v>
       </c>
       <c r="E205" t="s">
-        <v>1652</v>
+        <v>1643</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>1018</v>
@@ -10587,7 +10590,7 @@
         <v>1022</v>
       </c>
       <c r="E206" t="s">
-        <v>1653</v>
+        <v>1644</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>1023</v>
@@ -10610,7 +10613,7 @@
         <v>1027</v>
       </c>
       <c r="E207" t="s">
-        <v>1654</v>
+        <v>1645</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>1028</v>
@@ -10633,7 +10636,7 @@
         <v>1032</v>
       </c>
       <c r="E208" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>1033</v>
@@ -10656,7 +10659,7 @@
         <v>1037</v>
       </c>
       <c r="E209" t="s">
-        <v>1655</v>
+        <v>1646</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>1038</v>
@@ -10679,7 +10682,7 @@
         <v>1042</v>
       </c>
       <c r="E210" t="s">
-        <v>1656</v>
+        <v>1647</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>1043</v>
@@ -10702,7 +10705,7 @@
         <v>1047</v>
       </c>
       <c r="E211" t="s">
-        <v>1657</v>
+        <v>1648</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>1048</v>
@@ -10725,7 +10728,7 @@
         <v>1052</v>
       </c>
       <c r="E212" t="s">
-        <v>1658</v>
+        <v>1649</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>1053</v>
@@ -10748,7 +10751,7 @@
         <v>1057</v>
       </c>
       <c r="E213" t="s">
-        <v>1654</v>
+        <v>1645</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>1058</v>
@@ -10771,7 +10774,7 @@
         <v>1062</v>
       </c>
       <c r="E214" t="s">
-        <v>1659</v>
+        <v>1650</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>1063</v>
@@ -10794,7 +10797,7 @@
         <v>1067</v>
       </c>
       <c r="E215" t="s">
-        <v>1660</v>
+        <v>1651</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>1068</v>
@@ -10817,7 +10820,7 @@
         <v>1072</v>
       </c>
       <c r="E216" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>1073</v>
@@ -10840,7 +10843,7 @@
         <v>1077</v>
       </c>
       <c r="E217" t="s">
-        <v>1661</v>
+        <v>1652</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>11</v>
@@ -10863,7 +10866,7 @@
         <v>1081</v>
       </c>
       <c r="E218" t="s">
-        <v>1662</v>
+        <v>1653</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>1082</v>
@@ -10886,7 +10889,7 @@
         <v>1086</v>
       </c>
       <c r="E219" t="s">
-        <v>1663</v>
+        <v>1654</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>1087</v>
@@ -10909,7 +10912,7 @@
         <v>1091</v>
       </c>
       <c r="E220" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>1092</v>
@@ -10932,7 +10935,7 @@
         <v>1096</v>
       </c>
       <c r="E221" t="s">
-        <v>1665</v>
+        <v>1656</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>1097</v>
@@ -10955,7 +10958,7 @@
         <v>1101</v>
       </c>
       <c r="E222" t="s">
-        <v>1666</v>
+        <v>1657</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>1102</v>
@@ -10978,7 +10981,7 @@
         <v>1106</v>
       </c>
       <c r="E223" t="s">
-        <v>1667</v>
+        <v>1658</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>1107</v>
@@ -11001,7 +11004,7 @@
         <v>1111</v>
       </c>
       <c r="E224" t="s">
-        <v>1668</v>
+        <v>1659</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>516</v>
@@ -11024,7 +11027,7 @@
         <v>1115</v>
       </c>
       <c r="E225" t="s">
-        <v>1669</v>
+        <v>1660</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>1116</v>
@@ -11047,7 +11050,7 @@
         <v>1120</v>
       </c>
       <c r="E226" t="s">
-        <v>1670</v>
+        <v>1661</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>1121</v>
@@ -11070,7 +11073,7 @@
         <v>16</v>
       </c>
       <c r="E227" t="s">
-        <v>1671</v>
+        <v>1662</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>1125</v>
@@ -11093,7 +11096,7 @@
         <v>1129</v>
       </c>
       <c r="E228" t="s">
-        <v>1672</v>
+        <v>1663</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>1130</v>
@@ -11116,7 +11119,7 @@
         <v>1134</v>
       </c>
       <c r="E229" t="s">
-        <v>1673</v>
+        <v>1664</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>1135</v>
@@ -11139,7 +11142,7 @@
         <v>1139</v>
       </c>
       <c r="E230" t="s">
-        <v>1674</v>
+        <v>1665</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>779</v>
@@ -11162,7 +11165,7 @@
         <v>1143</v>
       </c>
       <c r="E231" t="s">
-        <v>1675</v>
+        <v>1666</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>1144</v>
@@ -11185,7 +11188,7 @@
         <v>1148</v>
       </c>
       <c r="E232" t="s">
-        <v>1676</v>
+        <v>1667</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>1149</v>
@@ -11208,7 +11211,7 @@
         <v>1153</v>
       </c>
       <c r="E233" t="s">
-        <v>1677</v>
+        <v>1668</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>1154</v>
@@ -11231,7 +11234,7 @@
         <v>1158</v>
       </c>
       <c r="E234" t="s">
-        <v>1678</v>
+        <v>1669</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>1159</v>
@@ -11254,7 +11257,7 @@
         <v>1163</v>
       </c>
       <c r="E235" t="s">
-        <v>1679</v>
+        <v>1670</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>1164</v>
@@ -11277,7 +11280,7 @@
         <v>1170</v>
       </c>
       <c r="E236" t="s">
-        <v>1680</v>
+        <v>1671</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>1171</v>
@@ -11300,7 +11303,7 @@
         <v>1175</v>
       </c>
       <c r="E237" t="s">
-        <v>1681</v>
+        <v>1672</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>1176</v>
@@ -11323,7 +11326,7 @@
         <v>1180</v>
       </c>
       <c r="E238" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>1181</v>
@@ -11346,7 +11349,7 @@
         <v>1185</v>
       </c>
       <c r="E239" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>1186</v>
@@ -11369,7 +11372,7 @@
         <v>1190</v>
       </c>
       <c r="E240" t="s">
-        <v>1682</v>
+        <v>1673</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>1191</v>
@@ -11392,7 +11395,7 @@
         <v>8</v>
       </c>
       <c r="E241" t="s">
-        <v>1683</v>
+        <v>1674</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>1195</v>
@@ -11415,7 +11418,7 @@
         <v>1199</v>
       </c>
       <c r="E242" t="s">
-        <v>1684</v>
+        <v>1675</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>1200</v>
@@ -11438,7 +11441,7 @@
         <v>1204</v>
       </c>
       <c r="E243" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>1205</v>
@@ -11461,7 +11464,7 @@
         <v>1209</v>
       </c>
       <c r="E244" t="s">
-        <v>1685</v>
+        <v>1676</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>1210</v>
@@ -11484,7 +11487,7 @@
         <v>1214</v>
       </c>
       <c r="E245" t="s">
-        <v>1686</v>
+        <v>1677</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>1215</v>
@@ -11507,7 +11510,7 @@
         <v>1219</v>
       </c>
       <c r="E246" t="s">
-        <v>1687</v>
+        <v>1678</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>1220</v>
@@ -11530,7 +11533,7 @@
         <v>1224</v>
       </c>
       <c r="E247" t="s">
-        <v>1688</v>
+        <v>1679</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>1225</v>
@@ -11553,7 +11556,7 @@
         <v>1229</v>
       </c>
       <c r="E248" t="s">
-        <v>1689</v>
+        <v>1680</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>1230</v>
@@ -11576,7 +11579,7 @@
         <v>731</v>
       </c>
       <c r="E249" t="s">
-        <v>1690</v>
+        <v>1681</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>1234</v>
@@ -11599,7 +11602,7 @@
         <v>1238</v>
       </c>
       <c r="E250" t="s">
-        <v>1691</v>
+        <v>1682</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>6</v>
@@ -11622,7 +11625,7 @@
         <v>1242</v>
       </c>
       <c r="E251" t="s">
-        <v>1692</v>
+        <v>1683</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>1243</v>
@@ -11645,7 +11648,7 @@
         <v>1247</v>
       </c>
       <c r="E252" t="s">
-        <v>1693</v>
+        <v>1684</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>1248</v>
@@ -11668,7 +11671,7 @@
         <v>1252</v>
       </c>
       <c r="E253" t="s">
-        <v>1694</v>
+        <v>1685</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>1253</v>
@@ -11691,7 +11694,7 @@
         <v>1257</v>
       </c>
       <c r="E254" t="s">
-        <v>1695</v>
+        <v>1686</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>1258</v>
@@ -11714,7 +11717,7 @@
         <v>1262</v>
       </c>
       <c r="E255" t="s">
-        <v>1696</v>
+        <v>1687</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>1263</v>
@@ -11737,7 +11740,7 @@
         <v>1267</v>
       </c>
       <c r="E256" t="s">
-        <v>1697</v>
+        <v>1688</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>7</v>
@@ -11760,7 +11763,7 @@
         <v>3</v>
       </c>
       <c r="E257" t="s">
-        <v>1698</v>
+        <v>1689</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>1271</v>
@@ -11783,7 +11786,7 @@
         <v>1275</v>
       </c>
       <c r="E258" t="s">
-        <v>1699</v>
+        <v>1690</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>1153</v>
@@ -11806,7 +11809,7 @@
         <v>1279</v>
       </c>
       <c r="E259" t="s">
-        <v>1700</v>
+        <v>1691</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>1280</v>
@@ -11829,7 +11832,7 @@
         <v>1284</v>
       </c>
       <c r="E260" t="s">
-        <v>1701</v>
+        <v>1692</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>1285</v>
@@ -11852,7 +11855,7 @@
         <v>1289</v>
       </c>
       <c r="E261" t="s">
-        <v>1702</v>
+        <v>1693</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>1290</v>
@@ -11875,7 +11878,7 @@
         <v>1294</v>
       </c>
       <c r="E262" t="s">
-        <v>1703</v>
+        <v>1694</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>1295</v>
@@ -11898,7 +11901,7 @@
         <v>1299</v>
       </c>
       <c r="E263" t="s">
-        <v>1704</v>
+        <v>1695</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>1300</v>
@@ -11921,7 +11924,7 @@
         <v>1304</v>
       </c>
       <c r="E264" t="s">
-        <v>1705</v>
+        <v>1696</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>1305</v>
@@ -11944,7 +11947,7 @@
         <v>1309</v>
       </c>
       <c r="E265" t="s">
-        <v>1706</v>
+        <v>1697</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>1310</v>
@@ -11967,7 +11970,7 @@
         <v>1315</v>
       </c>
       <c r="E266" t="s">
-        <v>1707</v>
+        <v>1698</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>1316</v>
@@ -11990,7 +11993,7 @@
         <v>1319</v>
       </c>
       <c r="E267" t="s">
-        <v>1724</v>
+        <v>1715</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>1320</v>
@@ -12013,7 +12016,7 @@
         <v>1323</v>
       </c>
       <c r="E268" t="s">
-        <v>1725</v>
+        <v>1716</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>1324</v>
@@ -12036,7 +12039,7 @@
         <v>1295</v>
       </c>
       <c r="E269" t="s">
-        <v>1708</v>
+        <v>1699</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>4</v>
@@ -12059,7 +12062,7 @@
         <v>1331</v>
       </c>
       <c r="E270" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>1332</v>
@@ -12082,7 +12085,7 @@
         <v>1336</v>
       </c>
       <c r="E271" t="s">
-        <v>1709</v>
+        <v>1700</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>1337</v>
@@ -12108,7 +12111,7 @@
         <v>1341</v>
       </c>
       <c r="E272" t="s">
-        <v>1710</v>
+        <v>1701</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>1342</v>
@@ -12131,7 +12134,7 @@
         <v>1346</v>
       </c>
       <c r="E273" t="s">
-        <v>1711</v>
+        <v>1702</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>1347</v>
@@ -12154,7 +12157,7 @@
         <v>1351</v>
       </c>
       <c r="E274" t="s">
-        <v>1712</v>
+        <v>1703</v>
       </c>
       <c r="F274" s="2" t="s">
         <v>1352</v>
@@ -12177,7 +12180,7 @@
         <v>1356</v>
       </c>
       <c r="E275" t="s">
-        <v>1713</v>
+        <v>1704</v>
       </c>
       <c r="F275" s="2" t="s">
         <v>1357</v>
@@ -12200,7 +12203,7 @@
         <v>1361</v>
       </c>
       <c r="E276" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>1362</v>
@@ -12223,7 +12226,7 @@
         <v>1366</v>
       </c>
       <c r="E277" t="s">
-        <v>1658</v>
+        <v>1649</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>1367</v>
@@ -12243,7 +12246,7 @@
         <v>1371</v>
       </c>
       <c r="E278" t="s">
-        <v>1714</v>
+        <v>1705</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>1312</v>
@@ -12266,7 +12269,7 @@
         <v>1375</v>
       </c>
       <c r="E279" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>1376</v>
@@ -12289,7 +12292,7 @@
         <v>1380</v>
       </c>
       <c r="E280" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>1381</v>
@@ -12312,7 +12315,7 @@
         <v>1385</v>
       </c>
       <c r="E281" t="s">
-        <v>1715</v>
+        <v>1706</v>
       </c>
       <c r="F281" s="2" t="s">
         <v>1386</v>
@@ -12335,7 +12338,7 @@
         <v>1390</v>
       </c>
       <c r="E282" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="F282" s="2" t="s">
         <v>1391</v>
@@ -12358,7 +12361,7 @@
         <v>1395</v>
       </c>
       <c r="E283" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>1396</v>
@@ -12381,7 +12384,7 @@
         <v>1400</v>
       </c>
       <c r="E284" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>1401</v>
@@ -12404,7 +12407,7 @@
         <v>1405</v>
       </c>
       <c r="E285" t="s">
-        <v>1716</v>
+        <v>1707</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>1406</v>
@@ -12427,7 +12430,7 @@
         <v>1410</v>
       </c>
       <c r="E286" t="s">
-        <v>1717</v>
+        <v>1708</v>
       </c>
       <c r="F286" s="2" t="s">
         <v>171</v>
@@ -12447,7 +12450,7 @@
         <v>1414</v>
       </c>
       <c r="E287" t="s">
-        <v>1718</v>
+        <v>1709</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>1415</v>
@@ -12470,7 +12473,7 @@
         <v>1419</v>
       </c>
       <c r="E288" t="s">
-        <v>1719</v>
+        <v>1710</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>1420</v>
@@ -12493,7 +12496,7 @@
         <v>1167</v>
       </c>
       <c r="E289" t="s">
-        <v>1720</v>
+        <v>1711</v>
       </c>
       <c r="F289" s="2" t="s">
         <v>1423</v>
@@ -12516,7 +12519,7 @@
         <v>1427</v>
       </c>
       <c r="E290" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>1428</v>
@@ -12539,7 +12542,7 @@
         <v>1432</v>
       </c>
       <c r="E291" t="s">
-        <v>1721</v>
+        <v>1712</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>1433</v>
@@ -12562,7 +12565,7 @@
         <v>1437</v>
       </c>
       <c r="E292" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>1438</v>
@@ -12585,7 +12588,7 @@
         <v>1441</v>
       </c>
       <c r="E293" t="s">
-        <v>1722</v>
+        <v>1713</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>1442</v>
@@ -12608,7 +12611,7 @@
         <v>1077</v>
       </c>
       <c r="E294" t="s">
-        <v>1664</v>
+        <v>1655</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>1446</v>
@@ -12631,7 +12634,7 @@
         <v>1199</v>
       </c>
       <c r="E295" t="s">
-        <v>1684</v>
+        <v>1675</v>
       </c>
       <c r="F295" s="2" t="s">
         <v>1200</v>
@@ -12654,7 +12657,7 @@
         <v>1204</v>
       </c>
       <c r="E296" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>1205</v>
@@ -12677,7 +12680,7 @@
         <v>1209</v>
       </c>
       <c r="E297" t="s">
-        <v>1708</v>
+        <v>1699</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>1210</v>
@@ -12700,7 +12703,7 @@
         <v>1214</v>
       </c>
       <c r="E298" t="s">
-        <v>1723</v>
+        <v>1714</v>
       </c>
       <c r="F298" s="2" t="s">
         <v>1215</v>

--- a/public/data/Russian_Daily_Word.xlsx
+++ b/public/data/Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32FB89B-B479-4D50-AC53-D056DAFC431B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4A8997-7D6E-4DD6-B18C-59FBFFC67CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="1728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="1722">
   <si>
     <t>Topic</t>
   </si>
@@ -558,21 +558,6 @@
   </si>
   <si>
     <t>הצֶ'סְנוֹק עוצמתי כמו השח בשחמט</t>
-  </si>
-  <si>
-    <t>кура</t>
-  </si>
-  <si>
-    <t>קוּרָה</t>
-  </si>
-  <si>
-    <t>עוף</t>
-  </si>
-  <si>
-    <t>קוקוריקו</t>
-  </si>
-  <si>
-    <t>הקוּרָה קורה קוקוריקו כשהשמש זורחת</t>
   </si>
   <si>
     <t>грибы</t>
@@ -4790,9 +4775,6 @@
   </si>
   <si>
     <t>🧄</t>
-  </si>
-  <si>
-    <t>🍗</t>
   </si>
   <si>
     <t>🍄</t>
@@ -5849,7 +5831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L298"/>
+  <dimension ref="A1:L297"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -5866,27 +5848,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1717</v>
+        <v>1711</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -5898,7 +5880,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>20</v>
@@ -5909,7 +5891,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -5921,7 +5903,7 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>25</v>
@@ -5932,7 +5914,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -5944,18 +5926,18 @@
         <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -5967,7 +5949,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>34</v>
@@ -5978,7 +5960,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
@@ -5990,7 +5972,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>39</v>
@@ -6001,7 +5983,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
@@ -6013,7 +5995,7 @@
         <v>43</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>44</v>
@@ -6024,7 +6006,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
@@ -6036,7 +6018,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>49</v>
@@ -6047,7 +6029,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B9" t="s">
         <v>51</v>
@@ -6059,7 +6041,7 @@
         <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
@@ -6070,7 +6052,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
@@ -6082,7 +6064,7 @@
         <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>58</v>
@@ -6093,7 +6075,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B11" t="s">
         <v>60</v>
@@ -6105,7 +6087,7 @@
         <v>62</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>14</v>
@@ -6116,7 +6098,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B12" t="s">
         <v>64</v>
@@ -6128,7 +6110,7 @@
         <v>66</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>67</v>
@@ -6139,7 +6121,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
@@ -6151,7 +6133,7 @@
         <v>71</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>72</v>
@@ -6162,7 +6144,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B14" t="s">
         <v>74</v>
@@ -6174,7 +6156,7 @@
         <v>76</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
@@ -6185,7 +6167,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B15" t="s">
         <v>79</v>
@@ -6197,7 +6179,7 @@
         <v>81</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>82</v>
@@ -6208,7 +6190,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B16" t="s">
         <v>84</v>
@@ -6220,7 +6202,7 @@
         <v>86</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>87</v>
@@ -6231,7 +6213,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B17" t="s">
         <v>89</v>
@@ -6243,7 +6225,7 @@
         <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>92</v>
@@ -6254,7 +6236,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B18" t="s">
         <v>94</v>
@@ -6266,7 +6248,7 @@
         <v>96</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>97</v>
@@ -6277,7 +6259,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B19" t="s">
         <v>99</v>
@@ -6289,7 +6271,7 @@
         <v>101</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>102</v>
@@ -6300,7 +6282,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B20" t="s">
         <v>104</v>
@@ -6312,7 +6294,7 @@
         <v>106</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>107</v>
@@ -6323,7 +6305,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B21" t="s">
         <v>109</v>
@@ -6335,7 +6317,7 @@
         <v>111</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>112</v>
@@ -6346,7 +6328,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B22" t="s">
         <v>114</v>
@@ -6358,7 +6340,7 @@
         <v>116</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>117</v>
@@ -6369,7 +6351,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B23" t="s">
         <v>119</v>
@@ -6381,7 +6363,7 @@
         <v>121</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>122</v>
@@ -6392,7 +6374,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B24" t="s">
         <v>124</v>
@@ -6404,7 +6386,7 @@
         <v>126</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>127</v>
@@ -6415,7 +6397,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B25" t="s">
         <v>129</v>
@@ -6427,7 +6409,7 @@
         <v>131</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>132</v>
@@ -6438,7 +6420,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B26" t="s">
         <v>134</v>
@@ -6450,7 +6432,7 @@
         <v>136</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>137</v>
@@ -6461,7 +6443,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B27" t="s">
         <v>139</v>
@@ -6473,7 +6455,7 @@
         <v>141</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>142</v>
@@ -6484,7 +6466,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B28" t="s">
         <v>144</v>
@@ -6496,7 +6478,7 @@
         <v>146</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>147</v>
@@ -6507,7 +6489,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B29" t="s">
         <v>149</v>
@@ -6519,7 +6501,7 @@
         <v>151</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>152</v>
@@ -6530,7 +6512,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B30" t="s">
         <v>154</v>
@@ -6542,7 +6524,7 @@
         <v>156</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>157</v>
@@ -6553,7 +6535,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B31" t="s">
         <v>159</v>
@@ -6565,7 +6547,7 @@
         <v>161</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>162</v>
@@ -6576,7 +6558,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B32" t="s">
         <v>164</v>
@@ -6588,7 +6570,7 @@
         <v>166</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>167</v>
@@ -6599,7 +6581,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B33" t="s">
         <v>169</v>
@@ -6611,7 +6593,7 @@
         <v>171</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>172</v>
@@ -6622,7 +6604,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B34" t="s">
         <v>174</v>
@@ -6634,7 +6616,7 @@
         <v>176</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>177</v>
@@ -6645,7 +6627,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B35" t="s">
         <v>179</v>
@@ -6657,7 +6639,7 @@
         <v>181</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>182</v>
@@ -6668,7 +6650,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B36" t="s">
         <v>184</v>
@@ -6677,33 +6659,33 @@
         <v>185</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="G36" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B37" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>191</v>
@@ -6714,7 +6696,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B38" t="s">
         <v>193</v>
@@ -6726,33 +6708,33 @@
         <v>195</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="F38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>201</v>
@@ -6760,7 +6742,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B40" t="s">
         <v>202</v>
@@ -6772,7 +6754,7 @@
         <v>204</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>205</v>
@@ -6783,7 +6765,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B41" t="s">
         <v>207</v>
@@ -6795,7 +6777,7 @@
         <v>209</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>210</v>
@@ -6806,7 +6788,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B42" t="s">
         <v>212</v>
@@ -6818,7 +6800,7 @@
         <v>214</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>215</v>
@@ -6829,7 +6811,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B43" t="s">
         <v>217</v>
@@ -6841,7 +6823,7 @@
         <v>219</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>220</v>
@@ -6852,7 +6834,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B44" t="s">
         <v>222</v>
@@ -6864,7 +6846,7 @@
         <v>224</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>225</v>
@@ -6875,7 +6857,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B45" t="s">
         <v>227</v>
@@ -6887,7 +6869,7 @@
         <v>229</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1514</v>
+        <v>1712</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>230</v>
@@ -6898,7 +6880,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B46" t="s">
         <v>232</v>
@@ -6910,7 +6892,7 @@
         <v>234</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1718</v>
+        <v>1509</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>235</v>
@@ -6921,7 +6903,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B47" t="s">
         <v>237</v>
@@ -6933,7 +6915,7 @@
         <v>239</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1515</v>
+        <v>1713</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>240</v>
@@ -6944,7 +6926,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B48" t="s">
         <v>242</v>
@@ -6956,7 +6938,7 @@
         <v>244</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1719</v>
+        <v>1510</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>245</v>
@@ -6967,7 +6949,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B49" t="s">
         <v>247</v>
@@ -6979,7 +6961,7 @@
         <v>249</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>250</v>
@@ -6990,7 +6972,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B50" t="s">
         <v>252</v>
@@ -7002,7 +6984,7 @@
         <v>254</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>255</v>
@@ -7013,7 +6995,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B51" t="s">
         <v>257</v>
@@ -7025,7 +7007,7 @@
         <v>259</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>260</v>
@@ -7036,7 +7018,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B52" t="s">
         <v>262</v>
@@ -7048,7 +7030,7 @@
         <v>264</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>265</v>
@@ -7059,7 +7041,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B53" t="s">
         <v>267</v>
@@ -7071,7 +7053,7 @@
         <v>269</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1520</v>
+        <v>1492</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>270</v>
@@ -7082,7 +7064,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B54" t="s">
         <v>272</v>
@@ -7094,7 +7076,7 @@
         <v>274</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1497</v>
+        <v>1520</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>275</v>
@@ -7105,7 +7087,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="B55" t="s">
         <v>277</v>
@@ -7117,7 +7099,7 @@
         <v>279</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>280</v>
@@ -7128,7 +7110,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="B56" t="s">
         <v>282</v>
@@ -7140,7 +7122,7 @@
         <v>284</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1527</v>
+        <v>1515</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>285</v>
@@ -7151,7 +7133,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B57" t="s">
         <v>287</v>
@@ -7163,7 +7145,7 @@
         <v>289</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>290</v>
@@ -7174,7 +7156,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B58" t="s">
         <v>292</v>
@@ -7186,7 +7168,7 @@
         <v>294</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>295</v>
@@ -7197,7 +7179,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B59" t="s">
         <v>297</v>
@@ -7209,7 +7191,7 @@
         <v>299</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>300</v>
@@ -7220,7 +7202,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B60" t="s">
         <v>302</v>
@@ -7232,7 +7214,7 @@
         <v>304</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>305</v>
@@ -7243,7 +7225,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B61" t="s">
         <v>307</v>
@@ -7255,7 +7237,7 @@
         <v>309</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>310</v>
@@ -7266,7 +7248,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B62" t="s">
         <v>312</v>
@@ -7278,7 +7260,7 @@
         <v>314</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>315</v>
@@ -7289,7 +7271,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B63" t="s">
         <v>317</v>
@@ -7298,59 +7280,59 @@
         <v>318</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>1529</v>
-      </c>
-      <c r="F63" s="2" t="s">
+      <c r="G63" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B64" t="s">
+        <v>321</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>1549</v>
-      </c>
       <c r="E64" s="2" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="F64" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B65" t="s">
+        <v>325</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>1530</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>2</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>329</v>
@@ -7358,7 +7340,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B66" t="s">
         <v>330</v>
@@ -7370,7 +7352,7 @@
         <v>332</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1531</v>
+        <v>1544</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>333</v>
@@ -7381,7 +7363,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B67" t="s">
         <v>335</v>
@@ -7393,7 +7375,7 @@
         <v>337</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1550</v>
+        <v>1526</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>338</v>
@@ -7404,7 +7386,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B68" t="s">
         <v>340</v>
@@ -7416,7 +7398,7 @@
         <v>342</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1532</v>
+        <v>1519</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>343</v>
@@ -7427,7 +7409,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B69" t="s">
         <v>345</v>
@@ -7439,7 +7421,7 @@
         <v>347</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>348</v>
@@ -7450,7 +7432,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B70" t="s">
         <v>350</v>
@@ -7462,7 +7444,7 @@
         <v>352</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>353</v>
@@ -7473,7 +7455,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B71" t="s">
         <v>355</v>
@@ -7485,7 +7467,7 @@
         <v>357</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1533</v>
+        <v>1714</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>358</v>
@@ -7496,7 +7478,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B72" t="s">
         <v>360</v>
@@ -7508,7 +7490,7 @@
         <v>362</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1720</v>
+        <v>1528</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>363</v>
@@ -7519,7 +7501,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B73" t="s">
         <v>365</v>
@@ -7531,7 +7513,7 @@
         <v>367</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>368</v>
@@ -7542,7 +7524,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B74" t="s">
         <v>370</v>
@@ -7554,7 +7536,7 @@
         <v>372</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>373</v>
@@ -7565,7 +7547,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B75" t="s">
         <v>375</v>
@@ -7577,7 +7559,7 @@
         <v>377</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>378</v>
@@ -7588,7 +7570,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B76" t="s">
         <v>380</v>
@@ -7600,7 +7582,7 @@
         <v>382</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>383</v>
@@ -7611,7 +7593,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B77" t="s">
         <v>385</v>
@@ -7623,7 +7605,7 @@
         <v>387</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>388</v>
@@ -7634,7 +7616,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B78" t="s">
         <v>390</v>
@@ -7646,7 +7628,7 @@
         <v>392</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1539</v>
+        <v>1517</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>393</v>
@@ -7657,7 +7639,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B79" t="s">
         <v>395</v>
@@ -7669,7 +7651,7 @@
         <v>397</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1523</v>
+        <v>1534</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>398</v>
@@ -7680,7 +7662,7 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B80" t="s">
         <v>400</v>
@@ -7692,7 +7674,7 @@
         <v>402</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>403</v>
@@ -7703,7 +7685,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B81" t="s">
         <v>405</v>
@@ -7715,7 +7697,7 @@
         <v>407</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>408</v>
@@ -7726,7 +7708,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B82" t="s">
         <v>410</v>
@@ -7738,7 +7720,7 @@
         <v>412</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1542</v>
+        <v>1515</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>413</v>
@@ -7749,7 +7731,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B83" t="s">
         <v>415</v>
@@ -7761,7 +7743,7 @@
         <v>417</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>418</v>
@@ -7772,7 +7754,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B84" t="s">
         <v>420</v>
@@ -7784,33 +7766,33 @@
         <v>422</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1524</v>
+        <v>1537</v>
       </c>
       <c r="F84" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G84" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="B85" t="s">
+        <v>424</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>1543</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>428</v>
@@ -7818,7 +7800,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B86" t="s">
         <v>429</v>
@@ -7830,7 +7812,7 @@
         <v>431</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>432</v>
@@ -7841,7 +7823,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B87" t="s">
         <v>434</v>
@@ -7853,7 +7835,7 @@
         <v>436</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>437</v>
@@ -7864,7 +7846,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B88" t="s">
         <v>439</v>
@@ -7876,7 +7858,7 @@
         <v>441</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1546</v>
+        <v>1715</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>442</v>
@@ -7887,7 +7869,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B89" t="s">
         <v>444</v>
@@ -7899,7 +7881,7 @@
         <v>446</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1721</v>
+        <v>1716</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>447</v>
@@ -7910,7 +7892,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B90" t="s">
         <v>449</v>
@@ -7922,7 +7904,7 @@
         <v>451</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1722</v>
+        <v>1542</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>452</v>
@@ -7933,7 +7915,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B91" t="s">
         <v>454</v>
@@ -7945,7 +7927,7 @@
         <v>456</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>457</v>
@@ -7956,7 +7938,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B92" t="s">
         <v>459</v>
@@ -7968,7 +7950,7 @@
         <v>461</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>462</v>
@@ -7979,7 +7961,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B93" t="s">
         <v>464</v>
@@ -7990,8 +7972,8 @@
       <c r="D93" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>1548</v>
+      <c r="E93" t="s">
+        <v>1546</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>467</v>
@@ -8002,7 +7984,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B94" t="s">
         <v>469</v>
@@ -8014,7 +7996,7 @@
         <v>471</v>
       </c>
       <c r="E94" t="s">
-        <v>1552</v>
+        <v>1541</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>472</v>
@@ -8025,7 +8007,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B95" t="s">
         <v>474</v>
@@ -8048,7 +8030,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B96" t="s">
         <v>479</v>
@@ -8060,7 +8042,7 @@
         <v>481</v>
       </c>
       <c r="E96" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>482</v>
@@ -8071,7 +8053,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B97" t="s">
         <v>484</v>
@@ -8083,7 +8065,7 @@
         <v>486</v>
       </c>
       <c r="E97" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>487</v>
@@ -8094,7 +8076,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B98" t="s">
         <v>489</v>
@@ -8106,7 +8088,7 @@
         <v>491</v>
       </c>
       <c r="E98" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>492</v>
@@ -8117,7 +8099,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B99" t="s">
         <v>494</v>
@@ -8129,7 +8111,7 @@
         <v>496</v>
       </c>
       <c r="E99" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>497</v>
@@ -8140,7 +8122,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="B100" t="s">
         <v>499</v>
@@ -8152,7 +8134,7 @@
         <v>501</v>
       </c>
       <c r="E100" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>502</v>
@@ -8163,7 +8145,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B101" t="s">
         <v>504</v>
@@ -8175,7 +8157,7 @@
         <v>506</v>
       </c>
       <c r="E101" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>507</v>
@@ -8186,7 +8168,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B102" t="s">
         <v>509</v>
@@ -8198,7 +8180,7 @@
         <v>511</v>
       </c>
       <c r="E102" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>512</v>
@@ -8209,7 +8191,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B103" t="s">
         <v>514</v>
@@ -8221,7 +8203,7 @@
         <v>516</v>
       </c>
       <c r="E103" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>517</v>
@@ -8232,7 +8214,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B104" t="s">
         <v>519</v>
@@ -8244,7 +8226,7 @@
         <v>521</v>
       </c>
       <c r="E104" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>522</v>
@@ -8255,7 +8237,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B105" t="s">
         <v>524</v>
@@ -8267,7 +8249,7 @@
         <v>526</v>
       </c>
       <c r="E105" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>527</v>
@@ -8278,7 +8260,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B106" t="s">
         <v>529</v>
@@ -8290,7 +8272,7 @@
         <v>531</v>
       </c>
       <c r="E106" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>532</v>
@@ -8301,7 +8283,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B107" t="s">
         <v>534</v>
@@ -8313,7 +8295,7 @@
         <v>536</v>
       </c>
       <c r="E107" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>537</v>
@@ -8324,7 +8306,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B108" t="s">
         <v>539</v>
@@ -8336,7 +8318,7 @@
         <v>541</v>
       </c>
       <c r="E108" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>542</v>
@@ -8347,7 +8329,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B109" t="s">
         <v>544</v>
@@ -8359,7 +8341,7 @@
         <v>546</v>
       </c>
       <c r="E109" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>547</v>
@@ -8370,7 +8352,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B110" t="s">
         <v>549</v>
@@ -8382,33 +8364,33 @@
         <v>551</v>
       </c>
       <c r="E110" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="F110" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B111" t="s">
+        <v>553</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="E111" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F111" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="E111" t="s">
-        <v>1568</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>557</v>
@@ -8416,7 +8398,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B112" t="s">
         <v>558</v>
@@ -8428,7 +8410,7 @@
         <v>560</v>
       </c>
       <c r="E112" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>561</v>
@@ -8439,7 +8421,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B113" t="s">
         <v>563</v>
@@ -8451,7 +8433,7 @@
         <v>565</v>
       </c>
       <c r="E113" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>566</v>
@@ -8462,7 +8444,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B114" t="s">
         <v>568</v>
@@ -8474,33 +8456,33 @@
         <v>570</v>
       </c>
       <c r="E114" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
       <c r="F114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G114" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B115" t="s">
+        <v>572</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="E115" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F115" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="E115" t="s">
-        <v>1572</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>576</v>
@@ -8508,7 +8490,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B116" t="s">
         <v>577</v>
@@ -8520,33 +8502,33 @@
         <v>579</v>
       </c>
       <c r="E116" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="F116" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B117" t="s">
+        <v>581</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="E117" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="E117" t="s">
-        <v>1574</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>585</v>
@@ -8554,7 +8536,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B118" t="s">
         <v>586</v>
@@ -8566,7 +8548,7 @@
         <v>588</v>
       </c>
       <c r="E118" t="s">
-        <v>1521</v>
+        <v>1569</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>589</v>
@@ -8577,7 +8559,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B119" t="s">
         <v>591</v>
@@ -8589,33 +8571,33 @@
         <v>593</v>
       </c>
       <c r="E119" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="F119" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G119" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B120" t="s">
+        <v>595</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="E120" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="E120" t="s">
-        <v>1576</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>599</v>
@@ -8623,7 +8605,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B121" t="s">
         <v>600</v>
@@ -8635,7 +8617,7 @@
         <v>602</v>
       </c>
       <c r="E121" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>603</v>
@@ -8646,7 +8628,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B122" t="s">
         <v>605</v>
@@ -8658,7 +8640,7 @@
         <v>607</v>
       </c>
       <c r="E122" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>608</v>
@@ -8669,7 +8651,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B123" t="s">
         <v>610</v>
@@ -8681,7 +8663,7 @@
         <v>612</v>
       </c>
       <c r="E123" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>613</v>
@@ -8692,7 +8674,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B124" t="s">
         <v>615</v>
@@ -8704,33 +8686,33 @@
         <v>617</v>
       </c>
       <c r="E124" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="F124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B125" t="s">
+        <v>619</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="E125" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F125" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="E125" t="s">
-        <v>1581</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>623</v>
@@ -8738,7 +8720,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B126" t="s">
         <v>624</v>
@@ -8750,7 +8732,7 @@
         <v>626</v>
       </c>
       <c r="E126" t="s">
-        <v>1582</v>
+        <v>1517</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>627</v>
@@ -8761,7 +8743,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B127" t="s">
         <v>629</v>
@@ -8773,7 +8755,7 @@
         <v>631</v>
       </c>
       <c r="E127" t="s">
-        <v>1523</v>
+        <v>1577</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>632</v>
@@ -8784,7 +8766,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B128" t="s">
         <v>634</v>
@@ -8796,7 +8778,7 @@
         <v>636</v>
       </c>
       <c r="E128" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>637</v>
@@ -8807,7 +8789,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B129" t="s">
         <v>639</v>
@@ -8819,7 +8801,7 @@
         <v>641</v>
       </c>
       <c r="E129" t="s">
-        <v>1584</v>
+        <v>1553</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>642</v>
@@ -8830,7 +8812,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B130" t="s">
         <v>644</v>
@@ -8842,7 +8824,7 @@
         <v>646</v>
       </c>
       <c r="E130" t="s">
-        <v>1559</v>
+        <v>1720</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>647</v>
@@ -8853,7 +8835,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B131" t="s">
         <v>649</v>
@@ -8865,33 +8847,33 @@
         <v>651</v>
       </c>
       <c r="E131" t="s">
-        <v>1726</v>
+        <v>1721</v>
       </c>
       <c r="F131" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G131" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B132" t="s">
+        <v>653</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="E132" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="E132" t="s">
-        <v>1727</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>657</v>
@@ -8899,7 +8881,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B133" t="s">
         <v>658</v>
@@ -8911,7 +8893,7 @@
         <v>660</v>
       </c>
       <c r="E133" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>661</v>
@@ -8922,7 +8904,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B134" t="s">
         <v>663</v>
@@ -8934,7 +8916,7 @@
         <v>665</v>
       </c>
       <c r="E134" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>666</v>
@@ -8945,7 +8927,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B135" t="s">
         <v>668</v>
@@ -8957,7 +8939,7 @@
         <v>670</v>
       </c>
       <c r="E135" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>671</v>
@@ -8968,7 +8950,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B136" t="s">
         <v>673</v>
@@ -8980,7 +8962,7 @@
         <v>675</v>
       </c>
       <c r="E136" t="s">
-        <v>1587</v>
+        <v>1536</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>676</v>
@@ -8991,7 +8973,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B137" t="s">
         <v>678</v>
@@ -9003,7 +8985,7 @@
         <v>680</v>
       </c>
       <c r="E137" t="s">
-        <v>1542</v>
+        <v>1582</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>681</v>
@@ -9014,7 +8996,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B138" t="s">
         <v>683</v>
@@ -9026,7 +9008,7 @@
         <v>685</v>
       </c>
       <c r="E138" t="s">
-        <v>1588</v>
+        <v>1558</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>686</v>
@@ -9037,7 +9019,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B139" t="s">
         <v>688</v>
@@ -9049,7 +9031,7 @@
         <v>690</v>
       </c>
       <c r="E139" t="s">
-        <v>1564</v>
+        <v>1583</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>691</v>
@@ -9060,7 +9042,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1451</v>
+        <v>1445</v>
       </c>
       <c r="B140" t="s">
         <v>693</v>
@@ -9072,7 +9054,7 @@
         <v>695</v>
       </c>
       <c r="E140" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>696</v>
@@ -9083,7 +9065,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B141" t="s">
         <v>698</v>
@@ -9095,7 +9077,7 @@
         <v>700</v>
       </c>
       <c r="E141" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>701</v>
@@ -9106,7 +9088,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B142" t="s">
         <v>703</v>
@@ -9118,7 +9100,7 @@
         <v>705</v>
       </c>
       <c r="E142" t="s">
-        <v>1591</v>
+        <v>1547</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>706</v>
@@ -9129,7 +9111,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B143" t="s">
         <v>708</v>
@@ -9141,7 +9123,7 @@
         <v>710</v>
       </c>
       <c r="E143" t="s">
-        <v>1553</v>
+        <v>1586</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>711</v>
@@ -9152,7 +9134,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B144" t="s">
         <v>713</v>
@@ -9164,7 +9146,7 @@
         <v>715</v>
       </c>
       <c r="E144" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>716</v>
@@ -9175,7 +9157,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B145" t="s">
         <v>718</v>
@@ -9187,7 +9169,7 @@
         <v>720</v>
       </c>
       <c r="E145" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>721</v>
@@ -9198,7 +9180,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B146" t="s">
         <v>723</v>
@@ -9210,7 +9192,7 @@
         <v>725</v>
       </c>
       <c r="E146" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>726</v>
@@ -9221,7 +9203,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B147" t="s">
         <v>728</v>
@@ -9233,7 +9215,7 @@
         <v>730</v>
       </c>
       <c r="E147" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>731</v>
@@ -9244,7 +9226,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B148" t="s">
         <v>733</v>
@@ -9256,7 +9238,7 @@
         <v>735</v>
       </c>
       <c r="E148" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>736</v>
@@ -9267,7 +9249,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B149" t="s">
         <v>738</v>
@@ -9276,59 +9258,59 @@
         <v>739</v>
       </c>
       <c r="D149" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E149" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F149" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="E149" t="s">
-        <v>1597</v>
-      </c>
-      <c r="F149" s="2" t="s">
+      <c r="G149" s="1" t="s">
         <v>741</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B150" t="s">
+        <v>742</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="D150" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="D150" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E150" t="s">
-        <v>1597</v>
+        <v>1591</v>
       </c>
       <c r="F150" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G150" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B151" t="s">
+        <v>746</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="E151" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F151" s="2" t="s">
         <v>749</v>
-      </c>
-      <c r="E151" t="s">
-        <v>1597</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>750</v>
@@ -9336,7 +9318,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B152" t="s">
         <v>751</v>
@@ -9348,7 +9330,7 @@
         <v>753</v>
       </c>
       <c r="E152" t="s">
-        <v>1597</v>
+        <v>1717</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>754</v>
@@ -9359,7 +9341,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B153" t="s">
         <v>756</v>
@@ -9371,7 +9353,7 @@
         <v>758</v>
       </c>
       <c r="E153" t="s">
-        <v>1723</v>
+        <v>1718</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>759</v>
@@ -9382,7 +9364,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B154" t="s">
         <v>761</v>
@@ -9394,7 +9376,7 @@
         <v>763</v>
       </c>
       <c r="E154" t="s">
-        <v>1724</v>
+        <v>1592</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>764</v>
@@ -9405,7 +9387,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B155" t="s">
         <v>766</v>
@@ -9417,7 +9399,7 @@
         <v>768</v>
       </c>
       <c r="E155" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>769</v>
@@ -9428,7 +9410,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B156" t="s">
         <v>771</v>
@@ -9440,7 +9422,7 @@
         <v>773</v>
       </c>
       <c r="E156" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>774</v>
@@ -9451,7 +9433,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B157" t="s">
         <v>776</v>
@@ -9463,7 +9445,7 @@
         <v>778</v>
       </c>
       <c r="E157" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>779</v>
@@ -9474,7 +9456,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B158" t="s">
         <v>781</v>
@@ -9486,7 +9468,7 @@
         <v>783</v>
       </c>
       <c r="E158" t="s">
-        <v>1601</v>
+        <v>1568</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>784</v>
@@ -9497,7 +9479,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B159" t="s">
         <v>786</v>
@@ -9509,7 +9491,7 @@
         <v>788</v>
       </c>
       <c r="E159" t="s">
-        <v>1574</v>
+        <v>1596</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>789</v>
@@ -9520,7 +9502,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B160" t="s">
         <v>791</v>
@@ -9532,7 +9514,7 @@
         <v>793</v>
       </c>
       <c r="E160" t="s">
-        <v>1602</v>
+        <v>1719</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>794</v>
@@ -9543,7 +9525,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
       <c r="B161" t="s">
         <v>796</v>
@@ -9555,7 +9537,7 @@
         <v>798</v>
       </c>
       <c r="E161" t="s">
-        <v>1725</v>
+        <v>1596</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>799</v>
@@ -9566,7 +9548,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B162" t="s">
         <v>801</v>
@@ -9578,7 +9560,7 @@
         <v>803</v>
       </c>
       <c r="E162" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>804</v>
@@ -9589,7 +9571,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B163" t="s">
         <v>806</v>
@@ -9601,7 +9583,7 @@
         <v>808</v>
       </c>
       <c r="E163" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>809</v>
@@ -9612,7 +9594,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B164" t="s">
         <v>811</v>
@@ -9624,7 +9606,7 @@
         <v>813</v>
       </c>
       <c r="E164" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>814</v>
@@ -9635,7 +9617,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B165" t="s">
         <v>816</v>
@@ -9647,7 +9629,7 @@
         <v>818</v>
       </c>
       <c r="E165" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>819</v>
@@ -9658,7 +9640,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B166" t="s">
         <v>821</v>
@@ -9670,7 +9652,7 @@
         <v>823</v>
       </c>
       <c r="E166" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>824</v>
@@ -9681,7 +9663,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B167" t="s">
         <v>826</v>
@@ -9693,7 +9675,7 @@
         <v>828</v>
       </c>
       <c r="E167" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>829</v>
@@ -9704,7 +9686,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B168" t="s">
         <v>831</v>
@@ -9716,7 +9698,7 @@
         <v>833</v>
       </c>
       <c r="E168" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>834</v>
@@ -9727,7 +9709,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B169" t="s">
         <v>836</v>
@@ -9739,7 +9721,7 @@
         <v>838</v>
       </c>
       <c r="E169" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>839</v>
@@ -9750,7 +9732,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B170" t="s">
         <v>841</v>
@@ -9762,7 +9744,7 @@
         <v>843</v>
       </c>
       <c r="E170" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>844</v>
@@ -9773,7 +9755,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B171" t="s">
         <v>846</v>
@@ -9785,7 +9767,7 @@
         <v>848</v>
       </c>
       <c r="E171" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>849</v>
@@ -9796,7 +9778,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B172" t="s">
         <v>851</v>
@@ -9808,7 +9790,7 @@
         <v>853</v>
       </c>
       <c r="E172" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>854</v>
@@ -9819,7 +9801,7 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B173" t="s">
         <v>856</v>
@@ -9831,7 +9813,7 @@
         <v>858</v>
       </c>
       <c r="E173" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>859</v>
@@ -9842,7 +9824,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B174" t="s">
         <v>861</v>
@@ -9854,7 +9836,7 @@
         <v>863</v>
       </c>
       <c r="E174" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>864</v>
@@ -9865,7 +9847,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B175" t="s">
         <v>866</v>
@@ -9877,7 +9859,7 @@
         <v>868</v>
       </c>
       <c r="E175" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>869</v>
@@ -9888,7 +9870,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B176" t="s">
         <v>871</v>
@@ -9900,7 +9882,7 @@
         <v>873</v>
       </c>
       <c r="E176" t="s">
-        <v>1616</v>
+        <v>1611</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>874</v>
@@ -9911,7 +9893,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B177" t="s">
         <v>876</v>
@@ -9923,7 +9905,7 @@
         <v>878</v>
       </c>
       <c r="E177" t="s">
-        <v>1617</v>
+        <v>1612</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>879</v>
@@ -9934,7 +9916,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B178" t="s">
         <v>881</v>
@@ -9946,7 +9928,7 @@
         <v>883</v>
       </c>
       <c r="E178" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>884</v>
@@ -9957,7 +9939,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B179" t="s">
         <v>886</v>
@@ -9969,7 +9951,7 @@
         <v>888</v>
       </c>
       <c r="E179" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>889</v>
@@ -9980,7 +9962,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B180" t="s">
         <v>891</v>
@@ -9992,7 +9974,7 @@
         <v>893</v>
       </c>
       <c r="E180" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>894</v>
@@ -10003,7 +9985,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B181" t="s">
         <v>896</v>
@@ -10015,7 +9997,7 @@
         <v>898</v>
       </c>
       <c r="E181" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>899</v>
@@ -10026,7 +10008,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B182" t="s">
         <v>901</v>
@@ -10038,7 +10020,7 @@
         <v>903</v>
       </c>
       <c r="E182" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>904</v>
@@ -10049,7 +10031,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B183" t="s">
         <v>906</v>
@@ -10061,7 +10043,7 @@
         <v>908</v>
       </c>
       <c r="E183" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>909</v>
@@ -10072,7 +10054,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B184" t="s">
         <v>911</v>
@@ -10084,7 +10066,7 @@
         <v>913</v>
       </c>
       <c r="E184" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>914</v>
@@ -10095,7 +10077,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B185" t="s">
         <v>916</v>
@@ -10107,7 +10089,7 @@
         <v>918</v>
       </c>
       <c r="E185" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>919</v>
@@ -10118,7 +10100,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B186" t="s">
         <v>921</v>
@@ -10130,7 +10112,7 @@
         <v>923</v>
       </c>
       <c r="E186" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>924</v>
@@ -10141,7 +10123,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B187" t="s">
         <v>926</v>
@@ -10153,7 +10135,7 @@
         <v>928</v>
       </c>
       <c r="E187" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>929</v>
@@ -10164,7 +10146,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B188" t="s">
         <v>931</v>
@@ -10176,7 +10158,7 @@
         <v>933</v>
       </c>
       <c r="E188" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>934</v>
@@ -10187,7 +10169,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B189" t="s">
         <v>936</v>
@@ -10199,7 +10181,7 @@
         <v>938</v>
       </c>
       <c r="E189" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>939</v>
@@ -10210,7 +10192,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B190" t="s">
         <v>941</v>
@@ -10222,7 +10204,7 @@
         <v>943</v>
       </c>
       <c r="E190" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>944</v>
@@ -10233,7 +10215,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B191" t="s">
         <v>946</v>
@@ -10245,33 +10227,33 @@
         <v>948</v>
       </c>
       <c r="E191" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="F191" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G191" s="1" t="s">
         <v>949</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B192" t="s">
+        <v>950</v>
+      </c>
+      <c r="C192" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="D192" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="E192" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F192" s="2" t="s">
         <v>953</v>
-      </c>
-      <c r="E192" t="s">
-        <v>1632</v>
-      </c>
-      <c r="F192" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>954</v>
@@ -10279,7 +10261,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B193" t="s">
         <v>955</v>
@@ -10291,7 +10273,7 @@
         <v>957</v>
       </c>
       <c r="E193" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>958</v>
@@ -10302,7 +10284,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B194" t="s">
         <v>960</v>
@@ -10314,7 +10296,7 @@
         <v>962</v>
       </c>
       <c r="E194" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>963</v>
@@ -10325,7 +10307,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B195" t="s">
         <v>965</v>
@@ -10337,7 +10319,7 @@
         <v>967</v>
       </c>
       <c r="E195" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>968</v>
@@ -10348,7 +10330,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B196" t="s">
         <v>970</v>
@@ -10360,7 +10342,7 @@
         <v>972</v>
       </c>
       <c r="E196" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>973</v>
@@ -10371,7 +10353,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B197" t="s">
         <v>975</v>
@@ -10383,7 +10365,7 @@
         <v>977</v>
       </c>
       <c r="E197" t="s">
-        <v>1637</v>
+        <v>1601</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>978</v>
@@ -10394,7 +10376,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B198" t="s">
         <v>980</v>
@@ -10406,7 +10388,7 @@
         <v>982</v>
       </c>
       <c r="E198" t="s">
-        <v>1607</v>
+        <v>1632</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>983</v>
@@ -10417,7 +10399,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B199" t="s">
         <v>985</v>
@@ -10429,7 +10411,7 @@
         <v>987</v>
       </c>
       <c r="E199" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>988</v>
@@ -10440,7 +10422,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B200" t="s">
         <v>990</v>
@@ -10452,7 +10434,7 @@
         <v>992</v>
       </c>
       <c r="E200" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>993</v>
@@ -10463,7 +10445,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B201" t="s">
         <v>995</v>
@@ -10475,7 +10457,7 @@
         <v>997</v>
       </c>
       <c r="E201" t="s">
-        <v>1640</v>
+        <v>1609</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>998</v>
@@ -10486,7 +10468,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B202" t="s">
         <v>1000</v>
@@ -10498,7 +10480,7 @@
         <v>1002</v>
       </c>
       <c r="E202" t="s">
-        <v>1615</v>
+        <v>1635</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>1003</v>
@@ -10509,7 +10491,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B203" t="s">
         <v>1005</v>
@@ -10521,7 +10503,7 @@
         <v>1007</v>
       </c>
       <c r="E203" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>1008</v>
@@ -10532,7 +10514,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B204" t="s">
         <v>1010</v>
@@ -10544,7 +10526,7 @@
         <v>1012</v>
       </c>
       <c r="E204" t="s">
-        <v>1642</v>
+        <v>1637</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>1013</v>
@@ -10555,7 +10537,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="B205" t="s">
         <v>1015</v>
@@ -10567,7 +10549,7 @@
         <v>1017</v>
       </c>
       <c r="E205" t="s">
-        <v>1643</v>
+        <v>1638</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>1018</v>
@@ -10578,7 +10560,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B206" t="s">
         <v>1020</v>
@@ -10590,7 +10572,7 @@
         <v>1022</v>
       </c>
       <c r="E206" t="s">
-        <v>1644</v>
+        <v>1639</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>1023</v>
@@ -10601,7 +10583,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B207" t="s">
         <v>1025</v>
@@ -10613,7 +10595,7 @@
         <v>1027</v>
       </c>
       <c r="E207" t="s">
-        <v>1645</v>
+        <v>1523</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>1028</v>
@@ -10624,7 +10606,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B208" t="s">
         <v>1030</v>
@@ -10636,7 +10618,7 @@
         <v>1032</v>
       </c>
       <c r="E208" t="s">
-        <v>1529</v>
+        <v>1640</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>1033</v>
@@ -10647,7 +10629,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B209" t="s">
         <v>1035</v>
@@ -10659,7 +10641,7 @@
         <v>1037</v>
       </c>
       <c r="E209" t="s">
-        <v>1646</v>
+        <v>1641</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>1038</v>
@@ -10670,7 +10652,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B210" t="s">
         <v>1040</v>
@@ -10682,7 +10664,7 @@
         <v>1042</v>
       </c>
       <c r="E210" t="s">
-        <v>1647</v>
+        <v>1642</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>1043</v>
@@ -10693,7 +10675,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B211" t="s">
         <v>1045</v>
@@ -10705,7 +10687,7 @@
         <v>1047</v>
       </c>
       <c r="E211" t="s">
-        <v>1648</v>
+        <v>1643</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>1048</v>
@@ -10716,7 +10698,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B212" t="s">
         <v>1050</v>
@@ -10728,7 +10710,7 @@
         <v>1052</v>
       </c>
       <c r="E212" t="s">
-        <v>1649</v>
+        <v>1639</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>1053</v>
@@ -10739,7 +10721,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B213" t="s">
         <v>1055</v>
@@ -10751,7 +10733,7 @@
         <v>1057</v>
       </c>
       <c r="E213" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>1058</v>
@@ -10762,7 +10744,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B214" t="s">
         <v>1060</v>
@@ -10774,7 +10756,7 @@
         <v>1062</v>
       </c>
       <c r="E214" t="s">
-        <v>1650</v>
+        <v>1645</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>1063</v>
@@ -10785,7 +10767,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B215" t="s">
         <v>1065</v>
@@ -10797,7 +10779,7 @@
         <v>1067</v>
       </c>
       <c r="E215" t="s">
-        <v>1651</v>
+        <v>1571</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>1068</v>
@@ -10808,7 +10790,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B216" t="s">
         <v>1070</v>
@@ -10820,33 +10802,33 @@
         <v>1072</v>
       </c>
       <c r="E216" t="s">
-        <v>1577</v>
+        <v>1646</v>
       </c>
       <c r="F216" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G216" s="1" t="s">
         <v>1073</v>
-      </c>
-      <c r="G216" s="1" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B217" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C217" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="D217" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="E217" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F217" s="2" t="s">
         <v>1077</v>
-      </c>
-      <c r="E217" t="s">
-        <v>1652</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>1078</v>
@@ -10854,7 +10836,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B218" t="s">
         <v>1079</v>
@@ -10866,7 +10848,7 @@
         <v>1081</v>
       </c>
       <c r="E218" t="s">
-        <v>1653</v>
+        <v>1648</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>1082</v>
@@ -10877,7 +10859,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B219" t="s">
         <v>1084</v>
@@ -10889,7 +10871,7 @@
         <v>1086</v>
       </c>
       <c r="E219" t="s">
-        <v>1654</v>
+        <v>1649</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>1087</v>
@@ -10900,7 +10882,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B220" t="s">
         <v>1089</v>
@@ -10912,7 +10894,7 @@
         <v>1091</v>
       </c>
       <c r="E220" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>1092</v>
@@ -10923,7 +10905,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B221" t="s">
         <v>1094</v>
@@ -10935,7 +10917,7 @@
         <v>1096</v>
       </c>
       <c r="E221" t="s">
-        <v>1656</v>
+        <v>1651</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>1097</v>
@@ -10946,7 +10928,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B222" t="s">
         <v>1099</v>
@@ -10958,7 +10940,7 @@
         <v>1101</v>
       </c>
       <c r="E222" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>1102</v>
@@ -10969,7 +10951,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B223" t="s">
         <v>1104</v>
@@ -10981,33 +10963,33 @@
         <v>1106</v>
       </c>
       <c r="E223" t="s">
-        <v>1658</v>
+        <v>1653</v>
       </c>
       <c r="F223" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="G223" s="1" t="s">
         <v>1107</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B224" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C224" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="C224" s="1" t="s">
+      <c r="D224" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="D224" s="1" t="s">
+      <c r="E224" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>1111</v>
-      </c>
-      <c r="E224" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>1112</v>
@@ -11015,7 +10997,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B225" t="s">
         <v>1113</v>
@@ -11027,7 +11009,7 @@
         <v>1115</v>
       </c>
       <c r="E225" t="s">
-        <v>1660</v>
+        <v>1655</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>1116</v>
@@ -11038,7 +11020,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="B226" t="s">
         <v>1118</v>
@@ -11047,33 +11029,33 @@
         <v>1119</v>
       </c>
       <c r="D226" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E226" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F226" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="E226" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F226" s="2" t="s">
+      <c r="G226" s="1" t="s">
         <v>1121</v>
-      </c>
-      <c r="G226" s="1" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1453</v>
+        <v>1446</v>
       </c>
       <c r="B227" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C227" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="C227" s="1" t="s">
+      <c r="D227" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="D227" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="E227" t="s">
-        <v>1662</v>
+        <v>1657</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>1125</v>
@@ -11084,7 +11066,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B228" t="s">
         <v>1127</v>
@@ -11096,7 +11078,7 @@
         <v>1129</v>
       </c>
       <c r="E228" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>1130</v>
@@ -11107,7 +11089,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B229" t="s">
         <v>1132</v>
@@ -11119,33 +11101,33 @@
         <v>1134</v>
       </c>
       <c r="E229" t="s">
-        <v>1664</v>
+        <v>1659</v>
       </c>
       <c r="F229" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="G229" s="1" t="s">
         <v>1135</v>
-      </c>
-      <c r="G229" s="1" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B230" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C230" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="C230" s="1" t="s">
+      <c r="D230" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="D230" s="1" t="s">
+      <c r="E230" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>1139</v>
-      </c>
-      <c r="E230" t="s">
-        <v>1665</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>779</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>1140</v>
@@ -11153,7 +11135,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B231" t="s">
         <v>1141</v>
@@ -11165,7 +11147,7 @@
         <v>1143</v>
       </c>
       <c r="E231" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>1144</v>
@@ -11176,7 +11158,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="B232" t="s">
         <v>1146</v>
@@ -11188,7 +11170,7 @@
         <v>1148</v>
       </c>
       <c r="E232" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>1149</v>
@@ -11199,7 +11181,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="B233" t="s">
         <v>1151</v>
@@ -11211,7 +11193,7 @@
         <v>1153</v>
       </c>
       <c r="E233" t="s">
-        <v>1668</v>
+        <v>1663</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>1154</v>
@@ -11222,7 +11204,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="B234" t="s">
         <v>1156</v>
@@ -11234,7 +11216,7 @@
         <v>1158</v>
       </c>
       <c r="E234" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>1159</v>
@@ -11245,30 +11227,30 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="B235" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="E235" t="s">
-        <v>1670</v>
+        <v>1665</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="B236" t="s">
         <v>1168</v>
@@ -11280,7 +11262,7 @@
         <v>1170</v>
       </c>
       <c r="E236" t="s">
-        <v>1671</v>
+        <v>1666</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>1171</v>
@@ -11291,7 +11273,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="B237" t="s">
         <v>1173</v>
@@ -11303,7 +11285,7 @@
         <v>1175</v>
       </c>
       <c r="E237" t="s">
-        <v>1672</v>
+        <v>1563</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>1176</v>
@@ -11314,7 +11296,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="B238" t="s">
         <v>1178</v>
@@ -11326,7 +11308,7 @@
         <v>1180</v>
       </c>
       <c r="E238" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>1181</v>
@@ -11337,7 +11319,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="B239" t="s">
         <v>1183</v>
@@ -11349,7 +11331,7 @@
         <v>1185</v>
       </c>
       <c r="E239" t="s">
-        <v>1577</v>
+        <v>1667</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>1186</v>
@@ -11360,7 +11342,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="B240" t="s">
         <v>1188</v>
@@ -11369,33 +11351,33 @@
         <v>1189</v>
       </c>
       <c r="D240" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E240" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="E240" t="s">
-        <v>1673</v>
-      </c>
-      <c r="F240" s="2" t="s">
+      <c r="G240" s="1" t="s">
         <v>1191</v>
-      </c>
-      <c r="G240" s="1" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="B241" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C241" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="C241" s="1" t="s">
+      <c r="D241" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="D241" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E241" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>1195</v>
@@ -11406,7 +11388,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B242" t="s">
         <v>1197</v>
@@ -11418,7 +11400,7 @@
         <v>1199</v>
       </c>
       <c r="E242" t="s">
-        <v>1675</v>
+        <v>1539</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>1200</v>
@@ -11429,7 +11411,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B243" t="s">
         <v>1202</v>
@@ -11441,7 +11423,7 @@
         <v>1204</v>
       </c>
       <c r="E243" t="s">
-        <v>1545</v>
+        <v>1670</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>1205</v>
@@ -11452,7 +11434,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B244" t="s">
         <v>1207</v>
@@ -11464,7 +11446,7 @@
         <v>1209</v>
       </c>
       <c r="E244" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>1210</v>
@@ -11475,7 +11457,7 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B245" t="s">
         <v>1212</v>
@@ -11487,7 +11469,7 @@
         <v>1214</v>
       </c>
       <c r="E245" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>1215</v>
@@ -11498,7 +11480,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B246" t="s">
         <v>1217</v>
@@ -11510,7 +11492,7 @@
         <v>1219</v>
       </c>
       <c r="E246" t="s">
-        <v>1678</v>
+        <v>1673</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>1220</v>
@@ -11521,7 +11503,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B247" t="s">
         <v>1222</v>
@@ -11533,7 +11515,7 @@
         <v>1224</v>
       </c>
       <c r="E247" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>1225</v>
@@ -11544,7 +11526,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B248" t="s">
         <v>1227</v>
@@ -11553,59 +11535,59 @@
         <v>1228</v>
       </c>
       <c r="D248" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E248" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F248" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="E248" t="s">
-        <v>1680</v>
-      </c>
-      <c r="F248" s="2" t="s">
+      <c r="G248" s="1" t="s">
         <v>1230</v>
-      </c>
-      <c r="G248" s="1" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B249" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C249" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="C249" s="1" t="s">
+      <c r="D249" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="D249" s="1" t="s">
-        <v>731</v>
-      </c>
       <c r="E249" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
       <c r="F249" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G249" s="1" t="s">
         <v>1234</v>
-      </c>
-      <c r="G249" s="1" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B250" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C250" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="C250" s="1" t="s">
+      <c r="D250" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="D250" s="1" t="s">
+      <c r="E250" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>1238</v>
-      </c>
-      <c r="E250" t="s">
-        <v>1682</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>1239</v>
@@ -11613,7 +11595,7 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B251" t="s">
         <v>1240</v>
@@ -11625,7 +11607,7 @@
         <v>1242</v>
       </c>
       <c r="E251" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>1243</v>
@@ -11636,7 +11618,7 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B252" t="s">
         <v>1245</v>
@@ -11648,7 +11630,7 @@
         <v>1247</v>
       </c>
       <c r="E252" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>1248</v>
@@ -11659,7 +11641,7 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="B253" t="s">
         <v>1250</v>
@@ -11671,7 +11653,7 @@
         <v>1252</v>
       </c>
       <c r="E253" t="s">
-        <v>1685</v>
+        <v>1680</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>1253</v>
@@ -11682,7 +11664,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="B254" t="s">
         <v>1255</v>
@@ -11694,7 +11676,7 @@
         <v>1257</v>
       </c>
       <c r="E254" t="s">
-        <v>1686</v>
+        <v>1681</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>1258</v>
@@ -11705,7 +11687,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="B255" t="s">
         <v>1260</v>
@@ -11717,79 +11699,79 @@
         <v>1262</v>
       </c>
       <c r="E255" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
       <c r="F255" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G255" s="1" t="s">
         <v>1263</v>
-      </c>
-      <c r="G255" s="1" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="B256" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C256" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="C256" s="1" t="s">
+      <c r="D256" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E256" t="s">
+        <v>1683</v>
+      </c>
+      <c r="F256" s="2" t="s">
         <v>1266</v>
       </c>
-      <c r="D256" s="1" t="s">
+      <c r="G256" s="1" t="s">
         <v>1267</v>
-      </c>
-      <c r="E256" t="s">
-        <v>1688</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G256" s="1" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="B257" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C257" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="C257" s="1" t="s">
+      <c r="D257" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D257" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="E257" t="s">
-        <v>1689</v>
+        <v>1684</v>
       </c>
       <c r="F257" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G257" s="1" t="s">
         <v>1271</v>
-      </c>
-      <c r="G257" s="1" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B258" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C258" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="C258" s="1" t="s">
+      <c r="D258" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="D258" s="1" t="s">
+      <c r="E258" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F258" s="2" t="s">
         <v>1275</v>
-      </c>
-      <c r="E258" t="s">
-        <v>1690</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>1153</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>1276</v>
@@ -11797,7 +11779,7 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B259" t="s">
         <v>1277</v>
@@ -11809,7 +11791,7 @@
         <v>1279</v>
       </c>
       <c r="E259" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>1280</v>
@@ -11820,7 +11802,7 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B260" t="s">
         <v>1282</v>
@@ -11832,7 +11814,7 @@
         <v>1284</v>
       </c>
       <c r="E260" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>1285</v>
@@ -11843,7 +11825,7 @@
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B261" t="s">
         <v>1287</v>
@@ -11855,7 +11837,7 @@
         <v>1289</v>
       </c>
       <c r="E261" t="s">
-        <v>1693</v>
+        <v>1688</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>1290</v>
@@ -11866,7 +11848,7 @@
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B262" t="s">
         <v>1292</v>
@@ -11878,7 +11860,7 @@
         <v>1294</v>
       </c>
       <c r="E262" t="s">
-        <v>1694</v>
+        <v>1689</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>1295</v>
@@ -11889,7 +11871,7 @@
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B263" t="s">
         <v>1297</v>
@@ -11901,7 +11883,7 @@
         <v>1299</v>
       </c>
       <c r="E263" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>1300</v>
@@ -11912,7 +11894,7 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="B264" t="s">
         <v>1302</v>
@@ -11924,7 +11906,7 @@
         <v>1304</v>
       </c>
       <c r="E264" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>1305</v>
@@ -11935,76 +11917,76 @@
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="B265" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E265" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1462</v>
+        <v>1449</v>
       </c>
       <c r="B266" t="s">
         <v>1313</v>
       </c>
       <c r="C266" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="D266" s="1" t="s">
+      <c r="E266" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F266" s="2" t="s">
         <v>1315</v>
       </c>
-      <c r="E266" t="s">
-        <v>1698</v>
-      </c>
-      <c r="F266" s="2" t="s">
-        <v>1316</v>
-      </c>
       <c r="G266" s="1" t="s">
-        <v>1317</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B267" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D267" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="C267" s="1" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D267" s="1" t="s">
+      <c r="E267" t="s">
+        <v>1710</v>
+      </c>
+      <c r="F267" s="2" t="s">
         <v>1319</v>
       </c>
-      <c r="E267" t="s">
-        <v>1715</v>
-      </c>
-      <c r="F267" s="2" t="s">
+      <c r="G267" s="1" t="s">
         <v>1320</v>
-      </c>
-      <c r="G267" s="1" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
       <c r="B268" t="s">
         <v>1321</v>
@@ -12013,36 +11995,36 @@
         <v>1322</v>
       </c>
       <c r="D268" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E268" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G268" s="1" t="s">
         <v>1323</v>
-      </c>
-      <c r="E268" t="s">
-        <v>1716</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>1324</v>
-      </c>
-      <c r="G268" s="1" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="B269" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="C269" s="1" t="s">
+      <c r="E269" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F269" s="2" t="s">
         <v>1327</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>1295</v>
-      </c>
-      <c r="E269" t="s">
-        <v>1699</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>1328</v>
@@ -12050,7 +12032,7 @@
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1461</v>
+        <v>1447</v>
       </c>
       <c r="B270" t="s">
         <v>1329</v>
@@ -12062,7 +12044,7 @@
         <v>1331</v>
       </c>
       <c r="E270" t="s">
-        <v>1584</v>
+        <v>1694</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>1332</v>
@@ -12070,10 +12052,13 @@
       <c r="G270" s="1" t="s">
         <v>1333</v>
       </c>
+      <c r="L270" t="s">
+        <v>1442</v>
+      </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="B271" t="s">
         <v>1334</v>
@@ -12085,7 +12070,7 @@
         <v>1336</v>
       </c>
       <c r="E271" t="s">
-        <v>1700</v>
+        <v>1695</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>1337</v>
@@ -12093,13 +12078,10 @@
       <c r="G271" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="L271" t="s">
-        <v>1447</v>
-      </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="B272" t="s">
         <v>1339</v>
@@ -12111,7 +12093,7 @@
         <v>1341</v>
       </c>
       <c r="E272" t="s">
-        <v>1701</v>
+        <v>1696</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>1342</v>
@@ -12122,7 +12104,7 @@
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1462</v>
+        <v>1449</v>
       </c>
       <c r="B273" t="s">
         <v>1344</v>
@@ -12134,7 +12116,7 @@
         <v>1346</v>
       </c>
       <c r="E273" t="s">
-        <v>1702</v>
+        <v>1697</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>1347</v>
@@ -12145,7 +12127,7 @@
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B274" t="s">
         <v>1349</v>
@@ -12157,7 +12139,7 @@
         <v>1351</v>
       </c>
       <c r="E274" t="s">
-        <v>1703</v>
+        <v>1698</v>
       </c>
       <c r="F274" s="2" t="s">
         <v>1352</v>
@@ -12168,7 +12150,7 @@
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
       <c r="B275" t="s">
         <v>1354</v>
@@ -12180,7 +12162,7 @@
         <v>1356</v>
       </c>
       <c r="E275" t="s">
-        <v>1704</v>
+        <v>1545</v>
       </c>
       <c r="F275" s="2" t="s">
         <v>1357</v>
@@ -12191,7 +12173,7 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="B276" t="s">
         <v>1359</v>
@@ -12203,7 +12185,7 @@
         <v>1361</v>
       </c>
       <c r="E276" t="s">
-        <v>1551</v>
+        <v>1643</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>1362</v>
@@ -12213,9 +12195,6 @@
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
-        <v>1453</v>
-      </c>
       <c r="B277" t="s">
         <v>1364</v>
       </c>
@@ -12226,38 +12205,41 @@
         <v>1366</v>
       </c>
       <c r="E277" t="s">
-        <v>1649</v>
+        <v>1699</v>
       </c>
       <c r="F277" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G277" s="1" t="s">
         <v>1367</v>
       </c>
-      <c r="G277" s="1" t="s">
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B278" t="s">
         <v>1368</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B278" t="s">
+      <c r="C278" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="C278" s="1" t="s">
+      <c r="D278" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="D278" s="1" t="s">
+      <c r="E278" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>1371</v>
-      </c>
-      <c r="E278" t="s">
-        <v>1705</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>1312</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>1372</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B279" t="s">
         <v>1373</v>
@@ -12269,7 +12251,7 @@
         <v>1375</v>
       </c>
       <c r="E279" t="s">
-        <v>1543</v>
+        <v>1537</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>1376</v>
@@ -12280,7 +12262,7 @@
     </row>
     <row r="280" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="B280" t="s">
         <v>1378</v>
@@ -12292,7 +12274,7 @@
         <v>1380</v>
       </c>
       <c r="E280" t="s">
-        <v>1543</v>
+        <v>1700</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>1381</v>
@@ -12303,7 +12285,7 @@
     </row>
     <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1454</v>
+        <v>1445</v>
       </c>
       <c r="B281" t="s">
         <v>1383</v>
@@ -12315,7 +12297,7 @@
         <v>1385</v>
       </c>
       <c r="E281" t="s">
-        <v>1706</v>
+        <v>1550</v>
       </c>
       <c r="F281" s="2" t="s">
         <v>1386</v>
@@ -12324,9 +12306,9 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B282" t="s">
         <v>1388</v>
@@ -12338,7 +12320,7 @@
         <v>1390</v>
       </c>
       <c r="E282" t="s">
-        <v>1556</v>
+        <v>1535</v>
       </c>
       <c r="F282" s="2" t="s">
         <v>1391</v>
@@ -12347,9 +12329,9 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B283" t="s">
         <v>1393</v>
@@ -12361,7 +12343,7 @@
         <v>1395</v>
       </c>
       <c r="E283" t="s">
-        <v>1541</v>
+        <v>1573</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>1396</v>
@@ -12370,9 +12352,9 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1450</v>
+        <v>1455</v>
       </c>
       <c r="B284" t="s">
         <v>1398</v>
@@ -12384,7 +12366,7 @@
         <v>1400</v>
       </c>
       <c r="E284" t="s">
-        <v>1579</v>
+        <v>1701</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>1401</v>
@@ -12393,9 +12375,9 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1460</v>
+        <v>1451</v>
       </c>
       <c r="B285" t="s">
         <v>1403</v>
@@ -12407,39 +12389,39 @@
         <v>1405</v>
       </c>
       <c r="E285" t="s">
-        <v>1707</v>
+        <v>1702</v>
       </c>
       <c r="F285" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G285" s="1" t="s">
         <v>1406</v>
       </c>
-      <c r="G285" s="1" t="s">
+    </row>
+    <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B286" t="s">
         <v>1407</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A286" t="s">
-        <v>1456</v>
-      </c>
-      <c r="B286" t="s">
+      <c r="C286" s="1" t="s">
         <v>1408</v>
       </c>
-      <c r="C286" s="1" t="s">
+      <c r="D286" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="D286" s="1" t="s">
+      <c r="E286" t="s">
+        <v>1703</v>
+      </c>
+      <c r="F286" s="2" t="s">
         <v>1410</v>
-      </c>
-      <c r="E286" t="s">
-        <v>1708</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>1411</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>1456</v>
+      </c>
       <c r="B287" t="s">
         <v>1412</v>
       </c>
@@ -12450,7 +12432,7 @@
         <v>1414</v>
       </c>
       <c r="E287" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>1415</v>
@@ -12461,42 +12443,42 @@
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1461</v>
+        <v>1450</v>
       </c>
       <c r="B288" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C288" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="C288" s="1" t="s">
+      <c r="D288" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E288" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F288" s="2" t="s">
         <v>1418</v>
       </c>
-      <c r="D288" s="1" t="s">
+      <c r="G288" s="1" t="s">
         <v>1419</v>
-      </c>
-      <c r="E288" t="s">
-        <v>1710</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="G288" s="1" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="B289" t="s">
-        <v>1166</v>
+        <v>1420</v>
       </c>
       <c r="C289" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="D289" s="1" t="s">
-        <v>1167</v>
-      </c>
       <c r="E289" t="s">
-        <v>1711</v>
+        <v>1557</v>
       </c>
       <c r="F289" s="2" t="s">
         <v>1423</v>
@@ -12505,9 +12487,9 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>1456</v>
+        <v>1447</v>
       </c>
       <c r="B290" t="s">
         <v>1425</v>
@@ -12519,7 +12501,7 @@
         <v>1427</v>
       </c>
       <c r="E290" t="s">
-        <v>1563</v>
+        <v>1706</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>1428</v>
@@ -12528,9 +12510,9 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="B291" t="s">
         <v>1430</v>
@@ -12542,7 +12524,7 @@
         <v>1432</v>
       </c>
       <c r="E291" t="s">
-        <v>1712</v>
+        <v>1578</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>1433</v>
@@ -12553,76 +12535,76 @@
     </row>
     <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B292" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C292" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="C292" s="1" t="s">
+      <c r="D292" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="D292" s="1" t="s">
+      <c r="E292" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F292" s="2" t="s">
         <v>1437</v>
       </c>
-      <c r="E292" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F292" s="2" t="s">
+      <c r="G292" s="1" t="s">
         <v>1438</v>
-      </c>
-      <c r="G292" s="1" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="B293" t="s">
-        <v>1260</v>
+        <v>1439</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>1440</v>
       </c>
       <c r="D293" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E293" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F293" s="2" t="s">
         <v>1441</v>
       </c>
-      <c r="E293" t="s">
-        <v>1713</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>1442</v>
-      </c>
       <c r="G293" s="1" t="s">
-        <v>1443</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>1461</v>
+        <v>1452</v>
       </c>
       <c r="B294" t="s">
-        <v>1444</v>
+        <v>1192</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>1445</v>
+        <v>1193</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>1077</v>
+        <v>1194</v>
       </c>
       <c r="E294" t="s">
-        <v>1655</v>
+        <v>1669</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>1446</v>
+        <v>1195</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>1463</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B295" t="s">
         <v>1197</v>
@@ -12634,7 +12616,7 @@
         <v>1199</v>
       </c>
       <c r="E295" t="s">
-        <v>1675</v>
+        <v>1539</v>
       </c>
       <c r="F295" s="2" t="s">
         <v>1200</v>
@@ -12645,7 +12627,7 @@
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B296" t="s">
         <v>1202</v>
@@ -12657,7 +12639,7 @@
         <v>1204</v>
       </c>
       <c r="E296" t="s">
-        <v>1545</v>
+        <v>1693</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>1205</v>
@@ -12668,7 +12650,7 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="B297" t="s">
         <v>1207</v>
@@ -12680,36 +12662,13 @@
         <v>1209</v>
       </c>
       <c r="E297" t="s">
-        <v>1699</v>
+        <v>1708</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>1210</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>1211</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
-        <v>1457</v>
-      </c>
-      <c r="B298" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>1214</v>
-      </c>
-      <c r="E298" t="s">
-        <v>1714</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="G298" s="1" t="s">
-        <v>1216</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Daily_Word.xlsx
+++ b/public/data/Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4A8997-7D6E-4DD6-B18C-59FBFFC67CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200142C2-C9BC-4B52-855F-8C56B8A37BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -200,9 +200,6 @@
     <t>תפוח</t>
   </si>
   <si>
-    <t>יַבְּלָקוֹ מזכיר 'בלוק' של תפוחים ערוכים יפה בסופר.</t>
-  </si>
-  <si>
     <t>чай</t>
   </si>
   <si>
@@ -377,9 +374,6 @@
     <t>מאוד (טעים)</t>
   </si>
   <si>
-    <t>מְיוֹד הוא טבעי ומאוד מתוק וטעים.</t>
-  </si>
-  <si>
     <t>варенье</t>
   </si>
   <si>
@@ -542,9 +536,6 @@
     <t>קפוץ</t>
   </si>
   <si>
-    <t>כרוב שמקפץ-טה כמו כדור</t>
-  </si>
-  <si>
     <t>чеснок</t>
   </si>
   <si>
@@ -731,9 +722,6 @@
     <t>Fire</t>
   </si>
   <si>
-    <t>הזֶפִּיר מזכיר מרשמלו - מתוק ורך שמושלם לכל Fire (מדורה).</t>
-  </si>
-  <si>
     <t>печенье</t>
   </si>
   <si>
@@ -848,12 +836,6 @@
     <t>פנקייק גבינה</t>
   </si>
   <si>
-    <t xml:space="preserve">סיר </t>
-  </si>
-  <si>
-    <t>אין כמו סִירְנִיקִי חם ישר מהסיר עם דבש מעל!</t>
-  </si>
-  <si>
     <t>хрен</t>
   </si>
   <si>
@@ -866,9 +848,6 @@
     <t>חריף</t>
   </si>
   <si>
-    <t>כפית את מהחְרֶן זה כמו פצצה של חריף למנה</t>
-  </si>
-  <si>
     <t>горчица</t>
   </si>
   <si>
@@ -1068,9 +1047,6 @@
   </si>
   <si>
     <t>קרס</t>
-  </si>
-  <si>
-    <t>כשמתרווחים בקְרֶסְלוֹ אחריי יום ארוך מרגישים איך הגוף "קורס" לתוכה.</t>
   </si>
   <si>
     <t>полка</t>
@@ -5450,6 +5426,30 @@
   </si>
   <si>
     <t>🔓🔑</t>
+  </si>
+  <si>
+    <t>הזֶפִּיר מתוק ורך שמושלם לכל Fire (מדורה).</t>
+  </si>
+  <si>
+    <t>קָפּוּסְטָה מקפץ כמו כדורגל</t>
+  </si>
+  <si>
+    <t>מְיוֹד הוא מאוד מתוק וטעים.</t>
+  </si>
+  <si>
+    <t>היַבְּלָקוֹ מסודר בבלוקים מסודרים יפה בסופר.</t>
+  </si>
+  <si>
+    <t>אין כמו סִירְנִיקִי חם ישר מהסיר לתוך הריבה!</t>
+  </si>
+  <si>
+    <t>סיר נקי</t>
+  </si>
+  <si>
+    <t>כפית אחת מהחְרֶן זה כמו פצצה של חריף למנה</t>
+  </si>
+  <si>
+    <t>אין כמו לשבת על קְרֶסְלוֹ עם הכרס בבטן.</t>
   </si>
 </sst>
 </file>
@@ -5848,27 +5848,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1711</v>
+        <v>1703</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1464</v>
+        <v>1456</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1463</v>
+        <v>1455</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1466</v>
+        <v>1458</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1462</v>
+        <v>1454</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -5880,7 +5880,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1467</v>
+        <v>1459</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>20</v>
@@ -5891,7 +5891,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -5903,7 +5903,7 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1468</v>
+        <v>1460</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>25</v>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -5926,18 +5926,18 @@
         <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1469</v>
+        <v>1461</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1465</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1470</v>
+        <v>1462</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>34</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
@@ -5972,7 +5972,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1471</v>
+        <v>1463</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>39</v>
@@ -5983,7 +5983,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
@@ -5995,7 +5995,7 @@
         <v>43</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1472</v>
+        <v>1464</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>44</v>
@@ -6006,7 +6006,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
@@ -6018,7 +6018,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1473</v>
+        <v>1465</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>49</v>
@@ -6029,7 +6029,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B9" t="s">
         <v>51</v>
@@ -6041,6634 +6041,6634 @@
         <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1474</v>
+        <v>1466</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>54</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>1475</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>1477</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>1482</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>1483</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>1484</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>1485</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>1486</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>113</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="E22" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>1503</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="E23" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="E24" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>1488</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="E25" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="E26" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="E27" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="E28" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>1491</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="E29" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>1492</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B30" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="E30" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>1493</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B31" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="E31" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="E32" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>168</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>1496</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>1497</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B35" t="s">
+        <v>176</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>1498</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1499</v>
+        <v>1491</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B37" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B38" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B39" t="s">
+        <v>194</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>1502</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B40" t="s">
+        <v>199</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B41" t="s">
+        <v>204</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>1505</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B42" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>1506</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B43" t="s">
+        <v>214</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B44" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>1508</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B45" t="s">
+        <v>224</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>1712</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="G45" s="1" t="s">
-        <v>231</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B46" t="s">
+        <v>228</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>1713</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B48" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B49" t="s">
+        <v>243</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>1511</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B50" t="s">
+        <v>248</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>1512</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B51" t="s">
+        <v>253</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>1513</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B52" t="s">
+        <v>258</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>1514</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B53" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>270</v>
+        <v>1719</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>271</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B54" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1520</v>
+        <v>1512</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>276</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B55" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1521</v>
+        <v>1513</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B56" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B57" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1516</v>
+        <v>1508</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B58" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1517</v>
+        <v>1509</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B59" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1518</v>
+        <v>1510</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B60" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B61" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B62" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1523</v>
+        <v>1515</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B63" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1543</v>
+        <v>1535</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1523</v>
+        <v>1515</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B64" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1524</v>
+        <v>1516</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B65" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1525</v>
+        <v>1517</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B66" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1544</v>
+        <v>1536</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B67" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1526</v>
+        <v>1518</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B68" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>344</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B69" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1518</v>
+        <v>1510</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B70" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1527</v>
+        <v>1519</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B71" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1714</v>
+        <v>1706</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B72" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1528</v>
+        <v>1520</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B73" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1529</v>
+        <v>1521</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B74" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1530</v>
+        <v>1522</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B75" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1531</v>
+        <v>1523</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B76" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B77" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1533</v>
+        <v>1525</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B78" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1517</v>
+        <v>1509</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B79" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1534</v>
+        <v>1526</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B80" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1535</v>
+        <v>1527</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B81" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B82" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B83" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1518</v>
+        <v>1510</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="B84" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1537</v>
+        <v>1529</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B85" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B86" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1539</v>
+        <v>1531</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B87" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1540</v>
+        <v>1532</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B88" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1715</v>
+        <v>1707</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B89" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1716</v>
+        <v>1708</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B90" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1542</v>
+        <v>1534</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B91" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1542</v>
+        <v>1534</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B92" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1542</v>
+        <v>1534</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B93" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="E93" t="s">
-        <v>1546</v>
+        <v>1538</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B94" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E94" t="s">
-        <v>1541</v>
+        <v>1533</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B95" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="E95" t="s">
-        <v>1547</v>
+        <v>1539</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B96" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="E96" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B97" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="E97" t="s">
-        <v>1549</v>
+        <v>1541</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B98" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="E98" t="s">
-        <v>1550</v>
+        <v>1542</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B99" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="E99" t="s">
-        <v>1551</v>
+        <v>1543</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B100" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="E100" t="s">
-        <v>1552</v>
+        <v>1544</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B101" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E101" t="s">
-        <v>1553</v>
+        <v>1545</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B102" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="E102" t="s">
-        <v>1554</v>
+        <v>1546</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B103" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="E103" t="s">
-        <v>1555</v>
+        <v>1547</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B104" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="E104" t="s">
-        <v>1556</v>
+        <v>1548</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B105" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="E105" t="s">
-        <v>1557</v>
+        <v>1549</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B106" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="E106" t="s">
-        <v>1558</v>
+        <v>1550</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B107" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="E107" t="s">
-        <v>1559</v>
+        <v>1551</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B108" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="E108" t="s">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B109" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="E109" t="s">
-        <v>1561</v>
+        <v>1553</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B110" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="E110" t="s">
-        <v>1562</v>
+        <v>1554</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B111" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="E111" t="s">
-        <v>1563</v>
+        <v>1555</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B112" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="E112" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B113" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="E113" t="s">
-        <v>1565</v>
+        <v>1557</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B114" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="E114" t="s">
-        <v>1566</v>
+        <v>1558</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B115" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="E115" t="s">
-        <v>1567</v>
+        <v>1559</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B116" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="E116" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B117" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="E117" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B118" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="E118" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B119" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="E119" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B120" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="E120" t="s">
-        <v>1571</v>
+        <v>1563</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B121" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E121" t="s">
-        <v>1572</v>
+        <v>1564</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B122" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E122" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B123" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E123" t="s">
-        <v>1574</v>
+        <v>1566</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B124" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="E124" t="s">
-        <v>1575</v>
+        <v>1567</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B125" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="E125" t="s">
-        <v>1576</v>
+        <v>1568</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B126" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="E126" t="s">
-        <v>1517</v>
+        <v>1509</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B127" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="E127" t="s">
-        <v>1577</v>
+        <v>1569</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B128" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="E128" t="s">
-        <v>1578</v>
+        <v>1570</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B129" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="E129" t="s">
-        <v>1553</v>
+        <v>1545</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B130" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="E130" t="s">
-        <v>1720</v>
+        <v>1712</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B131" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="E131" t="s">
-        <v>1721</v>
+        <v>1713</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B132" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="E132" t="s">
-        <v>1579</v>
+        <v>1571</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B133" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="E133" t="s">
-        <v>1580</v>
+        <v>1572</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B134" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="E134" t="s">
-        <v>1578</v>
+        <v>1570</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B135" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="E135" t="s">
-        <v>1581</v>
+        <v>1573</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B136" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="E136" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B137" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="E137" t="s">
-        <v>1582</v>
+        <v>1574</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B138" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="E138" t="s">
-        <v>1558</v>
+        <v>1550</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B139" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="E139" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B140" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="E140" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B141" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="E141" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B142" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="E142" t="s">
-        <v>1547</v>
+        <v>1539</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B143" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="E143" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B144" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="E144" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B145" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="E145" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B146" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="E146" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B147" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="E147" t="s">
-        <v>1590</v>
+        <v>1582</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B148" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="E148" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B149" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="E149" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B150" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="E150" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B151" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="E151" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B152" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="E152" t="s">
-        <v>1717</v>
+        <v>1709</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B153" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="E153" t="s">
-        <v>1718</v>
+        <v>1710</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B154" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="E154" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B155" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="E155" t="s">
-        <v>1593</v>
+        <v>1585</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B156" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="E156" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B157" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="E157" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B158" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="E158" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B159" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="E159" t="s">
-        <v>1596</v>
+        <v>1588</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B160" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="E160" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B161" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="E161" t="s">
-        <v>1596</v>
+        <v>1588</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B162" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="E162" t="s">
-        <v>1597</v>
+        <v>1589</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B163" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="E163" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B164" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="E164" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B165" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="E165" t="s">
-        <v>1600</v>
+        <v>1592</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B166" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="E166" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B167" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="E167" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B168" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="E168" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B169" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E169" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B170" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="E170" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B171" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="E171" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B172" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="E172" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B173" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
       <c r="E173" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B174" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="E174" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B175" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="E175" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B176" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="E176" t="s">
-        <v>1611</v>
+        <v>1603</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B177" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="E177" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B178" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="E178" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B179" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="E179" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B180" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="E180" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B181" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="E181" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B182" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="E182" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B183" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
       <c r="E183" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B184" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="E184" t="s">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B185" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="E185" t="s">
-        <v>1620</v>
+        <v>1612</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B186" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="E186" t="s">
-        <v>1621</v>
+        <v>1613</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B187" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="E187" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B188" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="E188" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B189" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="E189" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B190" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="E190" t="s">
-        <v>1625</v>
+        <v>1617</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B191" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="E191" t="s">
-        <v>1626</v>
+        <v>1618</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B192" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="E192" t="s">
-        <v>1627</v>
+        <v>1619</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B193" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="E193" t="s">
-        <v>1628</v>
+        <v>1620</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B194" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="E194" t="s">
-        <v>1629</v>
+        <v>1621</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B195" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="E195" t="s">
-        <v>1630</v>
+        <v>1622</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B196" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="E196" t="s">
-        <v>1631</v>
+        <v>1623</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B197" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="E197" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B198" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="E198" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B199" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="E199" t="s">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B200" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="E200" t="s">
-        <v>1634</v>
+        <v>1626</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B201" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="E201" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B202" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="E202" t="s">
-        <v>1635</v>
+        <v>1627</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B203" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="E203" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B204" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="E204" t="s">
-        <v>1637</v>
+        <v>1629</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B205" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="E205" t="s">
-        <v>1638</v>
+        <v>1630</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B206" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="E206" t="s">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B207" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="E207" t="s">
-        <v>1523</v>
+        <v>1515</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B208" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="E208" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B209" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="E209" t="s">
-        <v>1641</v>
+        <v>1633</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B210" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1041</v>
+        <v>1033</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="E210" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B211" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1046</v>
+        <v>1038</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
       <c r="E211" t="s">
-        <v>1643</v>
+        <v>1635</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B212" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="E212" t="s">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B213" t="s">
-        <v>1055</v>
+        <v>1047</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>1056</v>
+        <v>1048</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1057</v>
+        <v>1049</v>
       </c>
       <c r="E213" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>1058</v>
+        <v>1050</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1059</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B214" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="E214" t="s">
-        <v>1645</v>
+        <v>1637</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>1063</v>
+        <v>1055</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1064</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B215" t="s">
-        <v>1065</v>
+        <v>1057</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1067</v>
+        <v>1059</v>
       </c>
       <c r="E215" t="s">
-        <v>1571</v>
+        <v>1563</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B216" t="s">
-        <v>1070</v>
+        <v>1062</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>1071</v>
+        <v>1063</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>1072</v>
+        <v>1064</v>
       </c>
       <c r="E216" t="s">
-        <v>1646</v>
+        <v>1638</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1073</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B217" t="s">
-        <v>1074</v>
+        <v>1066</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>1075</v>
+        <v>1067</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>1076</v>
+        <v>1068</v>
       </c>
       <c r="E217" t="s">
-        <v>1647</v>
+        <v>1639</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>1077</v>
+        <v>1069</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B218" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
       <c r="E218" t="s">
-        <v>1648</v>
+        <v>1640</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B219" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
       <c r="E219" t="s">
-        <v>1649</v>
+        <v>1641</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>1088</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B220" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
       <c r="E220" t="s">
-        <v>1650</v>
+        <v>1642</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>1092</v>
+        <v>1084</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B221" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
       <c r="E221" t="s">
-        <v>1651</v>
+        <v>1643</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B222" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
       <c r="E222" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>1102</v>
+        <v>1094</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>1103</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B223" t="s">
-        <v>1104</v>
+        <v>1096</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>1105</v>
+        <v>1097</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>1106</v>
+        <v>1098</v>
       </c>
       <c r="E223" t="s">
-        <v>1653</v>
+        <v>1645</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1107</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B224" t="s">
-        <v>1108</v>
+        <v>1100</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="E224" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B225" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>1114</v>
+        <v>1106</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
       <c r="E225" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>1117</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B226" t="s">
-        <v>1118</v>
+        <v>1110</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>1119</v>
+        <v>1111</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E226" t="s">
-        <v>1656</v>
+        <v>1648</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>1120</v>
+        <v>1112</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>1121</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B227" t="s">
-        <v>1122</v>
+        <v>1114</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>1123</v>
+        <v>1115</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>1124</v>
+        <v>1116</v>
       </c>
       <c r="E227" t="s">
-        <v>1657</v>
+        <v>1649</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B228" t="s">
-        <v>1127</v>
+        <v>1119</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
       <c r="E228" t="s">
-        <v>1658</v>
+        <v>1650</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>1131</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B229" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="E229" t="s">
-        <v>1659</v>
+        <v>1651</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B230" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
       <c r="E230" t="s">
-        <v>1660</v>
+        <v>1652</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B231" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>1143</v>
+        <v>1135</v>
       </c>
       <c r="E231" t="s">
-        <v>1661</v>
+        <v>1653</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B232" t="s">
-        <v>1146</v>
+        <v>1138</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
       <c r="E232" t="s">
-        <v>1662</v>
+        <v>1654</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>1149</v>
+        <v>1141</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
       <c r="B233" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
       <c r="E233" t="s">
-        <v>1663</v>
+        <v>1655</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1155</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
       <c r="B234" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="E234" t="s">
-        <v>1664</v>
+        <v>1656</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
       <c r="B235" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>1165</v>
+        <v>1157</v>
       </c>
       <c r="E235" t="s">
-        <v>1665</v>
+        <v>1657</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>1166</v>
+        <v>1158</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1167</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="B236" t="s">
-        <v>1168</v>
+        <v>1160</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
       <c r="E236" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>1172</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="B237" t="s">
-        <v>1173</v>
+        <v>1165</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1174</v>
+        <v>1166</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>1175</v>
+        <v>1167</v>
       </c>
       <c r="E237" t="s">
-        <v>1563</v>
+        <v>1555</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="B238" t="s">
-        <v>1178</v>
+        <v>1170</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>1179</v>
+        <v>1171</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
       <c r="E238" t="s">
-        <v>1571</v>
+        <v>1563</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>1182</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="B239" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>1185</v>
+        <v>1177</v>
       </c>
       <c r="E239" t="s">
-        <v>1667</v>
+        <v>1659</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>1186</v>
+        <v>1178</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1187</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="B240" t="s">
-        <v>1188</v>
+        <v>1180</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>1189</v>
+        <v>1181</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>1190</v>
+        <v>1182</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>1191</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B241" t="s">
-        <v>1192</v>
+        <v>1184</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="E241" t="s">
-        <v>1669</v>
+        <v>1661</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B242" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
       <c r="E242" t="s">
-        <v>1539</v>
+        <v>1531</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>1201</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B243" t="s">
-        <v>1202</v>
+        <v>1194</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>1203</v>
+        <v>1195</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>1204</v>
+        <v>1196</v>
       </c>
       <c r="E243" t="s">
-        <v>1670</v>
+        <v>1662</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>1206</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B244" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>1208</v>
+        <v>1200</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>1209</v>
+        <v>1201</v>
       </c>
       <c r="E244" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>1210</v>
+        <v>1202</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1211</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B245" t="s">
-        <v>1212</v>
+        <v>1204</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>1213</v>
+        <v>1205</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>1214</v>
+        <v>1206</v>
       </c>
       <c r="E245" t="s">
-        <v>1672</v>
+        <v>1664</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1215</v>
+        <v>1207</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1216</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B246" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1218</v>
+        <v>1210</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>1219</v>
+        <v>1211</v>
       </c>
       <c r="E246" t="s">
-        <v>1673</v>
+        <v>1665</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>1220</v>
+        <v>1212</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1221</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B247" t="s">
-        <v>1222</v>
+        <v>1214</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1223</v>
+        <v>1215</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1224</v>
+        <v>1216</v>
       </c>
       <c r="E247" t="s">
-        <v>1674</v>
+        <v>1666</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1225</v>
+        <v>1217</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1226</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B248" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="E248" t="s">
-        <v>1675</v>
+        <v>1667</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B249" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1232</v>
+        <v>1224</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="E249" t="s">
-        <v>1676</v>
+        <v>1668</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B250" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="E250" t="s">
-        <v>1677</v>
+        <v>1669</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B251" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
       <c r="E251" t="s">
-        <v>1678</v>
+        <v>1670</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B252" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="E252" t="s">
-        <v>1679</v>
+        <v>1671</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="B253" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="E253" t="s">
-        <v>1680</v>
+        <v>1672</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="B254" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
       <c r="E254" t="s">
-        <v>1681</v>
+        <v>1673</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1259</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="B255" t="s">
-        <v>1260</v>
+        <v>1252</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>1262</v>
+        <v>1254</v>
       </c>
       <c r="E255" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1454</v>
+        <v>1446</v>
       </c>
       <c r="B256" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E256" t="s">
-        <v>1683</v>
+        <v>1675</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="B257" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
       <c r="E257" t="s">
-        <v>1684</v>
+        <v>1676</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="B258" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>1273</v>
+        <v>1265</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="E258" t="s">
-        <v>1685</v>
+        <v>1677</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>1275</v>
+        <v>1267</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="B259" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1278</v>
+        <v>1270</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="E259" t="s">
-        <v>1686</v>
+        <v>1678</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>1281</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="B260" t="s">
-        <v>1282</v>
+        <v>1274</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1283</v>
+        <v>1275</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="E260" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="B261" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>1288</v>
+        <v>1280</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="E261" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="B262" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
       <c r="E262" t="s">
-        <v>1689</v>
+        <v>1681</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="B263" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
       <c r="E263" t="s">
-        <v>1690</v>
+        <v>1682</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="B264" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>1303</v>
+        <v>1295</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1304</v>
+        <v>1296</v>
       </c>
       <c r="E264" t="s">
-        <v>1691</v>
+        <v>1683</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>1305</v>
+        <v>1297</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1306</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1457</v>
+        <v>1449</v>
       </c>
       <c r="B265" t="s">
-        <v>1308</v>
+        <v>1300</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1309</v>
+        <v>1301</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
       <c r="E265" t="s">
-        <v>1692</v>
+        <v>1684</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B266" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>1459</v>
+        <v>1451</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
       <c r="E266" t="s">
-        <v>1709</v>
+        <v>1701</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1460</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B267" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>1317</v>
+        <v>1309</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="E267" t="s">
-        <v>1710</v>
+        <v>1702</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B268" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1322</v>
+        <v>1314</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="E268" t="s">
-        <v>1693</v>
+        <v>1685</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1323</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
       <c r="B269" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="E269" t="s">
-        <v>1578</v>
+        <v>1570</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B270" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
       <c r="E270" t="s">
-        <v>1694</v>
+        <v>1686</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
       <c r="L270" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1457</v>
+        <v>1449</v>
       </c>
       <c r="B271" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>1335</v>
+        <v>1327</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="E271" t="s">
-        <v>1695</v>
+        <v>1687</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1457</v>
+        <v>1449</v>
       </c>
       <c r="B272" t="s">
-        <v>1339</v>
+        <v>1331</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>1340</v>
+        <v>1332</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
       <c r="E272" t="s">
-        <v>1696</v>
+        <v>1688</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>1342</v>
+        <v>1334</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1343</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B273" t="s">
-        <v>1344</v>
+        <v>1336</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>1345</v>
+        <v>1337</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>1346</v>
+        <v>1338</v>
       </c>
       <c r="E273" t="s">
-        <v>1697</v>
+        <v>1689</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1347</v>
+        <v>1339</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1348</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B274" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
       <c r="E274" t="s">
-        <v>1698</v>
+        <v>1690</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>1352</v>
+        <v>1344</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B275" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>1356</v>
+        <v>1348</v>
       </c>
       <c r="E275" t="s">
-        <v>1545</v>
+        <v>1537</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>1357</v>
+        <v>1349</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1358</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B276" t="s">
-        <v>1359</v>
+        <v>1351</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1361</v>
+        <v>1353</v>
       </c>
       <c r="E276" t="s">
-        <v>1643</v>
+        <v>1635</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>1362</v>
+        <v>1354</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="E277" t="s">
-        <v>1699</v>
+        <v>1691</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>1307</v>
+        <v>1299</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B278" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>1369</v>
+        <v>1361</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>1370</v>
+        <v>1362</v>
       </c>
       <c r="E278" t="s">
-        <v>1537</v>
+        <v>1529</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1372</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B279" t="s">
-        <v>1373</v>
+        <v>1365</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="E279" t="s">
-        <v>1537</v>
+        <v>1529</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B280" t="s">
-        <v>1378</v>
+        <v>1370</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>1379</v>
+        <v>1371</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>1380</v>
+        <v>1372</v>
       </c>
       <c r="E280" t="s">
-        <v>1700</v>
+        <v>1692</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>1381</v>
+        <v>1373</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>1382</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B281" t="s">
-        <v>1383</v>
+        <v>1375</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>1385</v>
+        <v>1377</v>
       </c>
       <c r="E281" t="s">
-        <v>1550</v>
+        <v>1542</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>1386</v>
+        <v>1378</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1387</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B282" t="s">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>1389</v>
+        <v>1381</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
       <c r="E282" t="s">
-        <v>1535</v>
+        <v>1527</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1392</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B283" t="s">
-        <v>1393</v>
+        <v>1385</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>1394</v>
+        <v>1386</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>1395</v>
+        <v>1387</v>
       </c>
       <c r="E283" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>1396</v>
+        <v>1388</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1397</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="B284" t="s">
-        <v>1398</v>
+        <v>1390</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>1399</v>
+        <v>1391</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>1400</v>
+        <v>1392</v>
       </c>
       <c r="E284" t="s">
-        <v>1701</v>
+        <v>1693</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="B285" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>1404</v>
+        <v>1396</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="E285" t="s">
-        <v>1702</v>
+        <v>1694</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1406</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B286" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
       <c r="E286" t="s">
-        <v>1703</v>
+        <v>1695</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
       <c r="B287" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1413</v>
+        <v>1405</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1414</v>
+        <v>1406</v>
       </c>
       <c r="E287" t="s">
-        <v>1704</v>
+        <v>1696</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
       <c r="B288" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="E288" t="s">
-        <v>1705</v>
+        <v>1697</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>1418</v>
+        <v>1410</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="B289" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>1421</v>
+        <v>1413</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
       <c r="E289" t="s">
-        <v>1557</v>
+        <v>1549</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B290" t="s">
-        <v>1425</v>
+        <v>1417</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>1426</v>
+        <v>1418</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
       <c r="E290" t="s">
-        <v>1706</v>
+        <v>1698</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>1428</v>
+        <v>1420</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="B291" t="s">
-        <v>1430</v>
+        <v>1422</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="E291" t="s">
-        <v>1578</v>
+        <v>1570</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1434</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="B292" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>1435</v>
+        <v>1427</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="E292" t="s">
-        <v>1707</v>
+        <v>1699</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>1437</v>
+        <v>1429</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1438</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
       <c r="B293" t="s">
-        <v>1439</v>
+        <v>1431</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>1440</v>
+        <v>1432</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>1072</v>
+        <v>1064</v>
       </c>
       <c r="E293" t="s">
-        <v>1649</v>
+        <v>1641</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1458</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B294" t="s">
-        <v>1192</v>
+        <v>1184</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
       <c r="E294" t="s">
-        <v>1669</v>
+        <v>1661</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B295" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
       <c r="E295" t="s">
-        <v>1539</v>
+        <v>1531</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>1201</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B296" t="s">
-        <v>1202</v>
+        <v>1194</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>1203</v>
+        <v>1195</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>1204</v>
+        <v>1196</v>
       </c>
       <c r="E296" t="s">
-        <v>1693</v>
+        <v>1685</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>1206</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B297" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>1208</v>
+        <v>1200</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>1209</v>
+        <v>1201</v>
       </c>
       <c r="E297" t="s">
-        <v>1708</v>
+        <v>1700</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>1210</v>
+        <v>1202</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>1211</v>
+        <v>1203</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Daily_Word.xlsx
+++ b/public/data/Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200142C2-C9BC-4B52-855F-8C56B8A37BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE0D830-BBBF-47B5-BBE0-5FCE61ECFB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -171,9 +171,6 @@
   </si>
   <si>
     <t>יציאה</t>
-  </si>
-  <si>
-    <t>מהיַיִצוֹ יוצאים לעולם.</t>
   </si>
   <si>
     <t>Картошка</t>
@@ -5450,6 +5447,9 @@
   </si>
   <si>
     <t>אין כמו לשבת על קְרֶסְלוֹ עם הכרס בבטן.</t>
+  </si>
+  <si>
+    <t>מהיַיִצוֹ האפרוח יוצא לעולם.</t>
   </si>
 </sst>
 </file>
@@ -5848,27 +5848,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -5880,7 +5880,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>20</v>
@@ -5891,7 +5891,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -5903,7 +5903,7 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>25</v>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -5926,18 +5926,18 @@
         <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>34</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
@@ -5972,7 +5972,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>39</v>
@@ -5983,7 +5983,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
@@ -5995,6680 +5995,6680 @@
         <v>43</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>45</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>1465</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>1467</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>1469</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>1470</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>1471</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>1472</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>1473</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>1475</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>1476</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>1477</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>1482</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>1483</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B29" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>1484</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B30" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>1485</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B31" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>1486</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B33" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>1488</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="G33" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B34" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B36" t="s">
+        <v>180</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B37" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>1492</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="G37" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B38" t="s">
+        <v>189</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B39" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F39" s="2" t="s">
+      <c r="G39" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B40" t="s">
+        <v>198</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>1496</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="G40" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B41" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>1497</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="G41" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B42" t="s">
+        <v>208</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>1498</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="G42" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B43" t="s">
+        <v>213</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="G43" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B44" t="s">
+        <v>218</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B45" t="s">
+        <v>223</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>1704</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="G45" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B46" t="s">
+        <v>227</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>1501</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="G46" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B47" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>1705</v>
-      </c>
-      <c r="F47" s="2" t="s">
+      <c r="G47" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B48" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>1502</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="G48" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B49" t="s">
+        <v>242</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>1503</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="G49" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B50" t="s">
+        <v>247</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="G50" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B51" t="s">
+        <v>252</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>1505</v>
-      </c>
-      <c r="F51" s="2" t="s">
+      <c r="G51" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>1506</v>
-      </c>
-      <c r="F52" s="2" t="s">
+      <c r="G52" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B53" t="s">
+        <v>262</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="E53" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B54" t="s">
+        <v>265</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>1512</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B55" t="s">
+        <v>269</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>1513</v>
-      </c>
-      <c r="F55" s="2" t="s">
+      <c r="G55" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B56" t="s">
+        <v>274</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F56" s="2" t="s">
+      <c r="G56" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B57" t="s">
+        <v>279</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>1508</v>
-      </c>
-      <c r="F57" s="2" t="s">
+      <c r="G57" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B58" t="s">
+        <v>284</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B59" t="s">
+        <v>289</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F59" s="2" t="s">
+      <c r="G59" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B60" t="s">
+        <v>294</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>1511</v>
-      </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B61" t="s">
+        <v>299</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>1514</v>
-      </c>
-      <c r="F61" s="2" t="s">
+      <c r="G61" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B62" t="s">
+        <v>304</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>1515</v>
-      </c>
-      <c r="F62" s="2" t="s">
+      <c r="G62" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B63" t="s">
+        <v>309</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>1535</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>1515</v>
-      </c>
-      <c r="F63" s="2" t="s">
+      <c r="G63" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B64" t="s">
+        <v>313</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="E64" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B65" t="s">
+        <v>317</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>1517</v>
-      </c>
-      <c r="F65" s="2" t="s">
+      <c r="G65" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B66" t="s">
+        <v>322</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="E66" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>1536</v>
-      </c>
-      <c r="F66" s="2" t="s">
+      <c r="G66" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B67" t="s">
+        <v>327</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>1518</v>
-      </c>
-      <c r="F67" s="2" t="s">
+      <c r="G67" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B68" t="s">
+        <v>332</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>1511</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="G68" s="1" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B69" t="s">
+        <v>336</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="E69" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F69" s="2" t="s">
+      <c r="G69" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B70" t="s">
+        <v>341</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="E70" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>1519</v>
-      </c>
-      <c r="F70" s="2" t="s">
+      <c r="G70" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B71" t="s">
+        <v>346</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>1706</v>
-      </c>
-      <c r="F71" s="2" t="s">
+      <c r="G71" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B72" t="s">
+        <v>351</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="E72" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>1520</v>
-      </c>
-      <c r="F72" s="2" t="s">
+      <c r="G72" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B73" t="s">
+        <v>356</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>1521</v>
-      </c>
-      <c r="F73" s="2" t="s">
+      <c r="G73" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B74" t="s">
+        <v>361</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>1522</v>
-      </c>
-      <c r="F74" s="2" t="s">
+      <c r="G74" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B75" t="s">
+        <v>366</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>1523</v>
-      </c>
-      <c r="F75" s="2" t="s">
+      <c r="G75" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B76" t="s">
+        <v>371</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="E76" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>1524</v>
-      </c>
-      <c r="F76" s="2" t="s">
+      <c r="G76" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B77" t="s">
+        <v>376</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>1525</v>
-      </c>
-      <c r="F77" s="2" t="s">
+      <c r="G77" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B78" t="s">
+        <v>381</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="E78" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="F78" s="2" t="s">
+      <c r="G78" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B79" t="s">
+        <v>386</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="E79" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>1526</v>
-      </c>
-      <c r="F79" s="2" t="s">
+      <c r="G79" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B80" t="s">
+        <v>391</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="E80" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>1527</v>
-      </c>
-      <c r="F80" s="2" t="s">
+      <c r="G80" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B81" t="s">
+        <v>396</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="E81" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>1528</v>
-      </c>
-      <c r="F81" s="2" t="s">
+      <c r="G81" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B82" t="s">
+        <v>401</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="E82" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F82" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F82" s="2" t="s">
+      <c r="G82" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B83" t="s">
+        <v>406</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F83" s="2" t="s">
+      <c r="G83" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B84" t="s">
+        <v>411</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="E84" s="2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B85" t="s">
+        <v>415</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>1530</v>
-      </c>
-      <c r="F85" s="2" t="s">
+      <c r="G85" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B86" t="s">
+        <v>420</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="E86" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>1531</v>
-      </c>
-      <c r="F86" s="2" t="s">
+      <c r="G86" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B87" t="s">
+        <v>425</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="E87" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>1532</v>
-      </c>
-      <c r="F87" s="2" t="s">
+      <c r="G87" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B88" t="s">
+        <v>430</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>1707</v>
-      </c>
-      <c r="F88" s="2" t="s">
+      <c r="G88" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B89" t="s">
+        <v>435</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="E89" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F89" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>1708</v>
-      </c>
-      <c r="F89" s="2" t="s">
+      <c r="G89" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B90" t="s">
+        <v>440</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="E90" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>1534</v>
-      </c>
-      <c r="F90" s="2" t="s">
+      <c r="G90" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B91" t="s">
+        <v>445</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="E91" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>1534</v>
-      </c>
-      <c r="F91" s="2" t="s">
+      <c r="G91" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B92" t="s">
+        <v>450</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="E92" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>1534</v>
-      </c>
-      <c r="F92" s="2" t="s">
+      <c r="G92" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B93" t="s">
+        <v>455</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="E93" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F93" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="E93" t="s">
-        <v>1538</v>
-      </c>
-      <c r="F93" s="2" t="s">
+      <c r="G93" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B94" t="s">
+        <v>460</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="E94" t="s">
+        <v>1532</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="E94" t="s">
-        <v>1533</v>
-      </c>
-      <c r="F94" s="2" t="s">
+      <c r="G94" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B95" t="s">
+        <v>465</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="E95" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F95" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="E95" t="s">
-        <v>1539</v>
-      </c>
-      <c r="F95" s="2" t="s">
+      <c r="G95" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B96" t="s">
+        <v>470</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="E96" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="E96" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F96" s="2" t="s">
+      <c r="G96" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B97" t="s">
+        <v>475</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="D97" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="E97" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F97" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="E97" t="s">
-        <v>1541</v>
-      </c>
-      <c r="F97" s="2" t="s">
+      <c r="G97" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B98" t="s">
+        <v>480</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="E98" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="E98" t="s">
-        <v>1542</v>
-      </c>
-      <c r="F98" s="2" t="s">
+      <c r="G98" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B99" t="s">
+        <v>485</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="E99" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="E99" t="s">
-        <v>1543</v>
-      </c>
-      <c r="F99" s="2" t="s">
+      <c r="G99" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B100" t="s">
+        <v>490</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="E100" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="E100" t="s">
-        <v>1544</v>
-      </c>
-      <c r="F100" s="2" t="s">
+      <c r="G100" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B101" t="s">
+        <v>495</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="E101" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="E101" t="s">
-        <v>1545</v>
-      </c>
-      <c r="F101" s="2" t="s">
+      <c r="G101" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B102" t="s">
+        <v>500</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="E102" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="E102" t="s">
-        <v>1546</v>
-      </c>
-      <c r="F102" s="2" t="s">
+      <c r="G102" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B103" t="s">
+        <v>505</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="E103" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="E103" t="s">
-        <v>1547</v>
-      </c>
-      <c r="F103" s="2" t="s">
+      <c r="G103" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B104" t="s">
+        <v>510</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="D104" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="E104" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="E104" t="s">
-        <v>1548</v>
-      </c>
-      <c r="F104" s="2" t="s">
+      <c r="G104" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B105" t="s">
+        <v>515</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="E105" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="E105" t="s">
-        <v>1549</v>
-      </c>
-      <c r="F105" s="2" t="s">
+      <c r="G105" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B106" t="s">
+        <v>520</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="D106" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="E106" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="E106" t="s">
-        <v>1550</v>
-      </c>
-      <c r="F106" s="2" t="s">
+      <c r="G106" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B107" t="s">
+        <v>525</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="D107" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="E107" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="E107" t="s">
-        <v>1551</v>
-      </c>
-      <c r="F107" s="2" t="s">
+      <c r="G107" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B108" t="s">
+        <v>530</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="E108" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F108" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="E108" t="s">
-        <v>1552</v>
-      </c>
-      <c r="F108" s="2" t="s">
+      <c r="G108" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B109" t="s">
+        <v>535</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="E109" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="E109" t="s">
-        <v>1553</v>
-      </c>
-      <c r="F109" s="2" t="s">
+      <c r="G109" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B110" t="s">
+        <v>540</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="E110" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B111" t="s">
+        <v>544</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="E111" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F111" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="E111" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F111" s="2" t="s">
+      <c r="G111" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B112" t="s">
+        <v>549</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="E112" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F112" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="E112" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F112" s="2" t="s">
+      <c r="G112" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B113" t="s">
+        <v>554</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="E113" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="E113" t="s">
-        <v>1557</v>
-      </c>
-      <c r="F113" s="2" t="s">
+      <c r="G113" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B114" t="s">
+        <v>559</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>562</v>
-      </c>
       <c r="E114" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B115" t="s">
+        <v>563</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="E115" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F115" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="E115" t="s">
-        <v>1559</v>
-      </c>
-      <c r="F115" s="2" t="s">
+      <c r="G115" s="1" t="s">
         <v>567</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B116" t="s">
+        <v>568</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="E116" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="E116" t="s">
-        <v>1560</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B117" t="s">
+        <v>572</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="E117" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="E117" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F117" s="2" t="s">
+      <c r="G117" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B118" t="s">
+        <v>577</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="E118" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F118" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="E118" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F118" s="2" t="s">
+      <c r="G118" s="1" t="s">
         <v>581</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B119" t="s">
+        <v>582</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="D119" s="1" t="s">
-        <v>585</v>
-      </c>
       <c r="E119" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B120" t="s">
+        <v>586</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="E120" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="E120" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F120" s="2" t="s">
+      <c r="G120" s="1" t="s">
         <v>590</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B121" t="s">
+        <v>591</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="E121" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F121" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="E121" t="s">
-        <v>1564</v>
-      </c>
-      <c r="F121" s="2" t="s">
+      <c r="G121" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B122" t="s">
+        <v>596</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="D122" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="E122" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="E122" t="s">
-        <v>1565</v>
-      </c>
-      <c r="F122" s="2" t="s">
+      <c r="G122" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B123" t="s">
+        <v>601</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="E123" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="E123" t="s">
-        <v>1566</v>
-      </c>
-      <c r="F123" s="2" t="s">
+      <c r="G123" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B124" t="s">
+        <v>606</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>609</v>
-      </c>
       <c r="E124" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B125" t="s">
+        <v>610</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="E125" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F125" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="E125" t="s">
-        <v>1568</v>
-      </c>
-      <c r="F125" s="2" t="s">
+      <c r="G125" s="1" t="s">
         <v>614</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B126" t="s">
+        <v>615</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="E126" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="E126" t="s">
-        <v>1509</v>
-      </c>
-      <c r="F126" s="2" t="s">
+      <c r="G126" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B127" t="s">
+        <v>620</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="D127" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="E127" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F127" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="E127" t="s">
-        <v>1569</v>
-      </c>
-      <c r="F127" s="2" t="s">
+      <c r="G127" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B128" t="s">
+        <v>625</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="E128" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="E128" t="s">
-        <v>1570</v>
-      </c>
-      <c r="F128" s="2" t="s">
+      <c r="G128" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B129" t="s">
+        <v>630</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="D129" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="E129" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F129" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="E129" t="s">
-        <v>1545</v>
-      </c>
-      <c r="F129" s="2" t="s">
+      <c r="G129" s="1" t="s">
         <v>634</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B130" t="s">
+        <v>635</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="D130" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="E130" t="s">
+        <v>1711</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E130" t="s">
-        <v>1712</v>
-      </c>
-      <c r="F130" s="2" t="s">
+      <c r="G130" s="1" t="s">
         <v>639</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B131" t="s">
+        <v>640</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="E131" t="s">
+        <v>1712</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G131" s="1" t="s">
         <v>643</v>
-      </c>
-      <c r="E131" t="s">
-        <v>1713</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B132" t="s">
+        <v>644</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="E132" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="E132" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F132" s="2" t="s">
+      <c r="G132" s="1" t="s">
         <v>648</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B133" t="s">
+        <v>649</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="E133" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F133" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="E133" t="s">
-        <v>1572</v>
-      </c>
-      <c r="F133" s="2" t="s">
+      <c r="G133" s="1" t="s">
         <v>653</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B134" t="s">
+        <v>654</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="D134" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="E134" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="E134" t="s">
-        <v>1570</v>
-      </c>
-      <c r="F134" s="2" t="s">
+      <c r="G134" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B135" t="s">
+        <v>659</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="E135" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F135" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="E135" t="s">
-        <v>1573</v>
-      </c>
-      <c r="F135" s="2" t="s">
+      <c r="G135" s="1" t="s">
         <v>663</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B136" t="s">
+        <v>664</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="E136" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="E136" t="s">
-        <v>1528</v>
-      </c>
-      <c r="F136" s="2" t="s">
+      <c r="G136" s="1" t="s">
         <v>668</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B137" t="s">
+        <v>669</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="D137" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="E137" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E137" t="s">
-        <v>1574</v>
-      </c>
-      <c r="F137" s="2" t="s">
+      <c r="G137" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B138" t="s">
+        <v>674</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="D138" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="E138" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F138" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="E138" t="s">
-        <v>1550</v>
-      </c>
-      <c r="F138" s="2" t="s">
+      <c r="G138" s="1" t="s">
         <v>678</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B139" t="s">
+        <v>679</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="D139" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="E139" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F139" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="E139" t="s">
-        <v>1575</v>
-      </c>
-      <c r="F139" s="2" t="s">
+      <c r="G139" s="1" t="s">
         <v>683</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B140" t="s">
+        <v>684</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="E140" t="s">
+        <v>1575</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="E140" t="s">
-        <v>1576</v>
-      </c>
-      <c r="F140" s="2" t="s">
+      <c r="G140" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B141" t="s">
+        <v>689</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="D141" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F141" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="E141" t="s">
-        <v>1577</v>
-      </c>
-      <c r="F141" s="2" t="s">
+      <c r="G141" s="1" t="s">
         <v>693</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B142" t="s">
+        <v>694</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="D142" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="E142" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F142" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="E142" t="s">
-        <v>1539</v>
-      </c>
-      <c r="F142" s="2" t="s">
+      <c r="G142" s="1" t="s">
         <v>698</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B143" t="s">
+        <v>699</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="E143" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F143" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="E143" t="s">
-        <v>1578</v>
-      </c>
-      <c r="F143" s="2" t="s">
+      <c r="G143" s="1" t="s">
         <v>703</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B144" t="s">
+        <v>704</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="D144" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="E144" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F144" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="E144" t="s">
-        <v>1579</v>
-      </c>
-      <c r="F144" s="2" t="s">
+      <c r="G144" s="1" t="s">
         <v>708</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B145" t="s">
+        <v>709</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="E145" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F145" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="E145" t="s">
-        <v>1580</v>
-      </c>
-      <c r="F145" s="2" t="s">
+      <c r="G145" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B146" t="s">
+        <v>714</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>715</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="D146" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="E146" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="E146" t="s">
-        <v>1581</v>
-      </c>
-      <c r="F146" s="2" t="s">
+      <c r="G146" s="1" t="s">
         <v>718</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B147" t="s">
+        <v>719</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="D147" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="E147" t="s">
+        <v>1581</v>
+      </c>
+      <c r="F147" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="E147" t="s">
-        <v>1582</v>
-      </c>
-      <c r="F147" s="2" t="s">
+      <c r="G147" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B148" t="s">
+        <v>724</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="D148" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="E148" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F148" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="E148" t="s">
-        <v>1583</v>
-      </c>
-      <c r="F148" s="2" t="s">
+      <c r="G148" s="1" t="s">
         <v>728</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B149" t="s">
+        <v>729</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="D149" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E149" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F149" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E149" t="s">
-        <v>1583</v>
-      </c>
-      <c r="F149" s="2" t="s">
+      <c r="G149" s="1" t="s">
         <v>732</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B150" t="s">
+        <v>733</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="D150" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="D150" s="1" t="s">
-        <v>736</v>
-      </c>
       <c r="E150" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B151" t="s">
+        <v>737</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="E151" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F151" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="E151" t="s">
-        <v>1583</v>
-      </c>
-      <c r="F151" s="2" t="s">
+      <c r="G151" s="1" t="s">
         <v>741</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B152" t="s">
+        <v>742</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="D152" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="E152" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F152" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="E152" t="s">
-        <v>1709</v>
-      </c>
-      <c r="F152" s="2" t="s">
+      <c r="G152" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B153" t="s">
+        <v>747</v>
+      </c>
+      <c r="C153" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="D153" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="D153" s="1" t="s">
+      <c r="E153" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="E153" t="s">
-        <v>1710</v>
-      </c>
-      <c r="F153" s="2" t="s">
+      <c r="G153" s="1" t="s">
         <v>751</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B154" t="s">
+        <v>752</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="D154" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="E154" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="E154" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F154" s="2" t="s">
+      <c r="G154" s="1" t="s">
         <v>756</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B155" t="s">
+        <v>757</v>
+      </c>
+      <c r="C155" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="D155" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="E155" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="E155" t="s">
-        <v>1585</v>
-      </c>
-      <c r="F155" s="2" t="s">
+      <c r="G155" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B156" t="s">
+        <v>762</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="D156" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="E156" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="E156" t="s">
-        <v>1586</v>
-      </c>
-      <c r="F156" s="2" t="s">
+      <c r="G156" s="1" t="s">
         <v>766</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B157" t="s">
+        <v>767</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="D157" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="E157" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F157" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="E157" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F157" s="2" t="s">
+      <c r="G157" s="1" t="s">
         <v>771</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B158" t="s">
+        <v>772</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="D158" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="E158" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="E158" t="s">
-        <v>1560</v>
-      </c>
-      <c r="F158" s="2" t="s">
+      <c r="G158" s="1" t="s">
         <v>776</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B159" t="s">
+        <v>777</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="D159" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="D159" s="1" t="s">
+      <c r="E159" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F159" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="E159" t="s">
-        <v>1588</v>
-      </c>
-      <c r="F159" s="2" t="s">
+      <c r="G159" s="1" t="s">
         <v>781</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B160" t="s">
+        <v>782</v>
+      </c>
+      <c r="C160" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="D160" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="E160" t="s">
+        <v>1710</v>
+      </c>
+      <c r="F160" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="E160" t="s">
-        <v>1711</v>
-      </c>
-      <c r="F160" s="2" t="s">
+      <c r="G160" s="1" t="s">
         <v>786</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B161" t="s">
+        <v>787</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="D161" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="E161" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F161" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="E161" t="s">
-        <v>1588</v>
-      </c>
-      <c r="F161" s="2" t="s">
+      <c r="G161" s="1" t="s">
         <v>791</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B162" t="s">
+        <v>792</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="D162" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="E162" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="E162" t="s">
-        <v>1589</v>
-      </c>
-      <c r="F162" s="2" t="s">
+      <c r="G162" s="1" t="s">
         <v>796</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B163" t="s">
+        <v>797</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="D163" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="D163" s="1" t="s">
+      <c r="E163" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F163" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="E163" t="s">
-        <v>1590</v>
-      </c>
-      <c r="F163" s="2" t="s">
+      <c r="G163" s="1" t="s">
         <v>801</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B164" t="s">
+        <v>802</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="D164" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="E164" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F164" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="E164" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F164" s="2" t="s">
+      <c r="G164" s="1" t="s">
         <v>806</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B165" t="s">
+        <v>807</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="D165" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="E165" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="E165" t="s">
-        <v>1592</v>
-      </c>
-      <c r="F165" s="2" t="s">
+      <c r="G165" s="1" t="s">
         <v>811</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B166" t="s">
+        <v>812</v>
+      </c>
+      <c r="C166" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="D166" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="D166" s="1" t="s">
+      <c r="E166" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F166" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="E166" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F166" s="2" t="s">
+      <c r="G166" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B167" t="s">
+        <v>817</v>
+      </c>
+      <c r="C167" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="C167" s="1" t="s">
+      <c r="D167" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="E167" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F167" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="E167" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F167" s="2" t="s">
+      <c r="G167" s="1" t="s">
         <v>821</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B168" t="s">
+        <v>822</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="D168" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D168" s="1" t="s">
+      <c r="E168" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="E168" t="s">
-        <v>1595</v>
-      </c>
-      <c r="F168" s="2" t="s">
+      <c r="G168" s="1" t="s">
         <v>826</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B169" t="s">
+        <v>827</v>
+      </c>
+      <c r="C169" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="C169" s="1" t="s">
+      <c r="D169" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="E169" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F169" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="E169" t="s">
-        <v>1596</v>
-      </c>
-      <c r="F169" s="2" t="s">
+      <c r="G169" s="1" t="s">
         <v>831</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B170" t="s">
+        <v>832</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="C170" s="1" t="s">
+      <c r="D170" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="D170" s="1" t="s">
+      <c r="E170" t="s">
+        <v>1596</v>
+      </c>
+      <c r="F170" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="E170" t="s">
-        <v>1597</v>
-      </c>
-      <c r="F170" s="2" t="s">
+      <c r="G170" s="1" t="s">
         <v>836</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B171" t="s">
+        <v>837</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="C171" s="1" t="s">
+      <c r="D171" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="D171" s="1" t="s">
+      <c r="E171" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F171" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="E171" t="s">
-        <v>1598</v>
-      </c>
-      <c r="F171" s="2" t="s">
+      <c r="G171" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B172" t="s">
+        <v>842</v>
+      </c>
+      <c r="C172" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="C172" s="1" t="s">
+      <c r="D172" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="D172" s="1" t="s">
+      <c r="E172" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F172" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="E172" t="s">
-        <v>1599</v>
-      </c>
-      <c r="F172" s="2" t="s">
+      <c r="G172" s="1" t="s">
         <v>846</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B173" t="s">
+        <v>847</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="C173" s="1" t="s">
+      <c r="D173" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="D173" s="1" t="s">
+      <c r="E173" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F173" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="E173" t="s">
-        <v>1600</v>
-      </c>
-      <c r="F173" s="2" t="s">
+      <c r="G173" s="1" t="s">
         <v>851</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B174" t="s">
+        <v>852</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="C174" s="1" t="s">
+      <c r="D174" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="D174" s="1" t="s">
+      <c r="E174" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="E174" t="s">
-        <v>1601</v>
-      </c>
-      <c r="F174" s="2" t="s">
+      <c r="G174" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B175" t="s">
+        <v>857</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="C175" s="1" t="s">
+      <c r="D175" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="D175" s="1" t="s">
+      <c r="E175" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F175" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="E175" t="s">
-        <v>1602</v>
-      </c>
-      <c r="F175" s="2" t="s">
+      <c r="G175" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B176" t="s">
+        <v>862</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="C176" s="1" t="s">
+      <c r="D176" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="E176" t="s">
+        <v>1602</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="E176" t="s">
-        <v>1603</v>
-      </c>
-      <c r="F176" s="2" t="s">
+      <c r="G176" s="1" t="s">
         <v>866</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B177" t="s">
+        <v>867</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="C177" s="1" t="s">
+      <c r="D177" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="E177" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F177" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="E177" t="s">
-        <v>1604</v>
-      </c>
-      <c r="F177" s="2" t="s">
+      <c r="G177" s="1" t="s">
         <v>871</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B178" t="s">
+        <v>872</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="C178" s="1" t="s">
+      <c r="D178" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="D178" s="1" t="s">
+      <c r="E178" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F178" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="E178" t="s">
-        <v>1605</v>
-      </c>
-      <c r="F178" s="2" t="s">
+      <c r="G178" s="1" t="s">
         <v>876</v>
-      </c>
-      <c r="G178" s="1" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B179" t="s">
+        <v>877</v>
+      </c>
+      <c r="C179" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="C179" s="1" t="s">
+      <c r="D179" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="D179" s="1" t="s">
+      <c r="E179" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F179" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="E179" t="s">
-        <v>1606</v>
-      </c>
-      <c r="F179" s="2" t="s">
+      <c r="G179" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B180" t="s">
+        <v>882</v>
+      </c>
+      <c r="C180" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="D180" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="E180" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F180" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="E180" t="s">
-        <v>1607</v>
-      </c>
-      <c r="F180" s="2" t="s">
+      <c r="G180" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B181" t="s">
+        <v>887</v>
+      </c>
+      <c r="C181" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="C181" s="1" t="s">
+      <c r="D181" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="D181" s="1" t="s">
+      <c r="E181" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F181" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="E181" t="s">
-        <v>1608</v>
-      </c>
-      <c r="F181" s="2" t="s">
+      <c r="G181" s="1" t="s">
         <v>891</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B182" t="s">
+        <v>892</v>
+      </c>
+      <c r="C182" s="1" t="s">
         <v>893</v>
       </c>
-      <c r="C182" s="1" t="s">
+      <c r="D182" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="D182" s="1" t="s">
+      <c r="E182" t="s">
+        <v>1608</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="E182" t="s">
-        <v>1609</v>
-      </c>
-      <c r="F182" s="2" t="s">
+      <c r="G182" s="1" t="s">
         <v>896</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B183" t="s">
+        <v>897</v>
+      </c>
+      <c r="C183" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="C183" s="1" t="s">
+      <c r="D183" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="D183" s="1" t="s">
+      <c r="E183" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F183" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="E183" t="s">
-        <v>1610</v>
-      </c>
-      <c r="F183" s="2" t="s">
+      <c r="G183" s="1" t="s">
         <v>901</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B184" t="s">
+        <v>902</v>
+      </c>
+      <c r="C184" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="C184" s="1" t="s">
+      <c r="D184" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="E184" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F184" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="E184" t="s">
-        <v>1611</v>
-      </c>
-      <c r="F184" s="2" t="s">
+      <c r="G184" s="1" t="s">
         <v>906</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B185" t="s">
+        <v>907</v>
+      </c>
+      <c r="C185" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="C185" s="1" t="s">
+      <c r="D185" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="E185" t="s">
+        <v>1611</v>
+      </c>
+      <c r="F185" s="2" t="s">
         <v>910</v>
       </c>
-      <c r="E185" t="s">
-        <v>1612</v>
-      </c>
-      <c r="F185" s="2" t="s">
+      <c r="G185" s="1" t="s">
         <v>911</v>
-      </c>
-      <c r="G185" s="1" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B186" t="s">
+        <v>912</v>
+      </c>
+      <c r="C186" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="C186" s="1" t="s">
+      <c r="D186" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="E186" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F186" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="E186" t="s">
-        <v>1613</v>
-      </c>
-      <c r="F186" s="2" t="s">
+      <c r="G186" s="1" t="s">
         <v>916</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B187" t="s">
+        <v>917</v>
+      </c>
+      <c r="C187" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="C187" s="1" t="s">
+      <c r="D187" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="D187" s="1" t="s">
+      <c r="E187" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F187" s="2" t="s">
         <v>920</v>
       </c>
-      <c r="E187" t="s">
-        <v>1614</v>
-      </c>
-      <c r="F187" s="2" t="s">
+      <c r="G187" s="1" t="s">
         <v>921</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B188" t="s">
+        <v>922</v>
+      </c>
+      <c r="C188" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="C188" s="1" t="s">
+      <c r="D188" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="D188" s="1" t="s">
+      <c r="E188" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F188" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="E188" t="s">
-        <v>1615</v>
-      </c>
-      <c r="F188" s="2" t="s">
+      <c r="G188" s="1" t="s">
         <v>926</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B189" t="s">
+        <v>927</v>
+      </c>
+      <c r="C189" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="D189" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="E189" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F189" s="2" t="s">
         <v>930</v>
       </c>
-      <c r="E189" t="s">
-        <v>1616</v>
-      </c>
-      <c r="F189" s="2" t="s">
+      <c r="G189" s="1" t="s">
         <v>931</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B190" t="s">
+        <v>932</v>
+      </c>
+      <c r="C190" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="C190" s="1" t="s">
+      <c r="D190" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="D190" s="1" t="s">
+      <c r="E190" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F190" s="2" t="s">
         <v>935</v>
       </c>
-      <c r="E190" t="s">
-        <v>1617</v>
-      </c>
-      <c r="F190" s="2" t="s">
+      <c r="G190" s="1" t="s">
         <v>936</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B191" t="s">
+        <v>937</v>
+      </c>
+      <c r="C191" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="C191" s="1" t="s">
+      <c r="D191" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="E191" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G191" s="1" t="s">
         <v>940</v>
-      </c>
-      <c r="E191" t="s">
-        <v>1618</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B192" t="s">
+        <v>941</v>
+      </c>
+      <c r="C192" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="D192" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="E192" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F192" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="E192" t="s">
-        <v>1619</v>
-      </c>
-      <c r="F192" s="2" t="s">
+      <c r="G192" s="1" t="s">
         <v>945</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B193" t="s">
+        <v>946</v>
+      </c>
+      <c r="C193" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="D193" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="E193" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F193" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="E193" t="s">
-        <v>1620</v>
-      </c>
-      <c r="F193" s="2" t="s">
+      <c r="G193" s="1" t="s">
         <v>950</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B194" t="s">
+        <v>951</v>
+      </c>
+      <c r="C194" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="C194" s="1" t="s">
+      <c r="D194" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="E194" t="s">
+        <v>1620</v>
+      </c>
+      <c r="F194" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="E194" t="s">
-        <v>1621</v>
-      </c>
-      <c r="F194" s="2" t="s">
+      <c r="G194" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B195" t="s">
+        <v>956</v>
+      </c>
+      <c r="C195" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="D195" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="E195" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F195" s="2" t="s">
         <v>959</v>
       </c>
-      <c r="E195" t="s">
-        <v>1622</v>
-      </c>
-      <c r="F195" s="2" t="s">
+      <c r="G195" s="1" t="s">
         <v>960</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B196" t="s">
+        <v>961</v>
+      </c>
+      <c r="C196" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="C196" s="1" t="s">
+      <c r="D196" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="D196" s="1" t="s">
+      <c r="E196" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F196" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="E196" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F196" s="2" t="s">
+      <c r="G196" s="1" t="s">
         <v>965</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B197" t="s">
+        <v>966</v>
+      </c>
+      <c r="C197" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="D197" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="E197" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F197" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="E197" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F197" s="2" t="s">
+      <c r="G197" s="1" t="s">
         <v>970</v>
-      </c>
-      <c r="G197" s="1" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B198" t="s">
+        <v>971</v>
+      </c>
+      <c r="C198" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="D198" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="E198" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F198" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="E198" t="s">
-        <v>1624</v>
-      </c>
-      <c r="F198" s="2" t="s">
+      <c r="G198" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B199" t="s">
+        <v>976</v>
+      </c>
+      <c r="C199" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="C199" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="E199" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F199" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="E199" t="s">
-        <v>1625</v>
-      </c>
-      <c r="F199" s="2" t="s">
+      <c r="G199" s="1" t="s">
         <v>980</v>
-      </c>
-      <c r="G199" s="1" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B200" t="s">
+        <v>981</v>
+      </c>
+      <c r="C200" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="C200" s="1" t="s">
+      <c r="D200" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="E200" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F200" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="E200" t="s">
-        <v>1626</v>
-      </c>
-      <c r="F200" s="2" t="s">
+      <c r="G200" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B201" t="s">
+        <v>986</v>
+      </c>
+      <c r="C201" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="C201" s="1" t="s">
+      <c r="D201" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="D201" s="1" t="s">
+      <c r="E201" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F201" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="E201" t="s">
-        <v>1601</v>
-      </c>
-      <c r="F201" s="2" t="s">
+      <c r="G201" s="1" t="s">
         <v>990</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B202" t="s">
+        <v>991</v>
+      </c>
+      <c r="C202" s="1" t="s">
         <v>992</v>
       </c>
-      <c r="C202" s="1" t="s">
+      <c r="D202" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="D202" s="1" t="s">
+      <c r="E202" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F202" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="E202" t="s">
-        <v>1627</v>
-      </c>
-      <c r="F202" s="2" t="s">
+      <c r="G202" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="G202" s="1" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B203" t="s">
+        <v>996</v>
+      </c>
+      <c r="C203" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="D203" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="E203" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F203" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="E203" t="s">
-        <v>1628</v>
-      </c>
-      <c r="F203" s="2" t="s">
+      <c r="G203" s="1" t="s">
         <v>1000</v>
-      </c>
-      <c r="G203" s="1" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B204" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C204" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="C204" s="1" t="s">
+      <c r="D204" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="D204" s="1" t="s">
+      <c r="E204" t="s">
+        <v>1628</v>
+      </c>
+      <c r="F204" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="E204" t="s">
-        <v>1629</v>
-      </c>
-      <c r="F204" s="2" t="s">
+      <c r="G204" s="1" t="s">
         <v>1005</v>
-      </c>
-      <c r="G204" s="1" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B205" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C205" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="C205" s="1" t="s">
+      <c r="D205" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="E205" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F205" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="E205" t="s">
-        <v>1630</v>
-      </c>
-      <c r="F205" s="2" t="s">
+      <c r="G205" s="1" t="s">
         <v>1010</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B206" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C206" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="C206" s="1" t="s">
+      <c r="D206" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="E206" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F206" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="E206" t="s">
-        <v>1631</v>
-      </c>
-      <c r="F206" s="2" t="s">
+      <c r="G206" s="1" t="s">
         <v>1015</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B207" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C207" s="1" t="s">
         <v>1017</v>
       </c>
-      <c r="C207" s="1" t="s">
+      <c r="D207" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="E207" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F207" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="E207" t="s">
-        <v>1515</v>
-      </c>
-      <c r="F207" s="2" t="s">
+      <c r="G207" s="1" t="s">
         <v>1020</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B208" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C208" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="C208" s="1" t="s">
+      <c r="D208" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="E208" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="E208" t="s">
-        <v>1632</v>
-      </c>
-      <c r="F208" s="2" t="s">
+      <c r="G208" s="1" t="s">
         <v>1025</v>
-      </c>
-      <c r="G208" s="1" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B209" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C209" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="C209" s="1" t="s">
+      <c r="D209" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="E209" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F209" s="2" t="s">
         <v>1029</v>
       </c>
-      <c r="E209" t="s">
-        <v>1633</v>
-      </c>
-      <c r="F209" s="2" t="s">
+      <c r="G209" s="1" t="s">
         <v>1030</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B210" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C210" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="C210" s="1" t="s">
+      <c r="D210" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="E210" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F210" s="2" t="s">
         <v>1034</v>
       </c>
-      <c r="E210" t="s">
-        <v>1634</v>
-      </c>
-      <c r="F210" s="2" t="s">
+      <c r="G210" s="1" t="s">
         <v>1035</v>
-      </c>
-      <c r="G210" s="1" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B211" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C211" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="C211" s="1" t="s">
+      <c r="D211" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="E211" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F211" s="2" t="s">
         <v>1039</v>
       </c>
-      <c r="E211" t="s">
-        <v>1635</v>
-      </c>
-      <c r="F211" s="2" t="s">
+      <c r="G211" s="1" t="s">
         <v>1040</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B212" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C212" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="C212" s="1" t="s">
+      <c r="D212" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="E212" t="s">
+        <v>1630</v>
+      </c>
+      <c r="F212" s="2" t="s">
         <v>1044</v>
       </c>
-      <c r="E212" t="s">
-        <v>1631</v>
-      </c>
-      <c r="F212" s="2" t="s">
+      <c r="G212" s="1" t="s">
         <v>1045</v>
-      </c>
-      <c r="G212" s="1" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B213" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C213" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="C213" s="1" t="s">
+      <c r="D213" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="E213" t="s">
+        <v>1635</v>
+      </c>
+      <c r="F213" s="2" t="s">
         <v>1049</v>
       </c>
-      <c r="E213" t="s">
-        <v>1636</v>
-      </c>
-      <c r="F213" s="2" t="s">
+      <c r="G213" s="1" t="s">
         <v>1050</v>
-      </c>
-      <c r="G213" s="1" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B214" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="C214" s="1" t="s">
+      <c r="D214" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="E214" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F214" s="2" t="s">
         <v>1054</v>
       </c>
-      <c r="E214" t="s">
-        <v>1637</v>
-      </c>
-      <c r="F214" s="2" t="s">
+      <c r="G214" s="1" t="s">
         <v>1055</v>
-      </c>
-      <c r="G214" s="1" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B215" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C215" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="C215" s="1" t="s">
+      <c r="D215" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="E215" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F215" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="E215" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F215" s="2" t="s">
+      <c r="G215" s="1" t="s">
         <v>1060</v>
-      </c>
-      <c r="G215" s="1" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B216" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="C216" s="1" t="s">
+      <c r="D216" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="D216" s="1" t="s">
-        <v>1064</v>
-      </c>
       <c r="E216" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B217" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C217" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="D217" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="E217" t="s">
+        <v>1638</v>
+      </c>
+      <c r="F217" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="E217" t="s">
-        <v>1639</v>
-      </c>
-      <c r="F217" s="2" t="s">
+      <c r="G217" s="1" t="s">
         <v>1069</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B218" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C218" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="C218" s="1" t="s">
+      <c r="D218" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="E218" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F218" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="E218" t="s">
-        <v>1640</v>
-      </c>
-      <c r="F218" s="2" t="s">
+      <c r="G218" s="1" t="s">
         <v>1074</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B219" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C219" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="C219" s="1" t="s">
+      <c r="D219" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="E219" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F219" s="2" t="s">
         <v>1078</v>
       </c>
-      <c r="E219" t="s">
-        <v>1641</v>
-      </c>
-      <c r="F219" s="2" t="s">
+      <c r="G219" s="1" t="s">
         <v>1079</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B220" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C220" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="C220" s="1" t="s">
+      <c r="D220" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="D220" s="1" t="s">
+      <c r="E220" t="s">
+        <v>1641</v>
+      </c>
+      <c r="F220" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="E220" t="s">
-        <v>1642</v>
-      </c>
-      <c r="F220" s="2" t="s">
+      <c r="G220" s="1" t="s">
         <v>1084</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B221" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C221" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="C221" s="1" t="s">
+      <c r="D221" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="D221" s="1" t="s">
+      <c r="E221" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="E221" t="s">
-        <v>1643</v>
-      </c>
-      <c r="F221" s="2" t="s">
+      <c r="G221" s="1" t="s">
         <v>1089</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B222" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C222" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="C222" s="1" t="s">
+      <c r="D222" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="D222" s="1" t="s">
+      <c r="E222" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="E222" t="s">
-        <v>1644</v>
-      </c>
-      <c r="F222" s="2" t="s">
+      <c r="G222" s="1" t="s">
         <v>1094</v>
-      </c>
-      <c r="G222" s="1" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B223" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C223" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="C223" s="1" t="s">
+      <c r="D223" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="D223" s="1" t="s">
+      <c r="E223" t="s">
+        <v>1644</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="G223" s="1" t="s">
         <v>1098</v>
-      </c>
-      <c r="E223" t="s">
-        <v>1645</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B224" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C224" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="C224" s="1" t="s">
+      <c r="D224" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="D224" s="1" t="s">
+      <c r="E224" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="E224" t="s">
-        <v>1646</v>
-      </c>
-      <c r="F224" s="2" t="s">
+      <c r="G224" s="1" t="s">
         <v>1103</v>
-      </c>
-      <c r="G224" s="1" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B225" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C225" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="C225" s="1" t="s">
+      <c r="D225" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="D225" s="1" t="s">
+      <c r="E225" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F225" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="E225" t="s">
-        <v>1647</v>
-      </c>
-      <c r="F225" s="2" t="s">
+      <c r="G225" s="1" t="s">
         <v>1108</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B226" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C226" s="1" t="s">
         <v>1110</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>1111</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E226" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="F226" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G226" s="1" t="s">
         <v>1112</v>
-      </c>
-      <c r="G226" s="1" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B227" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C227" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="C227" s="1" t="s">
+      <c r="D227" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="E227" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F227" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="E227" t="s">
-        <v>1649</v>
-      </c>
-      <c r="F227" s="2" t="s">
+      <c r="G227" s="1" t="s">
         <v>1117</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B228" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C228" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="C228" s="1" t="s">
+      <c r="D228" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="D228" s="1" t="s">
+      <c r="E228" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F228" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="E228" t="s">
-        <v>1650</v>
-      </c>
-      <c r="F228" s="2" t="s">
+      <c r="G228" s="1" t="s">
         <v>1122</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B229" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C229" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="C229" s="1" t="s">
+      <c r="D229" s="1" t="s">
         <v>1125</v>
       </c>
-      <c r="D229" s="1" t="s">
+      <c r="E229" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="G229" s="1" t="s">
         <v>1126</v>
-      </c>
-      <c r="E229" t="s">
-        <v>1651</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="G229" s="1" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B230" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C230" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="C230" s="1" t="s">
+      <c r="D230" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="D230" s="1" t="s">
+      <c r="E230" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="E230" t="s">
-        <v>1652</v>
-      </c>
-      <c r="F230" s="2" t="s">
+      <c r="G230" s="1" t="s">
         <v>1131</v>
-      </c>
-      <c r="G230" s="1" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B231" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C231" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="C231" s="1" t="s">
+      <c r="D231" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="D231" s="1" t="s">
+      <c r="E231" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="E231" t="s">
-        <v>1653</v>
-      </c>
-      <c r="F231" s="2" t="s">
+      <c r="G231" s="1" t="s">
         <v>1136</v>
-      </c>
-      <c r="G231" s="1" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B232" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C232" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="C232" s="1" t="s">
+      <c r="D232" s="1" t="s">
         <v>1139</v>
       </c>
-      <c r="D232" s="1" t="s">
+      <c r="E232" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F232" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="E232" t="s">
-        <v>1654</v>
-      </c>
-      <c r="F232" s="2" t="s">
+      <c r="G232" s="1" t="s">
         <v>1141</v>
-      </c>
-      <c r="G232" s="1" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B233" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C233" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="C233" s="1" t="s">
+      <c r="D233" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="D233" s="1" t="s">
+      <c r="E233" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F233" s="2" t="s">
         <v>1145</v>
       </c>
-      <c r="E233" t="s">
-        <v>1655</v>
-      </c>
-      <c r="F233" s="2" t="s">
+      <c r="G233" s="1" t="s">
         <v>1146</v>
-      </c>
-      <c r="G233" s="1" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B234" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C234" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="C234" s="1" t="s">
+      <c r="D234" s="1" t="s">
         <v>1149</v>
       </c>
-      <c r="D234" s="1" t="s">
+      <c r="E234" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="E234" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F234" s="2" t="s">
+      <c r="G234" s="1" t="s">
         <v>1151</v>
-      </c>
-      <c r="G234" s="1" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B235" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C235" s="1" t="s">
         <v>1155</v>
       </c>
-      <c r="C235" s="1" t="s">
+      <c r="D235" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="D235" s="1" t="s">
+      <c r="E235" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="E235" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F235" s="2" t="s">
+      <c r="G235" s="1" t="s">
         <v>1158</v>
-      </c>
-      <c r="G235" s="1" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B236" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C236" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="C236" s="1" t="s">
+      <c r="D236" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="D236" s="1" t="s">
+      <c r="E236" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F236" s="2" t="s">
         <v>1162</v>
       </c>
-      <c r="E236" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F236" s="2" t="s">
+      <c r="G236" s="1" t="s">
         <v>1163</v>
-      </c>
-      <c r="G236" s="1" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B237" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C237" s="1" t="s">
         <v>1165</v>
       </c>
-      <c r="C237" s="1" t="s">
+      <c r="D237" s="1" t="s">
         <v>1166</v>
       </c>
-      <c r="D237" s="1" t="s">
+      <c r="E237" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F237" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="E237" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F237" s="2" t="s">
+      <c r="G237" s="1" t="s">
         <v>1168</v>
-      </c>
-      <c r="G237" s="1" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B238" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C238" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="C238" s="1" t="s">
+      <c r="D238" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="D238" s="1" t="s">
+      <c r="E238" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F238" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="E238" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F238" s="2" t="s">
+      <c r="G238" s="1" t="s">
         <v>1173</v>
-      </c>
-      <c r="G238" s="1" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B239" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C239" s="1" t="s">
         <v>1175</v>
       </c>
-      <c r="C239" s="1" t="s">
+      <c r="D239" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="D239" s="1" t="s">
+      <c r="E239" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="E239" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F239" s="2" t="s">
+      <c r="G239" s="1" t="s">
         <v>1178</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B240" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C240" s="1" t="s">
         <v>1180</v>
-      </c>
-      <c r="C240" s="1" t="s">
-        <v>1181</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="F240" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G240" s="1" t="s">
         <v>1182</v>
-      </c>
-      <c r="G240" s="1" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B241" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C241" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="C241" s="1" t="s">
+      <c r="D241" s="1" t="s">
         <v>1185</v>
       </c>
-      <c r="D241" s="1" t="s">
+      <c r="E241" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F241" s="2" t="s">
         <v>1186</v>
       </c>
-      <c r="E241" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F241" s="2" t="s">
+      <c r="G241" s="1" t="s">
         <v>1187</v>
-      </c>
-      <c r="G241" s="1" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B242" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C242" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="C242" s="1" t="s">
+      <c r="D242" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="E242" t="s">
+        <v>1530</v>
+      </c>
+      <c r="F242" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="E242" t="s">
-        <v>1531</v>
-      </c>
-      <c r="F242" s="2" t="s">
+      <c r="G242" s="1" t="s">
         <v>1192</v>
-      </c>
-      <c r="G242" s="1" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B243" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C243" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="C243" s="1" t="s">
+      <c r="D243" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="D243" s="1" t="s">
+      <c r="E243" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F243" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="E243" t="s">
-        <v>1662</v>
-      </c>
-      <c r="F243" s="2" t="s">
+      <c r="G243" s="1" t="s">
         <v>1197</v>
-      </c>
-      <c r="G243" s="1" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B244" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C244" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="C244" s="1" t="s">
+      <c r="D244" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="D244" s="1" t="s">
+      <c r="E244" t="s">
+        <v>1662</v>
+      </c>
+      <c r="F244" s="2" t="s">
         <v>1201</v>
       </c>
-      <c r="E244" t="s">
-        <v>1663</v>
-      </c>
-      <c r="F244" s="2" t="s">
+      <c r="G244" s="1" t="s">
         <v>1202</v>
-      </c>
-      <c r="G244" s="1" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B245" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C245" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="C245" s="1" t="s">
+      <c r="D245" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="D245" s="1" t="s">
+      <c r="E245" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F245" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="E245" t="s">
-        <v>1664</v>
-      </c>
-      <c r="F245" s="2" t="s">
+      <c r="G245" s="1" t="s">
         <v>1207</v>
-      </c>
-      <c r="G245" s="1" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B246" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C246" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="C246" s="1" t="s">
+      <c r="D246" s="1" t="s">
         <v>1210</v>
       </c>
-      <c r="D246" s="1" t="s">
+      <c r="E246" t="s">
+        <v>1664</v>
+      </c>
+      <c r="F246" s="2" t="s">
         <v>1211</v>
       </c>
-      <c r="E246" t="s">
-        <v>1665</v>
-      </c>
-      <c r="F246" s="2" t="s">
+      <c r="G246" s="1" t="s">
         <v>1212</v>
-      </c>
-      <c r="G246" s="1" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B247" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C247" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="C247" s="1" t="s">
+      <c r="D247" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="D247" s="1" t="s">
+      <c r="E247" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F247" s="2" t="s">
         <v>1216</v>
       </c>
-      <c r="E247" t="s">
-        <v>1666</v>
-      </c>
-      <c r="F247" s="2" t="s">
+      <c r="G247" s="1" t="s">
         <v>1217</v>
-      </c>
-      <c r="G247" s="1" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B248" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C248" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="C248" s="1" t="s">
+      <c r="D248" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="E248" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F248" s="2" t="s">
         <v>1220</v>
       </c>
-      <c r="D248" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="E248" t="s">
-        <v>1667</v>
-      </c>
-      <c r="F248" s="2" t="s">
+      <c r="G248" s="1" t="s">
         <v>1221</v>
-      </c>
-      <c r="G248" s="1" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B249" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C249" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="C249" s="1" t="s">
+      <c r="D249" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="D249" s="1" t="s">
-        <v>1225</v>
-      </c>
       <c r="E249" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B250" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C250" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="C250" s="1" t="s">
+      <c r="D250" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="D250" s="1" t="s">
+      <c r="E250" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="E250" t="s">
-        <v>1669</v>
-      </c>
-      <c r="F250" s="2" t="s">
+      <c r="G250" s="1" t="s">
         <v>1230</v>
-      </c>
-      <c r="G250" s="1" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B251" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C251" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="C251" s="1" t="s">
+      <c r="D251" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="D251" s="1" t="s">
+      <c r="E251" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F251" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="E251" t="s">
-        <v>1670</v>
-      </c>
-      <c r="F251" s="2" t="s">
+      <c r="G251" s="1" t="s">
         <v>1235</v>
-      </c>
-      <c r="G251" s="1" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B252" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C252" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="C252" s="1" t="s">
+      <c r="D252" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="D252" s="1" t="s">
+      <c r="E252" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F252" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="E252" t="s">
-        <v>1671</v>
-      </c>
-      <c r="F252" s="2" t="s">
+      <c r="G252" s="1" t="s">
         <v>1240</v>
-      </c>
-      <c r="G252" s="1" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B253" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C253" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="C253" s="1" t="s">
+      <c r="D253" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="D253" s="1" t="s">
+      <c r="E253" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F253" s="2" t="s">
         <v>1244</v>
       </c>
-      <c r="E253" t="s">
-        <v>1672</v>
-      </c>
-      <c r="F253" s="2" t="s">
+      <c r="G253" s="1" t="s">
         <v>1245</v>
-      </c>
-      <c r="G253" s="1" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B254" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C254" s="1" t="s">
         <v>1247</v>
       </c>
-      <c r="C254" s="1" t="s">
+      <c r="D254" s="1" t="s">
         <v>1248</v>
       </c>
-      <c r="D254" s="1" t="s">
+      <c r="E254" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>1249</v>
       </c>
-      <c r="E254" t="s">
-        <v>1673</v>
-      </c>
-      <c r="F254" s="2" t="s">
+      <c r="G254" s="1" t="s">
         <v>1250</v>
-      </c>
-      <c r="G254" s="1" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B255" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C255" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="C255" s="1" t="s">
+      <c r="D255" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="D255" s="1" t="s">
-        <v>1254</v>
-      </c>
       <c r="E255" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B256" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C256" s="1" t="s">
         <v>1256</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>1257</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E256" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="F256" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G256" s="1" t="s">
         <v>1258</v>
-      </c>
-      <c r="G256" s="1" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B257" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C257" s="1" t="s">
         <v>1260</v>
       </c>
-      <c r="C257" s="1" t="s">
+      <c r="D257" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="D257" s="1" t="s">
+      <c r="E257" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G257" s="1" t="s">
         <v>1262</v>
-      </c>
-      <c r="E257" t="s">
-        <v>1676</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>1140</v>
-      </c>
-      <c r="G257" s="1" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B258" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C258" s="1" t="s">
         <v>1264</v>
       </c>
-      <c r="C258" s="1" t="s">
+      <c r="D258" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="D258" s="1" t="s">
+      <c r="E258" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F258" s="2" t="s">
         <v>1266</v>
       </c>
-      <c r="E258" t="s">
-        <v>1677</v>
-      </c>
-      <c r="F258" s="2" t="s">
+      <c r="G258" s="1" t="s">
         <v>1267</v>
-      </c>
-      <c r="G258" s="1" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B259" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C259" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="C259" s="1" t="s">
+      <c r="D259" s="1" t="s">
         <v>1270</v>
       </c>
-      <c r="D259" s="1" t="s">
+      <c r="E259" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F259" s="2" t="s">
         <v>1271</v>
       </c>
-      <c r="E259" t="s">
-        <v>1678</v>
-      </c>
-      <c r="F259" s="2" t="s">
+      <c r="G259" s="1" t="s">
         <v>1272</v>
-      </c>
-      <c r="G259" s="1" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B260" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C260" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="C260" s="1" t="s">
+      <c r="D260" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="D260" s="1" t="s">
+      <c r="E260" t="s">
+        <v>1678</v>
+      </c>
+      <c r="F260" s="2" t="s">
         <v>1276</v>
       </c>
-      <c r="E260" t="s">
-        <v>1679</v>
-      </c>
-      <c r="F260" s="2" t="s">
+      <c r="G260" s="1" t="s">
         <v>1277</v>
-      </c>
-      <c r="G260" s="1" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B261" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C261" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="C261" s="1" t="s">
+      <c r="D261" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="D261" s="1" t="s">
+      <c r="E261" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F261" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="E261" t="s">
-        <v>1680</v>
-      </c>
-      <c r="F261" s="2" t="s">
+      <c r="G261" s="1" t="s">
         <v>1282</v>
-      </c>
-      <c r="G261" s="1" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B262" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C262" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="C262" s="1" t="s">
+      <c r="D262" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="D262" s="1" t="s">
+      <c r="E262" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F262" s="2" t="s">
         <v>1286</v>
       </c>
-      <c r="E262" t="s">
-        <v>1681</v>
-      </c>
-      <c r="F262" s="2" t="s">
+      <c r="G262" s="1" t="s">
         <v>1287</v>
-      </c>
-      <c r="G262" s="1" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B263" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C263" s="1" t="s">
         <v>1289</v>
       </c>
-      <c r="C263" s="1" t="s">
+      <c r="D263" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="D263" s="1" t="s">
+      <c r="E263" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F263" s="2" t="s">
         <v>1291</v>
       </c>
-      <c r="E263" t="s">
-        <v>1682</v>
-      </c>
-      <c r="F263" s="2" t="s">
+      <c r="G263" s="1" t="s">
         <v>1292</v>
-      </c>
-      <c r="G263" s="1" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B264" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C264" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="C264" s="1" t="s">
+      <c r="D264" s="1" t="s">
         <v>1295</v>
       </c>
-      <c r="D264" s="1" t="s">
+      <c r="E264" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F264" s="2" t="s">
         <v>1296</v>
       </c>
-      <c r="E264" t="s">
-        <v>1683</v>
-      </c>
-      <c r="F264" s="2" t="s">
+      <c r="G264" s="1" t="s">
         <v>1297</v>
-      </c>
-      <c r="G264" s="1" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B265" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C265" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="C265" s="1" t="s">
+      <c r="D265" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="D265" s="1" t="s">
+      <c r="E265" t="s">
+        <v>1683</v>
+      </c>
+      <c r="F265" s="2" t="s">
         <v>1302</v>
       </c>
-      <c r="E265" t="s">
-        <v>1684</v>
-      </c>
-      <c r="F265" s="2" t="s">
+      <c r="G265" s="1" t="s">
         <v>1303</v>
-      </c>
-      <c r="G265" s="1" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B266" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>1305</v>
       </c>
-      <c r="C266" s="1" t="s">
+      <c r="E266" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F266" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G266" s="1" t="s">
         <v>1451</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E266" t="s">
-        <v>1701</v>
-      </c>
-      <c r="F266" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="G266" s="1" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B267" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C267" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="C267" s="1" t="s">
+      <c r="D267" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="D267" s="1" t="s">
+      <c r="E267" t="s">
+        <v>1701</v>
+      </c>
+      <c r="F267" s="2" t="s">
         <v>1310</v>
       </c>
-      <c r="E267" t="s">
-        <v>1702</v>
-      </c>
-      <c r="F267" s="2" t="s">
+      <c r="G267" s="1" t="s">
         <v>1311</v>
-      </c>
-      <c r="G267" s="1" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B268" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C268" s="1" t="s">
         <v>1313</v>
       </c>
-      <c r="C268" s="1" t="s">
-        <v>1314</v>
-      </c>
       <c r="D268" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="E268" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B269" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C269" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="C269" s="1" t="s">
+      <c r="D269" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="D269" s="1" t="s">
+      <c r="E269" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F269" s="2" t="s">
         <v>1318</v>
       </c>
-      <c r="E269" t="s">
-        <v>1570</v>
-      </c>
-      <c r="F269" s="2" t="s">
+      <c r="G269" s="1" t="s">
         <v>1319</v>
-      </c>
-      <c r="G269" s="1" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B270" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C270" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="C270" s="1" t="s">
+      <c r="D270" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="D270" s="1" t="s">
+      <c r="E270" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F270" s="2" t="s">
         <v>1323</v>
       </c>
-      <c r="E270" t="s">
-        <v>1686</v>
-      </c>
-      <c r="F270" s="2" t="s">
+      <c r="G270" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="G270" s="1" t="s">
-        <v>1325</v>
-      </c>
       <c r="L270" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B271" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C271" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="C271" s="1" t="s">
+      <c r="D271" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="D271" s="1" t="s">
+      <c r="E271" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F271" s="2" t="s">
         <v>1328</v>
       </c>
-      <c r="E271" t="s">
-        <v>1687</v>
-      </c>
-      <c r="F271" s="2" t="s">
+      <c r="G271" s="1" t="s">
         <v>1329</v>
-      </c>
-      <c r="G271" s="1" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B272" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C272" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="C272" s="1" t="s">
+      <c r="D272" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="D272" s="1" t="s">
+      <c r="E272" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F272" s="2" t="s">
         <v>1333</v>
       </c>
-      <c r="E272" t="s">
-        <v>1688</v>
-      </c>
-      <c r="F272" s="2" t="s">
+      <c r="G272" s="1" t="s">
         <v>1334</v>
-      </c>
-      <c r="G272" s="1" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B273" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C273" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="C273" s="1" t="s">
+      <c r="D273" s="1" t="s">
         <v>1337</v>
       </c>
-      <c r="D273" s="1" t="s">
+      <c r="E273" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>1338</v>
       </c>
-      <c r="E273" t="s">
-        <v>1689</v>
-      </c>
-      <c r="F273" s="2" t="s">
+      <c r="G273" s="1" t="s">
         <v>1339</v>
-      </c>
-      <c r="G273" s="1" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B274" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C274" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="C274" s="1" t="s">
+      <c r="D274" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="D274" s="1" t="s">
+      <c r="E274" t="s">
+        <v>1689</v>
+      </c>
+      <c r="F274" s="2" t="s">
         <v>1343</v>
       </c>
-      <c r="E274" t="s">
-        <v>1690</v>
-      </c>
-      <c r="F274" s="2" t="s">
+      <c r="G274" s="1" t="s">
         <v>1344</v>
-      </c>
-      <c r="G274" s="1" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B275" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C275" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="C275" s="1" t="s">
+      <c r="D275" s="1" t="s">
         <v>1347</v>
       </c>
-      <c r="D275" s="1" t="s">
+      <c r="E275" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>1348</v>
       </c>
-      <c r="E275" t="s">
-        <v>1537</v>
-      </c>
-      <c r="F275" s="2" t="s">
+      <c r="G275" s="1" t="s">
         <v>1349</v>
-      </c>
-      <c r="G275" s="1" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B276" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C276" s="1" t="s">
         <v>1351</v>
       </c>
-      <c r="C276" s="1" t="s">
+      <c r="D276" s="1" t="s">
         <v>1352</v>
       </c>
-      <c r="D276" s="1" t="s">
+      <c r="E276" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F276" s="2" t="s">
         <v>1353</v>
       </c>
-      <c r="E276" t="s">
-        <v>1635</v>
-      </c>
-      <c r="F276" s="2" t="s">
+      <c r="G276" s="1" t="s">
         <v>1354</v>
-      </c>
-      <c r="G276" s="1" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C277" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="C277" s="1" t="s">
+      <c r="D277" s="1" t="s">
         <v>1357</v>
       </c>
-      <c r="D277" s="1" t="s">
+      <c r="E277" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F277" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G277" s="1" t="s">
         <v>1358</v>
-      </c>
-      <c r="E277" t="s">
-        <v>1691</v>
-      </c>
-      <c r="F277" s="2" t="s">
-        <v>1299</v>
-      </c>
-      <c r="G277" s="1" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B278" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C278" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="C278" s="1" t="s">
+      <c r="D278" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="D278" s="1" t="s">
+      <c r="E278" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>1362</v>
       </c>
-      <c r="E278" t="s">
-        <v>1529</v>
-      </c>
-      <c r="F278" s="2" t="s">
+      <c r="G278" s="1" t="s">
         <v>1363</v>
-      </c>
-      <c r="G278" s="1" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B279" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C279" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="C279" s="1" t="s">
+      <c r="D279" s="1" t="s">
         <v>1366</v>
       </c>
-      <c r="D279" s="1" t="s">
+      <c r="E279" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F279" s="2" t="s">
         <v>1367</v>
       </c>
-      <c r="E279" t="s">
-        <v>1529</v>
-      </c>
-      <c r="F279" s="2" t="s">
+      <c r="G279" s="1" t="s">
         <v>1368</v>
-      </c>
-      <c r="G279" s="1" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B280" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C280" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="C280" s="1" t="s">
+      <c r="D280" s="1" t="s">
         <v>1371</v>
       </c>
-      <c r="D280" s="1" t="s">
+      <c r="E280" t="s">
+        <v>1691</v>
+      </c>
+      <c r="F280" s="2" t="s">
         <v>1372</v>
       </c>
-      <c r="E280" t="s">
-        <v>1692</v>
-      </c>
-      <c r="F280" s="2" t="s">
+      <c r="G280" s="1" t="s">
         <v>1373</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B281" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C281" s="1" t="s">
         <v>1375</v>
       </c>
-      <c r="C281" s="1" t="s">
+      <c r="D281" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="D281" s="1" t="s">
+      <c r="E281" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F281" s="2" t="s">
         <v>1377</v>
       </c>
-      <c r="E281" t="s">
-        <v>1542</v>
-      </c>
-      <c r="F281" s="2" t="s">
+      <c r="G281" s="1" t="s">
         <v>1378</v>
-      </c>
-      <c r="G281" s="1" t="s">
-        <v>1379</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B282" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C282" s="1" t="s">
         <v>1380</v>
       </c>
-      <c r="C282" s="1" t="s">
+      <c r="D282" s="1" t="s">
         <v>1381</v>
       </c>
-      <c r="D282" s="1" t="s">
+      <c r="E282" t="s">
+        <v>1526</v>
+      </c>
+      <c r="F282" s="2" t="s">
         <v>1382</v>
       </c>
-      <c r="E282" t="s">
-        <v>1527</v>
-      </c>
-      <c r="F282" s="2" t="s">
+      <c r="G282" s="1" t="s">
         <v>1383</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B283" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C283" s="1" t="s">
         <v>1385</v>
       </c>
-      <c r="C283" s="1" t="s">
+      <c r="D283" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="D283" s="1" t="s">
+      <c r="E283" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>1387</v>
       </c>
-      <c r="E283" t="s">
-        <v>1565</v>
-      </c>
-      <c r="F283" s="2" t="s">
+      <c r="G283" s="1" t="s">
         <v>1388</v>
-      </c>
-      <c r="G283" s="1" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B284" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C284" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="C284" s="1" t="s">
+      <c r="D284" s="1" t="s">
         <v>1391</v>
       </c>
-      <c r="D284" s="1" t="s">
+      <c r="E284" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F284" s="2" t="s">
         <v>1392</v>
       </c>
-      <c r="E284" t="s">
-        <v>1693</v>
-      </c>
-      <c r="F284" s="2" t="s">
+      <c r="G284" s="1" t="s">
         <v>1393</v>
-      </c>
-      <c r="G284" s="1" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B285" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C285" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="C285" s="1" t="s">
+      <c r="D285" s="1" t="s">
         <v>1396</v>
       </c>
-      <c r="D285" s="1" t="s">
+      <c r="E285" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F285" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G285" s="1" t="s">
         <v>1397</v>
-      </c>
-      <c r="E285" t="s">
-        <v>1694</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G285" s="1" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B286" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C286" s="1" t="s">
         <v>1399</v>
       </c>
-      <c r="C286" s="1" t="s">
+      <c r="D286" s="1" t="s">
         <v>1400</v>
       </c>
-      <c r="D286" s="1" t="s">
+      <c r="E286" t="s">
+        <v>1694</v>
+      </c>
+      <c r="F286" s="2" t="s">
         <v>1401</v>
       </c>
-      <c r="E286" t="s">
-        <v>1695</v>
-      </c>
-      <c r="F286" s="2" t="s">
+      <c r="G286" s="1" t="s">
         <v>1402</v>
-      </c>
-      <c r="G286" s="1" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B287" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C287" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="C287" s="1" t="s">
+      <c r="D287" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D287" s="1" t="s">
+      <c r="E287" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F287" s="2" t="s">
         <v>1406</v>
       </c>
-      <c r="E287" t="s">
-        <v>1696</v>
-      </c>
-      <c r="F287" s="2" t="s">
+      <c r="G287" s="1" t="s">
         <v>1407</v>
-      </c>
-      <c r="G287" s="1" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B288" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="C288" s="1" t="s">
+      <c r="E288" t="s">
+        <v>1696</v>
+      </c>
+      <c r="F288" s="2" t="s">
         <v>1409</v>
       </c>
-      <c r="D288" s="1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="E288" t="s">
-        <v>1697</v>
-      </c>
-      <c r="F288" s="2" t="s">
+      <c r="G288" s="1" t="s">
         <v>1410</v>
-      </c>
-      <c r="G288" s="1" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B289" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C289" s="1" t="s">
         <v>1412</v>
       </c>
-      <c r="C289" s="1" t="s">
+      <c r="D289" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="D289" s="1" t="s">
+      <c r="E289" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>1414</v>
       </c>
-      <c r="E289" t="s">
-        <v>1549</v>
-      </c>
-      <c r="F289" s="2" t="s">
+      <c r="G289" s="1" t="s">
         <v>1415</v>
-      </c>
-      <c r="G289" s="1" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B290" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C290" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="C290" s="1" t="s">
+      <c r="D290" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="D290" s="1" t="s">
+      <c r="E290" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>1419</v>
       </c>
-      <c r="E290" t="s">
-        <v>1698</v>
-      </c>
-      <c r="F290" s="2" t="s">
+      <c r="G290" s="1" t="s">
         <v>1420</v>
-      </c>
-      <c r="G290" s="1" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B291" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C291" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="C291" s="1" t="s">
+      <c r="D291" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="D291" s="1" t="s">
+      <c r="E291" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F291" s="2" t="s">
         <v>1424</v>
       </c>
-      <c r="E291" t="s">
-        <v>1570</v>
-      </c>
-      <c r="F291" s="2" t="s">
+      <c r="G291" s="1" t="s">
         <v>1425</v>
-      </c>
-      <c r="G291" s="1" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B292" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C292" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="D292" s="1" t="s">
+      <c r="E292" t="s">
+        <v>1698</v>
+      </c>
+      <c r="F292" s="2" t="s">
         <v>1428</v>
       </c>
-      <c r="E292" t="s">
-        <v>1699</v>
-      </c>
-      <c r="F292" s="2" t="s">
+      <c r="G292" s="1" t="s">
         <v>1429</v>
-      </c>
-      <c r="G292" s="1" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B293" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C293" s="1" t="s">
         <v>1431</v>
       </c>
-      <c r="C293" s="1" t="s">
+      <c r="D293" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E293" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F293" s="2" t="s">
         <v>1432</v>
       </c>
-      <c r="D293" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E293" t="s">
-        <v>1641</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>1433</v>
-      </c>
       <c r="G293" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B294" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C294" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="C294" s="1" t="s">
+      <c r="D294" s="1" t="s">
         <v>1185</v>
       </c>
-      <c r="D294" s="1" t="s">
+      <c r="E294" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F294" s="2" t="s">
         <v>1186</v>
       </c>
-      <c r="E294" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F294" s="2" t="s">
+      <c r="G294" s="1" t="s">
         <v>1187</v>
-      </c>
-      <c r="G294" s="1" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B295" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C295" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="C295" s="1" t="s">
+      <c r="D295" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="D295" s="1" t="s">
+      <c r="E295" t="s">
+        <v>1530</v>
+      </c>
+      <c r="F295" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="E295" t="s">
-        <v>1531</v>
-      </c>
-      <c r="F295" s="2" t="s">
+      <c r="G295" s="1" t="s">
         <v>1192</v>
-      </c>
-      <c r="G295" s="1" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B296" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C296" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="C296" s="1" t="s">
+      <c r="D296" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="D296" s="1" t="s">
+      <c r="E296" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F296" s="2" t="s">
         <v>1196</v>
       </c>
-      <c r="E296" t="s">
-        <v>1685</v>
-      </c>
-      <c r="F296" s="2" t="s">
+      <c r="G296" s="1" t="s">
         <v>1197</v>
-      </c>
-      <c r="G296" s="1" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B297" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C297" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="C297" s="1" t="s">
+      <c r="D297" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="D297" s="1" t="s">
+      <c r="E297" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F297" s="2" t="s">
         <v>1201</v>
       </c>
-      <c r="E297" t="s">
-        <v>1700</v>
-      </c>
-      <c r="F297" s="2" t="s">
+      <c r="G297" s="1" t="s">
         <v>1202</v>
-      </c>
-      <c r="G297" s="1" t="s">
-        <v>1203</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Daily_Word.xlsx
+++ b/public/data/Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE0D830-BBBF-47B5-BBE0-5FCE61ECFB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE08650C-96A4-4FB0-B68B-D8396518026D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -176,9 +176,6 @@
     <t>Картошка</t>
   </si>
   <si>
-    <t>קַרְטוֹשְׁקָה</t>
-  </si>
-  <si>
     <t>תפוח אדמה</t>
   </si>
   <si>
@@ -191,9 +188,6 @@
     <t>яблоко</t>
   </si>
   <si>
-    <t>יַבְּלָקוֹ</t>
-  </si>
-  <si>
     <t>תפוח</t>
   </si>
   <si>
@@ -227,18 +221,12 @@
     <t>масло</t>
   </si>
   <si>
-    <t>מַאסְלָה</t>
-  </si>
-  <si>
     <t>חמאה</t>
   </si>
   <si>
     <t xml:space="preserve">מס </t>
   </si>
   <si>
-    <t xml:space="preserve"> מזכיר מס - מַאסְלָה היא מוצר בסיסי אך יקר.</t>
-  </si>
-  <si>
     <t>хурма</t>
   </si>
   <si>
@@ -389,16 +377,10 @@
     <t>сметана</t>
   </si>
   <si>
-    <t>סְמֶטָאנָה</t>
-  </si>
-  <si>
     <t>שמנת חמוצה</t>
   </si>
   <si>
     <t>סמיכה</t>
-  </si>
-  <si>
-    <t>אין כמו למרוח את הסְמֶטָאנָה על הפנקייק כאילו היא השמיכה שלו</t>
   </si>
   <si>
     <t>пирог</t>
@@ -5434,9 +5416,6 @@
     <t>מְיוֹד הוא מאוד מתוק וטעים.</t>
   </si>
   <si>
-    <t>היַבְּלָקוֹ מסודר בבלוקים מסודרים יפה בסופר.</t>
-  </si>
-  <si>
     <t>אין כמו סִירְנִיקִי חם ישר מהסיר לתוך הריבה!</t>
   </si>
   <si>
@@ -5450,6 +5429,27 @@
   </si>
   <si>
     <t>מהיַיִצוֹ האפרוח יוצא לעולם.</t>
+  </si>
+  <si>
+    <t>יַבְּלָקָה</t>
+  </si>
+  <si>
+    <t>היַבְּלָקָה מסודר בבלוקים מסודרים יפה בסופר.</t>
+  </si>
+  <si>
+    <t>סְמֶטָנָה</t>
+  </si>
+  <si>
+    <t>אין כמו למרוח את הסְמֶטָנָה על הפנקייק כאילו היא השמיכה שלו</t>
+  </si>
+  <si>
+    <t>קַרְטוֹשְקָה</t>
+  </si>
+  <si>
+    <t>מַסְלָה</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> מזכיר מס - מַסְלָה היא מוצר בסיסי אך יקר.</t>
   </si>
 </sst>
 </file>
@@ -5848,27 +5848,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1702</v>
+        <v>1696</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1455</v>
+        <v>1449</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1453</v>
+        <v>1447</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1452</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
@@ -5880,7 +5880,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>20</v>
@@ -5891,7 +5891,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -5903,7 +5903,7 @@
         <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>25</v>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
@@ -5926,18 +5926,18 @@
         <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1456</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -5949,7 +5949,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>34</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
@@ -5972,7 +5972,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>39</v>
@@ -5983,7 +5983,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
@@ -5995,53 +5995,53 @@
         <v>43</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>44</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1721</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B8" t="s">
         <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>1464</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
@@ -6052,6623 +6052,6623 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1466</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>1468</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="G12" s="1" t="s">
-        <v>66</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>1469</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>1470</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>1471</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>1472</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>1473</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>1475</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>1476</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1715</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>117</v>
+        <v>1717</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>120</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B29" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1484</v>
+        <v>1478</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B31" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B32" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1714</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B34" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1488</v>
+        <v>1482</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B36" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1490</v>
+        <v>1484</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B37" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1491</v>
+        <v>1485</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1492</v>
+        <v>1486</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B39" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1493</v>
+        <v>1487</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B40" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B41" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1496</v>
+        <v>1490</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B42" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1497</v>
+        <v>1491</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B43" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1498</v>
+        <v>1492</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B44" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1499</v>
+        <v>1493</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B45" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1703</v>
+        <v>1697</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1713</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B46" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B47" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1704</v>
+        <v>1698</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B48" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B49" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B50" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B51" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B52" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1505</v>
+        <v>1499</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B53" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B54" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1511</v>
+        <v>1505</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B55" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B56" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B57" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1507</v>
+        <v>1501</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B58" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B59" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B60" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1510</v>
+        <v>1504</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B61" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1513</v>
+        <v>1507</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B62" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1514</v>
+        <v>1508</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B63" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1514</v>
+        <v>1508</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B64" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1515</v>
+        <v>1509</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B65" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1516</v>
+        <v>1510</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B66" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B67" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B68" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1510</v>
+        <v>1504</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1720</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B69" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B70" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B71" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1705</v>
+        <v>1699</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B72" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1519</v>
+        <v>1513</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B73" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1520</v>
+        <v>1514</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B74" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1521</v>
+        <v>1515</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B75" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1522</v>
+        <v>1516</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B76" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1523</v>
+        <v>1517</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B77" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B78" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B79" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1525</v>
+        <v>1519</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B80" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B81" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B82" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B83" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="B84" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B85" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B86" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B87" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B88" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1706</v>
+        <v>1700</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B89" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1707</v>
+        <v>1701</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B90" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B91" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B92" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B93" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="E93" t="s">
-        <v>1537</v>
+        <v>1531</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B94" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="E94" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B95" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E95" t="s">
-        <v>1538</v>
+        <v>1532</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B96" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="E96" t="s">
-        <v>1539</v>
+        <v>1533</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B97" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="E97" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B98" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="E98" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B99" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="E99" t="s">
-        <v>1542</v>
+        <v>1536</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B100" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="E100" t="s">
-        <v>1543</v>
+        <v>1537</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B101" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="E101" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B102" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E102" t="s">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B103" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E103" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B104" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E104" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B105" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="E105" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B106" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="E106" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B107" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="E107" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B108" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E108" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B109" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="E109" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B110" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="E110" t="s">
-        <v>1553</v>
+        <v>1547</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B111" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E111" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B112" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="E112" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B113" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="E113" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B114" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="E114" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B115" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="E115" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B116" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E116" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B117" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="E117" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B118" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="E118" t="s">
-        <v>1560</v>
+        <v>1554</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B119" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="E119" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B120" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="E120" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B121" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="E121" t="s">
-        <v>1563</v>
+        <v>1557</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B122" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="E122" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B123" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="E123" t="s">
-        <v>1565</v>
+        <v>1559</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B124" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="E124" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B125" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="E125" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B126" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="E126" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B127" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="E127" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B128" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="E128" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B129" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="E129" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B130" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="E130" t="s">
-        <v>1711</v>
+        <v>1705</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B131" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="E131" t="s">
-        <v>1712</v>
+        <v>1706</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B132" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="E132" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B133" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="E133" t="s">
-        <v>1571</v>
+        <v>1565</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B134" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="E134" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B135" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="E135" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B136" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E136" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B137" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E137" t="s">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B138" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="E138" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B139" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="E139" t="s">
-        <v>1574</v>
+        <v>1568</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B140" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="E140" t="s">
-        <v>1575</v>
+        <v>1569</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B141" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="E141" t="s">
-        <v>1576</v>
+        <v>1570</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B142" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="E142" t="s">
-        <v>1538</v>
+        <v>1532</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B143" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E143" t="s">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B144" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="E144" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B145" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="E145" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B146" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="E146" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B147" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="E147" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B148" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="E148" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B149" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E149" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B150" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="E150" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B151" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="E151" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B152" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="E152" t="s">
-        <v>1708</v>
+        <v>1702</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B153" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="E153" t="s">
-        <v>1709</v>
+        <v>1703</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B154" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="E154" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B155" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="E155" t="s">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B156" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="E156" t="s">
-        <v>1585</v>
+        <v>1579</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B157" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="E157" t="s">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B158" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="E158" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B159" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="E159" t="s">
-        <v>1587</v>
+        <v>1581</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B160" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="E160" t="s">
-        <v>1710</v>
+        <v>1704</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B161" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="E161" t="s">
-        <v>1587</v>
+        <v>1581</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B162" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="E162" t="s">
-        <v>1588</v>
+        <v>1582</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B163" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="E163" t="s">
-        <v>1589</v>
+        <v>1583</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B164" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="E164" t="s">
-        <v>1590</v>
+        <v>1584</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B165" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="E165" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B166" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="E166" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B167" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="E167" t="s">
-        <v>1593</v>
+        <v>1587</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B168" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="E168" t="s">
-        <v>1594</v>
+        <v>1588</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B169" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="E169" t="s">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B170" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="E170" t="s">
-        <v>1596</v>
+        <v>1590</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B171" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="E171" t="s">
-        <v>1597</v>
+        <v>1591</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B172" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="E172" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B173" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="E173" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B174" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="E174" t="s">
-        <v>1600</v>
+        <v>1594</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B175" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="E175" t="s">
-        <v>1601</v>
+        <v>1595</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B176" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="E176" t="s">
-        <v>1602</v>
+        <v>1596</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B177" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="E177" t="s">
-        <v>1603</v>
+        <v>1597</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B178" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="E178" t="s">
-        <v>1604</v>
+        <v>1598</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B179" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="E179" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B180" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="E180" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B181" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="E181" t="s">
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B182" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="E182" t="s">
-        <v>1608</v>
+        <v>1602</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B183" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="E183" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B184" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="E184" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B185" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="E185" t="s">
-        <v>1611</v>
+        <v>1605</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B186" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="E186" t="s">
-        <v>1612</v>
+        <v>1606</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B187" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="E187" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B188" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="E188" t="s">
-        <v>1614</v>
+        <v>1608</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B189" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="E189" t="s">
-        <v>1615</v>
+        <v>1609</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B190" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="E190" t="s">
-        <v>1616</v>
+        <v>1610</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B191" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="E191" t="s">
-        <v>1617</v>
+        <v>1611</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B192" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="E192" t="s">
-        <v>1618</v>
+        <v>1612</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B193" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="E193" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B194" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="E194" t="s">
-        <v>1620</v>
+        <v>1614</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B195" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="E195" t="s">
-        <v>1621</v>
+        <v>1615</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B196" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="E196" t="s">
-        <v>1622</v>
+        <v>1616</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B197" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="E197" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B198" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="E198" t="s">
-        <v>1623</v>
+        <v>1617</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B199" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="E199" t="s">
-        <v>1624</v>
+        <v>1618</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B200" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="E200" t="s">
-        <v>1625</v>
+        <v>1619</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B201" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="E201" t="s">
-        <v>1600</v>
+        <v>1594</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B202" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="E202" t="s">
-        <v>1626</v>
+        <v>1620</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B203" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="E203" t="s">
-        <v>1627</v>
+        <v>1621</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B204" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="E204" t="s">
-        <v>1628</v>
+        <v>1622</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B205" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="E205" t="s">
-        <v>1629</v>
+        <v>1623</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B206" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="E206" t="s">
-        <v>1630</v>
+        <v>1624</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B207" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="E207" t="s">
-        <v>1514</v>
+        <v>1508</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B208" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="E208" t="s">
-        <v>1631</v>
+        <v>1625</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B209" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="E209" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B210" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="E210" t="s">
-        <v>1633</v>
+        <v>1627</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B211" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="E211" t="s">
-        <v>1634</v>
+        <v>1628</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B212" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="E212" t="s">
-        <v>1630</v>
+        <v>1624</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B213" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="E213" t="s">
-        <v>1635</v>
+        <v>1629</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B214" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="E214" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B215" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="E215" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B216" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="E216" t="s">
-        <v>1637</v>
+        <v>1631</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B217" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="E217" t="s">
-        <v>1638</v>
+        <v>1632</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B218" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="E218" t="s">
-        <v>1639</v>
+        <v>1633</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B219" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="E219" t="s">
-        <v>1640</v>
+        <v>1634</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B220" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="E220" t="s">
-        <v>1641</v>
+        <v>1635</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B221" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="E221" t="s">
-        <v>1642</v>
+        <v>1636</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B222" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="E222" t="s">
-        <v>1643</v>
+        <v>1637</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B223" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="E223" t="s">
-        <v>1644</v>
+        <v>1638</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B224" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="E224" t="s">
-        <v>1645</v>
+        <v>1639</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B225" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="E225" t="s">
-        <v>1646</v>
+        <v>1640</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B226" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E226" t="s">
-        <v>1647</v>
+        <v>1641</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B227" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="E227" t="s">
-        <v>1648</v>
+        <v>1642</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B228" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="E228" t="s">
-        <v>1649</v>
+        <v>1643</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B229" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="E229" t="s">
-        <v>1650</v>
+        <v>1644</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B230" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="E230" t="s">
-        <v>1651</v>
+        <v>1645</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="B231" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="E231" t="s">
-        <v>1652</v>
+        <v>1646</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B232" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="E232" t="s">
-        <v>1653</v>
+        <v>1647</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="B233" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="E233" t="s">
-        <v>1654</v>
+        <v>1648</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="B234" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="E234" t="s">
-        <v>1655</v>
+        <v>1649</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="B235" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="E235" t="s">
-        <v>1656</v>
+        <v>1650</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="B236" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="E236" t="s">
-        <v>1657</v>
+        <v>1651</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="B237" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="E237" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="B238" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="E238" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="B239" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="E239" t="s">
-        <v>1658</v>
+        <v>1652</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="B240" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>1659</v>
+        <v>1653</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B241" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="E241" t="s">
-        <v>1660</v>
+        <v>1654</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B242" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="E242" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B243" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="E243" t="s">
-        <v>1661</v>
+        <v>1655</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B244" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="E244" t="s">
-        <v>1662</v>
+        <v>1656</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B245" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="E245" t="s">
-        <v>1663</v>
+        <v>1657</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B246" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="E246" t="s">
-        <v>1664</v>
+        <v>1658</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B247" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="E247" t="s">
-        <v>1665</v>
+        <v>1659</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B248" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="E248" t="s">
-        <v>1666</v>
+        <v>1660</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B249" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="E249" t="s">
-        <v>1667</v>
+        <v>1661</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B250" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="E250" t="s">
-        <v>1668</v>
+        <v>1662</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B251" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="E251" t="s">
-        <v>1669</v>
+        <v>1663</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B252" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="E252" t="s">
-        <v>1670</v>
+        <v>1664</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="B253" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="E253" t="s">
-        <v>1671</v>
+        <v>1665</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="B254" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="E254" t="s">
-        <v>1672</v>
+        <v>1666</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="B255" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
       <c r="E255" t="s">
-        <v>1673</v>
+        <v>1667</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1445</v>
+        <v>1439</v>
       </c>
       <c r="B256" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E256" t="s">
-        <v>1674</v>
+        <v>1668</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="B257" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
       <c r="E257" t="s">
-        <v>1675</v>
+        <v>1669</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="B258" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="E258" t="s">
-        <v>1676</v>
+        <v>1670</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="B259" t="s">
-        <v>1268</v>
+        <v>1262</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="E259" t="s">
-        <v>1677</v>
+        <v>1671</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="B260" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1275</v>
+        <v>1269</v>
       </c>
       <c r="E260" t="s">
-        <v>1678</v>
+        <v>1672</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>1276</v>
+        <v>1270</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="B261" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="E261" t="s">
-        <v>1679</v>
+        <v>1673</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="B262" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>1285</v>
+        <v>1279</v>
       </c>
       <c r="E262" t="s">
-        <v>1680</v>
+        <v>1674</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>1287</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="B263" t="s">
-        <v>1288</v>
+        <v>1282</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="E263" t="s">
-        <v>1681</v>
+        <v>1675</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="B264" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>1294</v>
+        <v>1288</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="E264" t="s">
-        <v>1682</v>
+        <v>1676</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>1296</v>
+        <v>1290</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1297</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="B265" t="s">
-        <v>1299</v>
+        <v>1293</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1301</v>
+        <v>1295</v>
       </c>
       <c r="E265" t="s">
-        <v>1683</v>
+        <v>1677</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B266" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>1450</v>
+        <v>1444</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>1305</v>
+        <v>1299</v>
       </c>
       <c r="E266" t="s">
-        <v>1700</v>
+        <v>1694</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1451</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B267" t="s">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1309</v>
+        <v>1303</v>
       </c>
       <c r="E267" t="s">
-        <v>1701</v>
+        <v>1695</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1311</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B268" t="s">
-        <v>1312</v>
+        <v>1306</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1313</v>
+        <v>1307</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
       <c r="E268" t="s">
-        <v>1684</v>
+        <v>1678</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1314</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1447</v>
+        <v>1441</v>
       </c>
       <c r="B269" t="s">
-        <v>1315</v>
+        <v>1309</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1317</v>
+        <v>1311</v>
       </c>
       <c r="E269" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>1318</v>
+        <v>1312</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1319</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B270" t="s">
-        <v>1320</v>
+        <v>1314</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="E270" t="s">
-        <v>1685</v>
+        <v>1679</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="L270" t="s">
-        <v>1433</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="B271" t="s">
-        <v>1325</v>
+        <v>1319</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>1326</v>
+        <v>1320</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1327</v>
+        <v>1321</v>
       </c>
       <c r="E271" t="s">
-        <v>1686</v>
+        <v>1680</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>1328</v>
+        <v>1322</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1329</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="B272" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>1331</v>
+        <v>1325</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1332</v>
+        <v>1326</v>
       </c>
       <c r="E272" t="s">
-        <v>1687</v>
+        <v>1681</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B273" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
       <c r="E273" t="s">
-        <v>1688</v>
+        <v>1682</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B274" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="E274" t="s">
-        <v>1689</v>
+        <v>1683</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B275" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="E275" t="s">
-        <v>1536</v>
+        <v>1530</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="B276" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1351</v>
+        <v>1345</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1352</v>
+        <v>1346</v>
       </c>
       <c r="E276" t="s">
-        <v>1634</v>
+        <v>1628</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="E277" t="s">
-        <v>1690</v>
+        <v>1684</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B278" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>1361</v>
+        <v>1355</v>
       </c>
       <c r="E278" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>1362</v>
+        <v>1356</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1363</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B279" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E279" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1368</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B280" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>1370</v>
+        <v>1364</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
       <c r="E280" t="s">
-        <v>1691</v>
+        <v>1685</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>1372</v>
+        <v>1366</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B281" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>1375</v>
+        <v>1369</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>1376</v>
+        <v>1370</v>
       </c>
       <c r="E281" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>1377</v>
+        <v>1371</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B282" t="s">
-        <v>1379</v>
+        <v>1373</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="E282" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B283" t="s">
-        <v>1384</v>
+        <v>1378</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>1385</v>
+        <v>1379</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="E283" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1388</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="B284" t="s">
-        <v>1389</v>
+        <v>1383</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="E284" t="s">
-        <v>1692</v>
+        <v>1686</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1393</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="B285" t="s">
-        <v>1394</v>
+        <v>1388</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="E285" t="s">
-        <v>1693</v>
+        <v>1687</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1397</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B286" t="s">
-        <v>1398</v>
+        <v>1392</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>1399</v>
+        <v>1393</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>1400</v>
+        <v>1394</v>
       </c>
       <c r="E286" t="s">
-        <v>1694</v>
+        <v>1688</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>1401</v>
+        <v>1395</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1402</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1447</v>
+        <v>1441</v>
       </c>
       <c r="B287" t="s">
-        <v>1403</v>
+        <v>1397</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1404</v>
+        <v>1398</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1405</v>
+        <v>1399</v>
       </c>
       <c r="E287" t="s">
-        <v>1695</v>
+        <v>1689</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1407</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="B288" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>1408</v>
+        <v>1402</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="E288" t="s">
-        <v>1696</v>
+        <v>1690</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>1409</v>
+        <v>1403</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="B289" t="s">
-        <v>1411</v>
+        <v>1405</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>1412</v>
+        <v>1406</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
       <c r="E289" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="B290" t="s">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>1417</v>
+        <v>1411</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="E290" t="s">
-        <v>1697</v>
+        <v>1691</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>1419</v>
+        <v>1413</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1420</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="B291" t="s">
-        <v>1421</v>
+        <v>1415</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>1422</v>
+        <v>1416</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>1423</v>
+        <v>1417</v>
       </c>
       <c r="E291" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>1424</v>
+        <v>1418</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1425</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="B292" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>1426</v>
+        <v>1420</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="E292" t="s">
-        <v>1698</v>
+        <v>1692</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>1428</v>
+        <v>1422</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1429</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1447</v>
+        <v>1441</v>
       </c>
       <c r="B293" t="s">
-        <v>1430</v>
+        <v>1424</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>1431</v>
+        <v>1425</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="E293" t="s">
-        <v>1640</v>
+        <v>1634</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>1432</v>
+        <v>1426</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1449</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B294" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="E294" t="s">
-        <v>1660</v>
+        <v>1654</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B295" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="E295" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B296" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="E296" t="s">
-        <v>1684</v>
+        <v>1678</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="B297" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="E297" t="s">
-        <v>1699</v>
+        <v>1693</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Daily_Word.xlsx
+++ b/public/data/Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10CB8EF-9BFD-465B-8FEC-5382AD9296EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFEFC95-AE1A-412C-B4E5-4A5994DB7F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,9 +80,6 @@
     <t>פרי</t>
   </si>
   <si>
-    <t>וודקה</t>
-  </si>
-  <si>
     <t>וידאו</t>
   </si>
   <si>
@@ -140,12 +137,6 @@
     <t>בשר</t>
   </si>
   <si>
-    <t>מיסה (סעודה)</t>
-  </si>
-  <si>
-    <t>מיסה זו סעודה - מזכיר בשר.</t>
-  </si>
-  <si>
     <t>рыба</t>
   </si>
   <si>
@@ -215,9 +206,6 @@
     <t>מים</t>
   </si>
   <si>
-    <t>וָדָה זה משקה יומיומי כמו וודקה לרוסים.</t>
-  </si>
-  <si>
     <t>масло</t>
   </si>
   <si>
@@ -1124,9 +1112,6 @@
     <t>רקוב</t>
   </si>
   <si>
-    <t>אסור לשכוח לנקות את הרָקוֹבִינָה ממשחת שיניים. אחרת הכל נראה רקוב פה.</t>
-  </si>
-  <si>
     <t>душ</t>
   </si>
   <si>
@@ -1175,18 +1160,12 @@
     <t>одеяло</t>
   </si>
   <si>
-    <t>אָדִייָאלוֹ</t>
-  </si>
-  <si>
     <t>שמיכה</t>
   </si>
   <si>
     <t>אידיאלי</t>
   </si>
   <si>
-    <t>כשקר בחורף, המצב האידיאלי הוא להתעטף באָדִייָאלוֹ חמה וגדולה</t>
-  </si>
-  <si>
     <t>часы</t>
   </si>
   <si>
@@ -1214,9 +1193,6 @@
     <t>סתכלו</t>
   </si>
   <si>
-    <t>סתכלו איזה יפה אני במראת הסְטֶקְלוֹ!</t>
-  </si>
-  <si>
     <t>кухня</t>
   </si>
   <si>
@@ -1316,9 +1292,6 @@
     <t>נוצה</t>
   </si>
   <si>
-    <t>בנוֹצְ אני נרדם רק כרית רכה כמו נוצה!</t>
-  </si>
-  <si>
     <t>час</t>
   </si>
   <si>
@@ -1359,9 +1332,6 @@
   </si>
   <si>
     <t>Mess</t>
-  </si>
-  <si>
-    <t>הגיע החוחף הגדול! זה מֶסִיאַץ שאפשר לעשות בו מלא Mess</t>
   </si>
   <si>
     <t>год</t>
@@ -5450,6 +5420,36 @@
   </si>
   <si>
     <t>בכל סתיו אני יוצא אל החורשה לחפש חוּרְמַה, כאילו העצים שומרים עליה כסוד מתוק מהשמש</t>
+  </si>
+  <si>
+    <t>miss</t>
+  </si>
+  <si>
+    <t>מאז שהפכתי לצמחוני אני miss לטעם של מְיַסָה</t>
+  </si>
+  <si>
+    <t>וודאי שאני אשמח לשתות וָדָה</t>
+  </si>
+  <si>
+    <t>וודאי</t>
+  </si>
+  <si>
+    <t>אסור לשכוח לנקות את הרָקוֹבִינָה. אחרת הכל נראה רקוב.</t>
+  </si>
+  <si>
+    <t>אָדִייָאלָה</t>
+  </si>
+  <si>
+    <t>כשקר בחורף, המצב האידיאלי הוא להתעטף באָדִייָאלָה חמה וגדולה</t>
+  </si>
+  <si>
+    <t>סתכלו איזה יפה אני דרך הסְטֶקְלוֹ</t>
+  </si>
+  <si>
+    <t>בנוֹצְ אני נרדם עם כרית רכה כמו נוצה!</t>
+  </si>
+  <si>
+    <t>הגיע החורף הגדול! זה מֶסִיאַץ שעלול להתרחש בו הרבה Mess</t>
   </si>
 </sst>
 </file>
@@ -5848,6827 +5848,6827 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1694</v>
+        <v>1684</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1447</v>
+        <v>1437</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1446</v>
+        <v>1436</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1449</v>
+        <v>1439</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1445</v>
+        <v>1435</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1444</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>1450</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>1451</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1452</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>1448</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>1453</v>
+        <v>1443</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>1712</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>35</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1454</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>1712</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1717</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1456</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1713</v>
+        <v>1703</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1457</v>
+        <v>1447</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1714</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1458</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1459</v>
+        <v>1449</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>14</v>
+        <v>1715</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>59</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1718</v>
+        <v>1708</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1460</v>
+        <v>1450</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1719</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1461</v>
+        <v>1451</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1720</v>
+        <v>1710</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1721</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>1462</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>1463</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>1464</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>1465</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>1466</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>1467</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>1468</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1469</v>
+        <v>1459</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1707</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>1486</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1715</v>
+        <v>1705</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1470</v>
+        <v>1460</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1716</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>1471</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>1472</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>1473</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>1470</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B29" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>1475</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B30" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>1476</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>1477</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B32" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1478</v>
+        <v>1468</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1706</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B33" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B34" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B35" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1482</v>
+        <v>1472</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B37" t="s">
+        <v>172</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>1483</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B38" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1484</v>
+        <v>1474</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B39" t="s">
+        <v>181</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>1485</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B40" t="s">
+        <v>186</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B41" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>1488</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B42" t="s">
+        <v>196</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B43" t="s">
+        <v>201</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B44" t="s">
+        <v>206</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>1491</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B45" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E45" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>1695</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B46" t="s">
+        <v>215</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>1492</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B47" t="s">
+        <v>220</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>1696</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B48" t="s">
+        <v>225</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>1493</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B49" t="s">
+        <v>230</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B50" t="s">
+        <v>235</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B51" t="s">
+        <v>240</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>1496</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B52" t="s">
+        <v>245</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>1497</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B53" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1475</v>
+        <v>1465</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1709</v>
+        <v>1699</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1708</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B54" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1503</v>
+        <v>1493</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1710</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1426</v>
+        <v>1416</v>
       </c>
       <c r="B55" t="s">
+        <v>257</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B56" t="s">
+        <v>262</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>1498</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B57" t="s">
+        <v>267</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B58" t="s">
+        <v>272</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B59" t="s">
+        <v>277</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>1501</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B60" t="s">
+        <v>282</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>1502</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B61" t="s">
+        <v>287</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>1505</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B62" t="s">
+        <v>292</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>1506</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B63" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1526</v>
+        <v>1516</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1506</v>
+        <v>1496</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B64" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1507</v>
+        <v>1497</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B65" t="s">
+        <v>305</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>1508</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B66" t="s">
+        <v>310</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>1527</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B67" t="s">
+        <v>315</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B68" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1502</v>
+        <v>1492</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1711</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B69" t="s">
+        <v>324</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>1501</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B70" t="s">
+        <v>329</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B71" t="s">
+        <v>334</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>1697</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B72" t="s">
+        <v>339</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>1511</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B73" t="s">
+        <v>344</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>1512</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B74" t="s">
+        <v>349</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>1513</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B75" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1514</v>
+        <v>1504</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>362</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B76" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1515</v>
+        <v>1505</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B77" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1516</v>
+        <v>1506</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B78" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1500</v>
+        <v>1490</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B79" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>379</v>
+        <v>1717</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1517</v>
+        <v>1507</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>382</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B80" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1518</v>
+        <v>1508</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B81" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1519</v>
+        <v>1509</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>392</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B82" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B83" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1501</v>
+        <v>1491</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1427</v>
+        <v>1417</v>
       </c>
       <c r="B84" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1520</v>
+        <v>1510</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B85" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1521</v>
+        <v>1511</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B86" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1522</v>
+        <v>1512</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B87" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1523</v>
+        <v>1513</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B88" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1698</v>
+        <v>1688</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>426</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B89" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1699</v>
+        <v>1689</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B90" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1525</v>
+        <v>1515</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B91" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1525</v>
+        <v>1515</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>441</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B92" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1525</v>
+        <v>1515</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B93" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="E93" t="s">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B94" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E94" t="s">
-        <v>1524</v>
+        <v>1514</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B95" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="E95" t="s">
-        <v>1530</v>
+        <v>1520</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B96" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="E96" t="s">
-        <v>1531</v>
+        <v>1521</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B97" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="E97" t="s">
-        <v>1532</v>
+        <v>1522</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B98" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="E98" t="s">
-        <v>1533</v>
+        <v>1523</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B99" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="E99" t="s">
-        <v>1534</v>
+        <v>1524</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B100" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="E100" t="s">
-        <v>1535</v>
+        <v>1525</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B101" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="E101" t="s">
-        <v>1536</v>
+        <v>1526</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B102" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="E102" t="s">
-        <v>1537</v>
+        <v>1527</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B103" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="E103" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B104" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="E104" t="s">
-        <v>1539</v>
+        <v>1529</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B105" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="E105" t="s">
-        <v>1540</v>
+        <v>1530</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B106" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="E106" t="s">
-        <v>1541</v>
+        <v>1531</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B107" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="E107" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B108" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="E108" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B109" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="E109" t="s">
-        <v>1544</v>
+        <v>1534</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B110" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="E110" t="s">
-        <v>1545</v>
+        <v>1535</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B111" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="E111" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B112" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="E112" t="s">
-        <v>1547</v>
+        <v>1537</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B113" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="E113" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B114" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="E114" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B115" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="E115" t="s">
-        <v>1550</v>
+        <v>1540</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B116" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="E116" t="s">
-        <v>1551</v>
+        <v>1541</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B117" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="E117" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B118" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="E118" t="s">
-        <v>1552</v>
+        <v>1542</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B119" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="E119" t="s">
-        <v>1553</v>
+        <v>1543</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B120" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="E120" t="s">
-        <v>1554</v>
+        <v>1544</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B121" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="E121" t="s">
-        <v>1555</v>
+        <v>1545</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B122" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="E122" t="s">
-        <v>1556</v>
+        <v>1546</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B123" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="E123" t="s">
-        <v>1557</v>
+        <v>1547</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B124" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="E124" t="s">
-        <v>1558</v>
+        <v>1548</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B125" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="E125" t="s">
-        <v>1559</v>
+        <v>1549</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B126" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="E126" t="s">
-        <v>1500</v>
+        <v>1490</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B127" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="E127" t="s">
-        <v>1560</v>
+        <v>1550</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B128" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="E128" t="s">
-        <v>1561</v>
+        <v>1551</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B129" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="E129" t="s">
-        <v>1536</v>
+        <v>1526</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B130" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="E130" t="s">
-        <v>1703</v>
+        <v>1693</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B131" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="E131" t="s">
-        <v>1704</v>
+        <v>1694</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B132" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="E132" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B133" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="E133" t="s">
-        <v>1563</v>
+        <v>1553</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B134" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="E134" t="s">
-        <v>1561</v>
+        <v>1551</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B135" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E135" t="s">
-        <v>1564</v>
+        <v>1554</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B136" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="E136" t="s">
-        <v>1519</v>
+        <v>1509</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B137" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="E137" t="s">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B138" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="E138" t="s">
-        <v>1541</v>
+        <v>1531</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B139" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="E139" t="s">
-        <v>1566</v>
+        <v>1556</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B140" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="E140" t="s">
-        <v>1567</v>
+        <v>1557</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B141" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="E141" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B142" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="E142" t="s">
-        <v>1530</v>
+        <v>1520</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B143" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="E143" t="s">
-        <v>1569</v>
+        <v>1559</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B144" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="E144" t="s">
-        <v>1570</v>
+        <v>1560</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B145" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="E145" t="s">
-        <v>1571</v>
+        <v>1561</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B146" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="E146" t="s">
-        <v>1572</v>
+        <v>1562</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B147" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="E147" t="s">
-        <v>1573</v>
+        <v>1563</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B148" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="E148" t="s">
-        <v>1574</v>
+        <v>1564</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B149" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E149" t="s">
-        <v>1574</v>
+        <v>1564</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B150" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="E150" t="s">
-        <v>1574</v>
+        <v>1564</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B151" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="E151" t="s">
-        <v>1574</v>
+        <v>1564</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B152" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="E152" t="s">
-        <v>1700</v>
+        <v>1690</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B153" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="E153" t="s">
-        <v>1701</v>
+        <v>1691</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B154" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="E154" t="s">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B155" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="E155" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B156" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="E156" t="s">
-        <v>1577</v>
+        <v>1567</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B157" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="E157" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B158" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="E158" t="s">
-        <v>1551</v>
+        <v>1541</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B159" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="E159" t="s">
-        <v>1579</v>
+        <v>1569</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B160" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="E160" t="s">
-        <v>1702</v>
+        <v>1692</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B161" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="E161" t="s">
-        <v>1579</v>
+        <v>1569</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B162" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="E162" t="s">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B163" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="E163" t="s">
-        <v>1581</v>
+        <v>1571</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B164" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="E164" t="s">
-        <v>1582</v>
+        <v>1572</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B165" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="E165" t="s">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B166" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="E166" t="s">
-        <v>1584</v>
+        <v>1574</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B167" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="E167" t="s">
-        <v>1585</v>
+        <v>1575</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B168" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="E168" t="s">
-        <v>1586</v>
+        <v>1576</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B169" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="E169" t="s">
-        <v>1587</v>
+        <v>1577</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B170" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="E170" t="s">
-        <v>1588</v>
+        <v>1578</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B171" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="E171" t="s">
-        <v>1589</v>
+        <v>1579</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B172" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="E172" t="s">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B173" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="E173" t="s">
-        <v>1591</v>
+        <v>1581</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B174" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="E174" t="s">
-        <v>1592</v>
+        <v>1582</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B175" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="E175" t="s">
-        <v>1593</v>
+        <v>1583</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B176" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>855</v>
+        <v>845</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
       <c r="E176" t="s">
-        <v>1594</v>
+        <v>1584</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B177" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>860</v>
+        <v>850</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
       <c r="E177" t="s">
-        <v>1595</v>
+        <v>1585</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B178" t="s">
-        <v>864</v>
+        <v>854</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>866</v>
+        <v>856</v>
       </c>
       <c r="E178" t="s">
-        <v>1596</v>
+        <v>1586</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B179" t="s">
-        <v>869</v>
+        <v>859</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>871</v>
+        <v>861</v>
       </c>
       <c r="E179" t="s">
-        <v>1597</v>
+        <v>1587</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>872</v>
+        <v>862</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B180" t="s">
-        <v>874</v>
+        <v>864</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>875</v>
+        <v>865</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
       <c r="E180" t="s">
-        <v>1598</v>
+        <v>1588</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>877</v>
+        <v>867</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>878</v>
+        <v>868</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B181" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="E181" t="s">
-        <v>1599</v>
+        <v>1589</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>882</v>
+        <v>872</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>883</v>
+        <v>873</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B182" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
       <c r="E182" t="s">
-        <v>1600</v>
+        <v>1590</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>887</v>
+        <v>877</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B183" t="s">
-        <v>889</v>
+        <v>879</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>890</v>
+        <v>880</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>891</v>
+        <v>881</v>
       </c>
       <c r="E183" t="s">
-        <v>1601</v>
+        <v>1591</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>892</v>
+        <v>882</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>893</v>
+        <v>883</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B184" t="s">
-        <v>894</v>
+        <v>884</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>895</v>
+        <v>885</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>896</v>
+        <v>886</v>
       </c>
       <c r="E184" t="s">
-        <v>1602</v>
+        <v>1592</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>897</v>
+        <v>887</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>898</v>
+        <v>888</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B185" t="s">
-        <v>899</v>
+        <v>889</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>901</v>
+        <v>891</v>
       </c>
       <c r="E185" t="s">
-        <v>1603</v>
+        <v>1593</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>903</v>
+        <v>893</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B186" t="s">
-        <v>904</v>
+        <v>894</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="E186" t="s">
-        <v>1604</v>
+        <v>1594</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B187" t="s">
-        <v>909</v>
+        <v>899</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>911</v>
+        <v>901</v>
       </c>
       <c r="E187" t="s">
-        <v>1605</v>
+        <v>1595</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>913</v>
+        <v>903</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B188" t="s">
-        <v>914</v>
+        <v>904</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>915</v>
+        <v>905</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>916</v>
+        <v>906</v>
       </c>
       <c r="E188" t="s">
-        <v>1606</v>
+        <v>1596</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>917</v>
+        <v>907</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>918</v>
+        <v>908</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B189" t="s">
-        <v>919</v>
+        <v>909</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>921</v>
+        <v>911</v>
       </c>
       <c r="E189" t="s">
-        <v>1607</v>
+        <v>1597</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>922</v>
+        <v>912</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>923</v>
+        <v>913</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B190" t="s">
-        <v>924</v>
+        <v>914</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>925</v>
+        <v>915</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>926</v>
+        <v>916</v>
       </c>
       <c r="E190" t="s">
-        <v>1608</v>
+        <v>1598</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>927</v>
+        <v>917</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>928</v>
+        <v>918</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B191" t="s">
-        <v>929</v>
+        <v>919</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>930</v>
+        <v>920</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>931</v>
+        <v>921</v>
       </c>
       <c r="E191" t="s">
-        <v>1609</v>
+        <v>1599</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>932</v>
+        <v>922</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B192" t="s">
-        <v>933</v>
+        <v>923</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>934</v>
+        <v>924</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>935</v>
+        <v>925</v>
       </c>
       <c r="E192" t="s">
-        <v>1610</v>
+        <v>1600</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>936</v>
+        <v>926</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>937</v>
+        <v>927</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B193" t="s">
-        <v>938</v>
+        <v>928</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>939</v>
+        <v>929</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>940</v>
+        <v>930</v>
       </c>
       <c r="E193" t="s">
-        <v>1611</v>
+        <v>1601</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>941</v>
+        <v>931</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>942</v>
+        <v>932</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B194" t="s">
-        <v>943</v>
+        <v>933</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>944</v>
+        <v>934</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>945</v>
+        <v>935</v>
       </c>
       <c r="E194" t="s">
-        <v>1612</v>
+        <v>1602</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>946</v>
+        <v>936</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>947</v>
+        <v>937</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B195" t="s">
-        <v>948</v>
+        <v>938</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>949</v>
+        <v>939</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>950</v>
+        <v>940</v>
       </c>
       <c r="E195" t="s">
-        <v>1613</v>
+        <v>1603</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>951</v>
+        <v>941</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>952</v>
+        <v>942</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B196" t="s">
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>954</v>
+        <v>944</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>955</v>
+        <v>945</v>
       </c>
       <c r="E196" t="s">
-        <v>1614</v>
+        <v>1604</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>956</v>
+        <v>946</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B197" t="s">
-        <v>958</v>
+        <v>948</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>959</v>
+        <v>949</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="E197" t="s">
-        <v>1584</v>
+        <v>1574</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>961</v>
+        <v>951</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>962</v>
+        <v>952</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B198" t="s">
-        <v>963</v>
+        <v>953</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>964</v>
+        <v>954</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>965</v>
+        <v>955</v>
       </c>
       <c r="E198" t="s">
-        <v>1615</v>
+        <v>1605</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>966</v>
+        <v>956</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B199" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>969</v>
+        <v>959</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>970</v>
+        <v>960</v>
       </c>
       <c r="E199" t="s">
-        <v>1616</v>
+        <v>1606</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>971</v>
+        <v>961</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>972</v>
+        <v>962</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B200" t="s">
-        <v>973</v>
+        <v>963</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>974</v>
+        <v>964</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>975</v>
+        <v>965</v>
       </c>
       <c r="E200" t="s">
-        <v>1617</v>
+        <v>1607</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B201" t="s">
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="E201" t="s">
-        <v>1592</v>
+        <v>1582</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>981</v>
+        <v>971</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>982</v>
+        <v>972</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B202" t="s">
-        <v>983</v>
+        <v>973</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>984</v>
+        <v>974</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>985</v>
+        <v>975</v>
       </c>
       <c r="E202" t="s">
-        <v>1618</v>
+        <v>1608</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>986</v>
+        <v>976</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>987</v>
+        <v>977</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B203" t="s">
-        <v>988</v>
+        <v>978</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>989</v>
+        <v>979</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="E203" t="s">
-        <v>1619</v>
+        <v>1609</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B204" t="s">
-        <v>993</v>
+        <v>983</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>994</v>
+        <v>984</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>995</v>
+        <v>985</v>
       </c>
       <c r="E204" t="s">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>996</v>
+        <v>986</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>997</v>
+        <v>987</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B205" t="s">
-        <v>998</v>
+        <v>988</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>999</v>
+        <v>989</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="E205" t="s">
-        <v>1621</v>
+        <v>1611</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>1001</v>
+        <v>991</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>1002</v>
+        <v>992</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B206" t="s">
-        <v>1003</v>
+        <v>993</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>1004</v>
+        <v>994</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>1005</v>
+        <v>995</v>
       </c>
       <c r="E206" t="s">
-        <v>1622</v>
+        <v>1612</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>1006</v>
+        <v>996</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>1007</v>
+        <v>997</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B207" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>1009</v>
+        <v>999</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="E207" t="s">
-        <v>1506</v>
+        <v>1496</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>1011</v>
+        <v>1001</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>1012</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B208" t="s">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>1014</v>
+        <v>1004</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1015</v>
+        <v>1005</v>
       </c>
       <c r="E208" t="s">
-        <v>1623</v>
+        <v>1613</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>1016</v>
+        <v>1006</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>1017</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B209" t="s">
-        <v>1018</v>
+        <v>1008</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>1019</v>
+        <v>1009</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="E209" t="s">
-        <v>1624</v>
+        <v>1614</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>1022</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B210" t="s">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1025</v>
+        <v>1015</v>
       </c>
       <c r="E210" t="s">
-        <v>1625</v>
+        <v>1615</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>1026</v>
+        <v>1016</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>1027</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B211" t="s">
-        <v>1028</v>
+        <v>1018</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1029</v>
+        <v>1019</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="E211" t="s">
-        <v>1626</v>
+        <v>1616</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1032</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B212" t="s">
-        <v>1033</v>
+        <v>1023</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>1034</v>
+        <v>1024</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1035</v>
+        <v>1025</v>
       </c>
       <c r="E212" t="s">
-        <v>1622</v>
+        <v>1612</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>1036</v>
+        <v>1026</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1037</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B213" t="s">
-        <v>1038</v>
+        <v>1028</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>1039</v>
+        <v>1029</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="E213" t="s">
-        <v>1627</v>
+        <v>1617</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>1041</v>
+        <v>1031</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1042</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B214" t="s">
-        <v>1043</v>
+        <v>1033</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1045</v>
+        <v>1035</v>
       </c>
       <c r="E214" t="s">
-        <v>1628</v>
+        <v>1618</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1047</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B215" t="s">
-        <v>1048</v>
+        <v>1038</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>1049</v>
+        <v>1039</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="E215" t="s">
-        <v>1554</v>
+        <v>1544</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>1051</v>
+        <v>1041</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1052</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B216" t="s">
-        <v>1053</v>
+        <v>1043</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>1054</v>
+        <v>1044</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="E216" t="s">
-        <v>1629</v>
+        <v>1619</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1056</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B217" t="s">
-        <v>1057</v>
+        <v>1047</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>1058</v>
+        <v>1048</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="E217" t="s">
-        <v>1630</v>
+        <v>1620</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>1061</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B218" t="s">
-        <v>1062</v>
+        <v>1052</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>1063</v>
+        <v>1053</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>1064</v>
+        <v>1054</v>
       </c>
       <c r="E218" t="s">
-        <v>1631</v>
+        <v>1621</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>1065</v>
+        <v>1055</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>1066</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B219" t="s">
-        <v>1067</v>
+        <v>1057</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>1068</v>
+        <v>1058</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>1069</v>
+        <v>1059</v>
       </c>
       <c r="E219" t="s">
-        <v>1632</v>
+        <v>1622</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>1071</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B220" t="s">
-        <v>1072</v>
+        <v>1062</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>1073</v>
+        <v>1063</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1074</v>
+        <v>1064</v>
       </c>
       <c r="E220" t="s">
-        <v>1633</v>
+        <v>1623</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>1075</v>
+        <v>1065</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>1076</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B221" t="s">
-        <v>1077</v>
+        <v>1067</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>1078</v>
+        <v>1068</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>1079</v>
+        <v>1069</v>
       </c>
       <c r="E221" t="s">
-        <v>1634</v>
+        <v>1624</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>1081</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B222" t="s">
-        <v>1082</v>
+        <v>1072</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>1083</v>
+        <v>1073</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>1084</v>
+        <v>1074</v>
       </c>
       <c r="E222" t="s">
-        <v>1635</v>
+        <v>1625</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>1085</v>
+        <v>1075</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B223" t="s">
-        <v>1087</v>
+        <v>1077</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>1088</v>
+        <v>1078</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>1089</v>
+        <v>1079</v>
       </c>
       <c r="E223" t="s">
-        <v>1636</v>
+        <v>1626</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1090</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B224" t="s">
-        <v>1091</v>
+        <v>1081</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>1092</v>
+        <v>1082</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>1093</v>
+        <v>1083</v>
       </c>
       <c r="E224" t="s">
-        <v>1637</v>
+        <v>1627</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>1094</v>
+        <v>1084</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>1095</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B225" t="s">
-        <v>1096</v>
+        <v>1086</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>1097</v>
+        <v>1087</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>1098</v>
+        <v>1088</v>
       </c>
       <c r="E225" t="s">
-        <v>1638</v>
+        <v>1628</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>1099</v>
+        <v>1089</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>1100</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B226" t="s">
-        <v>1101</v>
+        <v>1091</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>1102</v>
+        <v>1092</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E226" t="s">
-        <v>1639</v>
+        <v>1629</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>1103</v>
+        <v>1093</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>1104</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B227" t="s">
-        <v>1105</v>
+        <v>1095</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>1106</v>
+        <v>1096</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>1107</v>
+        <v>1097</v>
       </c>
       <c r="E227" t="s">
-        <v>1640</v>
+        <v>1630</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>1108</v>
+        <v>1098</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>1109</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B228" t="s">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>1111</v>
+        <v>1101</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>1112</v>
+        <v>1102</v>
       </c>
       <c r="E228" t="s">
-        <v>1641</v>
+        <v>1631</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>1113</v>
+        <v>1103</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>1114</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B229" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1116</v>
+        <v>1106</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>1117</v>
+        <v>1107</v>
       </c>
       <c r="E229" t="s">
-        <v>1642</v>
+        <v>1632</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1118</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B230" t="s">
-        <v>1119</v>
+        <v>1109</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
       <c r="E230" t="s">
-        <v>1643</v>
+        <v>1633</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>1122</v>
+        <v>1112</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>1123</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1429</v>
+        <v>1419</v>
       </c>
       <c r="B231" t="s">
-        <v>1124</v>
+        <v>1114</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>1125</v>
+        <v>1115</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>1126</v>
+        <v>1116</v>
       </c>
       <c r="E231" t="s">
-        <v>1644</v>
+        <v>1634</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>1127</v>
+        <v>1117</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>1128</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B232" t="s">
-        <v>1129</v>
+        <v>1119</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>1131</v>
+        <v>1121</v>
       </c>
       <c r="E232" t="s">
-        <v>1645</v>
+        <v>1635</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>1132</v>
+        <v>1122</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>1133</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1433</v>
+        <v>1423</v>
       </c>
       <c r="B233" t="s">
-        <v>1134</v>
+        <v>1124</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>1135</v>
+        <v>1125</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>1136</v>
+        <v>1126</v>
       </c>
       <c r="E233" t="s">
-        <v>1646</v>
+        <v>1636</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1138</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1433</v>
+        <v>1423</v>
       </c>
       <c r="B234" t="s">
-        <v>1139</v>
+        <v>1129</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
       <c r="E234" t="s">
-        <v>1647</v>
+        <v>1637</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>1142</v>
+        <v>1132</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>1143</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1433</v>
+        <v>1423</v>
       </c>
       <c r="B235" t="s">
-        <v>1146</v>
+        <v>1136</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>1147</v>
+        <v>1137</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>1148</v>
+        <v>1138</v>
       </c>
       <c r="E235" t="s">
-        <v>1648</v>
+        <v>1638</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>1149</v>
+        <v>1139</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1150</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="B236" t="s">
-        <v>1151</v>
+        <v>1141</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>1152</v>
+        <v>1142</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>1153</v>
+        <v>1143</v>
       </c>
       <c r="E236" t="s">
-        <v>1649</v>
+        <v>1639</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>1154</v>
+        <v>1144</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>1155</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="B237" t="s">
-        <v>1156</v>
+        <v>1146</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1157</v>
+        <v>1147</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>1158</v>
+        <v>1148</v>
       </c>
       <c r="E237" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>1159</v>
+        <v>1149</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1160</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="B238" t="s">
-        <v>1161</v>
+        <v>1151</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>1162</v>
+        <v>1152</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>1163</v>
+        <v>1153</v>
       </c>
       <c r="E238" t="s">
-        <v>1554</v>
+        <v>1544</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>1164</v>
+        <v>1154</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>1165</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="B239" t="s">
-        <v>1166</v>
+        <v>1156</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1167</v>
+        <v>1157</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>1168</v>
+        <v>1158</v>
       </c>
       <c r="E239" t="s">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>1169</v>
+        <v>1159</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1170</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="B240" t="s">
-        <v>1171</v>
+        <v>1161</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>1172</v>
+        <v>1162</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>1651</v>
+        <v>1641</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>1173</v>
+        <v>1163</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>1174</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B241" t="s">
-        <v>1175</v>
+        <v>1165</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1176</v>
+        <v>1166</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>1177</v>
+        <v>1167</v>
       </c>
       <c r="E241" t="s">
-        <v>1652</v>
+        <v>1642</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>1178</v>
+        <v>1168</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1179</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B242" t="s">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>1181</v>
+        <v>1171</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>1182</v>
+        <v>1172</v>
       </c>
       <c r="E242" t="s">
-        <v>1522</v>
+        <v>1512</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>1184</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B243" t="s">
-        <v>1185</v>
+        <v>1175</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>1186</v>
+        <v>1176</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>1187</v>
+        <v>1177</v>
       </c>
       <c r="E243" t="s">
-        <v>1653</v>
+        <v>1643</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>1188</v>
+        <v>1178</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>1189</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B244" t="s">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="E244" t="s">
-        <v>1654</v>
+        <v>1644</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>1193</v>
+        <v>1183</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1194</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B245" t="s">
-        <v>1195</v>
+        <v>1185</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>1196</v>
+        <v>1186</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>1197</v>
+        <v>1187</v>
       </c>
       <c r="E245" t="s">
-        <v>1655</v>
+        <v>1645</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1198</v>
+        <v>1188</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1199</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B246" t="s">
-        <v>1200</v>
+        <v>1190</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1201</v>
+        <v>1191</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>1202</v>
+        <v>1192</v>
       </c>
       <c r="E246" t="s">
-        <v>1656</v>
+        <v>1646</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>1203</v>
+        <v>1193</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1204</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B247" t="s">
-        <v>1205</v>
+        <v>1195</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1206</v>
+        <v>1196</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1207</v>
+        <v>1197</v>
       </c>
       <c r="E247" t="s">
-        <v>1657</v>
+        <v>1647</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1208</v>
+        <v>1198</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1209</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B248" t="s">
-        <v>1210</v>
+        <v>1200</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>1211</v>
+        <v>1201</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="E248" t="s">
-        <v>1658</v>
+        <v>1648</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>1212</v>
+        <v>1202</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1213</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B249" t="s">
-        <v>1214</v>
+        <v>1204</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1215</v>
+        <v>1205</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1216</v>
+        <v>1206</v>
       </c>
       <c r="E249" t="s">
-        <v>1659</v>
+        <v>1649</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1217</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B250" t="s">
-        <v>1218</v>
+        <v>1208</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1219</v>
+        <v>1209</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="E250" t="s">
-        <v>1660</v>
+        <v>1650</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1221</v>
+        <v>1211</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1222</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B251" t="s">
-        <v>1223</v>
+        <v>1213</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1224</v>
+        <v>1214</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>1225</v>
+        <v>1215</v>
       </c>
       <c r="E251" t="s">
-        <v>1661</v>
+        <v>1651</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>1226</v>
+        <v>1216</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1227</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B252" t="s">
-        <v>1228</v>
+        <v>1218</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>1229</v>
+        <v>1219</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>1230</v>
+        <v>1220</v>
       </c>
       <c r="E252" t="s">
-        <v>1662</v>
+        <v>1652</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1436</v>
+        <v>1426</v>
       </c>
       <c r="B253" t="s">
-        <v>1233</v>
+        <v>1223</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>1234</v>
+        <v>1224</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1235</v>
+        <v>1225</v>
       </c>
       <c r="E253" t="s">
-        <v>1663</v>
+        <v>1653</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>1236</v>
+        <v>1226</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1237</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1436</v>
+        <v>1426</v>
       </c>
       <c r="B254" t="s">
-        <v>1238</v>
+        <v>1228</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>1239</v>
+        <v>1229</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1240</v>
+        <v>1230</v>
       </c>
       <c r="E254" t="s">
-        <v>1664</v>
+        <v>1654</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>1241</v>
+        <v>1231</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1242</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1436</v>
+        <v>1426</v>
       </c>
       <c r="B255" t="s">
-        <v>1243</v>
+        <v>1233</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>1244</v>
+        <v>1234</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>1245</v>
+        <v>1235</v>
       </c>
       <c r="E255" t="s">
-        <v>1665</v>
+        <v>1655</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1246</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1437</v>
+        <v>1427</v>
       </c>
       <c r="B256" t="s">
-        <v>1247</v>
+        <v>1237</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1248</v>
+        <v>1238</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E256" t="s">
-        <v>1666</v>
+        <v>1656</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>1249</v>
+        <v>1239</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>1250</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="B257" t="s">
-        <v>1251</v>
+        <v>1241</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1252</v>
+        <v>1242</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1253</v>
+        <v>1243</v>
       </c>
       <c r="E257" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>1131</v>
+        <v>1121</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1254</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="B258" t="s">
-        <v>1255</v>
+        <v>1245</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>1256</v>
+        <v>1246</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>1257</v>
+        <v>1247</v>
       </c>
       <c r="E258" t="s">
-        <v>1668</v>
+        <v>1658</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>1258</v>
+        <v>1248</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>1259</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="B259" t="s">
-        <v>1260</v>
+        <v>1250</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>1262</v>
+        <v>1252</v>
       </c>
       <c r="E259" t="s">
-        <v>1669</v>
+        <v>1659</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>1263</v>
+        <v>1253</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>1264</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="B260" t="s">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1266</v>
+        <v>1256</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1267</v>
+        <v>1257</v>
       </c>
       <c r="E260" t="s">
-        <v>1670</v>
+        <v>1660</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>1268</v>
+        <v>1258</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1269</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="B261" t="s">
-        <v>1270</v>
+        <v>1260</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>1271</v>
+        <v>1261</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1272</v>
+        <v>1262</v>
       </c>
       <c r="E261" t="s">
-        <v>1671</v>
+        <v>1661</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>1273</v>
+        <v>1263</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1274</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="B262" t="s">
-        <v>1275</v>
+        <v>1265</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>1276</v>
+        <v>1266</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>1277</v>
+        <v>1267</v>
       </c>
       <c r="E262" t="s">
-        <v>1672</v>
+        <v>1662</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>1278</v>
+        <v>1268</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>1279</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="B263" t="s">
-        <v>1280</v>
+        <v>1270</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>1281</v>
+        <v>1271</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1282</v>
+        <v>1272</v>
       </c>
       <c r="E263" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>1283</v>
+        <v>1273</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>1284</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="B264" t="s">
-        <v>1285</v>
+        <v>1275</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>1286</v>
+        <v>1276</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1287</v>
+        <v>1277</v>
       </c>
       <c r="E264" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>1288</v>
+        <v>1278</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1289</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="B265" t="s">
-        <v>1291</v>
+        <v>1281</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1292</v>
+        <v>1282</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1293</v>
+        <v>1283</v>
       </c>
       <c r="E265" t="s">
-        <v>1675</v>
+        <v>1665</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>1294</v>
+        <v>1284</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1295</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B266" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C266" s="1" t="s">
         <v>1432</v>
       </c>
-      <c r="B266" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C266" s="1" t="s">
-        <v>1442</v>
-      </c>
       <c r="D266" s="1" t="s">
-        <v>1297</v>
+        <v>1287</v>
       </c>
       <c r="E266" t="s">
-        <v>1692</v>
+        <v>1682</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>1298</v>
+        <v>1288</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1443</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B267" t="s">
-        <v>1299</v>
+        <v>1289</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>1300</v>
+        <v>1290</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1301</v>
+        <v>1291</v>
       </c>
       <c r="E267" t="s">
-        <v>1693</v>
+        <v>1683</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1302</v>
+        <v>1292</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1303</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B268" t="s">
-        <v>1304</v>
+        <v>1294</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1305</v>
+        <v>1295</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1273</v>
+        <v>1263</v>
       </c>
       <c r="E268" t="s">
-        <v>1676</v>
+        <v>1666</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1306</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1439</v>
+        <v>1429</v>
       </c>
       <c r="B269" t="s">
-        <v>1307</v>
+        <v>1297</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>1308</v>
+        <v>1298</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1309</v>
+        <v>1299</v>
       </c>
       <c r="E269" t="s">
-        <v>1561</v>
+        <v>1551</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>1310</v>
+        <v>1300</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1311</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B270" t="s">
-        <v>1312</v>
+        <v>1302</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>1313</v>
+        <v>1303</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1314</v>
+        <v>1304</v>
       </c>
       <c r="E270" t="s">
-        <v>1677</v>
+        <v>1667</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>1315</v>
+        <v>1305</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1316</v>
+        <v>1306</v>
       </c>
       <c r="L270" t="s">
-        <v>1425</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="B271" t="s">
-        <v>1317</v>
+        <v>1307</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>1318</v>
+        <v>1308</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1319</v>
+        <v>1309</v>
       </c>
       <c r="E271" t="s">
-        <v>1678</v>
+        <v>1668</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>1320</v>
+        <v>1310</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1321</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="B272" t="s">
-        <v>1322</v>
+        <v>1312</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>1323</v>
+        <v>1313</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1324</v>
+        <v>1314</v>
       </c>
       <c r="E272" t="s">
-        <v>1679</v>
+        <v>1669</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>1325</v>
+        <v>1315</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1326</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B273" t="s">
-        <v>1327</v>
+        <v>1317</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>1328</v>
+        <v>1318</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>1329</v>
+        <v>1319</v>
       </c>
       <c r="E273" t="s">
-        <v>1680</v>
+        <v>1670</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1330</v>
+        <v>1320</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1331</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B274" t="s">
-        <v>1332</v>
+        <v>1322</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>1333</v>
+        <v>1323</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1334</v>
+        <v>1324</v>
       </c>
       <c r="E274" t="s">
-        <v>1681</v>
+        <v>1671</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>1335</v>
+        <v>1325</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1336</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B275" t="s">
-        <v>1337</v>
+        <v>1327</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>1338</v>
+        <v>1328</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>1339</v>
+        <v>1329</v>
       </c>
       <c r="E275" t="s">
-        <v>1528</v>
+        <v>1518</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>1340</v>
+        <v>1330</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1341</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>1431</v>
+        <v>1421</v>
       </c>
       <c r="B276" t="s">
-        <v>1342</v>
+        <v>1332</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1343</v>
+        <v>1333</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1344</v>
+        <v>1334</v>
       </c>
       <c r="E276" t="s">
-        <v>1626</v>
+        <v>1616</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>1345</v>
+        <v>1335</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1346</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
-        <v>1347</v>
+        <v>1337</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>1348</v>
+        <v>1338</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>1349</v>
+        <v>1339</v>
       </c>
       <c r="E277" t="s">
-        <v>1682</v>
+        <v>1672</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>1290</v>
+        <v>1280</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1350</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B278" t="s">
-        <v>1351</v>
+        <v>1341</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>1352</v>
+        <v>1342</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>1353</v>
+        <v>1343</v>
       </c>
       <c r="E278" t="s">
-        <v>1520</v>
+        <v>1510</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>1354</v>
+        <v>1344</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1355</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B279" t="s">
-        <v>1356</v>
+        <v>1346</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1357</v>
+        <v>1347</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1358</v>
+        <v>1348</v>
       </c>
       <c r="E279" t="s">
-        <v>1520</v>
+        <v>1510</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>1359</v>
+        <v>1349</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1360</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B280" t="s">
-        <v>1361</v>
+        <v>1351</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>1362</v>
+        <v>1352</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>1363</v>
+        <v>1353</v>
       </c>
       <c r="E280" t="s">
-        <v>1683</v>
+        <v>1673</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>1364</v>
+        <v>1354</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>1365</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B281" t="s">
-        <v>1366</v>
+        <v>1356</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>1367</v>
+        <v>1357</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>1368</v>
+        <v>1358</v>
       </c>
       <c r="E281" t="s">
-        <v>1533</v>
+        <v>1523</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>1369</v>
+        <v>1359</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1370</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B282" t="s">
-        <v>1371</v>
+        <v>1361</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>1372</v>
+        <v>1362</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>1373</v>
+        <v>1363</v>
       </c>
       <c r="E282" t="s">
-        <v>1518</v>
+        <v>1508</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>1374</v>
+        <v>1364</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1375</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="B283" t="s">
-        <v>1376</v>
+        <v>1366</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>1377</v>
+        <v>1367</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>1378</v>
+        <v>1368</v>
       </c>
       <c r="E283" t="s">
-        <v>1556</v>
+        <v>1546</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>1379</v>
+        <v>1369</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1380</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1438</v>
+        <v>1428</v>
       </c>
       <c r="B284" t="s">
-        <v>1381</v>
+        <v>1371</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>1382</v>
+        <v>1372</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>1383</v>
+        <v>1373</v>
       </c>
       <c r="E284" t="s">
-        <v>1684</v>
+        <v>1674</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>1384</v>
+        <v>1374</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1385</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="B285" t="s">
-        <v>1386</v>
+        <v>1376</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>1387</v>
+        <v>1377</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>1388</v>
+        <v>1378</v>
       </c>
       <c r="E285" t="s">
-        <v>1685</v>
+        <v>1675</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1389</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B286" t="s">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>1391</v>
+        <v>1381</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>1392</v>
+        <v>1382</v>
       </c>
       <c r="E286" t="s">
-        <v>1686</v>
+        <v>1676</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>1393</v>
+        <v>1383</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1394</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1439</v>
+        <v>1429</v>
       </c>
       <c r="B287" t="s">
-        <v>1395</v>
+        <v>1385</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1396</v>
+        <v>1386</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1397</v>
+        <v>1387</v>
       </c>
       <c r="E287" t="s">
-        <v>1687</v>
+        <v>1677</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>1398</v>
+        <v>1388</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1399</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1433</v>
+        <v>1423</v>
       </c>
       <c r="B288" t="s">
-        <v>1144</v>
+        <v>1134</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>1400</v>
+        <v>1390</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1145</v>
+        <v>1135</v>
       </c>
       <c r="E288" t="s">
-        <v>1688</v>
+        <v>1678</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>1401</v>
+        <v>1391</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1402</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="B289" t="s">
-        <v>1403</v>
+        <v>1393</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>1404</v>
+        <v>1394</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1405</v>
+        <v>1395</v>
       </c>
       <c r="E289" t="s">
-        <v>1540</v>
+        <v>1530</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>1406</v>
+        <v>1396</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1407</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>1430</v>
+        <v>1420</v>
       </c>
       <c r="B290" t="s">
-        <v>1408</v>
+        <v>1398</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>1409</v>
+        <v>1399</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>1410</v>
+        <v>1400</v>
       </c>
       <c r="E290" t="s">
-        <v>1689</v>
+        <v>1679</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>1411</v>
+        <v>1401</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1412</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1432</v>
+        <v>1422</v>
       </c>
       <c r="B291" t="s">
-        <v>1413</v>
+        <v>1403</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>1414</v>
+        <v>1404</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>1415</v>
+        <v>1405</v>
       </c>
       <c r="E291" t="s">
-        <v>1561</v>
+        <v>1551</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>1416</v>
+        <v>1406</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1417</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1436</v>
+        <v>1426</v>
       </c>
       <c r="B292" t="s">
-        <v>1238</v>
+        <v>1228</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>1418</v>
+        <v>1408</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>1419</v>
+        <v>1409</v>
       </c>
       <c r="E292" t="s">
-        <v>1690</v>
+        <v>1680</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>1420</v>
+        <v>1410</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1421</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1439</v>
+        <v>1429</v>
       </c>
       <c r="B293" t="s">
-        <v>1422</v>
+        <v>1412</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>1423</v>
+        <v>1413</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="E293" t="s">
-        <v>1632</v>
+        <v>1622</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>1424</v>
+        <v>1414</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1441</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B294" t="s">
-        <v>1175</v>
+        <v>1165</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>1176</v>
+        <v>1166</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>1177</v>
+        <v>1167</v>
       </c>
       <c r="E294" t="s">
-        <v>1652</v>
+        <v>1642</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>1178</v>
+        <v>1168</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>1179</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B295" t="s">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>1181</v>
+        <v>1171</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>1182</v>
+        <v>1172</v>
       </c>
       <c r="E295" t="s">
-        <v>1522</v>
+        <v>1512</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>1184</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B296" t="s">
-        <v>1185</v>
+        <v>1175</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>1186</v>
+        <v>1176</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>1187</v>
+        <v>1177</v>
       </c>
       <c r="E296" t="s">
-        <v>1676</v>
+        <v>1666</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>1188</v>
+        <v>1178</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>1189</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="B297" t="s">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="E297" t="s">
-        <v>1691</v>
+        <v>1681</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>1193</v>
+        <v>1183</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>1194</v>
+        <v>1184</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Daily_Word.xlsx
+++ b/public/data/Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFEFC95-AE1A-412C-B4E5-4A5994DB7F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51090AB6-A816-4ADD-AE35-FE2E358CE4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1481,9 +1481,6 @@
     <t>Hot</t>
   </si>
   <si>
-    <t>ביום קר אני רגיל חוֹטֵט משהו טעים וHot</t>
-  </si>
-  <si>
     <t>работать</t>
   </si>
   <si>
@@ -1526,9 +1523,6 @@
     <t>נט</t>
   </si>
   <si>
-    <t>בוא סבא, אתה צריך זְנָאטְ להשתמש בנט (אינטרנט)</t>
-  </si>
-  <si>
     <t>думать</t>
   </si>
   <si>
@@ -1556,9 +1550,6 @@
     <t>פונט</t>
   </si>
   <si>
-    <t>כדאי שיוכלו פָּנִימָאטְ את המסר, צריך פונט טוב</t>
-  </si>
-  <si>
     <t>помнить</t>
   </si>
   <si>
@@ -1583,9 +1574,6 @@
     <t>לעשות</t>
   </si>
   <si>
-    <t>דיל</t>
-  </si>
-  <si>
     <t>מצאתי דיל טוב לקיץ! צריך להפסיק לחשוב ופשוט דֶּלָאטְ</t>
   </si>
   <si>
@@ -1682,12 +1670,6 @@
     <t>לשמוע</t>
   </si>
   <si>
-    <t>sent</t>
-  </si>
-  <si>
-    <t>אני sent (שלחתי) לך הודעה קולית סְלִישָׁאטְ</t>
-  </si>
-  <si>
     <t>спать</t>
   </si>
   <si>
@@ -1826,9 +1808,6 @@
     <t>סטטי</t>
   </si>
   <si>
-    <t>בטירונות צריך סְטָיָט בלי לזוז - להיות סטטי</t>
-  </si>
-  <si>
     <t>лежать</t>
   </si>
   <si>
@@ -2048,9 +2027,6 @@
     <t>סיביר</t>
   </si>
   <si>
-    <t>בסֵבֵר קר כמו בסיביר!</t>
-  </si>
-  <si>
     <t>юг</t>
   </si>
   <si>
@@ -2078,9 +2054,6 @@
     <t>סטוק</t>
   </si>
   <si>
-    <t>הסטוק של כל הדברים מיוצר בווֹסְטוֹק - בסין</t>
-  </si>
-  <si>
     <t>запад</t>
   </si>
   <si>
@@ -2093,9 +2066,6 @@
     <t>זפת</t>
   </si>
   <si>
-    <t>ארה"ב שנמצאת בזָאפַּד כדור הארץ משתמשת בהרבה זפת</t>
-  </si>
-  <si>
     <t>вперед</t>
   </si>
   <si>
@@ -2165,12 +2135,6 @@
     <t>רחוק</t>
   </si>
   <si>
-    <t>דליקה</t>
-  </si>
-  <si>
-    <t>כשיש אש דליקה, נראה אותה גם דָּאלֶקוֹ</t>
-  </si>
-  <si>
     <t>близко</t>
   </si>
   <si>
@@ -2252,9 +2216,6 @@
     <t>אתלט</t>
   </si>
   <si>
-    <t>אתלט הוא ספורטאי אָטְלִיצְ'נָה</t>
-  </si>
-  <si>
     <t>грустно</t>
   </si>
   <si>
@@ -2265,9 +2226,6 @@
   </si>
   <si>
     <t>גרוס</t>
-  </si>
-  <si>
-    <t>הסלט יצא ממש גרוס - איזה גרוּסְנָה!</t>
   </si>
   <si>
     <t>злой</t>
@@ -5450,6 +5408,48 @@
   </si>
   <si>
     <t>הגיע החורף הגדול! זה מֶסִיאַץ שעלול להתרחש בו הרבה Mess</t>
+  </si>
+  <si>
+    <t>ביום קר אני חוֹטֵט משהו טעים וHot</t>
+  </si>
+  <si>
+    <t>בוא אבא, אתה צריך זְנָאטְ להשתמש בנט (אינטרנט)</t>
+  </si>
+  <si>
+    <t>כדאי שיוכלו פָּנִימָאטְ את המסר של המצגת, צריך פונט טוב</t>
+  </si>
+  <si>
+    <t>דיל / do it</t>
+  </si>
+  <si>
+    <t>לעיסה</t>
+  </si>
+  <si>
+    <t>אתה לועס ממש חזק, אני לא מצליח סְלִישָׁאט שום דבר אחר</t>
+  </si>
+  <si>
+    <t>בטקסים צריך סְטָיָט בלי לזוז - להיות סטטי</t>
+  </si>
+  <si>
+    <t>סיביר הקרה נמצאת בסֵבֵר של אסיה</t>
+  </si>
+  <si>
+    <t>הסטוק של כל הדברים מיוצר בסין שבווֹסְטוֹק אסיה</t>
+  </si>
+  <si>
+    <t>ארה"ב שנמצאת בזָאפַּד משתמשת בהרבה זפת</t>
+  </si>
+  <si>
+    <t>דלק</t>
+  </si>
+  <si>
+    <t>דלק עוזר לנו לנסוע עם הרכב דָּאלֶקוֹ</t>
+  </si>
+  <si>
+    <t>אתלט הוא אדם העוסק הרבה בספורט, איזה אָטְלִיצְ'נָה!</t>
+  </si>
+  <si>
+    <t>הסלט יצא ממש גרוס - זה עושה אותי גרוּסְנָה!</t>
   </si>
 </sst>
 </file>
@@ -5848,27 +5848,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1684</v>
+        <v>1670</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1437</v>
+        <v>1423</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1436</v>
+        <v>1422</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1439</v>
+        <v>1425</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1435</v>
+        <v>1421</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1434</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -5880,7 +5880,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1440</v>
+        <v>1426</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
@@ -5891,7 +5891,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -5903,7 +5903,7 @@
         <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1441</v>
+        <v>1427</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>24</v>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -5926,18 +5926,18 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1442</v>
+        <v>1428</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1438</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -5949,18 +5949,18 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1443</v>
+        <v>1429</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1712</v>
+        <v>1698</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1713</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1444</v>
+        <v>1430</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>36</v>
@@ -5983,7 +5983,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B7" t="s">
         <v>38</v>
@@ -5995,30 +5995,30 @@
         <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1702</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B8" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1707</v>
+        <v>1693</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1446</v>
+        <v>1432</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>44</v>
@@ -6029,30 +6029,30 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B9" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1703</v>
+        <v>1689</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1447</v>
+        <v>1433</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1704</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B10" t="s">
         <v>48</v>
@@ -6064,7 +6064,7 @@
         <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1448</v>
+        <v>1434</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>51</v>
@@ -6075,7 +6075,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B11" t="s">
         <v>53</v>
@@ -6087,41 +6087,41 @@
         <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1449</v>
+        <v>1435</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1715</v>
+        <v>1701</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1714</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B12" t="s">
         <v>56</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1708</v>
+        <v>1694</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1450</v>
+        <v>1436</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>58</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1709</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B13" t="s">
         <v>59</v>
@@ -6133,18 +6133,18 @@
         <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1451</v>
+        <v>1437</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1710</v>
+        <v>1696</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1711</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B14" t="s">
         <v>62</v>
@@ -6156,7 +6156,7 @@
         <v>64</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1452</v>
+        <v>1438</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>65</v>
@@ -6167,7 +6167,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B15" t="s">
         <v>67</v>
@@ -6179,7 +6179,7 @@
         <v>69</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1453</v>
+        <v>1439</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -6190,7 +6190,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B16" t="s">
         <v>72</v>
@@ -6202,7 +6202,7 @@
         <v>74</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1454</v>
+        <v>1440</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>75</v>
@@ -6213,7 +6213,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B17" t="s">
         <v>77</v>
@@ -6225,7 +6225,7 @@
         <v>79</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1455</v>
+        <v>1441</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>80</v>
@@ -6236,7 +6236,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B18" t="s">
         <v>82</v>
@@ -6248,7 +6248,7 @@
         <v>84</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1456</v>
+        <v>1442</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>85</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B19" t="s">
         <v>87</v>
@@ -6271,7 +6271,7 @@
         <v>89</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1457</v>
+        <v>1443</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>90</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B20" t="s">
         <v>92</v>
@@ -6294,7 +6294,7 @@
         <v>94</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1458</v>
+        <v>1444</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>95</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B21" t="s">
         <v>97</v>
@@ -6317,18 +6317,18 @@
         <v>99</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1459</v>
+        <v>1445</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1697</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B22" t="s">
         <v>101</v>
@@ -6340,7 +6340,7 @@
         <v>103</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1476</v>
+        <v>1462</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>104</v>
@@ -6351,30 +6351,30 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B23" t="s">
         <v>106</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1705</v>
+        <v>1691</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1460</v>
+        <v>1446</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>108</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1706</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
@@ -6386,7 +6386,7 @@
         <v>111</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1461</v>
+        <v>1447</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>112</v>
@@ -6397,7 +6397,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B25" t="s">
         <v>114</v>
@@ -6409,7 +6409,7 @@
         <v>116</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1462</v>
+        <v>1448</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>117</v>
@@ -6420,7 +6420,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B26" t="s">
         <v>119</v>
@@ -6432,7 +6432,7 @@
         <v>121</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1463</v>
+        <v>1449</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>122</v>
@@ -6443,7 +6443,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B27" t="s">
         <v>124</v>
@@ -6455,7 +6455,7 @@
         <v>126</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1460</v>
+        <v>1446</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>127</v>
@@ -6466,7 +6466,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B28" t="s">
         <v>129</v>
@@ -6478,7 +6478,7 @@
         <v>131</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1464</v>
+        <v>1450</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>132</v>
@@ -6489,7 +6489,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B29" t="s">
         <v>134</v>
@@ -6501,7 +6501,7 @@
         <v>136</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1465</v>
+        <v>1451</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>137</v>
@@ -6512,7 +6512,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B30" t="s">
         <v>139</v>
@@ -6524,7 +6524,7 @@
         <v>141</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1466</v>
+        <v>1452</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>142</v>
@@ -6535,7 +6535,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B31" t="s">
         <v>144</v>
@@ -6547,7 +6547,7 @@
         <v>146</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1467</v>
+        <v>1453</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>147</v>
@@ -6558,7 +6558,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B32" t="s">
         <v>149</v>
@@ -6570,18 +6570,18 @@
         <v>151</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1468</v>
+        <v>1454</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>152</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1696</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B33" t="s">
         <v>153</v>
@@ -6593,7 +6593,7 @@
         <v>155</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1469</v>
+        <v>1455</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>156</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B34" t="s">
         <v>158</v>
@@ -6616,7 +6616,7 @@
         <v>160</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1470</v>
+        <v>1456</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>161</v>
@@ -6627,7 +6627,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B35" t="s">
         <v>163</v>
@@ -6639,7 +6639,7 @@
         <v>165</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1471</v>
+        <v>1457</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>166</v>
@@ -6650,7 +6650,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B36" t="s">
         <v>168</v>
@@ -6662,7 +6662,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1472</v>
+        <v>1458</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>170</v>
@@ -6673,7 +6673,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B37" t="s">
         <v>172</v>
@@ -6685,7 +6685,7 @@
         <v>174</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1473</v>
+        <v>1459</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>175</v>
@@ -6696,7 +6696,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B38" t="s">
         <v>177</v>
@@ -6708,7 +6708,7 @@
         <v>179</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1474</v>
+        <v>1460</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B39" t="s">
         <v>181</v>
@@ -6731,7 +6731,7 @@
         <v>183</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1475</v>
+        <v>1461</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>184</v>
@@ -6742,7 +6742,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B40" t="s">
         <v>186</v>
@@ -6754,7 +6754,7 @@
         <v>188</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1477</v>
+        <v>1463</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>189</v>
@@ -6765,7 +6765,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B41" t="s">
         <v>191</v>
@@ -6777,7 +6777,7 @@
         <v>193</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1478</v>
+        <v>1464</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>194</v>
@@ -6788,7 +6788,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B42" t="s">
         <v>196</v>
@@ -6800,7 +6800,7 @@
         <v>198</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1479</v>
+        <v>1465</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>199</v>
@@ -6811,7 +6811,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B43" t="s">
         <v>201</v>
@@ -6823,7 +6823,7 @@
         <v>203</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1480</v>
+        <v>1466</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>204</v>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B44" t="s">
         <v>206</v>
@@ -6846,7 +6846,7 @@
         <v>208</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1481</v>
+        <v>1467</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>209</v>
@@ -6857,7 +6857,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B45" t="s">
         <v>211</v>
@@ -6869,18 +6869,18 @@
         <v>213</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1685</v>
+        <v>1671</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>214</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1695</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B46" t="s">
         <v>215</v>
@@ -6892,7 +6892,7 @@
         <v>217</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1482</v>
+        <v>1468</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>218</v>
@@ -6903,7 +6903,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B47" t="s">
         <v>220</v>
@@ -6915,7 +6915,7 @@
         <v>222</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1686</v>
+        <v>1672</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>223</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B48" t="s">
         <v>225</v>
@@ -6938,7 +6938,7 @@
         <v>227</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1483</v>
+        <v>1469</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>228</v>
@@ -6949,7 +6949,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B49" t="s">
         <v>230</v>
@@ -6961,7 +6961,7 @@
         <v>232</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1484</v>
+        <v>1470</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>233</v>
@@ -6972,7 +6972,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B50" t="s">
         <v>235</v>
@@ -6984,7 +6984,7 @@
         <v>237</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1485</v>
+        <v>1471</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>238</v>
@@ -6995,7 +6995,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B51" t="s">
         <v>240</v>
@@ -7007,7 +7007,7 @@
         <v>242</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1486</v>
+        <v>1472</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>243</v>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B52" t="s">
         <v>245</v>
@@ -7030,7 +7030,7 @@
         <v>247</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1487</v>
+        <v>1473</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>248</v>
@@ -7041,7 +7041,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B53" t="s">
         <v>250</v>
@@ -7053,18 +7053,18 @@
         <v>252</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1465</v>
+        <v>1451</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1699</v>
+        <v>1685</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1698</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B54" t="s">
         <v>253</v>
@@ -7076,18 +7076,18 @@
         <v>255</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1493</v>
+        <v>1479</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>256</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1700</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1416</v>
+        <v>1402</v>
       </c>
       <c r="B55" t="s">
         <v>257</v>
@@ -7099,7 +7099,7 @@
         <v>259</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1494</v>
+        <v>1480</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>260</v>
@@ -7110,7 +7110,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B56" t="s">
         <v>262</v>
@@ -7122,7 +7122,7 @@
         <v>264</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1488</v>
+        <v>1474</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>265</v>
@@ -7133,7 +7133,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B57" t="s">
         <v>267</v>
@@ -7145,7 +7145,7 @@
         <v>269</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1489</v>
+        <v>1475</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>270</v>
@@ -7156,7 +7156,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B58" t="s">
         <v>272</v>
@@ -7168,7 +7168,7 @@
         <v>274</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1490</v>
+        <v>1476</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>275</v>
@@ -7179,7 +7179,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B59" t="s">
         <v>277</v>
@@ -7191,7 +7191,7 @@
         <v>279</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1491</v>
+        <v>1477</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>280</v>
@@ -7202,7 +7202,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B60" t="s">
         <v>282</v>
@@ -7214,7 +7214,7 @@
         <v>284</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1492</v>
+        <v>1478</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>285</v>
@@ -7225,7 +7225,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B61" t="s">
         <v>287</v>
@@ -7237,7 +7237,7 @@
         <v>289</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1495</v>
+        <v>1481</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>290</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B62" t="s">
         <v>292</v>
@@ -7260,7 +7260,7 @@
         <v>294</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1496</v>
+        <v>1482</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>295</v>
@@ -7271,7 +7271,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B63" t="s">
         <v>297</v>
@@ -7280,10 +7280,10 @@
         <v>298</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1516</v>
+        <v>1502</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1496</v>
+        <v>1482</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>299</v>
@@ -7294,7 +7294,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B64" t="s">
         <v>301</v>
@@ -7306,7 +7306,7 @@
         <v>303</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1497</v>
+        <v>1483</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
@@ -7317,7 +7317,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B65" t="s">
         <v>305</v>
@@ -7329,7 +7329,7 @@
         <v>307</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1498</v>
+        <v>1484</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>308</v>
@@ -7340,7 +7340,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B66" t="s">
         <v>310</v>
@@ -7352,7 +7352,7 @@
         <v>312</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1517</v>
+        <v>1503</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>313</v>
@@ -7363,7 +7363,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B67" t="s">
         <v>315</v>
@@ -7375,7 +7375,7 @@
         <v>317</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1499</v>
+        <v>1485</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>318</v>
@@ -7386,7 +7386,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B68" t="s">
         <v>320</v>
@@ -7398,18 +7398,18 @@
         <v>322</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1492</v>
+        <v>1478</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>323</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1701</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B69" t="s">
         <v>324</v>
@@ -7421,7 +7421,7 @@
         <v>326</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1491</v>
+        <v>1477</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>327</v>
@@ -7432,7 +7432,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B70" t="s">
         <v>329</v>
@@ -7444,7 +7444,7 @@
         <v>331</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1500</v>
+        <v>1486</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>332</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B71" t="s">
         <v>334</v>
@@ -7467,7 +7467,7 @@
         <v>336</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1687</v>
+        <v>1673</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>337</v>
@@ -7478,7 +7478,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B72" t="s">
         <v>339</v>
@@ -7490,7 +7490,7 @@
         <v>341</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1501</v>
+        <v>1487</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>342</v>
@@ -7501,7 +7501,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B73" t="s">
         <v>344</v>
@@ -7513,7 +7513,7 @@
         <v>346</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1502</v>
+        <v>1488</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>347</v>
@@ -7524,7 +7524,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B74" t="s">
         <v>349</v>
@@ -7536,7 +7536,7 @@
         <v>351</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1503</v>
+        <v>1489</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>352</v>
@@ -7547,7 +7547,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B75" t="s">
         <v>354</v>
@@ -7559,18 +7559,18 @@
         <v>356</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1504</v>
+        <v>1490</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>357</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1716</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B76" t="s">
         <v>358</v>
@@ -7582,7 +7582,7 @@
         <v>360</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1505</v>
+        <v>1491</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>361</v>
@@ -7593,7 +7593,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B77" t="s">
         <v>363</v>
@@ -7605,7 +7605,7 @@
         <v>365</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1506</v>
+        <v>1492</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>366</v>
@@ -7616,7 +7616,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B78" t="s">
         <v>368</v>
@@ -7628,7 +7628,7 @@
         <v>370</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1490</v>
+        <v>1476</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>371</v>
@@ -7639,30 +7639,30 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B79" t="s">
         <v>373</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1717</v>
+        <v>1703</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>374</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1507</v>
+        <v>1493</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>375</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1718</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B80" t="s">
         <v>376</v>
@@ -7674,7 +7674,7 @@
         <v>378</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1508</v>
+        <v>1494</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>379</v>
@@ -7685,7 +7685,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B81" t="s">
         <v>381</v>
@@ -7697,18 +7697,18 @@
         <v>383</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1509</v>
+        <v>1495</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>384</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1719</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B82" t="s">
         <v>385</v>
@@ -7720,7 +7720,7 @@
         <v>387</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1488</v>
+        <v>1474</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>388</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B83" t="s">
         <v>390</v>
@@ -7743,7 +7743,7 @@
         <v>392</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1491</v>
+        <v>1477</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>393</v>
@@ -7754,7 +7754,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1417</v>
+        <v>1403</v>
       </c>
       <c r="B84" t="s">
         <v>395</v>
@@ -7766,7 +7766,7 @@
         <v>397</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1510</v>
+        <v>1496</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B85" t="s">
         <v>399</v>
@@ -7789,7 +7789,7 @@
         <v>401</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1511</v>
+        <v>1497</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>402</v>
@@ -7800,7 +7800,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B86" t="s">
         <v>404</v>
@@ -7812,7 +7812,7 @@
         <v>406</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1512</v>
+        <v>1498</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>407</v>
@@ -7823,7 +7823,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B87" t="s">
         <v>409</v>
@@ -7835,7 +7835,7 @@
         <v>411</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1513</v>
+        <v>1499</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>412</v>
@@ -7846,7 +7846,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B88" t="s">
         <v>414</v>
@@ -7858,18 +7858,18 @@
         <v>416</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1688</v>
+        <v>1674</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>417</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1720</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B89" t="s">
         <v>418</v>
@@ -7881,7 +7881,7 @@
         <v>420</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1689</v>
+        <v>1675</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>421</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B90" t="s">
         <v>423</v>
@@ -7904,7 +7904,7 @@
         <v>425</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1515</v>
+        <v>1501</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>426</v>
@@ -7915,7 +7915,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B91" t="s">
         <v>428</v>
@@ -7927,18 +7927,18 @@
         <v>430</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1515</v>
+        <v>1501</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>431</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1721</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B92" t="s">
         <v>432</v>
@@ -7950,7 +7950,7 @@
         <v>434</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1515</v>
+        <v>1501</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>435</v>
@@ -7961,7 +7961,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B93" t="s">
         <v>437</v>
@@ -7973,7 +7973,7 @@
         <v>439</v>
       </c>
       <c r="E93" t="s">
-        <v>1519</v>
+        <v>1505</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>440</v>
@@ -7984,7 +7984,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B94" t="s">
         <v>442</v>
@@ -7996,7 +7996,7 @@
         <v>444</v>
       </c>
       <c r="E94" t="s">
-        <v>1514</v>
+        <v>1500</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>445</v>
@@ -8007,7 +8007,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B95" t="s">
         <v>447</v>
@@ -8019,7 +8019,7 @@
         <v>449</v>
       </c>
       <c r="E95" t="s">
-        <v>1520</v>
+        <v>1506</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>450</v>
@@ -8030,7 +8030,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B96" t="s">
         <v>452</v>
@@ -8042,7 +8042,7 @@
         <v>454</v>
       </c>
       <c r="E96" t="s">
-        <v>1521</v>
+        <v>1507</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>455</v>
@@ -8053,7 +8053,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B97" t="s">
         <v>457</v>
@@ -8065,7 +8065,7 @@
         <v>459</v>
       </c>
       <c r="E97" t="s">
-        <v>1522</v>
+        <v>1508</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>460</v>
@@ -8076,7 +8076,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B98" t="s">
         <v>462</v>
@@ -8088,7 +8088,7 @@
         <v>464</v>
       </c>
       <c r="E98" t="s">
-        <v>1523</v>
+        <v>1509</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>465</v>
@@ -8099,7 +8099,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B99" t="s">
         <v>467</v>
@@ -8111,7 +8111,7 @@
         <v>469</v>
       </c>
       <c r="E99" t="s">
-        <v>1524</v>
+        <v>1510</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>470</v>
@@ -8122,4553 +8122,4553 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B100" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="E100" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B101" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E101" t="s">
-        <v>1526</v>
+        <v>1511</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B102" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E102" t="s">
-        <v>1527</v>
+        <v>1512</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>486</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B103" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="E103" t="s">
-        <v>1528</v>
+        <v>1513</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B104" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="E104" t="s">
-        <v>1529</v>
+        <v>1514</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B105" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="E105" t="s">
-        <v>1530</v>
+        <v>1515</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>501</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B106" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="E106" t="s">
-        <v>1531</v>
+        <v>1516</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B107" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="E107" t="s">
-        <v>1532</v>
+        <v>1517</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>511</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B108" t="s">
+        <v>509</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E108" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="G108" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="E108" t="s">
-        <v>1533</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B109" t="s">
+        <v>513</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E109" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G109" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E109" t="s">
-        <v>1534</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B110" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E110" t="s">
-        <v>1535</v>
+        <v>1521</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B111" t="s">
+        <v>522</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1522</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G111" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="E111" t="s">
-        <v>1536</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B112" t="s">
+        <v>527</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E112" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="G112" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E112" t="s">
-        <v>1537</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B113" t="s">
+        <v>532</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E113" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G113" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="E113" t="s">
-        <v>1538</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B114" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="E114" t="s">
-        <v>1539</v>
+        <v>1525</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B115" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E115" t="s">
-        <v>1540</v>
+        <v>1526</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>548</v>
+        <v>1712</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>549</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B116" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E116" t="s">
-        <v>1541</v>
+        <v>1527</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>284</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B117" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="E117" t="s">
-        <v>1488</v>
+        <v>1474</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B118" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="E118" t="s">
-        <v>1542</v>
+        <v>1528</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B119" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="E119" t="s">
-        <v>1543</v>
+        <v>1529</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B120" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E120" t="s">
-        <v>1544</v>
+        <v>1530</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B121" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="E121" t="s">
-        <v>1545</v>
+        <v>1531</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B122" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="E122" t="s">
-        <v>1546</v>
+        <v>1532</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B123" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E123" t="s">
-        <v>1547</v>
+        <v>1533</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B124" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="E124" t="s">
-        <v>1548</v>
+        <v>1534</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B125" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="E125" t="s">
-        <v>1549</v>
+        <v>1535</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>596</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B126" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="E126" t="s">
-        <v>1490</v>
+        <v>1476</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B127" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="E127" t="s">
-        <v>1550</v>
+        <v>1536</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B128" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="E128" t="s">
-        <v>1551</v>
+        <v>1537</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B129" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="E129" t="s">
-        <v>1526</v>
+        <v>1512</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B130" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="E130" t="s">
-        <v>1693</v>
+        <v>1679</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B131" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="E131" t="s">
-        <v>1694</v>
+        <v>1680</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>294</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B132" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="E132" t="s">
-        <v>1552</v>
+        <v>1538</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B133" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="E133" t="s">
-        <v>1553</v>
+        <v>1539</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B134" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="E134" t="s">
-        <v>1551</v>
+        <v>1537</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B135" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="E135" t="s">
-        <v>1554</v>
+        <v>1540</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B136" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="E136" t="s">
-        <v>1509</v>
+        <v>1495</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B137" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="E137" t="s">
-        <v>1555</v>
+        <v>1541</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B138" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="E138" t="s">
-        <v>1531</v>
+        <v>1517</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B139" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="E139" t="s">
-        <v>1556</v>
+        <v>1542</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B140" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="E140" t="s">
-        <v>1557</v>
+        <v>1543</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>670</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B141" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="E141" t="s">
-        <v>1558</v>
+        <v>1544</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B142" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="E142" t="s">
-        <v>1520</v>
+        <v>1506</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>680</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B143" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="E143" t="s">
-        <v>1559</v>
+        <v>1545</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>685</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B144" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="E144" t="s">
-        <v>1560</v>
+        <v>1546</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B145" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="E145" t="s">
-        <v>1561</v>
+        <v>1547</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B146" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="E146" t="s">
-        <v>1562</v>
+        <v>1548</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B147" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="E147" t="s">
-        <v>1563</v>
+        <v>1549</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B148" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="E148" t="s">
-        <v>1564</v>
+        <v>1550</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>709</v>
+        <v>1718</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>710</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B149" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>275</v>
       </c>
       <c r="E149" t="s">
-        <v>1564</v>
+        <v>1550</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B150" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="E150" t="s">
-        <v>1564</v>
+        <v>1550</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B151" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="E151" t="s">
-        <v>1564</v>
+        <v>1550</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B152" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="E152" t="s">
-        <v>1690</v>
+        <v>1676</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B153" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="E153" t="s">
-        <v>1691</v>
+        <v>1677</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B154" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="E154" t="s">
-        <v>1565</v>
+        <v>1551</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>738</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B155" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="E155" t="s">
-        <v>1566</v>
+        <v>1552</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>743</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B156" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="E156" t="s">
-        <v>1567</v>
+        <v>1553</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B157" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>750</v>
+        <v>736</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>751</v>
+        <v>737</v>
       </c>
       <c r="E157" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>752</v>
+        <v>738</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>753</v>
+        <v>739</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B158" t="s">
-        <v>754</v>
+        <v>740</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>755</v>
+        <v>741</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
       <c r="E158" t="s">
-        <v>1541</v>
+        <v>1527</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>758</v>
+        <v>744</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B159" t="s">
-        <v>759</v>
+        <v>745</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="E159" t="s">
-        <v>1569</v>
+        <v>1555</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B160" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="E160" t="s">
-        <v>1692</v>
+        <v>1678</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B161" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="E161" t="s">
-        <v>1569</v>
+        <v>1555</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>772</v>
+        <v>758</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>773</v>
+        <v>759</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B162" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="E162" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>778</v>
+        <v>764</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B163" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>780</v>
+        <v>766</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>781</v>
+        <v>767</v>
       </c>
       <c r="E163" t="s">
-        <v>1571</v>
+        <v>1557</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>782</v>
+        <v>768</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>783</v>
+        <v>769</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B164" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="E164" t="s">
-        <v>1572</v>
+        <v>1558</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B165" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="E165" t="s">
-        <v>1573</v>
+        <v>1559</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B166" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="E166" t="s">
-        <v>1574</v>
+        <v>1560</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B167" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
       <c r="E167" t="s">
-        <v>1575</v>
+        <v>1561</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>802</v>
+        <v>788</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B168" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="E168" t="s">
-        <v>1576</v>
+        <v>1562</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B169" t="s">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="E169" t="s">
-        <v>1577</v>
+        <v>1563</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>813</v>
+        <v>799</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B170" t="s">
-        <v>814</v>
+        <v>800</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>815</v>
+        <v>801</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>816</v>
+        <v>802</v>
       </c>
       <c r="E170" t="s">
-        <v>1578</v>
+        <v>1564</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>817</v>
+        <v>803</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>818</v>
+        <v>804</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B171" t="s">
-        <v>819</v>
+        <v>805</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>820</v>
+        <v>806</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="E171" t="s">
-        <v>1579</v>
+        <v>1565</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>823</v>
+        <v>809</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B172" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="E172" t="s">
-        <v>1580</v>
+        <v>1566</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>828</v>
+        <v>814</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B173" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>831</v>
+        <v>817</v>
       </c>
       <c r="E173" t="s">
-        <v>1581</v>
+        <v>1567</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>833</v>
+        <v>819</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B174" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>835</v>
+        <v>821</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
       <c r="E174" t="s">
-        <v>1582</v>
+        <v>1568</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>837</v>
+        <v>823</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>838</v>
+        <v>824</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B175" t="s">
-        <v>839</v>
+        <v>825</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>840</v>
+        <v>826</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>841</v>
+        <v>827</v>
       </c>
       <c r="E175" t="s">
-        <v>1583</v>
+        <v>1569</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>843</v>
+        <v>829</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B176" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>846</v>
+        <v>832</v>
       </c>
       <c r="E176" t="s">
-        <v>1584</v>
+        <v>1570</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>847</v>
+        <v>833</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>848</v>
+        <v>834</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B177" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>851</v>
+        <v>837</v>
       </c>
       <c r="E177" t="s">
-        <v>1585</v>
+        <v>1571</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>852</v>
+        <v>838</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>853</v>
+        <v>839</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B178" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>855</v>
+        <v>841</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>856</v>
+        <v>842</v>
       </c>
       <c r="E178" t="s">
-        <v>1586</v>
+        <v>1572</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>858</v>
+        <v>844</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B179" t="s">
-        <v>859</v>
+        <v>845</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="E179" t="s">
-        <v>1587</v>
+        <v>1573</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>862</v>
+        <v>848</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>863</v>
+        <v>849</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B180" t="s">
-        <v>864</v>
+        <v>850</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>865</v>
+        <v>851</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>866</v>
+        <v>852</v>
       </c>
       <c r="E180" t="s">
-        <v>1588</v>
+        <v>1574</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>867</v>
+        <v>853</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>868</v>
+        <v>854</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B181" t="s">
-        <v>869</v>
+        <v>855</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="E181" t="s">
-        <v>1589</v>
+        <v>1575</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>872</v>
+        <v>858</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>873</v>
+        <v>859</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B182" t="s">
-        <v>874</v>
+        <v>860</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>876</v>
+        <v>862</v>
       </c>
       <c r="E182" t="s">
-        <v>1590</v>
+        <v>1576</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>878</v>
+        <v>864</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B183" t="s">
-        <v>879</v>
+        <v>865</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>880</v>
+        <v>866</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>881</v>
+        <v>867</v>
       </c>
       <c r="E183" t="s">
-        <v>1591</v>
+        <v>1577</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>882</v>
+        <v>868</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>883</v>
+        <v>869</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B184" t="s">
-        <v>884</v>
+        <v>870</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>885</v>
+        <v>871</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>886</v>
+        <v>872</v>
       </c>
       <c r="E184" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>887</v>
+        <v>873</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>888</v>
+        <v>874</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B185" t="s">
-        <v>889</v>
+        <v>875</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>891</v>
+        <v>877</v>
       </c>
       <c r="E185" t="s">
-        <v>1593</v>
+        <v>1579</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>892</v>
+        <v>878</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>893</v>
+        <v>879</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B186" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>895</v>
+        <v>881</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="E186" t="s">
-        <v>1594</v>
+        <v>1580</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>897</v>
+        <v>883</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>898</v>
+        <v>884</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B187" t="s">
-        <v>899</v>
+        <v>885</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>900</v>
+        <v>886</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>901</v>
+        <v>887</v>
       </c>
       <c r="E187" t="s">
-        <v>1595</v>
+        <v>1581</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>902</v>
+        <v>888</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>903</v>
+        <v>889</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B188" t="s">
-        <v>904</v>
+        <v>890</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>905</v>
+        <v>891</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>906</v>
+        <v>892</v>
       </c>
       <c r="E188" t="s">
-        <v>1596</v>
+        <v>1582</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>907</v>
+        <v>893</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>908</v>
+        <v>894</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B189" t="s">
-        <v>909</v>
+        <v>895</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>910</v>
+        <v>896</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>911</v>
+        <v>897</v>
       </c>
       <c r="E189" t="s">
-        <v>1597</v>
+        <v>1583</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>912</v>
+        <v>898</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>913</v>
+        <v>899</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B190" t="s">
-        <v>914</v>
+        <v>900</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>915</v>
+        <v>901</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>916</v>
+        <v>902</v>
       </c>
       <c r="E190" t="s">
-        <v>1598</v>
+        <v>1584</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>917</v>
+        <v>903</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>918</v>
+        <v>904</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B191" t="s">
-        <v>919</v>
+        <v>905</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>920</v>
+        <v>906</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>921</v>
+        <v>907</v>
       </c>
       <c r="E191" t="s">
-        <v>1599</v>
+        <v>1585</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>117</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>922</v>
+        <v>908</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B192" t="s">
-        <v>923</v>
+        <v>909</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>924</v>
+        <v>910</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>925</v>
+        <v>911</v>
       </c>
       <c r="E192" t="s">
-        <v>1600</v>
+        <v>1586</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>926</v>
+        <v>912</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>927</v>
+        <v>913</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B193" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>929</v>
+        <v>915</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>930</v>
+        <v>916</v>
       </c>
       <c r="E193" t="s">
-        <v>1601</v>
+        <v>1587</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>931</v>
+        <v>917</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>932</v>
+        <v>918</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B194" t="s">
-        <v>933</v>
+        <v>919</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>935</v>
+        <v>921</v>
       </c>
       <c r="E194" t="s">
-        <v>1602</v>
+        <v>1588</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>936</v>
+        <v>922</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>937</v>
+        <v>923</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B195" t="s">
-        <v>938</v>
+        <v>924</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>939</v>
+        <v>925</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>940</v>
+        <v>926</v>
       </c>
       <c r="E195" t="s">
-        <v>1603</v>
+        <v>1589</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>942</v>
+        <v>928</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B196" t="s">
-        <v>943</v>
+        <v>929</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>944</v>
+        <v>930</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>945</v>
+        <v>931</v>
       </c>
       <c r="E196" t="s">
-        <v>1604</v>
+        <v>1590</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>946</v>
+        <v>932</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>947</v>
+        <v>933</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B197" t="s">
-        <v>948</v>
+        <v>934</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="E197" t="s">
-        <v>1574</v>
+        <v>1560</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>951</v>
+        <v>937</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>952</v>
+        <v>938</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B198" t="s">
-        <v>953</v>
+        <v>939</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>954</v>
+        <v>940</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>955</v>
+        <v>941</v>
       </c>
       <c r="E198" t="s">
-        <v>1605</v>
+        <v>1591</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>956</v>
+        <v>942</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B199" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>959</v>
+        <v>945</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>960</v>
+        <v>946</v>
       </c>
       <c r="E199" t="s">
-        <v>1606</v>
+        <v>1592</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>961</v>
+        <v>947</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>962</v>
+        <v>948</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B200" t="s">
-        <v>963</v>
+        <v>949</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>965</v>
+        <v>951</v>
       </c>
       <c r="E200" t="s">
-        <v>1607</v>
+        <v>1593</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>966</v>
+        <v>952</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>967</v>
+        <v>953</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B201" t="s">
-        <v>968</v>
+        <v>954</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>969</v>
+        <v>955</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>970</v>
+        <v>956</v>
       </c>
       <c r="E201" t="s">
-        <v>1582</v>
+        <v>1568</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>971</v>
+        <v>957</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>972</v>
+        <v>958</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B202" t="s">
-        <v>973</v>
+        <v>959</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>974</v>
+        <v>960</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>975</v>
+        <v>961</v>
       </c>
       <c r="E202" t="s">
-        <v>1608</v>
+        <v>1594</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>976</v>
+        <v>962</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>977</v>
+        <v>963</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B203" t="s">
-        <v>978</v>
+        <v>964</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>979</v>
+        <v>965</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>980</v>
+        <v>966</v>
       </c>
       <c r="E203" t="s">
-        <v>1609</v>
+        <v>1595</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>981</v>
+        <v>967</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>982</v>
+        <v>968</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B204" t="s">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>984</v>
+        <v>970</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>985</v>
+        <v>971</v>
       </c>
       <c r="E204" t="s">
-        <v>1610</v>
+        <v>1596</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>986</v>
+        <v>972</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>987</v>
+        <v>973</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B205" t="s">
-        <v>988</v>
+        <v>974</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>989</v>
+        <v>975</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>990</v>
+        <v>976</v>
       </c>
       <c r="E205" t="s">
-        <v>1611</v>
+        <v>1597</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>991</v>
+        <v>977</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>992</v>
+        <v>978</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B206" t="s">
-        <v>993</v>
+        <v>979</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>994</v>
+        <v>980</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>995</v>
+        <v>981</v>
       </c>
       <c r="E206" t="s">
-        <v>1612</v>
+        <v>1598</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>996</v>
+        <v>982</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>997</v>
+        <v>983</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B207" t="s">
-        <v>998</v>
+        <v>984</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>999</v>
+        <v>985</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="E207" t="s">
-        <v>1496</v>
+        <v>1482</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>1001</v>
+        <v>987</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>1002</v>
+        <v>988</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B208" t="s">
-        <v>1003</v>
+        <v>989</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>1004</v>
+        <v>990</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>1005</v>
+        <v>991</v>
       </c>
       <c r="E208" t="s">
-        <v>1613</v>
+        <v>1599</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>1006</v>
+        <v>992</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>1007</v>
+        <v>993</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B209" t="s">
-        <v>1008</v>
+        <v>994</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>1009</v>
+        <v>995</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>1010</v>
+        <v>996</v>
       </c>
       <c r="E209" t="s">
-        <v>1614</v>
+        <v>1600</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>1011</v>
+        <v>997</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>1012</v>
+        <v>998</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B210" t="s">
-        <v>1013</v>
+        <v>999</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>1014</v>
+        <v>1000</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>1015</v>
+        <v>1001</v>
       </c>
       <c r="E210" t="s">
-        <v>1615</v>
+        <v>1601</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>1016</v>
+        <v>1002</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>1017</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B211" t="s">
-        <v>1018</v>
+        <v>1004</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>1020</v>
+        <v>1006</v>
       </c>
       <c r="E211" t="s">
-        <v>1616</v>
+        <v>1602</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>1021</v>
+        <v>1007</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>1022</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B212" t="s">
-        <v>1023</v>
+        <v>1009</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>1024</v>
+        <v>1010</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>1025</v>
+        <v>1011</v>
       </c>
       <c r="E212" t="s">
-        <v>1612</v>
+        <v>1598</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>1026</v>
+        <v>1012</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>1027</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B213" t="s">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>1029</v>
+        <v>1015</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>1030</v>
+        <v>1016</v>
       </c>
       <c r="E213" t="s">
-        <v>1617</v>
+        <v>1603</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>1031</v>
+        <v>1017</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>1032</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B214" t="s">
-        <v>1033</v>
+        <v>1019</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>1034</v>
+        <v>1020</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="E214" t="s">
-        <v>1618</v>
+        <v>1604</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>1037</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B215" t="s">
-        <v>1038</v>
+        <v>1024</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>1039</v>
+        <v>1025</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>1040</v>
+        <v>1026</v>
       </c>
       <c r="E215" t="s">
-        <v>1544</v>
+        <v>1530</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>1041</v>
+        <v>1027</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>1042</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B216" t="s">
-        <v>1043</v>
+        <v>1029</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>1044</v>
+        <v>1030</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>1045</v>
+        <v>1031</v>
       </c>
       <c r="E216" t="s">
-        <v>1619</v>
+        <v>1605</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1046</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B217" t="s">
-        <v>1047</v>
+        <v>1033</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>1048</v>
+        <v>1034</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>1049</v>
+        <v>1035</v>
       </c>
       <c r="E217" t="s">
-        <v>1620</v>
+        <v>1606</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>1050</v>
+        <v>1036</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>1051</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B218" t="s">
-        <v>1052</v>
+        <v>1038</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>1053</v>
+        <v>1039</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>1054</v>
+        <v>1040</v>
       </c>
       <c r="E218" t="s">
-        <v>1621</v>
+        <v>1607</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>1055</v>
+        <v>1041</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>1056</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B219" t="s">
-        <v>1057</v>
+        <v>1043</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>1058</v>
+        <v>1044</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>1059</v>
+        <v>1045</v>
       </c>
       <c r="E219" t="s">
-        <v>1622</v>
+        <v>1608</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>1060</v>
+        <v>1046</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>1061</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B220" t="s">
-        <v>1062</v>
+        <v>1048</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>1063</v>
+        <v>1049</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1064</v>
+        <v>1050</v>
       </c>
       <c r="E220" t="s">
-        <v>1623</v>
+        <v>1609</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>1065</v>
+        <v>1051</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>1066</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B221" t="s">
-        <v>1067</v>
+        <v>1053</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>1068</v>
+        <v>1054</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>1069</v>
+        <v>1055</v>
       </c>
       <c r="E221" t="s">
-        <v>1624</v>
+        <v>1610</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>1070</v>
+        <v>1056</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>1071</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B222" t="s">
-        <v>1072</v>
+        <v>1058</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>1073</v>
+        <v>1059</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>1074</v>
+        <v>1060</v>
       </c>
       <c r="E222" t="s">
-        <v>1625</v>
+        <v>1611</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>1076</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B223" t="s">
-        <v>1077</v>
+        <v>1063</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>1078</v>
+        <v>1064</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>1079</v>
+        <v>1065</v>
       </c>
       <c r="E223" t="s">
-        <v>1626</v>
+        <v>1612</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1080</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B224" t="s">
-        <v>1081</v>
+        <v>1067</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>1082</v>
+        <v>1068</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>1083</v>
+        <v>1069</v>
       </c>
       <c r="E224" t="s">
-        <v>1627</v>
+        <v>1613</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>1084</v>
+        <v>1070</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>1085</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B225" t="s">
-        <v>1086</v>
+        <v>1072</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>1087</v>
+        <v>1073</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>1088</v>
+        <v>1074</v>
       </c>
       <c r="E225" t="s">
-        <v>1628</v>
+        <v>1614</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>1089</v>
+        <v>1075</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>1090</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B226" t="s">
-        <v>1091</v>
+        <v>1077</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>1092</v>
+        <v>1078</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E226" t="s">
-        <v>1629</v>
+        <v>1615</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>1093</v>
+        <v>1079</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>1094</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B227" t="s">
-        <v>1095</v>
+        <v>1081</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>1096</v>
+        <v>1082</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>1097</v>
+        <v>1083</v>
       </c>
       <c r="E227" t="s">
-        <v>1630</v>
+        <v>1616</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>1099</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B228" t="s">
-        <v>1100</v>
+        <v>1086</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>1101</v>
+        <v>1087</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>1102</v>
+        <v>1088</v>
       </c>
       <c r="E228" t="s">
-        <v>1631</v>
+        <v>1617</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>1103</v>
+        <v>1089</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>1104</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B229" t="s">
-        <v>1105</v>
+        <v>1091</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>1106</v>
+        <v>1092</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>1107</v>
+        <v>1093</v>
       </c>
       <c r="E229" t="s">
-        <v>1632</v>
+        <v>1618</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1108</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B230" t="s">
-        <v>1109</v>
+        <v>1095</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>1110</v>
+        <v>1096</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>1111</v>
+        <v>1097</v>
       </c>
       <c r="E230" t="s">
-        <v>1633</v>
+        <v>1619</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>1112</v>
+        <v>1098</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>1113</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1419</v>
+        <v>1405</v>
       </c>
       <c r="B231" t="s">
-        <v>1114</v>
+        <v>1100</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>1115</v>
+        <v>1101</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>1116</v>
+        <v>1102</v>
       </c>
       <c r="E231" t="s">
-        <v>1634</v>
+        <v>1620</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>1117</v>
+        <v>1103</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>1118</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B232" t="s">
-        <v>1119</v>
+        <v>1105</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>1120</v>
+        <v>1106</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>1121</v>
+        <v>1107</v>
       </c>
       <c r="E232" t="s">
-        <v>1635</v>
+        <v>1621</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>1122</v>
+        <v>1108</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>1123</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1423</v>
+        <v>1409</v>
       </c>
       <c r="B233" t="s">
-        <v>1124</v>
+        <v>1110</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>1125</v>
+        <v>1111</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>1126</v>
+        <v>1112</v>
       </c>
       <c r="E233" t="s">
-        <v>1636</v>
+        <v>1622</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>1127</v>
+        <v>1113</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1128</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1423</v>
+        <v>1409</v>
       </c>
       <c r="B234" t="s">
-        <v>1129</v>
+        <v>1115</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1130</v>
+        <v>1116</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>1131</v>
+        <v>1117</v>
       </c>
       <c r="E234" t="s">
-        <v>1637</v>
+        <v>1623</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>1132</v>
+        <v>1118</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>1133</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1423</v>
+        <v>1409</v>
       </c>
       <c r="B235" t="s">
-        <v>1136</v>
+        <v>1122</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>1137</v>
+        <v>1123</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>1138</v>
+        <v>1124</v>
       </c>
       <c r="E235" t="s">
-        <v>1638</v>
+        <v>1624</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>1139</v>
+        <v>1125</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1140</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
       <c r="B236" t="s">
-        <v>1141</v>
+        <v>1127</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>1142</v>
+        <v>1128</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>1143</v>
+        <v>1129</v>
       </c>
       <c r="E236" t="s">
-        <v>1639</v>
+        <v>1625</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>1144</v>
+        <v>1130</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>1145</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
       <c r="B237" t="s">
-        <v>1146</v>
+        <v>1132</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1147</v>
+        <v>1133</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>1148</v>
+        <v>1134</v>
       </c>
       <c r="E237" t="s">
-        <v>1536</v>
+        <v>1522</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>1149</v>
+        <v>1135</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1150</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
       <c r="B238" t="s">
-        <v>1151</v>
+        <v>1137</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>1152</v>
+        <v>1138</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>1153</v>
+        <v>1139</v>
       </c>
       <c r="E238" t="s">
-        <v>1544</v>
+        <v>1530</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>1154</v>
+        <v>1140</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>1155</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
       <c r="B239" t="s">
-        <v>1156</v>
+        <v>1142</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1157</v>
+        <v>1143</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>1158</v>
+        <v>1144</v>
       </c>
       <c r="E239" t="s">
-        <v>1640</v>
+        <v>1626</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>1159</v>
+        <v>1145</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1160</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
       <c r="B240" t="s">
-        <v>1161</v>
+        <v>1147</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>1162</v>
+        <v>1148</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>1641</v>
+        <v>1627</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>1163</v>
+        <v>1149</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>1164</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B241" t="s">
-        <v>1165</v>
+        <v>1151</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1166</v>
+        <v>1152</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>1167</v>
+        <v>1153</v>
       </c>
       <c r="E241" t="s">
-        <v>1642</v>
+        <v>1628</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>1168</v>
+        <v>1154</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1169</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B242" t="s">
-        <v>1170</v>
+        <v>1156</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>1171</v>
+        <v>1157</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>1172</v>
+        <v>1158</v>
       </c>
       <c r="E242" t="s">
-        <v>1512</v>
+        <v>1498</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>1173</v>
+        <v>1159</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>1174</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B243" t="s">
-        <v>1175</v>
+        <v>1161</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>1176</v>
+        <v>1162</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>1177</v>
+        <v>1163</v>
       </c>
       <c r="E243" t="s">
-        <v>1643</v>
+        <v>1629</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>1178</v>
+        <v>1164</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>1179</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B244" t="s">
-        <v>1180</v>
+        <v>1166</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>1181</v>
+        <v>1167</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>1182</v>
+        <v>1168</v>
       </c>
       <c r="E244" t="s">
-        <v>1644</v>
+        <v>1630</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>1183</v>
+        <v>1169</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1184</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B245" t="s">
-        <v>1185</v>
+        <v>1171</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>1186</v>
+        <v>1172</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>1187</v>
+        <v>1173</v>
       </c>
       <c r="E245" t="s">
-        <v>1645</v>
+        <v>1631</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1188</v>
+        <v>1174</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1189</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B246" t="s">
-        <v>1190</v>
+        <v>1176</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1191</v>
+        <v>1177</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>1192</v>
+        <v>1178</v>
       </c>
       <c r="E246" t="s">
-        <v>1646</v>
+        <v>1632</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>1193</v>
+        <v>1179</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1194</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B247" t="s">
-        <v>1195</v>
+        <v>1181</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1196</v>
+        <v>1182</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1197</v>
+        <v>1183</v>
       </c>
       <c r="E247" t="s">
-        <v>1647</v>
+        <v>1633</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1198</v>
+        <v>1184</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1199</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B248" t="s">
-        <v>1200</v>
+        <v>1186</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>1201</v>
+        <v>1187</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="E248" t="s">
-        <v>1648</v>
+        <v>1634</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>1202</v>
+        <v>1188</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1203</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B249" t="s">
-        <v>1204</v>
+        <v>1190</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1205</v>
+        <v>1191</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1206</v>
+        <v>1192</v>
       </c>
       <c r="E249" t="s">
-        <v>1649</v>
+        <v>1635</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1207</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B250" t="s">
-        <v>1208</v>
+        <v>1194</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1209</v>
+        <v>1195</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1210</v>
+        <v>1196</v>
       </c>
       <c r="E250" t="s">
-        <v>1650</v>
+        <v>1636</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1211</v>
+        <v>1197</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1212</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B251" t="s">
-        <v>1213</v>
+        <v>1199</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1214</v>
+        <v>1200</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>1215</v>
+        <v>1201</v>
       </c>
       <c r="E251" t="s">
-        <v>1651</v>
+        <v>1637</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>1216</v>
+        <v>1202</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1217</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B252" t="s">
-        <v>1218</v>
+        <v>1204</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>1219</v>
+        <v>1205</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>1220</v>
+        <v>1206</v>
       </c>
       <c r="E252" t="s">
-        <v>1652</v>
+        <v>1638</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1221</v>
+        <v>1207</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1222</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1426</v>
+        <v>1412</v>
       </c>
       <c r="B253" t="s">
-        <v>1223</v>
+        <v>1209</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>1224</v>
+        <v>1210</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1225</v>
+        <v>1211</v>
       </c>
       <c r="E253" t="s">
-        <v>1653</v>
+        <v>1639</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>1226</v>
+        <v>1212</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1227</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1426</v>
+        <v>1412</v>
       </c>
       <c r="B254" t="s">
-        <v>1228</v>
+        <v>1214</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>1229</v>
+        <v>1215</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1230</v>
+        <v>1216</v>
       </c>
       <c r="E254" t="s">
-        <v>1654</v>
+        <v>1640</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>1231</v>
+        <v>1217</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1232</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1426</v>
+        <v>1412</v>
       </c>
       <c r="B255" t="s">
-        <v>1233</v>
+        <v>1219</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>1234</v>
+        <v>1220</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>1235</v>
+        <v>1221</v>
       </c>
       <c r="E255" t="s">
-        <v>1655</v>
+        <v>1641</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1236</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1427</v>
+        <v>1413</v>
       </c>
       <c r="B256" t="s">
-        <v>1237</v>
+        <v>1223</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1238</v>
+        <v>1224</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E256" t="s">
-        <v>1656</v>
+        <v>1642</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>1239</v>
+        <v>1225</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>1240</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
       <c r="B257" t="s">
-        <v>1241</v>
+        <v>1227</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1242</v>
+        <v>1228</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1243</v>
+        <v>1229</v>
       </c>
       <c r="E257" t="s">
-        <v>1657</v>
+        <v>1643</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>1121</v>
+        <v>1107</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1244</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
       <c r="B258" t="s">
-        <v>1245</v>
+        <v>1231</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>1246</v>
+        <v>1232</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>1247</v>
+        <v>1233</v>
       </c>
       <c r="E258" t="s">
-        <v>1658</v>
+        <v>1644</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>1248</v>
+        <v>1234</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>1249</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
       <c r="B259" t="s">
-        <v>1250</v>
+        <v>1236</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1251</v>
+        <v>1237</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>1252</v>
+        <v>1238</v>
       </c>
       <c r="E259" t="s">
-        <v>1659</v>
+        <v>1645</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>1253</v>
+        <v>1239</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>1254</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
       <c r="B260" t="s">
-        <v>1255</v>
+        <v>1241</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1256</v>
+        <v>1242</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1257</v>
+        <v>1243</v>
       </c>
       <c r="E260" t="s">
-        <v>1660</v>
+        <v>1646</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>1258</v>
+        <v>1244</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1259</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
       <c r="B261" t="s">
-        <v>1260</v>
+        <v>1246</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>1261</v>
+        <v>1247</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1262</v>
+        <v>1248</v>
       </c>
       <c r="E261" t="s">
-        <v>1661</v>
+        <v>1647</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>1263</v>
+        <v>1249</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1264</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
       <c r="B262" t="s">
-        <v>1265</v>
+        <v>1251</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>1266</v>
+        <v>1252</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>1267</v>
+        <v>1253</v>
       </c>
       <c r="E262" t="s">
-        <v>1662</v>
+        <v>1648</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>1268</v>
+        <v>1254</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>1269</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
       <c r="B263" t="s">
-        <v>1270</v>
+        <v>1256</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>1271</v>
+        <v>1257</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1272</v>
+        <v>1258</v>
       </c>
       <c r="E263" t="s">
-        <v>1663</v>
+        <v>1649</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>1273</v>
+        <v>1259</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>1274</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
       <c r="B264" t="s">
-        <v>1275</v>
+        <v>1261</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>1276</v>
+        <v>1262</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1277</v>
+        <v>1263</v>
       </c>
       <c r="E264" t="s">
-        <v>1664</v>
+        <v>1650</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>1278</v>
+        <v>1264</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1279</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1430</v>
+        <v>1416</v>
       </c>
       <c r="B265" t="s">
-        <v>1281</v>
+        <v>1267</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1282</v>
+        <v>1268</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1283</v>
+        <v>1269</v>
       </c>
       <c r="E265" t="s">
-        <v>1665</v>
+        <v>1651</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>1284</v>
+        <v>1270</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1285</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B266" t="s">
-        <v>1286</v>
+        <v>1272</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>1432</v>
+        <v>1418</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>1287</v>
+        <v>1273</v>
       </c>
       <c r="E266" t="s">
-        <v>1682</v>
+        <v>1668</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>1288</v>
+        <v>1274</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1433</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B267" t="s">
-        <v>1289</v>
+        <v>1275</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>1290</v>
+        <v>1276</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1291</v>
+        <v>1277</v>
       </c>
       <c r="E267" t="s">
-        <v>1683</v>
+        <v>1669</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1292</v>
+        <v>1278</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1293</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B268" t="s">
-        <v>1294</v>
+        <v>1280</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1295</v>
+        <v>1281</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1263</v>
+        <v>1249</v>
       </c>
       <c r="E268" t="s">
-        <v>1666</v>
+        <v>1652</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1296</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1429</v>
+        <v>1415</v>
       </c>
       <c r="B269" t="s">
-        <v>1297</v>
+        <v>1283</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>1298</v>
+        <v>1284</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1299</v>
+        <v>1285</v>
       </c>
       <c r="E269" t="s">
-        <v>1551</v>
+        <v>1537</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>1300</v>
+        <v>1286</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1301</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B270" t="s">
-        <v>1302</v>
+        <v>1288</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>1303</v>
+        <v>1289</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1304</v>
+        <v>1290</v>
       </c>
       <c r="E270" t="s">
-        <v>1667</v>
+        <v>1653</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>1305</v>
+        <v>1291</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1306</v>
+        <v>1292</v>
       </c>
       <c r="L270" t="s">
-        <v>1415</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1430</v>
+        <v>1416</v>
       </c>
       <c r="B271" t="s">
-        <v>1307</v>
+        <v>1293</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>1308</v>
+        <v>1294</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1309</v>
+        <v>1295</v>
       </c>
       <c r="E271" t="s">
-        <v>1668</v>
+        <v>1654</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>1310</v>
+        <v>1296</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1311</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1430</v>
+        <v>1416</v>
       </c>
       <c r="B272" t="s">
-        <v>1312</v>
+        <v>1298</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>1313</v>
+        <v>1299</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1314</v>
+        <v>1300</v>
       </c>
       <c r="E272" t="s">
-        <v>1669</v>
+        <v>1655</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>1315</v>
+        <v>1301</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1316</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B273" t="s">
-        <v>1317</v>
+        <v>1303</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>1318</v>
+        <v>1304</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>1319</v>
+        <v>1305</v>
       </c>
       <c r="E273" t="s">
-        <v>1670</v>
+        <v>1656</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1320</v>
+        <v>1306</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1321</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B274" t="s">
-        <v>1322</v>
+        <v>1308</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>1323</v>
+        <v>1309</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1324</v>
+        <v>1310</v>
       </c>
       <c r="E274" t="s">
-        <v>1671</v>
+        <v>1657</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>1325</v>
+        <v>1311</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1326</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B275" t="s">
-        <v>1327</v>
+        <v>1313</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>1328</v>
+        <v>1314</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>1329</v>
+        <v>1315</v>
       </c>
       <c r="E275" t="s">
-        <v>1518</v>
+        <v>1504</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>1330</v>
+        <v>1316</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1331</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>1421</v>
+        <v>1407</v>
       </c>
       <c r="B276" t="s">
-        <v>1332</v>
+        <v>1318</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1333</v>
+        <v>1319</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1334</v>
+        <v>1320</v>
       </c>
       <c r="E276" t="s">
-        <v>1616</v>
+        <v>1602</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>1335</v>
+        <v>1321</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1336</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
-        <v>1337</v>
+        <v>1323</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>1338</v>
+        <v>1324</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>1339</v>
+        <v>1325</v>
       </c>
       <c r="E277" t="s">
-        <v>1672</v>
+        <v>1658</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>1280</v>
+        <v>1266</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1340</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B278" t="s">
-        <v>1341</v>
+        <v>1327</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>1342</v>
+        <v>1328</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>1343</v>
+        <v>1329</v>
       </c>
       <c r="E278" t="s">
-        <v>1510</v>
+        <v>1496</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>1344</v>
+        <v>1330</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1345</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B279" t="s">
-        <v>1346</v>
+        <v>1332</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1347</v>
+        <v>1333</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1348</v>
+        <v>1334</v>
       </c>
       <c r="E279" t="s">
-        <v>1510</v>
+        <v>1496</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>1349</v>
+        <v>1335</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1350</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B280" t="s">
-        <v>1351</v>
+        <v>1337</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>1352</v>
+        <v>1338</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>1353</v>
+        <v>1339</v>
       </c>
       <c r="E280" t="s">
-        <v>1673</v>
+        <v>1659</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>1354</v>
+        <v>1340</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>1355</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B281" t="s">
-        <v>1356</v>
+        <v>1342</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>1357</v>
+        <v>1343</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>1358</v>
+        <v>1344</v>
       </c>
       <c r="E281" t="s">
-        <v>1523</v>
+        <v>1509</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>1359</v>
+        <v>1345</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1360</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B282" t="s">
-        <v>1361</v>
+        <v>1347</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>1362</v>
+        <v>1348</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>1363</v>
+        <v>1349</v>
       </c>
       <c r="E282" t="s">
-        <v>1508</v>
+        <v>1494</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>1364</v>
+        <v>1350</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1365</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="B283" t="s">
-        <v>1366</v>
+        <v>1352</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>1367</v>
+        <v>1353</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>1368</v>
+        <v>1354</v>
       </c>
       <c r="E283" t="s">
-        <v>1546</v>
+        <v>1532</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>1369</v>
+        <v>1355</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1370</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>1428</v>
+        <v>1414</v>
       </c>
       <c r="B284" t="s">
-        <v>1371</v>
+        <v>1357</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>1372</v>
+        <v>1358</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>1373</v>
+        <v>1359</v>
       </c>
       <c r="E284" t="s">
-        <v>1674</v>
+        <v>1660</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>1374</v>
+        <v>1360</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1375</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
       <c r="B285" t="s">
-        <v>1376</v>
+        <v>1362</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>1377</v>
+        <v>1363</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>1378</v>
+        <v>1364</v>
       </c>
       <c r="E285" t="s">
-        <v>1675</v>
+        <v>1661</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>155</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1379</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B286" t="s">
-        <v>1380</v>
+        <v>1366</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>1381</v>
+        <v>1367</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>1382</v>
+        <v>1368</v>
       </c>
       <c r="E286" t="s">
-        <v>1676</v>
+        <v>1662</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>1383</v>
+        <v>1369</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1384</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1429</v>
+        <v>1415</v>
       </c>
       <c r="B287" t="s">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1386</v>
+        <v>1372</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1387</v>
+        <v>1373</v>
       </c>
       <c r="E287" t="s">
-        <v>1677</v>
+        <v>1663</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>1388</v>
+        <v>1374</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1389</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1423</v>
+        <v>1409</v>
       </c>
       <c r="B288" t="s">
-        <v>1134</v>
+        <v>1120</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>1390</v>
+        <v>1376</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1135</v>
+        <v>1121</v>
       </c>
       <c r="E288" t="s">
-        <v>1678</v>
+        <v>1664</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>1391</v>
+        <v>1377</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1392</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="289" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1424</v>
+        <v>1410</v>
       </c>
       <c r="B289" t="s">
-        <v>1393</v>
+        <v>1379</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>1394</v>
+        <v>1380</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1395</v>
+        <v>1381</v>
       </c>
       <c r="E289" t="s">
-        <v>1530</v>
+        <v>1516</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>1396</v>
+        <v>1382</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1397</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="B290" t="s">
-        <v>1398</v>
+        <v>1384</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>1399</v>
+        <v>1385</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>1400</v>
+        <v>1386</v>
       </c>
       <c r="E290" t="s">
-        <v>1679</v>
+        <v>1665</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>1401</v>
+        <v>1387</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1402</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1422</v>
+        <v>1408</v>
       </c>
       <c r="B291" t="s">
-        <v>1403</v>
+        <v>1389</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>1405</v>
+        <v>1391</v>
       </c>
       <c r="E291" t="s">
-        <v>1551</v>
+        <v>1537</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>1406</v>
+        <v>1392</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>1407</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1426</v>
+        <v>1412</v>
       </c>
       <c r="B292" t="s">
-        <v>1228</v>
+        <v>1214</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>1408</v>
+        <v>1394</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>1409</v>
+        <v>1395</v>
       </c>
       <c r="E292" t="s">
-        <v>1680</v>
+        <v>1666</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>1410</v>
+        <v>1396</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1411</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1429</v>
+        <v>1415</v>
       </c>
       <c r="B293" t="s">
-        <v>1412</v>
+        <v>1398</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>1413</v>
+        <v>1399</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>1045</v>
+        <v>1031</v>
       </c>
       <c r="E293" t="s">
-        <v>1622</v>
+        <v>1608</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>1414</v>
+        <v>1400</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1431</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B294" t="s">
-        <v>1165</v>
+        <v>1151</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>1166</v>
+        <v>1152</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>1167</v>
+        <v>1153</v>
       </c>
       <c r="E294" t="s">
-        <v>1642</v>
+        <v>1628</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>1168</v>
+        <v>1154</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>1169</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B295" t="s">
-        <v>1170</v>
+        <v>1156</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>1171</v>
+        <v>1157</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>1172</v>
+        <v>1158</v>
       </c>
       <c r="E295" t="s">
-        <v>1512</v>
+        <v>1498</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>1173</v>
+        <v>1159</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>1174</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B296" t="s">
-        <v>1175</v>
+        <v>1161</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>1176</v>
+        <v>1162</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>1177</v>
+        <v>1163</v>
       </c>
       <c r="E296" t="s">
-        <v>1666</v>
+        <v>1652</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>1178</v>
+        <v>1164</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>1179</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>1425</v>
+        <v>1411</v>
       </c>
       <c r="B297" t="s">
-        <v>1180</v>
+        <v>1166</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>1181</v>
+        <v>1167</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>1182</v>
+        <v>1168</v>
       </c>
       <c r="E297" t="s">
-        <v>1681</v>
+        <v>1667</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>1183</v>
+        <v>1169</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>1184</v>
+        <v>1170</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Daily_Word.xlsx
+++ b/public/data/Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51090AB6-A816-4ADD-AE35-FE2E358CE4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D156AF-43B0-4077-A022-687AB54C0BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="1722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="1725">
   <si>
     <t>Topic</t>
   </si>
@@ -147,9 +147,6 @@
   </si>
   <si>
     <t>ריבוי</t>
-  </si>
-  <si>
-    <t>רִיבָּה מזכיר את ריבוי הדגים בים.</t>
   </si>
   <si>
     <t>яйцо</t>
@@ -4172,9 +4169,6 @@
     <t>Run</t>
   </si>
   <si>
-    <t>אם אתה רוצה ל-run, אתה צריך לקום רָנָה</t>
-  </si>
-  <si>
     <t>Поздно</t>
   </si>
   <si>
@@ -4354,39 +4348,10 @@
     <t>мечта</t>
   </si>
   <si>
-    <t>מֵצִ'טָה</t>
-  </si>
-  <si>
     <t>חלום</t>
   </si>
   <si>
     <t>משתלה</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ה-מֵצִ'טָה שלי הוא לפתוח </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>משתלה</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ענקית של פרחים נדירים</t>
-    </r>
   </si>
   <si>
     <t>тень</t>
@@ -5451,12 +5416,56 @@
   <si>
     <t>הסלט יצא ממש גרוס - זה עושה אותי גרוּסְנָה!</t>
   </si>
+  <si>
+    <t xml:space="preserve">יש הרבה דגים בים! </t>
+  </si>
+  <si>
+    <t>עושים</t>
+  </si>
+  <si>
+    <t>אנחנו במשפחה עושים כל אוֹסֵן טיולים להסתכל על השלכת</t>
+  </si>
+  <si>
+    <t>אין כמו לשתות קפה לאטה חם ולהתחמם כאילו עכשיו לֵטַה</t>
+  </si>
+  <si>
+    <t>מֵצְ'טָה</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ה-מֵצְ'טָה שלי הוא לפתוח </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>משתלה</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ענקית של פרחים נדירים</t>
+    </r>
+  </si>
+  <si>
+    <t>צריך לקום רָנָה אם אתה רוצה to run</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5482,6 +5491,13 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5519,7 +5535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -5529,6 +5545,16 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5848,27 +5874,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -5880,7 +5906,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
@@ -5891,7 +5917,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -5903,7 +5929,7 @@
         <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>24</v>
@@ -5914,7 +5940,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -5926,18 +5952,18 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -5949,18 +5975,18 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1698</v>
+        <v>1694</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1699</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -5972,6542 +5998,6542 @@
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>37</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>1431</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>1688</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>1693</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>1432</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>1689</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1690</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>1434</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1701</v>
+        <v>1697</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1700</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>1694</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>1436</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="G12" s="1" t="s">
-        <v>1695</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1697</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>1438</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>1439</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>1440</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>1441</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>1442</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>1443</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>1444</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>1445</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>1683</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>1462</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>1691</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>1446</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>1447</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>1448</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>1449</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>1446</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>1450</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B29" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>1451</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>1452</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>1453</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>1454</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B33" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="G33" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B34" t="s">
+        <v>157</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>1456</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B35" t="s">
+        <v>162</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>1457</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B36" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B37" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>1459</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="G37" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B38" t="s">
+        <v>176</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B39" t="s">
+        <v>180</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F39" s="2" t="s">
+      <c r="G39" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B40" t="s">
+        <v>185</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>1463</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="G40" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B41" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>1464</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="G41" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B42" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>1465</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="G42" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B43" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>1466</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="G43" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B44" t="s">
+        <v>205</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>1467</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B45" t="s">
+        <v>210</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>1671</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="G45" s="1" t="s">
-        <v>1681</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B46" t="s">
+        <v>214</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>1468</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="G46" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B47" t="s">
+        <v>219</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>1672</v>
-      </c>
-      <c r="F47" s="2" t="s">
+      <c r="G47" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B48" t="s">
+        <v>224</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>1469</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="G48" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B49" t="s">
+        <v>229</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>1470</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="G49" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B50" t="s">
+        <v>234</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>1471</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="G50" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B51" t="s">
+        <v>239</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>1472</v>
-      </c>
-      <c r="F51" s="2" t="s">
+      <c r="G51" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B52" t="s">
+        <v>244</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>1473</v>
-      </c>
-      <c r="F52" s="2" t="s">
+      <c r="G52" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B53" t="s">
+        <v>249</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="E53" s="2" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1684</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B54" t="s">
+        <v>252</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>1686</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B55" t="s">
+        <v>256</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>1480</v>
-      </c>
-      <c r="F55" s="2" t="s">
+      <c r="G55" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B56" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F56" s="2" t="s">
+      <c r="G56" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B57" t="s">
+        <v>266</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>1475</v>
-      </c>
-      <c r="F57" s="2" t="s">
+      <c r="G57" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B58" t="s">
+        <v>271</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>1476</v>
-      </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B59" t="s">
+        <v>276</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>1477</v>
-      </c>
-      <c r="F59" s="2" t="s">
+      <c r="G59" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B60" t="s">
+        <v>281</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B61" t="s">
+        <v>286</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>1481</v>
-      </c>
-      <c r="F61" s="2" t="s">
+      <c r="G61" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B62" t="s">
+        <v>291</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>1482</v>
-      </c>
-      <c r="F62" s="2" t="s">
+      <c r="G62" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B63" t="s">
+        <v>296</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>1502</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>1482</v>
-      </c>
-      <c r="F63" s="2" t="s">
+      <c r="G63" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B64" t="s">
+        <v>300</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E64" s="2" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B65" t="s">
+        <v>304</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>1484</v>
-      </c>
-      <c r="F65" s="2" t="s">
+      <c r="G65" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B66" t="s">
+        <v>309</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="E66" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>1503</v>
-      </c>
-      <c r="F66" s="2" t="s">
+      <c r="G66" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B67" t="s">
+        <v>314</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>1485</v>
-      </c>
-      <c r="F67" s="2" t="s">
+      <c r="G67" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B68" t="s">
+        <v>319</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>1478</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>323</v>
-      </c>
       <c r="G68" s="1" t="s">
-        <v>1687</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B69" t="s">
+        <v>323</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="E69" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>1477</v>
-      </c>
-      <c r="F69" s="2" t="s">
+      <c r="G69" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B70" t="s">
+        <v>328</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="E70" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>1486</v>
-      </c>
-      <c r="F70" s="2" t="s">
+      <c r="G70" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B71" t="s">
+        <v>333</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>1673</v>
-      </c>
-      <c r="F71" s="2" t="s">
+      <c r="G71" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B72" t="s">
+        <v>338</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="E72" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F72" s="2" t="s">
+      <c r="G72" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B73" t="s">
+        <v>343</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>1488</v>
-      </c>
-      <c r="F73" s="2" t="s">
+      <c r="G73" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B74" t="s">
+        <v>348</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F74" s="2" t="s">
+      <c r="G74" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B75" t="s">
+        <v>353</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="G75" s="1" t="s">
-        <v>1702</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B76" t="s">
+        <v>357</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="E76" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>1491</v>
-      </c>
-      <c r="F76" s="2" t="s">
+      <c r="G76" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B77" t="s">
+        <v>362</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>1492</v>
-      </c>
-      <c r="F77" s="2" t="s">
+      <c r="G77" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B78" t="s">
+        <v>367</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="E78" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>1476</v>
-      </c>
-      <c r="F78" s="2" t="s">
+      <c r="G78" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B79" t="s">
+        <v>372</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>1703</v>
-      </c>
-      <c r="D79" s="1" t="s">
+      <c r="E79" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>1493</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="G79" s="1" t="s">
-        <v>1704</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B80" t="s">
+        <v>375</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="E80" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F80" s="2" t="s">
+      <c r="G80" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B81" t="s">
+        <v>380</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="E81" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="G81" s="1" t="s">
-        <v>1705</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B82" t="s">
+        <v>384</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="E82" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F82" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F82" s="2" t="s">
+      <c r="G82" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B83" t="s">
+        <v>389</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>1477</v>
-      </c>
-      <c r="F83" s="2" t="s">
+      <c r="G83" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B84" t="s">
+        <v>394</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E84" s="2" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B85" t="s">
+        <v>398</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>1497</v>
-      </c>
-      <c r="F85" s="2" t="s">
+      <c r="G85" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B86" t="s">
+        <v>403</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="E86" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>1498</v>
-      </c>
-      <c r="F86" s="2" t="s">
+      <c r="G86" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B87" t="s">
+        <v>408</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="E87" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F87" s="2" t="s">
+      <c r="G87" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B88" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="2" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>1674</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="G88" s="1" t="s">
-        <v>1706</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B89" t="s">
+        <v>417</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="E89" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F89" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>1675</v>
-      </c>
-      <c r="F89" s="2" t="s">
+      <c r="G89" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B90" t="s">
+        <v>422</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="E90" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>1501</v>
-      </c>
-      <c r="F90" s="2" t="s">
+      <c r="G90" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B91" t="s">
+        <v>427</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="E91" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>1501</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="G91" s="1" t="s">
-        <v>1707</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B92" t="s">
+        <v>431</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="D92" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="E92" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>1501</v>
-      </c>
-      <c r="F92" s="2" t="s">
+      <c r="G92" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B93" t="s">
+        <v>436</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="E93" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F93" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="E93" t="s">
-        <v>1505</v>
-      </c>
-      <c r="F93" s="2" t="s">
+      <c r="G93" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B94" t="s">
+        <v>441</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="E94" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="E94" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F94" s="2" t="s">
+      <c r="G94" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B95" t="s">
+        <v>446</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="E95" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F95" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="E95" t="s">
-        <v>1506</v>
-      </c>
-      <c r="F95" s="2" t="s">
+      <c r="G95" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B96" t="s">
+        <v>451</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="E96" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="E96" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F96" s="2" t="s">
+      <c r="G96" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B97" t="s">
+        <v>456</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="D97" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="E97" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F97" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="E97" t="s">
-        <v>1508</v>
-      </c>
-      <c r="F97" s="2" t="s">
+      <c r="G97" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B98" t="s">
+        <v>461</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="E98" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="E98" t="s">
-        <v>1509</v>
-      </c>
-      <c r="F98" s="2" t="s">
+      <c r="G98" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B99" t="s">
+        <v>466</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="E99" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="E99" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F99" s="2" t="s">
+      <c r="G99" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B100" t="s">
+        <v>503</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="D100" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="E100" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="E100" t="s">
-        <v>1518</v>
-      </c>
-      <c r="F100" s="2" t="s">
+      <c r="G100" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B101" t="s">
+        <v>471</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="D101" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="E101" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="E101" t="s">
-        <v>1511</v>
-      </c>
-      <c r="F101" s="2" t="s">
+      <c r="G101" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B102" t="s">
+        <v>476</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="E102" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="E102" t="s">
-        <v>1512</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>480</v>
-      </c>
       <c r="G102" s="1" t="s">
-        <v>1708</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B103" t="s">
+        <v>480</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="E103" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="E103" t="s">
-        <v>1513</v>
-      </c>
-      <c r="F103" s="2" t="s">
+      <c r="G103" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B104" t="s">
+        <v>485</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="D104" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="E104" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="E104" t="s">
-        <v>1514</v>
-      </c>
-      <c r="F104" s="2" t="s">
+      <c r="G104" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B105" t="s">
+        <v>490</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="D105" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="E105" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="E105" t="s">
-        <v>1515</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>494</v>
-      </c>
       <c r="G105" s="1" t="s">
-        <v>1709</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B106" t="s">
+        <v>494</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="D106" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="E106" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="E106" t="s">
-        <v>1516</v>
-      </c>
-      <c r="F106" s="2" t="s">
+      <c r="G106" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B107" t="s">
+        <v>499</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="D107" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="E107" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="E107" t="s">
-        <v>1517</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>503</v>
-      </c>
       <c r="G107" s="1" t="s">
-        <v>1710</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B108" t="s">
+        <v>508</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="E108" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="G108" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="E108" t="s">
-        <v>1519</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>1711</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B109" t="s">
+        <v>512</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="E109" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="E109" t="s">
-        <v>1520</v>
-      </c>
-      <c r="F109" s="2" t="s">
+      <c r="G109" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B110" t="s">
+        <v>517</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="D110" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>520</v>
-      </c>
       <c r="E110" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B111" t="s">
+        <v>521</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="D111" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="E111" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F111" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="E111" t="s">
-        <v>1522</v>
-      </c>
-      <c r="F111" s="2" t="s">
+      <c r="G111" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B112" t="s">
+        <v>526</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="E112" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F112" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="E112" t="s">
-        <v>1523</v>
-      </c>
-      <c r="F112" s="2" t="s">
+      <c r="G112" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B113" t="s">
+        <v>531</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="D113" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="E113" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="E113" t="s">
-        <v>1524</v>
-      </c>
-      <c r="F113" s="2" t="s">
+      <c r="G113" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B114" t="s">
+        <v>536</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>539</v>
-      </c>
       <c r="E114" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B115" t="s">
+        <v>540</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="D115" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="E115" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1712</v>
+        <v>1708</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B116" t="s">
+        <v>543</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="D116" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="E116" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="E116" t="s">
-        <v>1527</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B117" t="s">
+        <v>547</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="D117" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="E117" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="E117" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F117" s="2" t="s">
+      <c r="G117" s="1" t="s">
         <v>551</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B118" t="s">
+        <v>552</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="D118" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="E118" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F118" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="E118" t="s">
-        <v>1528</v>
-      </c>
-      <c r="F118" s="2" t="s">
+      <c r="G118" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B119" t="s">
+        <v>557</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="D119" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="D119" s="1" t="s">
-        <v>560</v>
-      </c>
       <c r="E119" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B120" t="s">
+        <v>561</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="D120" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="E120" t="s">
+        <v>1526</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="E120" t="s">
-        <v>1530</v>
-      </c>
-      <c r="F120" s="2" t="s">
+      <c r="G120" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B121" t="s">
+        <v>566</v>
+      </c>
+      <c r="C121" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="D121" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="E121" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F121" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="E121" t="s">
-        <v>1531</v>
-      </c>
-      <c r="F121" s="2" t="s">
+      <c r="G121" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B122" t="s">
+        <v>571</v>
+      </c>
+      <c r="C122" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="D122" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="E122" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="E122" t="s">
-        <v>1532</v>
-      </c>
-      <c r="F122" s="2" t="s">
+      <c r="G122" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B123" t="s">
+        <v>576</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="D123" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="E123" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="E123" t="s">
-        <v>1533</v>
-      </c>
-      <c r="F123" s="2" t="s">
+      <c r="G123" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B124" t="s">
+        <v>581</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="D124" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="E124" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B125" t="s">
+        <v>585</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="D125" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="E125" t="s">
+        <v>1531</v>
+      </c>
+      <c r="F125" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="E125" t="s">
-        <v>1535</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>589</v>
-      </c>
       <c r="G125" s="1" t="s">
-        <v>1714</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B126" t="s">
+        <v>589</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="E126" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="E126" t="s">
-        <v>1476</v>
-      </c>
-      <c r="F126" s="2" t="s">
+      <c r="G126" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B127" t="s">
+        <v>594</v>
+      </c>
+      <c r="C127" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="D127" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="E127" t="s">
+        <v>1532</v>
+      </c>
+      <c r="F127" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="E127" t="s">
-        <v>1536</v>
-      </c>
-      <c r="F127" s="2" t="s">
+      <c r="G127" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B128" t="s">
+        <v>599</v>
+      </c>
+      <c r="C128" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="E128" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="E128" t="s">
-        <v>1537</v>
-      </c>
-      <c r="F128" s="2" t="s">
+      <c r="G128" s="1" t="s">
         <v>603</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B129" t="s">
+        <v>604</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="D129" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="E129" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F129" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="E129" t="s">
-        <v>1512</v>
-      </c>
-      <c r="F129" s="2" t="s">
+      <c r="G129" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B130" t="s">
+        <v>609</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="D130" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="E130" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="E130" t="s">
-        <v>1679</v>
-      </c>
-      <c r="F130" s="2" t="s">
+      <c r="G130" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B131" t="s">
+        <v>614</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="D131" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="E131" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="G131" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="E131" t="s">
-        <v>1680</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B132" t="s">
+        <v>618</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="D132" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="E132" t="s">
+        <v>1534</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="E132" t="s">
-        <v>1538</v>
-      </c>
-      <c r="F132" s="2" t="s">
+      <c r="G132" s="1" t="s">
         <v>622</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B133" t="s">
+        <v>623</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="D133" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="E133" t="s">
+        <v>1535</v>
+      </c>
+      <c r="F133" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="E133" t="s">
-        <v>1539</v>
-      </c>
-      <c r="F133" s="2" t="s">
+      <c r="G133" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B134" t="s">
+        <v>628</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="D134" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="E134" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="E134" t="s">
-        <v>1537</v>
-      </c>
-      <c r="F134" s="2" t="s">
+      <c r="G134" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B135" t="s">
+        <v>633</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="D135" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="E135" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F135" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="E135" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F135" s="2" t="s">
+      <c r="G135" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B136" t="s">
+        <v>638</v>
+      </c>
+      <c r="C136" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="D136" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="E136" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="E136" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F136" s="2" t="s">
+      <c r="G136" s="1" t="s">
         <v>642</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B137" t="s">
+        <v>643</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="D137" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="E137" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="E137" t="s">
-        <v>1541</v>
-      </c>
-      <c r="F137" s="2" t="s">
+      <c r="G137" s="1" t="s">
         <v>647</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B138" t="s">
+        <v>648</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="D138" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="E138" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F138" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="E138" t="s">
-        <v>1517</v>
-      </c>
-      <c r="F138" s="2" t="s">
+      <c r="G138" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B139" t="s">
+        <v>653</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="D139" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="E139" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F139" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="E139" t="s">
-        <v>1542</v>
-      </c>
-      <c r="F139" s="2" t="s">
+      <c r="G139" s="1" t="s">
         <v>657</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B140" t="s">
+        <v>658</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="E140" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="E140" t="s">
-        <v>1543</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>662</v>
-      </c>
       <c r="G140" s="1" t="s">
-        <v>1715</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B141" t="s">
+        <v>662</v>
+      </c>
+      <c r="C141" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="D141" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F141" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="E141" t="s">
-        <v>1544</v>
-      </c>
-      <c r="F141" s="2" t="s">
+      <c r="G141" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B142" t="s">
+        <v>667</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="D142" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="E142" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F142" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="E142" t="s">
-        <v>1506</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>671</v>
-      </c>
       <c r="G142" s="1" t="s">
-        <v>1716</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B143" t="s">
+        <v>671</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="D143" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="E143" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F143" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="E143" t="s">
-        <v>1545</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>675</v>
-      </c>
       <c r="G143" s="1" t="s">
-        <v>1717</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B144" t="s">
+        <v>675</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="D144" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="E144" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F144" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="E144" t="s">
-        <v>1546</v>
-      </c>
-      <c r="F144" s="2" t="s">
+      <c r="G144" s="1" t="s">
         <v>679</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B145" t="s">
+        <v>680</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="D145" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="E145" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F145" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="E145" t="s">
-        <v>1547</v>
-      </c>
-      <c r="F145" s="2" t="s">
+      <c r="G145" s="1" t="s">
         <v>684</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B146" t="s">
+        <v>685</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="D146" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="E146" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="E146" t="s">
-        <v>1548</v>
-      </c>
-      <c r="F146" s="2" t="s">
+      <c r="G146" s="1" t="s">
         <v>689</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B147" t="s">
+        <v>690</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="D147" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="E147" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F147" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="E147" t="s">
-        <v>1549</v>
-      </c>
-      <c r="F147" s="2" t="s">
+      <c r="G147" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B148" t="s">
+        <v>695</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="D148" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="D148" s="1" t="s">
-        <v>698</v>
-      </c>
       <c r="E148" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>1718</v>
+        <v>1714</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1719</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B149" t="s">
+        <v>698</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="D149" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E149" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F149" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E149" t="s">
-        <v>1550</v>
-      </c>
-      <c r="F149" s="2" t="s">
+      <c r="G149" s="1" t="s">
         <v>701</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B150" t="s">
+        <v>702</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="D150" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="D150" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="E150" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B151" t="s">
+        <v>706</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="D151" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="E151" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F151" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="E151" t="s">
-        <v>1550</v>
-      </c>
-      <c r="F151" s="2" t="s">
+      <c r="G151" s="1" t="s">
         <v>710</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B152" t="s">
+        <v>711</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="D152" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="E152" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F152" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="E152" t="s">
-        <v>1676</v>
-      </c>
-      <c r="F152" s="2" t="s">
+      <c r="G152" s="1" t="s">
         <v>715</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B153" t="s">
+        <v>716</v>
+      </c>
+      <c r="C153" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="C153" s="1" t="s">
+      <c r="D153" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="D153" s="1" t="s">
+      <c r="E153" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="E153" t="s">
-        <v>1677</v>
-      </c>
-      <c r="F153" s="2" t="s">
+      <c r="G153" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B154" t="s">
+        <v>721</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="D154" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="E154" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="E154" t="s">
-        <v>1551</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>725</v>
-      </c>
       <c r="G154" s="1" t="s">
-        <v>1720</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B155" t="s">
+        <v>725</v>
+      </c>
+      <c r="C155" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="D155" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="E155" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="E155" t="s">
-        <v>1552</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>729</v>
-      </c>
       <c r="G155" s="1" t="s">
-        <v>1721</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B156" t="s">
+        <v>729</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="D156" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="E156" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="E156" t="s">
-        <v>1553</v>
-      </c>
-      <c r="F156" s="2" t="s">
+      <c r="G156" s="1" t="s">
         <v>733</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B157" t="s">
+        <v>734</v>
+      </c>
+      <c r="C157" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="D157" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="E157" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F157" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="E157" t="s">
-        <v>1554</v>
-      </c>
-      <c r="F157" s="2" t="s">
+      <c r="G157" s="1" t="s">
         <v>738</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B158" t="s">
+        <v>739</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="D158" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="E158" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="E158" t="s">
-        <v>1527</v>
-      </c>
-      <c r="F158" s="2" t="s">
+      <c r="G158" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B159" t="s">
+        <v>744</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="D159" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="D159" s="1" t="s">
+      <c r="E159" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F159" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="E159" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F159" s="2" t="s">
+      <c r="G159" s="1" t="s">
         <v>748</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B160" t="s">
+        <v>749</v>
+      </c>
+      <c r="C160" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="D160" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="E160" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F160" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="E160" t="s">
-        <v>1678</v>
-      </c>
-      <c r="F160" s="2" t="s">
+      <c r="G160" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B161" t="s">
+        <v>754</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="D161" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="E161" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F161" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="E161" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F161" s="2" t="s">
+      <c r="G161" s="1" t="s">
         <v>758</v>
-      </c>
-      <c r="G161" s="1" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B162" t="s">
+        <v>759</v>
+      </c>
+      <c r="C162" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="C162" s="1" t="s">
+      <c r="D162" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="E162" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="E162" t="s">
-        <v>1556</v>
-      </c>
-      <c r="F162" s="2" t="s">
+      <c r="G162" s="1" t="s">
         <v>763</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B163" t="s">
+        <v>764</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="C163" s="1" t="s">
+      <c r="D163" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="D163" s="1" t="s">
+      <c r="E163" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F163" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="E163" t="s">
-        <v>1557</v>
-      </c>
-      <c r="F163" s="2" t="s">
+      <c r="G163" s="1" t="s">
         <v>768</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B164" t="s">
+        <v>769</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="C164" s="1" t="s">
+      <c r="D164" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="E164" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F164" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="E164" t="s">
-        <v>1558</v>
-      </c>
-      <c r="F164" s="2" t="s">
+      <c r="G164" s="1" t="s">
         <v>773</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B165" t="s">
+        <v>774</v>
+      </c>
+      <c r="C165" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="D165" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="E165" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="E165" t="s">
-        <v>1559</v>
-      </c>
-      <c r="F165" s="2" t="s">
+      <c r="G165" s="1" t="s">
         <v>778</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B166" t="s">
+        <v>779</v>
+      </c>
+      <c r="C166" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="C166" s="1" t="s">
+      <c r="D166" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="D166" s="1" t="s">
+      <c r="E166" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F166" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="E166" t="s">
-        <v>1560</v>
-      </c>
-      <c r="F166" s="2" t="s">
+      <c r="G166" s="1" t="s">
         <v>783</v>
-      </c>
-      <c r="G166" s="1" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B167" t="s">
+        <v>784</v>
+      </c>
+      <c r="C167" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="C167" s="1" t="s">
+      <c r="D167" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="E167" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F167" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="E167" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F167" s="2" t="s">
+      <c r="G167" s="1" t="s">
         <v>788</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B168" t="s">
+        <v>789</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="D168" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="D168" s="1" t="s">
+      <c r="E168" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="E168" t="s">
-        <v>1562</v>
-      </c>
-      <c r="F168" s="2" t="s">
+      <c r="G168" s="1" t="s">
         <v>793</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B169" t="s">
+        <v>794</v>
+      </c>
+      <c r="C169" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="C169" s="1" t="s">
+      <c r="D169" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="E169" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F169" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="E169" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F169" s="2" t="s">
+      <c r="G169" s="1" t="s">
         <v>798</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B170" t="s">
+        <v>799</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="C170" s="1" t="s">
+      <c r="D170" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="D170" s="1" t="s">
+      <c r="E170" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F170" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="E170" t="s">
-        <v>1564</v>
-      </c>
-      <c r="F170" s="2" t="s">
+      <c r="G170" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B171" t="s">
+        <v>804</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="C171" s="1" t="s">
+      <c r="D171" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="D171" s="1" t="s">
+      <c r="E171" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F171" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="E171" t="s">
-        <v>1565</v>
-      </c>
-      <c r="F171" s="2" t="s">
+      <c r="G171" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B172" t="s">
+        <v>809</v>
+      </c>
+      <c r="C172" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="C172" s="1" t="s">
+      <c r="D172" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="D172" s="1" t="s">
+      <c r="E172" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F172" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="E172" t="s">
-        <v>1566</v>
-      </c>
-      <c r="F172" s="2" t="s">
+      <c r="G172" s="1" t="s">
         <v>813</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B173" t="s">
+        <v>814</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="C173" s="1" t="s">
+      <c r="D173" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="D173" s="1" t="s">
+      <c r="E173" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F173" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="E173" t="s">
-        <v>1567</v>
-      </c>
-      <c r="F173" s="2" t="s">
+      <c r="G173" s="1" t="s">
         <v>818</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B174" t="s">
+        <v>819</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="C174" s="1" t="s">
+      <c r="D174" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="D174" s="1" t="s">
+      <c r="E174" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="E174" t="s">
-        <v>1568</v>
-      </c>
-      <c r="F174" s="2" t="s">
+      <c r="G174" s="1" t="s">
         <v>823</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B175" t="s">
+        <v>824</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="C175" s="1" t="s">
+      <c r="D175" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="D175" s="1" t="s">
+      <c r="E175" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F175" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="E175" t="s">
-        <v>1569</v>
-      </c>
-      <c r="F175" s="2" t="s">
+      <c r="G175" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B176" t="s">
+        <v>829</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="C176" s="1" t="s">
+      <c r="D176" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="E176" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="E176" t="s">
-        <v>1570</v>
-      </c>
-      <c r="F176" s="2" t="s">
+      <c r="G176" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B177" t="s">
+        <v>834</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="C177" s="1" t="s">
+      <c r="D177" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="E177" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F177" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="E177" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F177" s="2" t="s">
+      <c r="G177" s="1" t="s">
         <v>838</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B178" t="s">
+        <v>839</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="C178" s="1" t="s">
+      <c r="D178" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="D178" s="1" t="s">
+      <c r="E178" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F178" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="E178" t="s">
-        <v>1572</v>
-      </c>
-      <c r="F178" s="2" t="s">
+      <c r="G178" s="1" t="s">
         <v>843</v>
-      </c>
-      <c r="G178" s="1" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B179" t="s">
+        <v>844</v>
+      </c>
+      <c r="C179" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="C179" s="1" t="s">
+      <c r="D179" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="D179" s="1" t="s">
+      <c r="E179" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F179" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="E179" t="s">
-        <v>1573</v>
-      </c>
-      <c r="F179" s="2" t="s">
+      <c r="G179" s="1" t="s">
         <v>848</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B180" t="s">
+        <v>849</v>
+      </c>
+      <c r="C180" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="D180" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="E180" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F180" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="E180" t="s">
-        <v>1574</v>
-      </c>
-      <c r="F180" s="2" t="s">
+      <c r="G180" s="1" t="s">
         <v>853</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B181" t="s">
+        <v>854</v>
+      </c>
+      <c r="C181" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="C181" s="1" t="s">
+      <c r="D181" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="D181" s="1" t="s">
+      <c r="E181" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F181" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E181" t="s">
-        <v>1575</v>
-      </c>
-      <c r="F181" s="2" t="s">
+      <c r="G181" s="1" t="s">
         <v>858</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B182" t="s">
+        <v>859</v>
+      </c>
+      <c r="C182" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="C182" s="1" t="s">
+      <c r="D182" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="D182" s="1" t="s">
+      <c r="E182" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="E182" t="s">
-        <v>1576</v>
-      </c>
-      <c r="F182" s="2" t="s">
+      <c r="G182" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B183" t="s">
+        <v>864</v>
+      </c>
+      <c r="C183" s="1" t="s">
         <v>865</v>
       </c>
-      <c r="C183" s="1" t="s">
+      <c r="D183" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="D183" s="1" t="s">
+      <c r="E183" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F183" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="E183" t="s">
-        <v>1577</v>
-      </c>
-      <c r="F183" s="2" t="s">
+      <c r="G183" s="1" t="s">
         <v>868</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B184" t="s">
+        <v>869</v>
+      </c>
+      <c r="C184" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="C184" s="1" t="s">
+      <c r="D184" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="E184" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F184" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="E184" t="s">
-        <v>1578</v>
-      </c>
-      <c r="F184" s="2" t="s">
+      <c r="G184" s="1" t="s">
         <v>873</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B185" t="s">
+        <v>874</v>
+      </c>
+      <c r="C185" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="C185" s="1" t="s">
+      <c r="D185" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="E185" t="s">
+        <v>1575</v>
+      </c>
+      <c r="F185" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="E185" t="s">
-        <v>1579</v>
-      </c>
-      <c r="F185" s="2" t="s">
+      <c r="G185" s="1" t="s">
         <v>878</v>
-      </c>
-      <c r="G185" s="1" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B186" t="s">
+        <v>879</v>
+      </c>
+      <c r="C186" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="C186" s="1" t="s">
+      <c r="D186" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="E186" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F186" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="E186" t="s">
-        <v>1580</v>
-      </c>
-      <c r="F186" s="2" t="s">
+      <c r="G186" s="1" t="s">
         <v>883</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B187" t="s">
+        <v>884</v>
+      </c>
+      <c r="C187" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="C187" s="1" t="s">
+      <c r="D187" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="D187" s="1" t="s">
+      <c r="E187" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F187" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="E187" t="s">
-        <v>1581</v>
-      </c>
-      <c r="F187" s="2" t="s">
+      <c r="G187" s="1" t="s">
         <v>888</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B188" t="s">
+        <v>889</v>
+      </c>
+      <c r="C188" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="C188" s="1" t="s">
+      <c r="D188" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="D188" s="1" t="s">
+      <c r="E188" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F188" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="E188" t="s">
-        <v>1582</v>
-      </c>
-      <c r="F188" s="2" t="s">
+      <c r="G188" s="1" t="s">
         <v>893</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B189" t="s">
+        <v>894</v>
+      </c>
+      <c r="C189" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="D189" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="E189" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F189" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="E189" t="s">
-        <v>1583</v>
-      </c>
-      <c r="F189" s="2" t="s">
+      <c r="G189" s="1" t="s">
         <v>898</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B190" t="s">
+        <v>899</v>
+      </c>
+      <c r="C190" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="C190" s="1" t="s">
+      <c r="D190" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="D190" s="1" t="s">
+      <c r="E190" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F190" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="E190" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F190" s="2" t="s">
+      <c r="G190" s="1" t="s">
         <v>903</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B191" t="s">
+        <v>904</v>
+      </c>
+      <c r="C191" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="C191" s="1" t="s">
+      <c r="D191" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="E191" t="s">
+        <v>1581</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G191" s="1" t="s">
         <v>907</v>
-      </c>
-      <c r="E191" t="s">
-        <v>1585</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B192" t="s">
+        <v>908</v>
+      </c>
+      <c r="C192" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="D192" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="E192" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F192" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="E192" t="s">
-        <v>1586</v>
-      </c>
-      <c r="F192" s="2" t="s">
+      <c r="G192" s="1" t="s">
         <v>912</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B193" t="s">
+        <v>913</v>
+      </c>
+      <c r="C193" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="D193" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="E193" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F193" s="2" t="s">
         <v>916</v>
       </c>
-      <c r="E193" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F193" s="2" t="s">
+      <c r="G193" s="1" t="s">
         <v>917</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B194" t="s">
+        <v>918</v>
+      </c>
+      <c r="C194" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="C194" s="1" t="s">
+      <c r="D194" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="E194" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F194" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="E194" t="s">
-        <v>1588</v>
-      </c>
-      <c r="F194" s="2" t="s">
+      <c r="G194" s="1" t="s">
         <v>922</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B195" t="s">
+        <v>923</v>
+      </c>
+      <c r="C195" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="D195" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="E195" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F195" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="E195" t="s">
-        <v>1589</v>
-      </c>
-      <c r="F195" s="2" t="s">
+      <c r="G195" s="1" t="s">
         <v>927</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B196" t="s">
+        <v>928</v>
+      </c>
+      <c r="C196" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="C196" s="1" t="s">
+      <c r="D196" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="D196" s="1" t="s">
+      <c r="E196" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F196" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="E196" t="s">
-        <v>1590</v>
-      </c>
-      <c r="F196" s="2" t="s">
+      <c r="G196" s="1" t="s">
         <v>932</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B197" t="s">
+        <v>933</v>
+      </c>
+      <c r="C197" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="D197" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="E197" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F197" s="2" t="s">
         <v>936</v>
       </c>
-      <c r="E197" t="s">
-        <v>1560</v>
-      </c>
-      <c r="F197" s="2" t="s">
+      <c r="G197" s="1" t="s">
         <v>937</v>
-      </c>
-      <c r="G197" s="1" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B198" t="s">
+        <v>938</v>
+      </c>
+      <c r="C198" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="D198" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="E198" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F198" s="2" t="s">
         <v>941</v>
       </c>
-      <c r="E198" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F198" s="2" t="s">
+      <c r="G198" s="1" t="s">
         <v>942</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B199" t="s">
+        <v>943</v>
+      </c>
+      <c r="C199" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="C199" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="E199" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F199" s="2" t="s">
         <v>946</v>
       </c>
-      <c r="E199" t="s">
-        <v>1592</v>
-      </c>
-      <c r="F199" s="2" t="s">
+      <c r="G199" s="1" t="s">
         <v>947</v>
-      </c>
-      <c r="G199" s="1" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B200" t="s">
+        <v>948</v>
+      </c>
+      <c r="C200" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="C200" s="1" t="s">
+      <c r="D200" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="E200" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F200" s="2" t="s">
         <v>951</v>
       </c>
-      <c r="E200" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F200" s="2" t="s">
+      <c r="G200" s="1" t="s">
         <v>952</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B201" t="s">
+        <v>953</v>
+      </c>
+      <c r="C201" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="C201" s="1" t="s">
+      <c r="D201" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="D201" s="1" t="s">
+      <c r="E201" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F201" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="E201" t="s">
-        <v>1568</v>
-      </c>
-      <c r="F201" s="2" t="s">
+      <c r="G201" s="1" t="s">
         <v>957</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B202" t="s">
+        <v>958</v>
+      </c>
+      <c r="C202" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="C202" s="1" t="s">
+      <c r="D202" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="D202" s="1" t="s">
+      <c r="E202" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F202" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="E202" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F202" s="2" t="s">
+      <c r="G202" s="1" t="s">
         <v>962</v>
-      </c>
-      <c r="G202" s="1" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B203" t="s">
+        <v>963</v>
+      </c>
+      <c r="C203" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="D203" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="E203" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F203" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="E203" t="s">
-        <v>1595</v>
-      </c>
-      <c r="F203" s="2" t="s">
+      <c r="G203" s="1" t="s">
         <v>967</v>
-      </c>
-      <c r="G203" s="1" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B204" t="s">
+        <v>968</v>
+      </c>
+      <c r="C204" s="1" t="s">
         <v>969</v>
       </c>
-      <c r="C204" s="1" t="s">
+      <c r="D204" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="D204" s="1" t="s">
+      <c r="E204" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F204" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="E204" t="s">
-        <v>1596</v>
-      </c>
-      <c r="F204" s="2" t="s">
+      <c r="G204" s="1" t="s">
         <v>972</v>
-      </c>
-      <c r="G204" s="1" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B205" t="s">
+        <v>973</v>
+      </c>
+      <c r="C205" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="C205" s="1" t="s">
+      <c r="D205" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="E205" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F205" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="E205" t="s">
-        <v>1597</v>
-      </c>
-      <c r="F205" s="2" t="s">
+      <c r="G205" s="1" t="s">
         <v>977</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B206" t="s">
+        <v>978</v>
+      </c>
+      <c r="C206" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="C206" s="1" t="s">
+      <c r="D206" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="E206" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F206" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="E206" t="s">
-        <v>1598</v>
-      </c>
-      <c r="F206" s="2" t="s">
+      <c r="G206" s="1" t="s">
         <v>982</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B207" t="s">
+        <v>983</v>
+      </c>
+      <c r="C207" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="C207" s="1" t="s">
+      <c r="D207" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="E207" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F207" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="E207" t="s">
-        <v>1482</v>
-      </c>
-      <c r="F207" s="2" t="s">
+      <c r="G207" s="1" t="s">
         <v>987</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B208" t="s">
+        <v>988</v>
+      </c>
+      <c r="C208" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="C208" s="1" t="s">
+      <c r="D208" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="E208" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="E208" t="s">
-        <v>1599</v>
-      </c>
-      <c r="F208" s="2" t="s">
+      <c r="G208" s="1" t="s">
         <v>992</v>
-      </c>
-      <c r="G208" s="1" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B209" t="s">
+        <v>993</v>
+      </c>
+      <c r="C209" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="C209" s="1" t="s">
+      <c r="D209" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="E209" t="s">
+        <v>1596</v>
+      </c>
+      <c r="F209" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="E209" t="s">
-        <v>1600</v>
-      </c>
-      <c r="F209" s="2" t="s">
+      <c r="G209" s="1" t="s">
         <v>997</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B210" t="s">
+        <v>998</v>
+      </c>
+      <c r="C210" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="C210" s="1" t="s">
+      <c r="D210" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="E210" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F210" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="E210" t="s">
-        <v>1601</v>
-      </c>
-      <c r="F210" s="2" t="s">
+      <c r="G210" s="1" t="s">
         <v>1002</v>
-      </c>
-      <c r="G210" s="1" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B211" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C211" s="1" t="s">
         <v>1004</v>
       </c>
-      <c r="C211" s="1" t="s">
+      <c r="D211" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="E211" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F211" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="E211" t="s">
-        <v>1602</v>
-      </c>
-      <c r="F211" s="2" t="s">
+      <c r="G211" s="1" t="s">
         <v>1007</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B212" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C212" s="1" t="s">
         <v>1009</v>
       </c>
-      <c r="C212" s="1" t="s">
+      <c r="D212" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="E212" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F212" s="2" t="s">
         <v>1011</v>
       </c>
-      <c r="E212" t="s">
-        <v>1598</v>
-      </c>
-      <c r="F212" s="2" t="s">
+      <c r="G212" s="1" t="s">
         <v>1012</v>
-      </c>
-      <c r="G212" s="1" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B213" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C213" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="C213" s="1" t="s">
+      <c r="D213" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="E213" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F213" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="E213" t="s">
-        <v>1603</v>
-      </c>
-      <c r="F213" s="2" t="s">
+      <c r="G213" s="1" t="s">
         <v>1017</v>
-      </c>
-      <c r="G213" s="1" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B214" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="C214" s="1" t="s">
+      <c r="D214" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="E214" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F214" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="E214" t="s">
-        <v>1604</v>
-      </c>
-      <c r="F214" s="2" t="s">
+      <c r="G214" s="1" t="s">
         <v>1022</v>
-      </c>
-      <c r="G214" s="1" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B215" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C215" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="C215" s="1" t="s">
+      <c r="D215" s="1" t="s">
         <v>1025</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="E215" t="s">
+        <v>1526</v>
+      </c>
+      <c r="F215" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="E215" t="s">
-        <v>1530</v>
-      </c>
-      <c r="F215" s="2" t="s">
+      <c r="G215" s="1" t="s">
         <v>1027</v>
-      </c>
-      <c r="G215" s="1" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B216" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>1029</v>
       </c>
-      <c r="C216" s="1" t="s">
+      <c r="D216" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="D216" s="1" t="s">
-        <v>1031</v>
-      </c>
       <c r="E216" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B217" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C217" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="D217" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="E217" t="s">
+        <v>1602</v>
+      </c>
+      <c r="F217" s="2" t="s">
         <v>1035</v>
       </c>
-      <c r="E217" t="s">
-        <v>1606</v>
-      </c>
-      <c r="F217" s="2" t="s">
+      <c r="G217" s="1" t="s">
         <v>1036</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B218" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C218" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="C218" s="1" t="s">
+      <c r="D218" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="E218" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F218" s="2" t="s">
         <v>1040</v>
       </c>
-      <c r="E218" t="s">
-        <v>1607</v>
-      </c>
-      <c r="F218" s="2" t="s">
+      <c r="G218" s="1" t="s">
         <v>1041</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B219" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C219" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="C219" s="1" t="s">
+      <c r="D219" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="E219" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F219" s="2" t="s">
         <v>1045</v>
       </c>
-      <c r="E219" t="s">
-        <v>1608</v>
-      </c>
-      <c r="F219" s="2" t="s">
+      <c r="G219" s="1" t="s">
         <v>1046</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B220" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C220" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="C220" s="1" t="s">
+      <c r="D220" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="D220" s="1" t="s">
+      <c r="E220" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F220" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="E220" t="s">
-        <v>1609</v>
-      </c>
-      <c r="F220" s="2" t="s">
+      <c r="G220" s="1" t="s">
         <v>1051</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B221" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C221" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="C221" s="1" t="s">
+      <c r="D221" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="D221" s="1" t="s">
+      <c r="E221" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>1055</v>
       </c>
-      <c r="E221" t="s">
-        <v>1610</v>
-      </c>
-      <c r="F221" s="2" t="s">
+      <c r="G221" s="1" t="s">
         <v>1056</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B222" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C222" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="C222" s="1" t="s">
+      <c r="D222" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="D222" s="1" t="s">
+      <c r="E222" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="E222" t="s">
-        <v>1611</v>
-      </c>
-      <c r="F222" s="2" t="s">
+      <c r="G222" s="1" t="s">
         <v>1061</v>
-      </c>
-      <c r="G222" s="1" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B223" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C223" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="C223" s="1" t="s">
+      <c r="D223" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="D223" s="1" t="s">
+      <c r="E223" t="s">
+        <v>1608</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="G223" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="E223" t="s">
-        <v>1612</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B224" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C224" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="C224" s="1" t="s">
+      <c r="D224" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="D224" s="1" t="s">
+      <c r="E224" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="E224" t="s">
-        <v>1613</v>
-      </c>
-      <c r="F224" s="2" t="s">
+      <c r="G224" s="1" t="s">
         <v>1070</v>
-      </c>
-      <c r="G224" s="1" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B225" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C225" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="C225" s="1" t="s">
+      <c r="D225" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="D225" s="1" t="s">
+      <c r="E225" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F225" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="E225" t="s">
-        <v>1614</v>
-      </c>
-      <c r="F225" s="2" t="s">
+      <c r="G225" s="1" t="s">
         <v>1075</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B226" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C226" s="1" t="s">
         <v>1077</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>1078</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E226" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="F226" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G226" s="1" t="s">
         <v>1079</v>
-      </c>
-      <c r="G226" s="1" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B227" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C227" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="C227" s="1" t="s">
+      <c r="D227" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="E227" t="s">
+        <v>1612</v>
+      </c>
+      <c r="F227" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="E227" t="s">
-        <v>1616</v>
-      </c>
-      <c r="F227" s="2" t="s">
+      <c r="G227" s="1" t="s">
         <v>1084</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B228" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C228" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="C228" s="1" t="s">
+      <c r="D228" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="D228" s="1" t="s">
+      <c r="E228" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F228" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="E228" t="s">
-        <v>1617</v>
-      </c>
-      <c r="F228" s="2" t="s">
+      <c r="G228" s="1" t="s">
         <v>1089</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B229" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C229" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="C229" s="1" t="s">
+      <c r="D229" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="D229" s="1" t="s">
+      <c r="E229" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="G229" s="1" t="s">
         <v>1093</v>
-      </c>
-      <c r="E229" t="s">
-        <v>1618</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="G229" s="1" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B230" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C230" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="C230" s="1" t="s">
+      <c r="D230" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="D230" s="1" t="s">
+      <c r="E230" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="E230" t="s">
-        <v>1619</v>
-      </c>
-      <c r="F230" s="2" t="s">
+      <c r="G230" s="1" t="s">
         <v>1098</v>
-      </c>
-      <c r="G230" s="1" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B231" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C231" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="C231" s="1" t="s">
+      <c r="D231" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="D231" s="1" t="s">
+      <c r="E231" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="E231" t="s">
-        <v>1620</v>
-      </c>
-      <c r="F231" s="2" t="s">
+      <c r="G231" s="1" t="s">
         <v>1103</v>
-      </c>
-      <c r="G231" s="1" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B232" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C232" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="C232" s="1" t="s">
+      <c r="D232" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="D232" s="1" t="s">
+      <c r="E232" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F232" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="E232" t="s">
-        <v>1621</v>
-      </c>
-      <c r="F232" s="2" t="s">
+      <c r="G232" s="1" t="s">
         <v>1108</v>
-      </c>
-      <c r="G232" s="1" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="B233" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C233" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="C233" s="1" t="s">
+      <c r="D233" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="D233" s="1" t="s">
+      <c r="E233" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F233" s="2" t="s">
         <v>1112</v>
       </c>
-      <c r="E233" t="s">
-        <v>1622</v>
-      </c>
-      <c r="F233" s="2" t="s">
+      <c r="G233" s="1" t="s">
         <v>1113</v>
-      </c>
-      <c r="G233" s="1" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="B234" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C234" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="C234" s="1" t="s">
+      <c r="D234" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="D234" s="1" t="s">
+      <c r="E234" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="E234" t="s">
-        <v>1623</v>
-      </c>
-      <c r="F234" s="2" t="s">
+      <c r="G234" s="1" t="s">
         <v>1118</v>
-      </c>
-      <c r="G234" s="1" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="B235" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C235" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="C235" s="1" t="s">
+      <c r="D235" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="D235" s="1" t="s">
+      <c r="E235" t="s">
+        <v>1620</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="E235" t="s">
-        <v>1624</v>
-      </c>
-      <c r="F235" s="2" t="s">
+      <c r="G235" s="1" t="s">
         <v>1125</v>
-      </c>
-      <c r="G235" s="1" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B236" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C236" s="1" t="s">
         <v>1127</v>
       </c>
-      <c r="C236" s="1" t="s">
+      <c r="D236" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="D236" s="1" t="s">
+      <c r="E236" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F236" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="E236" t="s">
-        <v>1625</v>
-      </c>
-      <c r="F236" s="2" t="s">
+      <c r="G236" s="1" t="s">
         <v>1130</v>
-      </c>
-      <c r="G236" s="1" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B237" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C237" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="C237" s="1" t="s">
+      <c r="D237" s="1" t="s">
         <v>1133</v>
       </c>
-      <c r="D237" s="1" t="s">
+      <c r="E237" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F237" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="E237" t="s">
-        <v>1522</v>
-      </c>
-      <c r="F237" s="2" t="s">
+      <c r="G237" s="1" t="s">
         <v>1135</v>
-      </c>
-      <c r="G237" s="1" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B238" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C238" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="C238" s="1" t="s">
+      <c r="D238" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="D238" s="1" t="s">
+      <c r="E238" t="s">
+        <v>1526</v>
+      </c>
+      <c r="F238" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="E238" t="s">
-        <v>1530</v>
-      </c>
-      <c r="F238" s="2" t="s">
+      <c r="G238" s="1" t="s">
         <v>1140</v>
-      </c>
-      <c r="G238" s="1" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B239" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C239" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="C239" s="1" t="s">
+      <c r="D239" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="D239" s="1" t="s">
+      <c r="E239" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="E239" t="s">
-        <v>1626</v>
-      </c>
-      <c r="F239" s="2" t="s">
+      <c r="G239" s="1" t="s">
         <v>1145</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B240" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C240" s="1" t="s">
         <v>1147</v>
-      </c>
-      <c r="C240" s="1" t="s">
-        <v>1148</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>1627</v>
+        <v>1623</v>
       </c>
       <c r="F240" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G240" s="1" t="s">
         <v>1149</v>
-      </c>
-      <c r="G240" s="1" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B241" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C241" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="C241" s="1" t="s">
+      <c r="D241" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="D241" s="1" t="s">
+      <c r="E241" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F241" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="E241" t="s">
-        <v>1628</v>
-      </c>
-      <c r="F241" s="2" t="s">
+      <c r="G241" s="1" t="s">
         <v>1154</v>
-      </c>
-      <c r="G241" s="1" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B242" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C242" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="C242" s="1" t="s">
+      <c r="D242" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="E242" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F242" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="E242" t="s">
-        <v>1498</v>
-      </c>
-      <c r="F242" s="2" t="s">
+      <c r="G242" s="1" t="s">
         <v>1159</v>
-      </c>
-      <c r="G242" s="1" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B243" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C243" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="C243" s="1" t="s">
+      <c r="D243" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="D243" s="1" t="s">
+      <c r="E243" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F243" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="E243" t="s">
-        <v>1629</v>
-      </c>
-      <c r="F243" s="2" t="s">
+      <c r="G243" s="1" t="s">
         <v>1164</v>
-      </c>
-      <c r="G243" s="1" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B244" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C244" s="1" t="s">
         <v>1166</v>
       </c>
-      <c r="C244" s="1" t="s">
+      <c r="D244" s="1" t="s">
         <v>1167</v>
       </c>
-      <c r="D244" s="1" t="s">
+      <c r="E244" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F244" s="2" t="s">
         <v>1168</v>
       </c>
-      <c r="E244" t="s">
-        <v>1630</v>
-      </c>
-      <c r="F244" s="2" t="s">
+      <c r="G244" s="1" t="s">
         <v>1169</v>
-      </c>
-      <c r="G244" s="1" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B245" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="E245" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B246" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="E246" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B247" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1183</v>
+        <v>688</v>
       </c>
       <c r="E247" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B248" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>689</v>
+        <v>1191</v>
       </c>
       <c r="E248" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>1188</v>
+        <v>6</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B249" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="E249" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>6</v>
+        <v>1196</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B250" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="E250" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B251" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="E251" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="B252" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="E252" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="B253" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="E253" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="B254" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="E254" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>1217</v>
+        <v>7</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="B255" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>1221</v>
+        <v>3</v>
       </c>
       <c r="E255" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>7</v>
+        <v>1224</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="B256" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>3</v>
+        <v>1228</v>
       </c>
       <c r="E256" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>1225</v>
+        <v>1106</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="B257" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="E257" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>1107</v>
+        <v>1233</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="B258" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="E258" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="B259" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="E259" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="B260" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="E260" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="B261" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="E261" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="B262" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="E262" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="B263" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="E263" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="B264" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="E264" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1416</v>
+        <v>1404</v>
       </c>
       <c r="B265" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1268</v>
+        <v>1414</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="E265" t="s">
-        <v>1651</v>
+        <v>1664</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1271</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B266" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>1418</v>
+        <v>1275</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="E266" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1419</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1408</v>
+        <v>1402</v>
       </c>
       <c r="B267" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1277</v>
+        <v>1248</v>
       </c>
       <c r="E267" t="s">
-        <v>1669</v>
+        <v>1648</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>1278</v>
+        <v>4</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="B268" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1249</v>
+        <v>1284</v>
       </c>
       <c r="E268" t="s">
-        <v>1652</v>
+        <v>1533</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>4</v>
+        <v>1285</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1415</v>
+        <v>1402</v>
       </c>
       <c r="B269" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="E269" t="s">
-        <v>1537</v>
+        <v>1649</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1287</v>
+        <v>1291</v>
+      </c>
+      <c r="L269" t="s">
+        <v>1397</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="B270" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="E270" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1292</v>
-      </c>
-      <c r="L270" t="s">
-        <v>1401</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B271" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="E271" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1416</v>
+        <v>1404</v>
       </c>
       <c r="B272" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="E272" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B273" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="E273" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1408</v>
+        <v>1402</v>
       </c>
       <c r="B274" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="E274" t="s">
-        <v>1657</v>
+        <v>1500</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B275" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="E275" t="s">
-        <v>1504</v>
+        <v>1598</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A276" t="s">
-        <v>1407</v>
-      </c>
       <c r="B276" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="E276" t="s">
-        <v>1602</v>
+        <v>1654</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>1321</v>
+        <v>1265</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>1402</v>
+      </c>
       <c r="B277" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="E277" t="s">
-        <v>1658</v>
+        <v>1492</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>1266</v>
+        <v>1329</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B278" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="E278" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="B279" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="E279" t="s">
-        <v>1496</v>
+        <v>1655</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
       <c r="B280" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="E280" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F280" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G280" s="1" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B281" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E281" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F281" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G281" s="1" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B282" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E282" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F282" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G282" s="1" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B283" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E283" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F283" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G283" s="1" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B284" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E284" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F284" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G284" s="1" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B285" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E285" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F285" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G285" s="1" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B286" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E286" t="s">
         <v>1659</v>
       </c>
-      <c r="F280" s="2" t="s">
-        <v>1340</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A281" t="s">
-        <v>1404</v>
-      </c>
-      <c r="B281" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C281" s="1" t="s">
-        <v>1343</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>1344</v>
-      </c>
-      <c r="E281" t="s">
-        <v>1509</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>1345</v>
-      </c>
-      <c r="G281" s="1" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>1404</v>
-      </c>
-      <c r="B282" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>1348</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>1349</v>
-      </c>
-      <c r="E282" t="s">
-        <v>1494</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>1350</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A283" t="s">
-        <v>1404</v>
-      </c>
-      <c r="B283" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>1353</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>1354</v>
-      </c>
-      <c r="E283" t="s">
-        <v>1532</v>
-      </c>
-      <c r="F283" s="2" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G283" s="1" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
-        <v>1414</v>
-      </c>
-      <c r="B284" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C284" s="1" t="s">
-        <v>1358</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>1359</v>
-      </c>
-      <c r="E284" t="s">
-        <v>1660</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>1360</v>
-      </c>
-      <c r="G284" s="1" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A285" t="s">
-        <v>1410</v>
-      </c>
-      <c r="B285" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>1363</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>1364</v>
-      </c>
-      <c r="E285" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G285" s="1" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B286" t="s">
-        <v>1366</v>
-      </c>
-      <c r="C286" s="1" t="s">
-        <v>1367</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>1368</v>
-      </c>
-      <c r="E286" t="s">
-        <v>1662</v>
-      </c>
       <c r="F286" s="2" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1415</v>
+        <v>1405</v>
       </c>
       <c r="B287" t="s">
-        <v>1371</v>
+        <v>1119</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1373</v>
+        <v>1120</v>
       </c>
       <c r="E287" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="B288" t="s">
-        <v>1120</v>
+        <v>1377</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>1376</v>
+        <v>1722</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1121</v>
+        <v>1378</v>
       </c>
       <c r="E288" t="s">
-        <v>1664</v>
+        <v>1512</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
       <c r="B289" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E289" t="s">
-        <v>1516</v>
+        <v>1661</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="B290" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="E290" t="s">
-        <v>1665</v>
+        <v>1533</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
@@ -12515,7 +12541,7 @@
         <v>1408</v>
       </c>
       <c r="B291" t="s">
-        <v>1389</v>
+        <v>1213</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>1390</v>
@@ -12524,7 +12550,7 @@
         <v>1391</v>
       </c>
       <c r="E291" t="s">
-        <v>1537</v>
+        <v>1662</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>1392</v>
@@ -12535,140 +12561,140 @@
     </row>
     <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B292" t="s">
-        <v>1214</v>
+        <v>1394</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>1395</v>
+        <v>1030</v>
       </c>
       <c r="E292" t="s">
-        <v>1666</v>
+        <v>1604</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>1396</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="B293" t="s">
-        <v>1398</v>
+        <v>1150</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>1399</v>
+        <v>1151</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>1031</v>
+        <v>1152</v>
       </c>
       <c r="E293" t="s">
-        <v>1608</v>
+        <v>1624</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>1400</v>
+        <v>1153</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>1417</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>1411</v>
-      </c>
-      <c r="B294" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E294" t="s">
-        <v>1628</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="G294" s="1" t="s">
-        <v>1155</v>
+      <c r="A294" s="5" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D294" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E294" s="6" t="s">
+        <v>1627</v>
+      </c>
+      <c r="F294" s="8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G294" s="7" t="s">
+        <v>1174</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B295" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C295" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="C295" s="1" t="s">
+      <c r="D295" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="D295" s="1" t="s">
+      <c r="E295" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F295" s="2" t="s">
         <v>1158</v>
       </c>
-      <c r="E295" t="s">
-        <v>1498</v>
-      </c>
-      <c r="F295" s="2" t="s">
-        <v>1159</v>
-      </c>
       <c r="G295" s="1" t="s">
-        <v>1160</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B296" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C296" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="C296" s="1" t="s">
+      <c r="D296" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="D296" s="1" t="s">
+      <c r="E296" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F296" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="E296" t="s">
-        <v>1652</v>
-      </c>
-      <c r="F296" s="2" t="s">
+      <c r="G296" s="1" t="s">
         <v>1164</v>
-      </c>
-      <c r="G296" s="1" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B297" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C297" s="1" t="s">
         <v>1166</v>
       </c>
-      <c r="C297" s="1" t="s">
+      <c r="D297" s="1" t="s">
         <v>1167</v>
       </c>
-      <c r="D297" s="1" t="s">
-        <v>1168</v>
-      </c>
       <c r="E297" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>1169</v>
+        <v>1719</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>1170</v>
+        <v>1720</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Daily_Word.xlsx
+++ b/public/data/Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D156AF-43B0-4077-A022-687AB54C0BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941BE80D-E57A-4085-AFF0-2B4411867529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="1725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="1721">
   <si>
     <t>Topic</t>
   </si>
@@ -3955,9 +3955,6 @@
   </si>
   <si>
     <t>ליצן</t>
-  </si>
-  <si>
-    <t>הסתכלתי על הלִיצוֹ של הליצן, וצחקתי מהאיפור המצחיק. ליצן טוב משקיע באיפור הלִיצוֹ שלו</t>
   </si>
   <si>
     <t>Палец</t>
@@ -4432,15 +4429,6 @@
     </r>
   </si>
   <si>
-    <t>Магазин</t>
-  </si>
-  <si>
-    <t>מָגָזִין</t>
-  </si>
-  <si>
-    <t>Store</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -4487,22 +4475,6 @@
   </si>
   <si>
     <t>תקשורת ומידע</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">במגזין מוכרים </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>מגזין</t>
-    </r>
   </si>
   <si>
     <t>גְרוּד</t>
@@ -5459,6 +5431,9 @@
   </si>
   <si>
     <t>צריך לקום רָנָה אם אתה רוצה to run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הסתכלתי על הלִיצוֹ של הליצן, וצחקתי מהאיפור המצחיק. </t>
   </si>
 </sst>
 </file>
@@ -5857,7 +5832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L297"/>
+  <dimension ref="A1:L296"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -5874,27 +5849,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -5906,7 +5881,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
@@ -5917,7 +5892,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -5929,7 +5904,7 @@
         <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>24</v>
@@ -5940,7 +5915,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -5952,18 +5927,18 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -5975,18 +5950,18 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1694</v>
+        <v>1689</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -5998,18 +5973,18 @@
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1718</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B7" t="s">
         <v>37</v>
@@ -6021,30 +5996,30 @@
         <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1689</v>
+        <v>1684</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>43</v>
@@ -6055,30 +6030,30 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B9" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1685</v>
+        <v>1680</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1686</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
@@ -6090,7 +6065,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>50</v>
@@ -6101,7 +6076,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B11" t="s">
         <v>52</v>
@@ -6113,41 +6088,41 @@
         <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1690</v>
+        <v>1685</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B13" t="s">
         <v>58</v>
@@ -6159,18 +6134,18 @@
         <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1693</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B14" t="s">
         <v>61</v>
@@ -6182,7 +6157,7 @@
         <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>64</v>
@@ -6193,7 +6168,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B15" t="s">
         <v>66</v>
@@ -6205,7 +6180,7 @@
         <v>68</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
@@ -6216,7 +6191,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
@@ -6228,7 +6203,7 @@
         <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>74</v>
@@ -6239,7 +6214,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B17" t="s">
         <v>76</v>
@@ -6251,7 +6226,7 @@
         <v>78</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
@@ -6262,7 +6237,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B18" t="s">
         <v>81</v>
@@ -6274,7 +6249,7 @@
         <v>83</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -6285,7 +6260,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B19" t="s">
         <v>86</v>
@@ -6297,7 +6272,7 @@
         <v>88</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
@@ -6308,7 +6283,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B20" t="s">
         <v>91</v>
@@ -6320,7 +6295,7 @@
         <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>94</v>
@@ -6331,7 +6306,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B21" t="s">
         <v>96</v>
@@ -6343,18 +6318,18 @@
         <v>98</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>99</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B22" t="s">
         <v>100</v>
@@ -6366,7 +6341,7 @@
         <v>102</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>103</v>
@@ -6377,30 +6352,30 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B23" t="s">
         <v>105</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>107</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1688</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B24" t="s">
         <v>108</v>
@@ -6412,7 +6387,7 @@
         <v>110</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>111</v>
@@ -6423,7 +6398,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B25" t="s">
         <v>113</v>
@@ -6435,7 +6410,7 @@
         <v>115</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>116</v>
@@ -6446,7 +6421,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B26" t="s">
         <v>118</v>
@@ -6458,7 +6433,7 @@
         <v>120</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>121</v>
@@ -6469,7 +6444,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B27" t="s">
         <v>123</v>
@@ -6481,7 +6456,7 @@
         <v>125</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>126</v>
@@ -6492,7 +6467,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B28" t="s">
         <v>128</v>
@@ -6504,7 +6479,7 @@
         <v>130</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>131</v>
@@ -6515,7 +6490,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B29" t="s">
         <v>133</v>
@@ -6527,7 +6502,7 @@
         <v>135</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>136</v>
@@ -6538,7 +6513,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B30" t="s">
         <v>138</v>
@@ -6550,7 +6525,7 @@
         <v>140</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>141</v>
@@ -6561,7 +6536,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B31" t="s">
         <v>143</v>
@@ -6573,7 +6548,7 @@
         <v>145</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>146</v>
@@ -6584,7 +6559,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B32" t="s">
         <v>148</v>
@@ -6596,18 +6571,18 @@
         <v>150</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>151</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1678</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B33" t="s">
         <v>152</v>
@@ -6619,7 +6594,7 @@
         <v>154</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>155</v>
@@ -6630,7 +6605,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B34" t="s">
         <v>157</v>
@@ -6642,7 +6617,7 @@
         <v>159</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>160</v>
@@ -6653,7 +6628,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B35" t="s">
         <v>162</v>
@@ -6665,7 +6640,7 @@
         <v>164</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>165</v>
@@ -6676,7 +6651,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B36" t="s">
         <v>167</v>
@@ -6688,7 +6663,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>169</v>
@@ -6699,7 +6674,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B37" t="s">
         <v>171</v>
@@ -6711,7 +6686,7 @@
         <v>173</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>174</v>
@@ -6722,7 +6697,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B38" t="s">
         <v>176</v>
@@ -6734,7 +6709,7 @@
         <v>178</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
@@ -6745,7 +6720,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B39" t="s">
         <v>180</v>
@@ -6757,7 +6732,7 @@
         <v>182</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>183</v>
@@ -6768,7 +6743,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B40" t="s">
         <v>185</v>
@@ -6780,7 +6755,7 @@
         <v>187</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>188</v>
@@ -6791,7 +6766,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B41" t="s">
         <v>190</v>
@@ -6803,7 +6778,7 @@
         <v>192</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>193</v>
@@ -6814,7 +6789,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B42" t="s">
         <v>195</v>
@@ -6826,7 +6801,7 @@
         <v>197</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>198</v>
@@ -6837,7 +6812,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B43" t="s">
         <v>200</v>
@@ -6849,7 +6824,7 @@
         <v>202</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>203</v>
@@ -6860,7 +6835,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B44" t="s">
         <v>205</v>
@@ -6872,7 +6847,7 @@
         <v>207</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>208</v>
@@ -6883,7 +6858,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B45" t="s">
         <v>210</v>
@@ -6895,18 +6870,18 @@
         <v>212</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>213</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B46" t="s">
         <v>214</v>
@@ -6918,7 +6893,7 @@
         <v>216</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>217</v>
@@ -6929,7 +6904,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B47" t="s">
         <v>219</v>
@@ -6941,7 +6916,7 @@
         <v>221</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1668</v>
+        <v>1663</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>222</v>
@@ -6952,7 +6927,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B48" t="s">
         <v>224</v>
@@ -6964,7 +6939,7 @@
         <v>226</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>227</v>
@@ -6975,7 +6950,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B49" t="s">
         <v>229</v>
@@ -6987,7 +6962,7 @@
         <v>231</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>232</v>
@@ -6998,7 +6973,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B50" t="s">
         <v>234</v>
@@ -7010,7 +6985,7 @@
         <v>236</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>237</v>
@@ -7021,7 +6996,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B51" t="s">
         <v>239</v>
@@ -7033,7 +7008,7 @@
         <v>241</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>242</v>
@@ -7044,7 +7019,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B52" t="s">
         <v>244</v>
@@ -7056,7 +7031,7 @@
         <v>246</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>247</v>
@@ -7067,7 +7042,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B53" t="s">
         <v>249</v>
@@ -7079,18 +7054,18 @@
         <v>251</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B54" t="s">
         <v>252</v>
@@ -7102,18 +7077,18 @@
         <v>254</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>255</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1682</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="B55" t="s">
         <v>256</v>
@@ -7125,7 +7100,7 @@
         <v>258</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>259</v>
@@ -7136,7 +7111,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B56" t="s">
         <v>261</v>
@@ -7148,7 +7123,7 @@
         <v>263</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>264</v>
@@ -7159,7 +7134,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B57" t="s">
         <v>266</v>
@@ -7171,7 +7146,7 @@
         <v>268</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>269</v>
@@ -7182,7 +7157,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B58" t="s">
         <v>271</v>
@@ -7194,7 +7169,7 @@
         <v>273</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>274</v>
@@ -7205,7 +7180,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B59" t="s">
         <v>276</v>
@@ -7217,7 +7192,7 @@
         <v>278</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>279</v>
@@ -7228,7 +7203,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B60" t="s">
         <v>281</v>
@@ -7240,7 +7215,7 @@
         <v>283</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>284</v>
@@ -7251,7 +7226,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B61" t="s">
         <v>286</v>
@@ -7263,7 +7238,7 @@
         <v>288</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>289</v>
@@ -7274,7 +7249,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B62" t="s">
         <v>291</v>
@@ -7286,7 +7261,7 @@
         <v>293</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>294</v>
@@ -7297,7 +7272,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B63" t="s">
         <v>296</v>
@@ -7306,10 +7281,10 @@
         <v>297</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>298</v>
@@ -7320,7 +7295,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B64" t="s">
         <v>300</v>
@@ -7332,7 +7307,7 @@
         <v>302</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
@@ -7343,7 +7318,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B65" t="s">
         <v>304</v>
@@ -7355,7 +7330,7 @@
         <v>306</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>307</v>
@@ -7366,7 +7341,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B66" t="s">
         <v>309</v>
@@ -7378,7 +7353,7 @@
         <v>311</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>312</v>
@@ -7389,7 +7364,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B67" t="s">
         <v>314</v>
@@ -7401,7 +7376,7 @@
         <v>316</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>317</v>
@@ -7412,7 +7387,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B68" t="s">
         <v>319</v>
@@ -7424,18 +7399,18 @@
         <v>321</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>322</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B69" t="s">
         <v>323</v>
@@ -7447,7 +7422,7 @@
         <v>325</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>326</v>
@@ -7458,7 +7433,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B70" t="s">
         <v>328</v>
@@ -7470,7 +7445,7 @@
         <v>330</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>331</v>
@@ -7481,7 +7456,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B71" t="s">
         <v>333</v>
@@ -7493,7 +7468,7 @@
         <v>335</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>336</v>
@@ -7504,7 +7479,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B72" t="s">
         <v>338</v>
@@ -7516,7 +7491,7 @@
         <v>340</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>341</v>
@@ -7527,7 +7502,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B73" t="s">
         <v>343</v>
@@ -7539,7 +7514,7 @@
         <v>345</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>346</v>
@@ -7550,7 +7525,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B74" t="s">
         <v>348</v>
@@ -7562,7 +7537,7 @@
         <v>350</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>351</v>
@@ -7573,7 +7548,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B75" t="s">
         <v>353</v>
@@ -7585,18 +7560,18 @@
         <v>355</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>356</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1698</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B76" t="s">
         <v>357</v>
@@ -7608,7 +7583,7 @@
         <v>359</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>360</v>
@@ -7619,7 +7594,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B77" t="s">
         <v>362</v>
@@ -7631,7 +7606,7 @@
         <v>364</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>365</v>
@@ -7642,7 +7617,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B78" t="s">
         <v>367</v>
@@ -7654,7 +7629,7 @@
         <v>369</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>370</v>
@@ -7665,30 +7640,30 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B79" t="s">
         <v>372</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1699</v>
+        <v>1694</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>373</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>374</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1700</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B80" t="s">
         <v>375</v>
@@ -7700,7 +7675,7 @@
         <v>377</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>378</v>
@@ -7711,7 +7686,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B81" t="s">
         <v>380</v>
@@ -7723,18 +7698,18 @@
         <v>382</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>383</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1701</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B82" t="s">
         <v>384</v>
@@ -7746,7 +7721,7 @@
         <v>386</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>387</v>
@@ -7757,7 +7732,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B83" t="s">
         <v>389</v>
@@ -7769,7 +7744,7 @@
         <v>391</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>392</v>
@@ -7780,7 +7755,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B84" t="s">
         <v>394</v>
@@ -7792,7 +7767,7 @@
         <v>396</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
@@ -7803,7 +7778,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B85" t="s">
         <v>398</v>
@@ -7815,7 +7790,7 @@
         <v>400</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>401</v>
@@ -7826,7 +7801,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B86" t="s">
         <v>403</v>
@@ -7838,7 +7813,7 @@
         <v>405</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>406</v>
@@ -7849,7 +7824,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B87" t="s">
         <v>408</v>
@@ -7861,7 +7836,7 @@
         <v>410</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>411</v>
@@ -7872,7 +7847,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B88" t="s">
         <v>413</v>
@@ -7884,18 +7859,18 @@
         <v>415</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1670</v>
+        <v>1665</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>416</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1702</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B89" t="s">
         <v>417</v>
@@ -7907,7 +7882,7 @@
         <v>419</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1671</v>
+        <v>1666</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>420</v>
@@ -7918,7 +7893,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B90" t="s">
         <v>422</v>
@@ -7930,7 +7905,7 @@
         <v>424</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>425</v>
@@ -7941,7 +7916,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B91" t="s">
         <v>427</v>
@@ -7953,18 +7928,18 @@
         <v>429</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>430</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1703</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B92" t="s">
         <v>431</v>
@@ -7976,7 +7951,7 @@
         <v>433</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>434</v>
@@ -7987,7 +7962,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B93" t="s">
         <v>436</v>
@@ -7999,7 +7974,7 @@
         <v>438</v>
       </c>
       <c r="E93" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>439</v>
@@ -8010,7 +7985,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B94" t="s">
         <v>441</v>
@@ -8022,7 +7997,7 @@
         <v>443</v>
       </c>
       <c r="E94" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>444</v>
@@ -8033,7 +8008,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B95" t="s">
         <v>446</v>
@@ -8045,7 +8020,7 @@
         <v>448</v>
       </c>
       <c r="E95" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>449</v>
@@ -8056,7 +8031,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B96" t="s">
         <v>451</v>
@@ -8068,7 +8043,7 @@
         <v>453</v>
       </c>
       <c r="E96" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>454</v>
@@ -8079,7 +8054,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B97" t="s">
         <v>456</v>
@@ -8091,7 +8066,7 @@
         <v>458</v>
       </c>
       <c r="E97" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>459</v>
@@ -8102,7 +8077,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B98" t="s">
         <v>461</v>
@@ -8114,7 +8089,7 @@
         <v>463</v>
       </c>
       <c r="E98" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>464</v>
@@ -8125,7 +8100,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B99" t="s">
         <v>466</v>
@@ -8137,7 +8112,7 @@
         <v>468</v>
       </c>
       <c r="E99" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>469</v>
@@ -8148,7 +8123,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B100" t="s">
         <v>503</v>
@@ -8160,7 +8135,7 @@
         <v>505</v>
       </c>
       <c r="E100" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>506</v>
@@ -8171,7 +8146,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B101" t="s">
         <v>471</v>
@@ -8183,7 +8158,7 @@
         <v>473</v>
       </c>
       <c r="E101" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>474</v>
@@ -8194,7 +8169,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B102" t="s">
         <v>476</v>
@@ -8206,18 +8181,18 @@
         <v>478</v>
       </c>
       <c r="E102" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>479</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B103" t="s">
         <v>480</v>
@@ -8229,7 +8204,7 @@
         <v>482</v>
       </c>
       <c r="E103" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>483</v>
@@ -8240,7 +8215,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B104" t="s">
         <v>485</v>
@@ -8252,7 +8227,7 @@
         <v>487</v>
       </c>
       <c r="E104" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>488</v>
@@ -8263,7 +8238,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B105" t="s">
         <v>490</v>
@@ -8275,18 +8250,18 @@
         <v>492</v>
       </c>
       <c r="E105" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>493</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1705</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B106" t="s">
         <v>494</v>
@@ -8298,7 +8273,7 @@
         <v>496</v>
       </c>
       <c r="E106" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>497</v>
@@ -8309,7 +8284,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B107" t="s">
         <v>499</v>
@@ -8321,18 +8296,18 @@
         <v>501</v>
       </c>
       <c r="E107" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>502</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1706</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B108" t="s">
         <v>508</v>
@@ -8344,10 +8319,10 @@
         <v>510</v>
       </c>
       <c r="E108" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>1707</v>
+        <v>1702</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>511</v>
@@ -8355,7 +8330,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B109" t="s">
         <v>512</v>
@@ -8367,7 +8342,7 @@
         <v>514</v>
       </c>
       <c r="E109" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>515</v>
@@ -8378,7 +8353,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B110" t="s">
         <v>517</v>
@@ -8390,7 +8365,7 @@
         <v>519</v>
       </c>
       <c r="E110" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
@@ -8401,7 +8376,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B111" t="s">
         <v>521</v>
@@ -8413,7 +8388,7 @@
         <v>523</v>
       </c>
       <c r="E111" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>524</v>
@@ -8424,7 +8399,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B112" t="s">
         <v>526</v>
@@ -8436,7 +8411,7 @@
         <v>528</v>
       </c>
       <c r="E112" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>529</v>
@@ -8447,7 +8422,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B113" t="s">
         <v>531</v>
@@ -8459,7 +8434,7 @@
         <v>533</v>
       </c>
       <c r="E113" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>534</v>
@@ -8470,7 +8445,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B114" t="s">
         <v>536</v>
@@ -8482,7 +8457,7 @@
         <v>538</v>
       </c>
       <c r="E114" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>14</v>
@@ -8493,7 +8468,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B115" t="s">
         <v>540</v>
@@ -8505,18 +8480,18 @@
         <v>542</v>
       </c>
       <c r="E115" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1708</v>
+        <v>1703</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B116" t="s">
         <v>543</v>
@@ -8528,7 +8503,7 @@
         <v>545</v>
       </c>
       <c r="E116" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>283</v>
@@ -8539,7 +8514,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B117" t="s">
         <v>547</v>
@@ -8551,7 +8526,7 @@
         <v>549</v>
       </c>
       <c r="E117" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>550</v>
@@ -8562,7 +8537,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B118" t="s">
         <v>552</v>
@@ -8574,7 +8549,7 @@
         <v>554</v>
       </c>
       <c r="E118" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>555</v>
@@ -8585,7 +8560,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B119" t="s">
         <v>557</v>
@@ -8597,7 +8572,7 @@
         <v>559</v>
       </c>
       <c r="E119" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
@@ -8608,7 +8583,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B120" t="s">
         <v>561</v>
@@ -8620,7 +8595,7 @@
         <v>563</v>
       </c>
       <c r="E120" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>564</v>
@@ -8631,7 +8606,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B121" t="s">
         <v>566</v>
@@ -8643,7 +8618,7 @@
         <v>568</v>
       </c>
       <c r="E121" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>569</v>
@@ -8654,7 +8629,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B122" t="s">
         <v>571</v>
@@ -8666,7 +8641,7 @@
         <v>573</v>
       </c>
       <c r="E122" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>574</v>
@@ -8677,7 +8652,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B123" t="s">
         <v>576</v>
@@ -8689,7 +8664,7 @@
         <v>578</v>
       </c>
       <c r="E123" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>579</v>
@@ -8700,7 +8675,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B124" t="s">
         <v>581</v>
@@ -8712,7 +8687,7 @@
         <v>583</v>
       </c>
       <c r="E124" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
@@ -8723,7 +8698,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B125" t="s">
         <v>585</v>
@@ -8735,18 +8710,18 @@
         <v>587</v>
       </c>
       <c r="E125" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>588</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1710</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B126" t="s">
         <v>589</v>
@@ -8758,7 +8733,7 @@
         <v>591</v>
       </c>
       <c r="E126" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>592</v>
@@ -8769,7 +8744,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B127" t="s">
         <v>594</v>
@@ -8781,7 +8756,7 @@
         <v>596</v>
       </c>
       <c r="E127" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>597</v>
@@ -8792,7 +8767,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B128" t="s">
         <v>599</v>
@@ -8804,7 +8779,7 @@
         <v>601</v>
       </c>
       <c r="E128" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>602</v>
@@ -8815,7 +8790,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B129" t="s">
         <v>604</v>
@@ -8827,7 +8802,7 @@
         <v>606</v>
       </c>
       <c r="E129" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>607</v>
@@ -8838,7 +8813,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B130" t="s">
         <v>609</v>
@@ -8850,7 +8825,7 @@
         <v>611</v>
       </c>
       <c r="E130" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>612</v>
@@ -8861,7 +8836,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B131" t="s">
         <v>614</v>
@@ -8873,7 +8848,7 @@
         <v>616</v>
       </c>
       <c r="E131" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>293</v>
@@ -8884,7 +8859,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B132" t="s">
         <v>618</v>
@@ -8896,7 +8871,7 @@
         <v>620</v>
       </c>
       <c r="E132" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>621</v>
@@ -8907,7 +8882,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B133" t="s">
         <v>623</v>
@@ -8919,7 +8894,7 @@
         <v>625</v>
       </c>
       <c r="E133" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>626</v>
@@ -8930,7 +8905,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B134" t="s">
         <v>628</v>
@@ -8942,7 +8917,7 @@
         <v>630</v>
       </c>
       <c r="E134" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>631</v>
@@ -8953,7 +8928,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B135" t="s">
         <v>633</v>
@@ -8965,7 +8940,7 @@
         <v>635</v>
       </c>
       <c r="E135" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>636</v>
@@ -8976,7 +8951,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B136" t="s">
         <v>638</v>
@@ -8988,7 +8963,7 @@
         <v>640</v>
       </c>
       <c r="E136" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>641</v>
@@ -8999,7 +8974,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B137" t="s">
         <v>643</v>
@@ -9011,7 +8986,7 @@
         <v>645</v>
       </c>
       <c r="E137" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>646</v>
@@ -9022,7 +8997,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B138" t="s">
         <v>648</v>
@@ -9034,7 +9009,7 @@
         <v>650</v>
       </c>
       <c r="E138" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>651</v>
@@ -9045,7 +9020,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B139" t="s">
         <v>653</v>
@@ -9057,7 +9032,7 @@
         <v>655</v>
       </c>
       <c r="E139" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>656</v>
@@ -9068,7 +9043,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B140" t="s">
         <v>658</v>
@@ -9080,18 +9055,18 @@
         <v>660</v>
       </c>
       <c r="E140" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>661</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1711</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B141" t="s">
         <v>662</v>
@@ -9103,7 +9078,7 @@
         <v>664</v>
       </c>
       <c r="E141" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>665</v>
@@ -9114,7 +9089,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B142" t="s">
         <v>667</v>
@@ -9126,18 +9101,18 @@
         <v>669</v>
       </c>
       <c r="E142" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>670</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1712</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B143" t="s">
         <v>671</v>
@@ -9149,18 +9124,18 @@
         <v>673</v>
       </c>
       <c r="E143" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>674</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1713</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B144" t="s">
         <v>675</v>
@@ -9172,7 +9147,7 @@
         <v>677</v>
       </c>
       <c r="E144" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>678</v>
@@ -9183,7 +9158,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B145" t="s">
         <v>680</v>
@@ -9195,7 +9170,7 @@
         <v>682</v>
       </c>
       <c r="E145" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>683</v>
@@ -9206,7 +9181,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B146" t="s">
         <v>685</v>
@@ -9218,7 +9193,7 @@
         <v>687</v>
       </c>
       <c r="E146" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>688</v>
@@ -9229,7 +9204,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B147" t="s">
         <v>690</v>
@@ -9241,7 +9216,7 @@
         <v>692</v>
       </c>
       <c r="E147" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>693</v>
@@ -9252,7 +9227,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B148" t="s">
         <v>695</v>
@@ -9264,18 +9239,18 @@
         <v>697</v>
       </c>
       <c r="E148" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>1714</v>
+        <v>1709</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1715</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B149" t="s">
         <v>698</v>
@@ -9287,7 +9262,7 @@
         <v>274</v>
       </c>
       <c r="E149" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>700</v>
@@ -9298,7 +9273,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B150" t="s">
         <v>702</v>
@@ -9310,7 +9285,7 @@
         <v>704</v>
       </c>
       <c r="E150" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>4</v>
@@ -9321,7 +9296,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B151" t="s">
         <v>706</v>
@@ -9333,7 +9308,7 @@
         <v>708</v>
       </c>
       <c r="E151" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>709</v>
@@ -9344,7 +9319,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B152" t="s">
         <v>711</v>
@@ -9356,7 +9331,7 @@
         <v>713</v>
       </c>
       <c r="E152" t="s">
-        <v>1672</v>
+        <v>1667</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>714</v>
@@ -9367,7 +9342,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B153" t="s">
         <v>716</v>
@@ -9379,7 +9354,7 @@
         <v>718</v>
       </c>
       <c r="E153" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>719</v>
@@ -9390,7 +9365,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B154" t="s">
         <v>721</v>
@@ -9402,18 +9377,18 @@
         <v>723</v>
       </c>
       <c r="E154" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>724</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>1716</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B155" t="s">
         <v>725</v>
@@ -9425,18 +9400,18 @@
         <v>727</v>
       </c>
       <c r="E155" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>728</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>1717</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B156" t="s">
         <v>729</v>
@@ -9448,7 +9423,7 @@
         <v>731</v>
       </c>
       <c r="E156" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>732</v>
@@ -9459,7 +9434,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B157" t="s">
         <v>734</v>
@@ -9471,7 +9446,7 @@
         <v>736</v>
       </c>
       <c r="E157" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>737</v>
@@ -9482,7 +9457,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B158" t="s">
         <v>739</v>
@@ -9494,7 +9469,7 @@
         <v>741</v>
       </c>
       <c r="E158" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>742</v>
@@ -9505,7 +9480,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B159" t="s">
         <v>744</v>
@@ -9517,7 +9492,7 @@
         <v>746</v>
       </c>
       <c r="E159" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>747</v>
@@ -9528,7 +9503,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B160" t="s">
         <v>749</v>
@@ -9540,7 +9515,7 @@
         <v>751</v>
       </c>
       <c r="E160" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>752</v>
@@ -9551,7 +9526,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B161" t="s">
         <v>754</v>
@@ -9563,7 +9538,7 @@
         <v>756</v>
       </c>
       <c r="E161" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>757</v>
@@ -9574,7 +9549,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B162" t="s">
         <v>759</v>
@@ -9586,7 +9561,7 @@
         <v>761</v>
       </c>
       <c r="E162" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>762</v>
@@ -9597,7 +9572,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B163" t="s">
         <v>764</v>
@@ -9609,7 +9584,7 @@
         <v>766</v>
       </c>
       <c r="E163" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>767</v>
@@ -9620,7 +9595,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B164" t="s">
         <v>769</v>
@@ -9632,7 +9607,7 @@
         <v>771</v>
       </c>
       <c r="E164" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>772</v>
@@ -9643,7 +9618,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B165" t="s">
         <v>774</v>
@@ -9655,7 +9630,7 @@
         <v>776</v>
       </c>
       <c r="E165" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>777</v>
@@ -9666,7 +9641,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B166" t="s">
         <v>779</v>
@@ -9678,7 +9653,7 @@
         <v>781</v>
       </c>
       <c r="E166" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>782</v>
@@ -9689,7 +9664,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B167" t="s">
         <v>784</v>
@@ -9701,7 +9676,7 @@
         <v>786</v>
       </c>
       <c r="E167" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>787</v>
@@ -9712,7 +9687,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B168" t="s">
         <v>789</v>
@@ -9724,7 +9699,7 @@
         <v>791</v>
       </c>
       <c r="E168" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>792</v>
@@ -9735,7 +9710,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B169" t="s">
         <v>794</v>
@@ -9747,7 +9722,7 @@
         <v>796</v>
       </c>
       <c r="E169" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>797</v>
@@ -9758,7 +9733,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B170" t="s">
         <v>799</v>
@@ -9770,7 +9745,7 @@
         <v>801</v>
       </c>
       <c r="E170" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>802</v>
@@ -9781,7 +9756,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B171" t="s">
         <v>804</v>
@@ -9793,7 +9768,7 @@
         <v>806</v>
       </c>
       <c r="E171" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>807</v>
@@ -9804,7 +9779,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B172" t="s">
         <v>809</v>
@@ -9816,7 +9791,7 @@
         <v>811</v>
       </c>
       <c r="E172" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>812</v>
@@ -9827,7 +9802,7 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B173" t="s">
         <v>814</v>
@@ -9839,7 +9814,7 @@
         <v>816</v>
       </c>
       <c r="E173" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>817</v>
@@ -9850,7 +9825,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B174" t="s">
         <v>819</v>
@@ -9862,7 +9837,7 @@
         <v>821</v>
       </c>
       <c r="E174" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>822</v>
@@ -9873,7 +9848,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B175" t="s">
         <v>824</v>
@@ -9885,7 +9860,7 @@
         <v>826</v>
       </c>
       <c r="E175" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F175" s="2" t="s">
         <v>827</v>
@@ -9896,7 +9871,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B176" t="s">
         <v>829</v>
@@ -9908,7 +9883,7 @@
         <v>831</v>
       </c>
       <c r="E176" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>832</v>
@@ -9919,7 +9894,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B177" t="s">
         <v>834</v>
@@ -9931,7 +9906,7 @@
         <v>836</v>
       </c>
       <c r="E177" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>837</v>
@@ -9942,7 +9917,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B178" t="s">
         <v>839</v>
@@ -9954,7 +9929,7 @@
         <v>841</v>
       </c>
       <c r="E178" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>842</v>
@@ -9965,7 +9940,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B179" t="s">
         <v>844</v>
@@ -9977,7 +9952,7 @@
         <v>846</v>
       </c>
       <c r="E179" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>847</v>
@@ -9988,7 +9963,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B180" t="s">
         <v>849</v>
@@ -10000,7 +9975,7 @@
         <v>851</v>
       </c>
       <c r="E180" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>852</v>
@@ -10011,7 +9986,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B181" t="s">
         <v>854</v>
@@ -10023,7 +9998,7 @@
         <v>856</v>
       </c>
       <c r="E181" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>857</v>
@@ -10034,7 +10009,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B182" t="s">
         <v>859</v>
@@ -10046,7 +10021,7 @@
         <v>861</v>
       </c>
       <c r="E182" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>862</v>
@@ -10057,7 +10032,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B183" t="s">
         <v>864</v>
@@ -10069,7 +10044,7 @@
         <v>866</v>
       </c>
       <c r="E183" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>867</v>
@@ -10080,7 +10055,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B184" t="s">
         <v>869</v>
@@ -10092,7 +10067,7 @@
         <v>871</v>
       </c>
       <c r="E184" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>872</v>
@@ -10103,7 +10078,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B185" t="s">
         <v>874</v>
@@ -10115,7 +10090,7 @@
         <v>876</v>
       </c>
       <c r="E185" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>877</v>
@@ -10126,7 +10101,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B186" t="s">
         <v>879</v>
@@ -10138,7 +10113,7 @@
         <v>881</v>
       </c>
       <c r="E186" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>882</v>
@@ -10149,7 +10124,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B187" t="s">
         <v>884</v>
@@ -10161,7 +10136,7 @@
         <v>886</v>
       </c>
       <c r="E187" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>887</v>
@@ -10172,7 +10147,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B188" t="s">
         <v>889</v>
@@ -10184,7 +10159,7 @@
         <v>891</v>
       </c>
       <c r="E188" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>892</v>
@@ -10195,7 +10170,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B189" t="s">
         <v>894</v>
@@ -10207,7 +10182,7 @@
         <v>896</v>
       </c>
       <c r="E189" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>897</v>
@@ -10218,7 +10193,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B190" t="s">
         <v>899</v>
@@ -10230,7 +10205,7 @@
         <v>901</v>
       </c>
       <c r="E190" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>902</v>
@@ -10241,7 +10216,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B191" t="s">
         <v>904</v>
@@ -10253,7 +10228,7 @@
         <v>906</v>
       </c>
       <c r="E191" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>116</v>
@@ -10264,7 +10239,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B192" t="s">
         <v>908</v>
@@ -10276,7 +10251,7 @@
         <v>910</v>
       </c>
       <c r="E192" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>911</v>
@@ -10287,7 +10262,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B193" t="s">
         <v>913</v>
@@ -10299,7 +10274,7 @@
         <v>915</v>
       </c>
       <c r="E193" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>916</v>
@@ -10310,7 +10285,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B194" t="s">
         <v>918</v>
@@ -10322,7 +10297,7 @@
         <v>920</v>
       </c>
       <c r="E194" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>921</v>
@@ -10333,7 +10308,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B195" t="s">
         <v>923</v>
@@ -10345,7 +10320,7 @@
         <v>925</v>
       </c>
       <c r="E195" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>926</v>
@@ -10356,7 +10331,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B196" t="s">
         <v>928</v>
@@ -10368,7 +10343,7 @@
         <v>930</v>
       </c>
       <c r="E196" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>931</v>
@@ -10379,7 +10354,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B197" t="s">
         <v>933</v>
@@ -10391,7 +10366,7 @@
         <v>935</v>
       </c>
       <c r="E197" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>936</v>
@@ -10402,7 +10377,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B198" t="s">
         <v>938</v>
@@ -10414,7 +10389,7 @@
         <v>940</v>
       </c>
       <c r="E198" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>941</v>
@@ -10425,7 +10400,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B199" t="s">
         <v>943</v>
@@ -10437,7 +10412,7 @@
         <v>945</v>
       </c>
       <c r="E199" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>946</v>
@@ -10448,7 +10423,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B200" t="s">
         <v>948</v>
@@ -10460,7 +10435,7 @@
         <v>950</v>
       </c>
       <c r="E200" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>951</v>
@@ -10471,7 +10446,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B201" t="s">
         <v>953</v>
@@ -10483,7 +10458,7 @@
         <v>955</v>
       </c>
       <c r="E201" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>956</v>
@@ -10494,7 +10469,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B202" t="s">
         <v>958</v>
@@ -10506,7 +10481,7 @@
         <v>960</v>
       </c>
       <c r="E202" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>961</v>
@@ -10517,7 +10492,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B203" t="s">
         <v>963</v>
@@ -10529,7 +10504,7 @@
         <v>965</v>
       </c>
       <c r="E203" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>966</v>
@@ -10540,7 +10515,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B204" t="s">
         <v>968</v>
@@ -10552,7 +10527,7 @@
         <v>970</v>
       </c>
       <c r="E204" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>971</v>
@@ -10563,7 +10538,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B205" t="s">
         <v>973</v>
@@ -10575,7 +10550,7 @@
         <v>975</v>
       </c>
       <c r="E205" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>976</v>
@@ -10586,7 +10561,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B206" t="s">
         <v>978</v>
@@ -10598,7 +10573,7 @@
         <v>980</v>
       </c>
       <c r="E206" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>981</v>
@@ -10609,7 +10584,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B207" t="s">
         <v>983</v>
@@ -10621,7 +10596,7 @@
         <v>985</v>
       </c>
       <c r="E207" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>986</v>
@@ -10632,7 +10607,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B208" t="s">
         <v>988</v>
@@ -10644,7 +10619,7 @@
         <v>990</v>
       </c>
       <c r="E208" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>991</v>
@@ -10655,7 +10630,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B209" t="s">
         <v>993</v>
@@ -10667,7 +10642,7 @@
         <v>995</v>
       </c>
       <c r="E209" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>996</v>
@@ -10678,7 +10653,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B210" t="s">
         <v>998</v>
@@ -10690,7 +10665,7 @@
         <v>1000</v>
       </c>
       <c r="E210" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>1001</v>
@@ -10701,7 +10676,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B211" t="s">
         <v>1003</v>
@@ -10713,7 +10688,7 @@
         <v>1005</v>
       </c>
       <c r="E211" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>1006</v>
@@ -10724,7 +10699,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B212" t="s">
         <v>1008</v>
@@ -10736,7 +10711,7 @@
         <v>1010</v>
       </c>
       <c r="E212" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>1011</v>
@@ -10747,7 +10722,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B213" t="s">
         <v>1013</v>
@@ -10759,7 +10734,7 @@
         <v>1015</v>
       </c>
       <c r="E213" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>1016</v>
@@ -10770,7 +10745,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B214" t="s">
         <v>1018</v>
@@ -10782,7 +10757,7 @@
         <v>1020</v>
       </c>
       <c r="E214" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>1021</v>
@@ -10793,7 +10768,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B215" t="s">
         <v>1023</v>
@@ -10805,7 +10780,7 @@
         <v>1025</v>
       </c>
       <c r="E215" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>1026</v>
@@ -10816,7 +10791,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B216" t="s">
         <v>1028</v>
@@ -10828,7 +10803,7 @@
         <v>1030</v>
       </c>
       <c r="E216" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>11</v>
@@ -10839,7 +10814,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B217" t="s">
         <v>1032</v>
@@ -10851,7 +10826,7 @@
         <v>1034</v>
       </c>
       <c r="E217" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>1035</v>
@@ -10862,7 +10837,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B218" t="s">
         <v>1037</v>
@@ -10874,7 +10849,7 @@
         <v>1039</v>
       </c>
       <c r="E218" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>1040</v>
@@ -10885,7 +10860,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B219" t="s">
         <v>1042</v>
@@ -10897,7 +10872,7 @@
         <v>1044</v>
       </c>
       <c r="E219" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>1045</v>
@@ -10908,7 +10883,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B220" t="s">
         <v>1047</v>
@@ -10920,7 +10895,7 @@
         <v>1049</v>
       </c>
       <c r="E220" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>1050</v>
@@ -10931,7 +10906,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B221" t="s">
         <v>1052</v>
@@ -10943,7 +10918,7 @@
         <v>1054</v>
       </c>
       <c r="E221" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>1055</v>
@@ -10954,7 +10929,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B222" t="s">
         <v>1057</v>
@@ -10966,7 +10941,7 @@
         <v>1059</v>
       </c>
       <c r="E222" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>1060</v>
@@ -10977,7 +10952,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B223" t="s">
         <v>1062</v>
@@ -10989,7 +10964,7 @@
         <v>1064</v>
       </c>
       <c r="E223" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>482</v>
@@ -11000,7 +10975,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B224" t="s">
         <v>1066</v>
@@ -11012,7 +10987,7 @@
         <v>1068</v>
       </c>
       <c r="E224" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>1069</v>
@@ -11023,7 +10998,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B225" t="s">
         <v>1071</v>
@@ -11035,7 +11010,7 @@
         <v>1073</v>
       </c>
       <c r="E225" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>1074</v>
@@ -11046,7 +11021,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B226" t="s">
         <v>1076</v>
@@ -11058,7 +11033,7 @@
         <v>15</v>
       </c>
       <c r="E226" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>1078</v>
@@ -11069,7 +11044,7 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B227" t="s">
         <v>1080</v>
@@ -11081,7 +11056,7 @@
         <v>1082</v>
       </c>
       <c r="E227" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>1083</v>
@@ -11092,7 +11067,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B228" t="s">
         <v>1085</v>
@@ -11104,7 +11079,7 @@
         <v>1087</v>
       </c>
       <c r="E228" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>1088</v>
@@ -11115,7 +11090,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B229" t="s">
         <v>1090</v>
@@ -11127,7 +11102,7 @@
         <v>1092</v>
       </c>
       <c r="E229" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>732</v>
@@ -11138,7 +11113,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B230" t="s">
         <v>1094</v>
@@ -11150,7 +11125,7 @@
         <v>1096</v>
       </c>
       <c r="E230" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>1097</v>
@@ -11161,7 +11136,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B231" t="s">
         <v>1099</v>
@@ -11173,7 +11148,7 @@
         <v>1101</v>
       </c>
       <c r="E231" t="s">
-        <v>1616</v>
+        <v>1611</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>1102</v>
@@ -11184,7 +11159,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B232" t="s">
         <v>1104</v>
@@ -11196,7 +11171,7 @@
         <v>1106</v>
       </c>
       <c r="E232" t="s">
-        <v>1617</v>
+        <v>1612</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>1107</v>
@@ -11207,7 +11182,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B233" t="s">
         <v>1109</v>
@@ -11219,7 +11194,7 @@
         <v>1111</v>
       </c>
       <c r="E233" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="F233" s="2" t="s">
         <v>1112</v>
@@ -11230,7 +11205,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B234" t="s">
         <v>1114</v>
@@ -11242,7 +11217,7 @@
         <v>1116</v>
       </c>
       <c r="E234" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="F234" s="2" t="s">
         <v>1117</v>
@@ -11253,7 +11228,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B235" t="s">
         <v>1121</v>
@@ -11265,7 +11240,7 @@
         <v>1123</v>
       </c>
       <c r="E235" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>1124</v>
@@ -11276,7 +11251,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B236" t="s">
         <v>1126</v>
@@ -11288,7 +11263,7 @@
         <v>1128</v>
       </c>
       <c r="E236" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
       <c r="F236" s="2" t="s">
         <v>1129</v>
@@ -11299,7 +11274,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B237" t="s">
         <v>1131</v>
@@ -11311,7 +11286,7 @@
         <v>1133</v>
       </c>
       <c r="E237" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>1134</v>
@@ -11322,7 +11297,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B238" t="s">
         <v>1136</v>
@@ -11334,7 +11309,7 @@
         <v>1138</v>
       </c>
       <c r="E238" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="F238" s="2" t="s">
         <v>1139</v>
@@ -11345,7 +11320,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B239" t="s">
         <v>1141</v>
@@ -11357,7 +11332,7 @@
         <v>1143</v>
       </c>
       <c r="E239" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>1144</v>
@@ -11368,7 +11343,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B240" t="s">
         <v>1146</v>
@@ -11380,7 +11355,7 @@
         <v>8</v>
       </c>
       <c r="E240" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>1148</v>
@@ -11391,7 +11366,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B241" t="s">
         <v>1150</v>
@@ -11403,7 +11378,7 @@
         <v>1152</v>
       </c>
       <c r="E241" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>1153</v>
@@ -11414,7 +11389,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B242" t="s">
         <v>1155</v>
@@ -11426,7 +11401,7 @@
         <v>1157</v>
       </c>
       <c r="E242" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="F242" s="2" t="s">
         <v>1158</v>
@@ -11437,7 +11412,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B243" t="s">
         <v>1160</v>
@@ -11449,7 +11424,7 @@
         <v>1162</v>
       </c>
       <c r="E243" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>1163</v>
@@ -11460,7 +11435,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B244" t="s">
         <v>1165</v>
@@ -11472,7 +11447,7 @@
         <v>1167</v>
       </c>
       <c r="E244" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>1168</v>
@@ -11483,7 +11458,7 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B245" t="s">
         <v>1175</v>
@@ -11495,7 +11470,7 @@
         <v>1177</v>
       </c>
       <c r="E245" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
       <c r="F245" s="2" t="s">
         <v>1178</v>
@@ -11506,7 +11481,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B246" t="s">
         <v>1180</v>
@@ -11518,7 +11493,7 @@
         <v>1182</v>
       </c>
       <c r="E246" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>1183</v>
@@ -11529,7 +11504,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B247" t="s">
         <v>1185</v>
@@ -11541,7 +11516,7 @@
         <v>688</v>
       </c>
       <c r="E247" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>1187</v>
@@ -11552,7 +11527,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B248" t="s">
         <v>1189</v>
@@ -11564,7 +11539,7 @@
         <v>1191</v>
       </c>
       <c r="E248" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>6</v>
@@ -11575,7 +11550,7 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B249" t="s">
         <v>1193</v>
@@ -11587,7 +11562,7 @@
         <v>1195</v>
       </c>
       <c r="E249" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>1196</v>
@@ -11598,7 +11573,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B250" t="s">
         <v>1198</v>
@@ -11610,7 +11585,7 @@
         <v>1200</v>
       </c>
       <c r="E250" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>1201</v>
@@ -11621,7 +11596,7 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B251" t="s">
         <v>1203</v>
@@ -11633,7 +11608,7 @@
         <v>1205</v>
       </c>
       <c r="E251" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="F251" s="2" t="s">
         <v>1206</v>
@@ -11644,7 +11619,7 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B252" t="s">
         <v>1208</v>
@@ -11656,7 +11631,7 @@
         <v>1210</v>
       </c>
       <c r="E252" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>1211</v>
@@ -11667,7 +11642,7 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B253" t="s">
         <v>1213</v>
@@ -11679,7 +11654,7 @@
         <v>1215</v>
       </c>
       <c r="E253" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>1216</v>
@@ -11690,7 +11665,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B254" t="s">
         <v>1218</v>
@@ -11702,7 +11677,7 @@
         <v>1220</v>
       </c>
       <c r="E254" t="s">
-        <v>1637</v>
+        <v>1632</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>7</v>
@@ -11713,7 +11688,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="B255" t="s">
         <v>1222</v>
@@ -11725,7 +11700,7 @@
         <v>3</v>
       </c>
       <c r="E255" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>1224</v>
@@ -11736,7 +11711,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B256" t="s">
         <v>1226</v>
@@ -11748,7 +11723,7 @@
         <v>1228</v>
       </c>
       <c r="E256" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>1106</v>
@@ -11759,7 +11734,7 @@
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B257" t="s">
         <v>1230</v>
@@ -11771,7 +11746,7 @@
         <v>1232</v>
       </c>
       <c r="E257" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>1233</v>
@@ -11782,7 +11757,7 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B258" t="s">
         <v>1235</v>
@@ -11794,7 +11769,7 @@
         <v>1237</v>
       </c>
       <c r="E258" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>1238</v>
@@ -11805,7 +11780,7 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B259" t="s">
         <v>1240</v>
@@ -11817,7 +11792,7 @@
         <v>1242</v>
       </c>
       <c r="E259" t="s">
-        <v>1642</v>
+        <v>1637</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>1243</v>
@@ -11828,7 +11803,7 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B260" t="s">
         <v>1245</v>
@@ -11840,7 +11815,7 @@
         <v>1247</v>
       </c>
       <c r="E260" t="s">
-        <v>1643</v>
+        <v>1638</v>
       </c>
       <c r="F260" s="2" t="s">
         <v>1248</v>
@@ -11851,7 +11826,7 @@
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B261" t="s">
         <v>1250</v>
@@ -11863,7 +11838,7 @@
         <v>1252</v>
       </c>
       <c r="E261" t="s">
-        <v>1644</v>
+        <v>1639</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>1253</v>
@@ -11874,7 +11849,7 @@
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B262" t="s">
         <v>1255</v>
@@ -11886,7 +11861,7 @@
         <v>1257</v>
       </c>
       <c r="E262" t="s">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="F262" s="2" t="s">
         <v>1258</v>
@@ -11897,7 +11872,7 @@
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B263" t="s">
         <v>1260</v>
@@ -11909,7 +11884,7 @@
         <v>1262</v>
       </c>
       <c r="E263" t="s">
-        <v>1646</v>
+        <v>1641</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>1263</v>
@@ -11920,7 +11895,7 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="B264" t="s">
         <v>1266</v>
@@ -11932,7 +11907,7 @@
         <v>1268</v>
       </c>
       <c r="E264" t="s">
-        <v>1647</v>
+        <v>1642</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>1269</v>
@@ -11943,30 +11918,30 @@
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B265" t="s">
         <v>1271</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>1272</v>
       </c>
       <c r="E265" t="s">
-        <v>1664</v>
+        <v>1659</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>1273</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B266" t="s">
         <v>1274</v>
@@ -11978,7 +11953,7 @@
         <v>1276</v>
       </c>
       <c r="E266" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>1277</v>
@@ -11989,7 +11964,7 @@
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B267" t="s">
         <v>1279</v>
@@ -12001,7 +11976,7 @@
         <v>1248</v>
       </c>
       <c r="E267" t="s">
-        <v>1648</v>
+        <v>1643</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>4</v>
@@ -12012,7 +11987,7 @@
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B268" t="s">
         <v>1282</v>
@@ -12024,7 +11999,7 @@
         <v>1284</v>
       </c>
       <c r="E268" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="F268" s="2" t="s">
         <v>1285</v>
@@ -12035,7 +12010,7 @@
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B269" t="s">
         <v>1287</v>
@@ -12047,7 +12022,7 @@
         <v>1289</v>
       </c>
       <c r="E269" t="s">
-        <v>1649</v>
+        <v>1644</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>1290</v>
@@ -12056,12 +12031,12 @@
         <v>1291</v>
       </c>
       <c r="L269" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="B270" t="s">
         <v>1292</v>
@@ -12073,7 +12048,7 @@
         <v>1294</v>
       </c>
       <c r="E270" t="s">
-        <v>1650</v>
+        <v>1645</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>1295</v>
@@ -12084,7 +12059,7 @@
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="B271" t="s">
         <v>1297</v>
@@ -12096,7 +12071,7 @@
         <v>1299</v>
       </c>
       <c r="E271" t="s">
-        <v>1651</v>
+        <v>1646</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>1300</v>
@@ -12107,7 +12082,7 @@
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B272" t="s">
         <v>1302</v>
@@ -12119,582 +12094,559 @@
         <v>1304</v>
       </c>
       <c r="E272" t="s">
-        <v>1652</v>
+        <v>1647</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>1305</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1306</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B273" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C273" s="1" t="s">
         <v>1307</v>
       </c>
-      <c r="C273" s="1" t="s">
+      <c r="D273" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="D273" s="1" t="s">
+      <c r="E273" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>1309</v>
       </c>
-      <c r="E273" t="s">
-        <v>1653</v>
-      </c>
-      <c r="F273" s="2" t="s">
+      <c r="G273" s="1" t="s">
         <v>1310</v>
-      </c>
-      <c r="G273" s="1" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B274" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C274" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="C274" s="1" t="s">
+      <c r="D274" s="1" t="s">
         <v>1313</v>
       </c>
-      <c r="D274" s="1" t="s">
+      <c r="E274" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F274" s="2" t="s">
         <v>1314</v>
       </c>
-      <c r="E274" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F274" s="2" t="s">
+      <c r="G274" s="1" t="s">
         <v>1315</v>
-      </c>
-      <c r="G274" s="1" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B275" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C275" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="C275" s="1" t="s">
+      <c r="D275" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="D275" s="1" t="s">
+      <c r="E275" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>1319</v>
       </c>
-      <c r="E275" t="s">
-        <v>1598</v>
-      </c>
-      <c r="F275" s="2" t="s">
+      <c r="G275" s="1" t="s">
         <v>1320</v>
-      </c>
-      <c r="G275" s="1" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B276" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C276" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="C276" s="1" t="s">
+      <c r="D276" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="D276" s="1" t="s">
-        <v>1324</v>
-      </c>
       <c r="E276" t="s">
-        <v>1654</v>
+        <v>1649</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>1265</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B277" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C277" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="C277" s="1" t="s">
+      <c r="D277" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="D277" s="1" t="s">
+      <c r="E277" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F277" s="2" t="s">
         <v>1328</v>
       </c>
-      <c r="E277" t="s">
-        <v>1492</v>
-      </c>
-      <c r="F277" s="2" t="s">
+      <c r="G277" s="1" t="s">
         <v>1329</v>
-      </c>
-      <c r="G277" s="1" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="278" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B278" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C278" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="C278" s="1" t="s">
+      <c r="D278" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="D278" s="1" t="s">
+      <c r="E278" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>1333</v>
       </c>
-      <c r="E278" t="s">
-        <v>1492</v>
-      </c>
-      <c r="F278" s="2" t="s">
+      <c r="G278" s="1" t="s">
         <v>1334</v>
-      </c>
-      <c r="G278" s="1" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B279" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C279" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="C279" s="1" t="s">
+      <c r="D279" s="1" t="s">
         <v>1337</v>
       </c>
-      <c r="D279" s="1" t="s">
+      <c r="E279" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F279" s="2" t="s">
         <v>1338</v>
       </c>
-      <c r="E279" t="s">
-        <v>1655</v>
-      </c>
-      <c r="F279" s="2" t="s">
+      <c r="G279" s="1" t="s">
         <v>1339</v>
-      </c>
-      <c r="G279" s="1" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B280" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C280" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="C280" s="1" t="s">
+      <c r="D280" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="D280" s="1" t="s">
+      <c r="E280" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F280" s="2" t="s">
         <v>1343</v>
       </c>
-      <c r="E280" t="s">
-        <v>1505</v>
-      </c>
-      <c r="F280" s="2" t="s">
+      <c r="G280" s="1" t="s">
         <v>1344</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B281" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C281" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="C281" s="1" t="s">
+      <c r="D281" s="1" t="s">
         <v>1347</v>
       </c>
-      <c r="D281" s="1" t="s">
+      <c r="E281" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F281" s="2" t="s">
         <v>1348</v>
       </c>
-      <c r="E281" t="s">
-        <v>1490</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>1349</v>
-      </c>
       <c r="G281" s="1" t="s">
-        <v>1724</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B282" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C282" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="C282" s="1" t="s">
+      <c r="D282" s="1" t="s">
         <v>1351</v>
       </c>
-      <c r="D282" s="1" t="s">
+      <c r="E282" t="s">
+        <v>1523</v>
+      </c>
+      <c r="F282" s="2" t="s">
         <v>1352</v>
       </c>
-      <c r="E282" t="s">
-        <v>1528</v>
-      </c>
-      <c r="F282" s="2" t="s">
+      <c r="G282" s="1" t="s">
         <v>1353</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B283" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C283" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="C283" s="1" t="s">
+      <c r="D283" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="D283" s="1" t="s">
+      <c r="E283" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>1357</v>
       </c>
-      <c r="E283" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F283" s="2" t="s">
+      <c r="G283" s="1" t="s">
         <v>1358</v>
-      </c>
-      <c r="G283" s="1" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="284" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B284" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C284" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="C284" s="1" t="s">
+      <c r="D284" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="D284" s="1" t="s">
-        <v>1362</v>
-      </c>
       <c r="E284" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>154</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B285" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C285" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="C285" s="1" t="s">
+      <c r="D285" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="D285" s="1" t="s">
+      <c r="E285" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F285" s="2" t="s">
         <v>1366</v>
       </c>
-      <c r="E285" t="s">
-        <v>1658</v>
-      </c>
-      <c r="F285" s="2" t="s">
+      <c r="G285" s="1" t="s">
         <v>1367</v>
-      </c>
-      <c r="G285" s="1" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B286" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C286" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="C286" s="1" t="s">
+      <c r="D286" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="D286" s="1" t="s">
+      <c r="E286" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F286" s="2" t="s">
         <v>1371</v>
       </c>
-      <c r="E286" t="s">
-        <v>1659</v>
-      </c>
-      <c r="F286" s="2" t="s">
+      <c r="G286" s="1" t="s">
         <v>1372</v>
-      </c>
-      <c r="G286" s="1" t="s">
-        <v>1373</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B287" t="s">
         <v>1119</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>1120</v>
       </c>
       <c r="E287" t="s">
-        <v>1660</v>
+        <v>1655</v>
       </c>
       <c r="F287" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G287" s="1" t="s">
         <v>1375</v>
-      </c>
-      <c r="G287" s="1" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B288" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>1377</v>
       </c>
-      <c r="C288" s="1" t="s">
-        <v>1722</v>
-      </c>
-      <c r="D288" s="1" t="s">
+      <c r="E288" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F288" s="2" t="s">
         <v>1378</v>
       </c>
-      <c r="E288" t="s">
-        <v>1512</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>1379</v>
-      </c>
       <c r="G288" s="1" t="s">
-        <v>1723</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B289" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C289" s="1" t="s">
         <v>1380</v>
       </c>
-      <c r="C289" s="1" t="s">
+      <c r="D289" s="1" t="s">
         <v>1381</v>
       </c>
-      <c r="D289" s="1" t="s">
+      <c r="E289" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>1382</v>
       </c>
-      <c r="E289" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F289" s="2" t="s">
+      <c r="G289" s="1" t="s">
         <v>1383</v>
-      </c>
-      <c r="G289" s="1" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="290" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B290" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C290" s="1" t="s">
         <v>1385</v>
       </c>
-      <c r="C290" s="1" t="s">
+      <c r="D290" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="D290" s="1" t="s">
+      <c r="E290" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>1387</v>
       </c>
-      <c r="E290" t="s">
-        <v>1533</v>
-      </c>
-      <c r="F290" s="2" t="s">
+      <c r="G290" s="1" t="s">
         <v>1388</v>
-      </c>
-      <c r="G290" s="1" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B291" t="s">
         <v>1213</v>
       </c>
       <c r="C291" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D291" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="D291" s="1" t="s">
+      <c r="E291" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F291" s="2" t="s">
         <v>1391</v>
       </c>
-      <c r="E291" t="s">
-        <v>1662</v>
-      </c>
-      <c r="F291" s="2" t="s">
+      <c r="G291" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="G291" s="1" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="B292" t="s">
-        <v>1394</v>
+        <v>1150</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>1395</v>
+        <v>1151</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>1030</v>
+        <v>1152</v>
       </c>
       <c r="E292" t="s">
-        <v>1604</v>
+        <v>1619</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>1396</v>
+        <v>1153</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>1413</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
-        <v>1407</v>
-      </c>
-      <c r="B293" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C293" s="1" t="s">
-        <v>1151</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="E293" t="s">
-        <v>1624</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G293" s="1" t="s">
-        <v>1154</v>
+      <c r="A293" s="5" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D293" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E293" s="6" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F293" s="8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G293" s="7" t="s">
+        <v>1174</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" s="5" t="s">
-        <v>1407</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C294" s="7" t="s">
-        <v>1171</v>
-      </c>
-      <c r="D294" s="7" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E294" s="6" t="s">
-        <v>1627</v>
-      </c>
-      <c r="F294" s="8" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G294" s="7" t="s">
-        <v>1174</v>
+      <c r="A294" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B294" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E294" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F294" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G294" s="1" t="s">
+        <v>1716</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B295" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="E295" t="s">
-        <v>1494</v>
+        <v>1643</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>1721</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B296" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="E296" t="s">
-        <v>1648</v>
+        <v>1658</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>1163</v>
+        <v>1714</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
-        <v>1407</v>
-      </c>
-      <c r="B297" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>1166</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E297" t="s">
-        <v>1663</v>
-      </c>
-      <c r="F297" s="2" t="s">
-        <v>1719</v>
-      </c>
-      <c r="G297" s="1" t="s">
-        <v>1720</v>
+        <v>1715</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/Russian_Daily_Word.xlsx
+++ b/public/data/Russian_Daily_Word.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Desktop\Git\LearnRussianNew_clean2\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941BE80D-E57A-4085-AFF0-2B4411867529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CB510C-69C4-4851-8A80-D7D86685948C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="1721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="1727">
   <si>
     <t>Topic</t>
   </si>
@@ -2477,9 +2477,6 @@
     <t>מְיוֹד דבש</t>
   </si>
   <si>
-    <t>מֵדוֵודְ אוהב מְיוֹד (דבש)</t>
-  </si>
-  <si>
     <t>волк</t>
   </si>
   <si>
@@ -2552,9 +2549,6 @@
     <t>קריסה</t>
   </si>
   <si>
-    <t>כשיש קריסה של מבנה ישן, תמיד רואים קְרִיסָה יוצאת ממנו!</t>
-  </si>
-  <si>
     <t>еж</t>
   </si>
   <si>
@@ -3315,9 +3309,6 @@
   </si>
   <si>
     <t>ירוק</t>
-  </si>
-  <si>
-    <t>כשאני מוצא משהו זול, מיד אני שולף את השטר זִלוֹנִי מהארנק ומשלם בלי לחשוב פעמיים</t>
   </si>
   <si>
     <t>чёрный</t>
@@ -5434,6 +5425,33 @@
   </si>
   <si>
     <t xml:space="preserve">הסתכלתי על הלִיצוֹ של הליצן, וצחקתי מהאיפור המצחיק. </t>
+  </si>
+  <si>
+    <t>губы</t>
+  </si>
+  <si>
+    <t>גוּבִּי</t>
+  </si>
+  <si>
+    <t>שפתיים</t>
+  </si>
+  <si>
+    <t>גומי</t>
+  </si>
+  <si>
+    <t>כשאני מוצא משהו זול, מיד אני שולף את השטר ה-זִלוֹנִי מהארנק וקונה אותו</t>
+  </si>
+  <si>
+    <t>💋</t>
+  </si>
+  <si>
+    <t>כשמתנשקים ה גוּבִּי מרגישות כמו גומי</t>
+  </si>
+  <si>
+    <t>מֵדוֵודְ אוהב מְיוֹד (דבש ברוסית)</t>
+  </si>
+  <si>
+    <t>כשיש קריסה של מבנה ישן, עדיין אפשר לראות קְרִיסָה מסתובבת לידו</t>
   </si>
 </sst>
 </file>
@@ -5510,7 +5528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -5530,6 +5548,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5832,7 +5851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L296"/>
+  <dimension ref="A1:L298"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -5849,27 +5868,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>1413</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>1416</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -5881,7 +5900,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>19</v>
@@ -5892,7 +5911,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -5904,7 +5923,7 @@
         <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>24</v>
@@ -5915,7 +5934,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -5927,18 +5946,18 @@
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -5950,18 +5969,18 @@
         <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
@@ -5973,18 +5992,18 @@
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B7" t="s">
         <v>37</v>
@@ -5996,30 +6015,30 @@
         <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>43</v>
@@ -6030,30 +6049,30 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B9" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
@@ -6065,7 +6084,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>50</v>
@@ -6076,7 +6095,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B11" t="s">
         <v>52</v>
@@ -6088,41 +6107,41 @@
         <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B13" t="s">
         <v>58</v>
@@ -6134,18 +6153,18 @@
         <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B14" t="s">
         <v>61</v>
@@ -6157,7 +6176,7 @@
         <v>63</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>64</v>
@@ -6168,7 +6187,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B15" t="s">
         <v>66</v>
@@ -6180,7 +6199,7 @@
         <v>68</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
@@ -6191,7 +6210,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
@@ -6203,7 +6222,7 @@
         <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>74</v>
@@ -6214,7 +6233,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B17" t="s">
         <v>76</v>
@@ -6226,7 +6245,7 @@
         <v>78</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
@@ -6237,7 +6256,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B18" t="s">
         <v>81</v>
@@ -6249,7 +6268,7 @@
         <v>83</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -6260,7 +6279,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B19" t="s">
         <v>86</v>
@@ -6272,7 +6291,7 @@
         <v>88</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>89</v>
@@ -6283,7 +6302,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B20" t="s">
         <v>91</v>
@@ -6295,7 +6314,7 @@
         <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>94</v>
@@ -6306,7 +6325,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B21" t="s">
         <v>96</v>
@@ -6318,18 +6337,18 @@
         <v>98</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>99</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B22" t="s">
         <v>100</v>
@@ -6341,7 +6360,7 @@
         <v>102</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>103</v>
@@ -6352,30 +6371,30 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B23" t="s">
         <v>105</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>106</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>107</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B24" t="s">
         <v>108</v>
@@ -6387,7 +6406,7 @@
         <v>110</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>111</v>
@@ -6398,7 +6417,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B25" t="s">
         <v>113</v>
@@ -6410,7 +6429,7 @@
         <v>115</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>116</v>
@@ -6421,7 +6440,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B26" t="s">
         <v>118</v>
@@ -6433,7 +6452,7 @@
         <v>120</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>121</v>
@@ -6444,7 +6463,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B27" t="s">
         <v>123</v>
@@ -6456,7 +6475,7 @@
         <v>125</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>126</v>
@@ -6467,7 +6486,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B28" t="s">
         <v>128</v>
@@ -6479,7 +6498,7 @@
         <v>130</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>131</v>
@@ -6490,7 +6509,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B29" t="s">
         <v>133</v>
@@ -6502,7 +6521,7 @@
         <v>135</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>136</v>
@@ -6513,7 +6532,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B30" t="s">
         <v>138</v>
@@ -6525,7 +6544,7 @@
         <v>140</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>141</v>
@@ -6536,7 +6555,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B31" t="s">
         <v>143</v>
@@ -6548,7 +6567,7 @@
         <v>145</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>146</v>
@@ -6559,7 +6578,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B32" t="s">
         <v>148</v>
@@ -6571,18 +6590,18 @@
         <v>150</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>151</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B33" t="s">
         <v>152</v>
@@ -6594,7 +6613,7 @@
         <v>154</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>155</v>
@@ -6605,7 +6624,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B34" t="s">
         <v>157</v>
@@ -6617,7 +6636,7 @@
         <v>159</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>160</v>
@@ -6628,7 +6647,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B35" t="s">
         <v>162</v>
@@ -6640,7 +6659,7 @@
         <v>164</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>165</v>
@@ -6651,7 +6670,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B36" t="s">
         <v>167</v>
@@ -6663,7 +6682,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>169</v>
@@ -6674,7 +6693,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B37" t="s">
         <v>171</v>
@@ -6686,7 +6705,7 @@
         <v>173</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>174</v>
@@ -6697,7 +6716,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B38" t="s">
         <v>176</v>
@@ -6709,7 +6728,7 @@
         <v>178</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>5</v>
@@ -6720,7 +6739,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B39" t="s">
         <v>180</v>
@@ -6732,7 +6751,7 @@
         <v>182</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>183</v>
@@ -6743,7 +6762,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B40" t="s">
         <v>185</v>
@@ -6755,7 +6774,7 @@
         <v>187</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>188</v>
@@ -6766,7 +6785,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B41" t="s">
         <v>190</v>
@@ -6778,7 +6797,7 @@
         <v>192</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>193</v>
@@ -6789,7 +6808,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B42" t="s">
         <v>195</v>
@@ -6801,7 +6820,7 @@
         <v>197</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>198</v>
@@ -6812,7 +6831,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B43" t="s">
         <v>200</v>
@@ -6824,7 +6843,7 @@
         <v>202</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>203</v>
@@ -6835,7 +6854,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B44" t="s">
         <v>205</v>
@@ -6847,7 +6866,7 @@
         <v>207</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>208</v>
@@ -6858,7 +6877,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B45" t="s">
         <v>210</v>
@@ -6870,18 +6889,18 @@
         <v>212</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>213</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B46" t="s">
         <v>214</v>
@@ -6893,7 +6912,7 @@
         <v>216</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>217</v>
@@ -6904,7 +6923,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B47" t="s">
         <v>219</v>
@@ -6916,7 +6935,7 @@
         <v>221</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>222</v>
@@ -6927,7 +6946,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B48" t="s">
         <v>224</v>
@@ -6939,7 +6958,7 @@
         <v>226</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>227</v>
@@ -6950,7 +6969,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B49" t="s">
         <v>229</v>
@@ -6962,7 +6981,7 @@
         <v>231</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>232</v>
@@ -6973,7 +6992,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B50" t="s">
         <v>234</v>
@@ -6985,7 +7004,7 @@
         <v>236</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>237</v>
@@ -6996,7 +7015,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B51" t="s">
         <v>239</v>
@@ -7008,7 +7027,7 @@
         <v>241</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>242</v>
@@ -7019,7 +7038,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B52" t="s">
         <v>244</v>
@@ -7031,7 +7050,7 @@
         <v>246</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>247</v>
@@ -7042,7 +7061,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B53" t="s">
         <v>249</v>
@@ -7054,18 +7073,18 @@
         <v>251</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B54" t="s">
         <v>252</v>
@@ -7077,18 +7096,18 @@
         <v>254</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>255</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B55" t="s">
         <v>256</v>
@@ -7100,7 +7119,7 @@
         <v>258</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>259</v>
@@ -7111,7 +7130,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B56" t="s">
         <v>261</v>
@@ -7123,7 +7142,7 @@
         <v>263</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>264</v>
@@ -7134,7 +7153,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B57" t="s">
         <v>266</v>
@@ -7146,7 +7165,7 @@
         <v>268</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>269</v>
@@ -7157,7 +7176,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B58" t="s">
         <v>271</v>
@@ -7169,7 +7188,7 @@
         <v>273</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>274</v>
@@ -7180,7 +7199,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B59" t="s">
         <v>276</v>
@@ -7192,7 +7211,7 @@
         <v>278</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>279</v>
@@ -7203,7 +7222,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B60" t="s">
         <v>281</v>
@@ -7215,7 +7234,7 @@
         <v>283</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>284</v>
@@ -7226,7 +7245,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B61" t="s">
         <v>286</v>
@@ -7238,7 +7257,7 @@
         <v>288</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>289</v>
@@ -7249,7 +7268,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B62" t="s">
         <v>291</v>
@@ -7261,7 +7280,7 @@
         <v>293</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>294</v>
@@ -7272,7 +7291,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B63" t="s">
         <v>296</v>
@@ -7281,10 +7300,10 @@
         <v>297</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>298</v>
@@ -7295,7 +7314,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B64" t="s">
         <v>300</v>
@@ -7307,7 +7326,7 @@
         <v>302</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>2</v>
@@ -7318,7 +7337,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B65" t="s">
         <v>304</v>
@@ -7330,7 +7349,7 @@
         <v>306</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>307</v>
@@ -7341,7 +7360,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B66" t="s">
         <v>309</v>
@@ -7353,7 +7372,7 @@
         <v>311</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>312</v>
@@ -7364,7 +7383,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B67" t="s">
         <v>314</v>
@@ -7376,7 +7395,7 @@
         <v>316</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>317</v>
@@ -7387,7 +7406,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B68" t="s">
         <v>319</v>
@@ -7399,18 +7418,18 @@
         <v>321</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>322</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B69" t="s">
         <v>323</v>
@@ -7422,7 +7441,7 @@
         <v>325</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>326</v>
@@ -7433,7 +7452,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B70" t="s">
         <v>328</v>
@@ -7445,7 +7464,7 @@
         <v>330</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>331</v>
@@ -7456,7 +7475,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B71" t="s">
         <v>333</v>
@@ -7468,7 +7487,7 @@
         <v>335</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>336</v>
@@ -7479,7 +7498,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B72" t="s">
         <v>338</v>
@@ -7491,7 +7510,7 @@
         <v>340</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>341</v>
@@ -7502,7 +7521,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B73" t="s">
         <v>343</v>
@@ -7514,7 +7533,7 @@
         <v>345</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>346</v>
@@ -7525,7 +7544,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B74" t="s">
         <v>348</v>
@@ -7537,7 +7556,7 @@
         <v>350</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>351</v>
@@ -7548,7 +7567,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B75" t="s">
         <v>353</v>
@@ -7560,18 +7579,18 @@
         <v>355</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>356</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B76" t="s">
         <v>357</v>
@@ -7583,7 +7602,7 @@
         <v>359</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>360</v>
@@ -7594,7 +7613,7 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B77" t="s">
         <v>362</v>
@@ -7606,7 +7625,7 @@
         <v>364</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>365</v>
@@ -7617,7 +7636,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B78" t="s">
         <v>367</v>
@@ -7629,7 +7648,7 @@
         <v>369</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>370</v>
@@ -7640,30 +7659,30 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B79" t="s">
         <v>372</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>373</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>374</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B80" t="s">
         <v>375</v>
@@ -7675,7 +7694,7 @@
         <v>377</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>378</v>
@@ -7686,7 +7705,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B81" t="s">
         <v>380</v>
@@ -7698,18 +7717,18 @@
         <v>382</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>383</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B82" t="s">
         <v>384</v>
@@ -7721,7 +7740,7 @@
         <v>386</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>387</v>
@@ -7732,7 +7751,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B83" t="s">
         <v>389</v>
@@ -7744,7 +7763,7 @@
         <v>391</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>392</v>
@@ -7755,7 +7774,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B84" t="s">
         <v>394</v>
@@ -7767,7 +7786,7 @@
         <v>396</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
@@ -7778,7 +7797,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B85" t="s">
         <v>398</v>
@@ -7790,7 +7809,7 @@
         <v>400</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>401</v>
@@ -7801,7 +7820,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B86" t="s">
         <v>403</v>
@@ -7813,7 +7832,7 @@
         <v>405</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>406</v>
@@ -7824,7 +7843,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B87" t="s">
         <v>408</v>
@@ -7836,7 +7855,7 @@
         <v>410</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>411</v>
@@ -7847,7 +7866,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B88" t="s">
         <v>413</v>
@@ -7859,18 +7878,18 @@
         <v>415</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>416</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B89" t="s">
         <v>417</v>
@@ -7882,7 +7901,7 @@
         <v>419</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>420</v>
@@ -7893,7 +7912,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B90" t="s">
         <v>422</v>
@@ -7905,7 +7924,7 @@
         <v>424</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>425</v>
@@ -7916,7 +7935,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B91" t="s">
         <v>427</v>
@@ -7928,18 +7947,18 @@
         <v>429</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>430</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B92" t="s">
         <v>431</v>
@@ -7951,7 +7970,7 @@
         <v>433</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>434</v>
@@ -7962,7 +7981,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B93" t="s">
         <v>436</v>
@@ -7974,7 +7993,7 @@
         <v>438</v>
       </c>
       <c r="E93" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>439</v>
@@ -7985,7 +8004,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B94" t="s">
         <v>441</v>
@@ -7997,7 +8016,7 @@
         <v>443</v>
       </c>
       <c r="E94" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>444</v>
@@ -8008,7 +8027,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B95" t="s">
         <v>446</v>
@@ -8020,7 +8039,7 @@
         <v>448</v>
       </c>
       <c r="E95" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>449</v>
@@ -8031,7 +8050,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B96" t="s">
         <v>451</v>
@@ -8043,7 +8062,7 @@
         <v>453</v>
       </c>
       <c r="E96" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>454</v>
@@ -8054,7 +8073,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B97" t="s">
         <v>456</v>
@@ -8066,7 +8085,7 @@
         <v>458</v>
       </c>
       <c r="E97" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>459</v>
@@ -8077,7 +8096,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B98" t="s">
         <v>461</v>
@@ -8089,7 +8108,7 @@
         <v>463</v>
       </c>
       <c r="E98" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>464</v>
@@ -8100,7 +8119,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B99" t="s">
         <v>466</v>
@@ -8112,7 +8131,7 @@
         <v>468</v>
       </c>
       <c r="E99" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>469</v>
@@ -8123,7 +8142,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B100" t="s">
         <v>503</v>
@@ -8135,7 +8154,7 @@
         <v>505</v>
       </c>
       <c r="E100" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>506</v>
@@ -8146,7 +8165,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B101" t="s">
         <v>471</v>
@@ -8158,7 +8177,7 @@
         <v>473</v>
       </c>
       <c r="E101" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>474</v>
@@ -8169,7 +8188,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B102" t="s">
         <v>476</v>
@@ -8181,18 +8200,18 @@
         <v>478</v>
       </c>
       <c r="E102" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>479</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B103" t="s">
         <v>480</v>
@@ -8204,7 +8223,7 @@
         <v>482</v>
       </c>
       <c r="E103" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>483</v>
@@ -8215,7 +8234,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B104" t="s">
         <v>485</v>
@@ -8227,7 +8246,7 @@
         <v>487</v>
       </c>
       <c r="E104" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>488</v>
@@ -8238,7 +8257,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B105" t="s">
         <v>490</v>
@@ -8250,18 +8269,18 @@
         <v>492</v>
       </c>
       <c r="E105" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>493</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B106" t="s">
         <v>494</v>
@@ -8273,7 +8292,7 @@
         <v>496</v>
       </c>
       <c r="E106" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>497</v>
@@ -8284,7 +8303,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B107" t="s">
         <v>499</v>
@@ -8296,18 +8315,18 @@
         <v>501</v>
       </c>
       <c r="E107" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>502</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B108" t="s">
         <v>508</v>
@@ -8319,10 +8338,10 @@
         <v>510</v>
       </c>
       <c r="E108" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>511</v>
@@ -8330,7 +8349,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B109" t="s">
         <v>512</v>
@@ -8342,7 +8361,7 @@
         <v>514</v>
       </c>
       <c r="E109" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>515</v>
@@ -8353,7 +8372,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B110" t="s">
         <v>517</v>
@@ -8365,7 +8384,7 @@
         <v>519</v>
       </c>
       <c r="E110" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
@@ -8376,7 +8395,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B111" t="s">
         <v>521</v>
@@ -8388,7 +8407,7 @@
         <v>523</v>
       </c>
       <c r="E111" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>524</v>
@@ -8399,7 +8418,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B112" t="s">
         <v>526</v>
@@ -8411,7 +8430,7 @@
         <v>528</v>
       </c>
       <c r="E112" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>529</v>
@@ -8422,7 +8441,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B113" t="s">
         <v>531</v>
@@ -8434,7 +8453,7 @@
         <v>533</v>
       </c>
       <c r="E113" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>534</v>
@@ -8445,7 +8464,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B114" t="s">
         <v>536</v>
@@ -8457,7 +8476,7 @@
         <v>538</v>
       </c>
       <c r="E114" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>14</v>
@@ -8468,7 +8487,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B115" t="s">
         <v>540</v>
@@ -8480,18 +8499,18 @@
         <v>542</v>
       </c>
       <c r="E115" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B116" t="s">
         <v>543</v>
@@ -8503,7 +8522,7 @@
         <v>545</v>
       </c>
       <c r="E116" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>283</v>
@@ -8514,7 +8533,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B117" t="s">
         <v>547</v>
@@ -8526,7 +8545,7 @@
         <v>549</v>
       </c>
       <c r="E117" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>550</v>
@@ -8537,7 +8556,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B118" t="s">
         <v>552</v>
@@ -8549,7 +8568,7 @@
         <v>554</v>
       </c>
       <c r="E118" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>555</v>
@@ -8560,7 +8579,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B119" t="s">
         <v>557</v>
@@ -8572,7 +8591,7 @@
         <v>559</v>
       </c>
       <c r="E119" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>9</v>
@@ -8583,7 +8602,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B120" t="s">
         <v>561</v>
@@ -8595,7 +8614,7 @@
         <v>563</v>
       </c>
       <c r="E120" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>564</v>
@@ -8606,7 +8625,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B121" t="s">
         <v>566</v>
@@ -8618,7 +8637,7 @@
         <v>568</v>
       </c>
       <c r="E121" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>569</v>
@@ -8629,7 +8648,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B122" t="s">
         <v>571</v>
@@ -8641,7 +8660,7 @@
         <v>573</v>
       </c>
       <c r="E122" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>574</v>
@@ -8652,7 +8671,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B123" t="s">
         <v>576</v>
@@ -8664,7 +8683,7 @@
         <v>578</v>
       </c>
       <c r="E123" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>579</v>
@@ -8675,7 +8694,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B124" t="s">
         <v>581</v>
@@ -8687,7 +8706,7 @@
         <v>583</v>
       </c>
       <c r="E124" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>12</v>
@@ -8698,7 +8717,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B125" t="s">
         <v>585</v>
@@ -8710,18 +8729,18 @@
         <v>587</v>
       </c>
       <c r="E125" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>588</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B126" t="s">
         <v>589</v>
@@ -8733,7 +8752,7 @@
         <v>591</v>
       </c>
       <c r="E126" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>592</v>
@@ -8744,7 +8763,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B127" t="s">
         <v>594</v>
@@ -8756,7 +8775,7 @@
         <v>596</v>
       </c>
       <c r="E127" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>597</v>
@@ -8767,7 +8786,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B128" t="s">
         <v>599</v>
@@ -8779,7 +8798,7 @@
         <v>601</v>
       </c>
       <c r="E128" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>602</v>
@@ -8790,7 +8809,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B129" t="s">
         <v>604</v>
@@ -8802,7 +8821,7 @@
         <v>606</v>
       </c>
       <c r="E129" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>607</v>
@@ -8813,7 +8832,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B130" t="s">
         <v>609</v>
@@ -8825,7 +8844,7 @@
         <v>611</v>
       </c>
       <c r="E130" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>612</v>
@@ -8836,7 +8855,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B131" t="s">
         <v>614</v>
@@ -8848,7 +8867,7 @@
         <v>616</v>
       </c>
       <c r="E131" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>293</v>
@@ -8859,7 +8878,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B132" t="s">
         <v>618</v>
@@ -8871,7 +8890,7 @@
         <v>620</v>
       </c>
       <c r="E132" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>621</v>
@@ -8882,7 +8901,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B133" t="s">
         <v>623</v>
@@ -8894,7 +8913,7 @@
         <v>625</v>
       </c>
       <c r="E133" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>626</v>
@@ -8905,7 +8924,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B134" t="s">
         <v>628</v>
@@ -8917,7 +8936,7 @@
         <v>630</v>
       </c>
       <c r="E134" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>631</v>
@@ -8928,7 +8947,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B135" t="s">
         <v>633</v>
@@ -8940,7 +8959,7 @@
         <v>635</v>
       </c>
       <c r="E135" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>636</v>
@@ -8951,7 +8970,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B136" t="s">
         <v>638</v>
@@ -8963,7 +8982,7 @@
         <v>640</v>
       </c>
       <c r="E136" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>641</v>
@@ -8974,7 +8993,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B137" t="s">
         <v>643</v>
@@ -8986,7 +9005,7 @@
         <v>645</v>
       </c>
       <c r="E137" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>646</v>
@@ -8997,7 +9016,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B138" t="s">
         <v>648</v>
@@ -9009,7 +9028,7 @@
         <v>650</v>
       </c>
       <c r="E138" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>651</v>
@@ -9020,7 +9039,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B139" t="s">
         <v>653</v>
@@ -9032,7 +9051,7 @@
         <v>655</v>
       </c>
       <c r="E139" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>656</v>
@@ -9043,7 +9062,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B140" t="s">
         <v>658</v>
@@ -9055,18 +9074,18 @@
         <v>660</v>
       </c>
       <c r="E140" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>661</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B141" t="s">
         <v>662</v>
@@ -9078,7 +9097,7 @@
         <v>664</v>
       </c>
       <c r="E141" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>665</v>
@@ -9089,7 +9108,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B142" t="s">
         <v>667</v>
@@ -9101,18 +9120,18 @@
         <v>669</v>
       </c>
       <c r="E142" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>670</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B143" t="s">
         <v>671</v>
@@ -9124,18 +9143,18 @@
         <v>673</v>
       </c>
       <c r="E143" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>674</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B144" t="s">
         <v>675</v>
@@ -9147,7 +9166,7 @@
         <v>677</v>
       </c>
       <c r="E144" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>678</v>
@@ -9158,7 +9177,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B145" t="s">
         <v>680</v>
@@ -9170,7 +9189,7 @@
         <v>682</v>
       </c>
       <c r="E145" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>683</v>
@@ -9181,7 +9200,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B146" t="s">
         <v>685</v>
@@ -9193,7 +9212,7 @@
         <v>687</v>
       </c>
       <c r="E146" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>688</v>
@@ -9204,7 +9223,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B147" t="s">
         <v>690</v>
@@ -9216,7 +9235,7 @@
         <v>692</v>
       </c>
       <c r="E147" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>693</v>
@@ -9227,7 +9246,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B148" t="s">
         <v>695</v>
@@ -9239,18 +9258,18 @@
         <v>697</v>
       </c>
       <c r="E148" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B149" t="s">
         <v>698</v>
@@ -9262,7 +9281,7 @@
         <v>274</v>
       </c>
       <c r="E149" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>700</v>
@@ -9273,7 +9292,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B150" t="s">
         <v>702</v>
@@ -9285,7 +9304,7 @@
         <v>704</v>
       </c>
       <c r="E150" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>4</v>
@@ -9296,7 +9315,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B151" t="s">
         <v>706</v>
@@ -9308,7 +9327,7 @@
         <v>708</v>
       </c>
       <c r="E151" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>709</v>
@@ -9319,7 +9338,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B152" t="s">
         <v>711</v>
@@ -9331,7 +9350,7 @@
         <v>713</v>
       </c>
       <c r="E152" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>714</v>
@@ -9342,7 +9361,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B153" t="s">
         <v>716</v>
@@ -9354,7 +9373,7 @@
         <v>718</v>
       </c>
       <c r="E153" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>719</v>
@@ -9365,7 +9384,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B154" t="s">
         <v>721</v>
@@ -9377,18 +9396,18 @@
         <v>723</v>
       </c>
       <c r="E154" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>724</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B155" t="s">
         <v>725</v>
@@ -9400,18 +9419,18 @@
         <v>727</v>
       </c>
       <c r="E155" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>728</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B156" t="s">
         <v>729</v>
@@ -9423,7 +9442,7 @@
         <v>731</v>
       </c>
       <c r="E156" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>732</v>
@@ -9434,7 +9453,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B157" t="s">
         <v>734</v>
@@ -9446,7 +9465,7 @@
         <v>736</v>
       </c>
       <c r="E157" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>737</v>
@@ -9457,7 +9476,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B158" t="s">
         <v>739</v>
@@ -9469,7 +9488,7 @@
         <v>741</v>
       </c>
       <c r="E158" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>742</v>
@@ -9480,7 +9499,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B159" t="s">
         <v>744</v>
@@ -9492,7 +9511,7 @@
         <v>746</v>
       </c>
       <c r="E159" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>747</v>
@@ -9503,7 +9522,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B160" t="s">
         <v>749</v>
@@ -9515,7 +9534,7 @@
         <v>751</v>
       </c>
       <c r="E160" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>752</v>
@@ -9526,7 +9545,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B161" t="s">
         <v>754</v>
@@ -9538,7 +9557,7 @@
         <v>756</v>
       </c>
       <c r="E161" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>757</v>
@@ -9549,7 +9568,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B162" t="s">
         <v>759</v>
@@ -9561,7 +9580,7 @@
         <v>761</v>
       </c>
       <c r="E162" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>762</v>
@@ -9572,7 +9591,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B163" t="s">
         <v>764</v>
@@ -9584,7 +9603,7 @@
         <v>766</v>
       </c>
       <c r="E163" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>767</v>
@@ -9595,7 +9614,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B164" t="s">
         <v>769</v>
@@ -9607,7 +9626,7 @@
         <v>771</v>
       </c>
       <c r="E164" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>772</v>
@@ -9618,7 +9637,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B165" t="s">
         <v>774</v>
@@ -9630,7 +9649,7 @@
         <v>776</v>
       </c>
       <c r="E165" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>777</v>
@@ -9641,7 +9660,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B166" t="s">
         <v>779</v>
@@ -9653,7 +9672,7 @@
         <v>781</v>
       </c>
       <c r="E166" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>782</v>
@@ -9664,7 +9683,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B167" t="s">
         <v>784</v>
@@ -9676,7 +9695,7 @@
         <v>786</v>
       </c>
       <c r="E167" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>787</v>
@@ -9687,7 +9706,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B168" t="s">
         <v>789</v>
@@ -9699,7 +9718,7 @@
         <v>791</v>
       </c>
       <c r="E168" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>792</v>
@@ -9710,7 +9729,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B169" t="s">
         <v>794</v>
@@ -9722,7 +9741,7 @@
         <v>796</v>
       </c>
       <c r="E169" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>797</v>
@@ -9733,7 +9752,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B170" t="s">
         <v>799</v>
@@ -9745,7 +9764,7 @@
         <v>801</v>
       </c>
       <c r="E170" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>802</v>
@@ -9756,7 +9775,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B171" t="s">
         <v>804</v>
@@ -9768,7 +9787,7 @@
         <v>806</v>
       </c>
       <c r="E171" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>807</v>
@@ -9779,7 +9798,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B172" t="s">
         <v>809</v>
@@ -9791,2862 +9810,2885 @@
         <v>811</v>
       </c>
       <c r="E172" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>812</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>813</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B173" t="s">
+        <v>813</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="C173" s="1" t="s">
+      <c r="D173" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="D173" s="1" t="s">
+      <c r="E173" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F173" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="E173" t="s">
-        <v>1558</v>
-      </c>
-      <c r="F173" s="2" t="s">
+      <c r="G173" s="1" t="s">
         <v>817</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B174" t="s">
+        <v>818</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="C174" s="1" t="s">
+      <c r="D174" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="D174" s="1" t="s">
+      <c r="E174" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="E174" t="s">
-        <v>1559</v>
-      </c>
-      <c r="F174" s="2" t="s">
+      <c r="G174" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B175" t="s">
+        <v>823</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="C175" s="1" t="s">
+      <c r="D175" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="D175" s="1" t="s">
+      <c r="E175" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F175" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="E175" t="s">
-        <v>1560</v>
-      </c>
-      <c r="F175" s="2" t="s">
+      <c r="G175" s="1" t="s">
         <v>827</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B176" t="s">
+        <v>828</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="C176" s="1" t="s">
+      <c r="D176" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="E176" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="E176" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F176" s="2" t="s">
+      <c r="G176" s="1" t="s">
         <v>832</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B177" t="s">
+        <v>833</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="C177" s="1" t="s">
+      <c r="D177" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="E177" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F177" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="E177" t="s">
-        <v>1562</v>
-      </c>
-      <c r="F177" s="2" t="s">
-        <v>837</v>
-      </c>
       <c r="G177" s="1" t="s">
-        <v>838</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B178" t="s">
+        <v>837</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="C178" s="1" t="s">
+      <c r="E178" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F178" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="D178" s="1" t="s">
+      <c r="G178" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="E178" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F178" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="G178" s="1" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B179" t="s">
+        <v>842</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="C179" s="1" t="s">
+      <c r="E179" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F179" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="D179" s="1" t="s">
+      <c r="G179" s="1" t="s">
         <v>846</v>
-      </c>
-      <c r="E179" t="s">
-        <v>1564</v>
-      </c>
-      <c r="F179" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B180" t="s">
+        <v>847</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="E180" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F180" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="G180" s="1" t="s">
         <v>851</v>
-      </c>
-      <c r="E180" t="s">
-        <v>1565</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B181" t="s">
+        <v>852</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="C181" s="1" t="s">
+      <c r="E181" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F181" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="D181" s="1" t="s">
+      <c r="G181" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="E181" t="s">
-        <v>1566</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="G181" s="1" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B182" t="s">
+        <v>857</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="C182" s="1" t="s">
+      <c r="E182" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="D182" s="1" t="s">
+      <c r="G182" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="E182" t="s">
-        <v>1567</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="G182" s="1" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B183" t="s">
+        <v>862</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="C183" s="1" t="s">
+      <c r="E183" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F183" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="D183" s="1" t="s">
+      <c r="G183" s="1" t="s">
         <v>866</v>
-      </c>
-      <c r="E183" t="s">
-        <v>1568</v>
-      </c>
-      <c r="F183" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B184" t="s">
+        <v>867</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="C184" s="1" t="s">
+      <c r="E184" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F184" s="2" t="s">
         <v>870</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="G184" s="1" t="s">
         <v>871</v>
-      </c>
-      <c r="E184" t="s">
-        <v>1569</v>
-      </c>
-      <c r="F184" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B185" t="s">
+        <v>872</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="C185" s="1" t="s">
+      <c r="E185" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F185" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="G185" s="1" t="s">
         <v>876</v>
-      </c>
-      <c r="E185" t="s">
-        <v>1570</v>
-      </c>
-      <c r="F185" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="G185" s="1" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B186" t="s">
+        <v>877</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="C186" s="1" t="s">
+      <c r="E186" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F186" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="G186" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="E186" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F186" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B187" t="s">
+        <v>882</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="C187" s="1" t="s">
+      <c r="E187" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F187" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="D187" s="1" t="s">
+      <c r="G187" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="E187" t="s">
-        <v>1572</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B188" t="s">
+        <v>887</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="C188" s="1" t="s">
+      <c r="E188" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F188" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="D188" s="1" t="s">
+      <c r="G188" s="1" t="s">
         <v>891</v>
-      </c>
-      <c r="E188" t="s">
-        <v>1573</v>
-      </c>
-      <c r="F188" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B189" t="s">
+        <v>892</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="E189" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F189" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="G189" s="1" t="s">
         <v>896</v>
-      </c>
-      <c r="E189" t="s">
-        <v>1574</v>
-      </c>
-      <c r="F189" s="2" t="s">
-        <v>897</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B190" t="s">
+        <v>897</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="C190" s="1" t="s">
+      <c r="E190" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F190" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="D190" s="1" t="s">
+      <c r="G190" s="1" t="s">
         <v>901</v>
-      </c>
-      <c r="E190" t="s">
-        <v>1575</v>
-      </c>
-      <c r="F190" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B191" t="s">
+        <v>902</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>906</v>
-      </c>
       <c r="E191" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>116</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B192" t="s">
+        <v>906</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="E192" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F192" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="G192" s="1" t="s">
         <v>910</v>
-      </c>
-      <c r="E192" t="s">
-        <v>1577</v>
-      </c>
-      <c r="F192" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B193" t="s">
+        <v>911</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="E193" t="s">
+        <v>1575</v>
+      </c>
+      <c r="F193" s="2" t="s">
         <v>914</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="G193" s="1" t="s">
         <v>915</v>
-      </c>
-      <c r="E193" t="s">
-        <v>1578</v>
-      </c>
-      <c r="F193" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B194" t="s">
+        <v>916</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="C194" s="1" t="s">
+      <c r="E194" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F194" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="G194" s="1" t="s">
         <v>920</v>
-      </c>
-      <c r="E194" t="s">
-        <v>1579</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B195" t="s">
+        <v>921</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="E195" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F195" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="G195" s="1" t="s">
         <v>925</v>
-      </c>
-      <c r="E195" t="s">
-        <v>1580</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>926</v>
-      </c>
-      <c r="G195" s="1" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B196" t="s">
+        <v>926</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="C196" s="1" t="s">
+      <c r="E196" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F196" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="D196" s="1" t="s">
+      <c r="G196" s="1" t="s">
         <v>930</v>
-      </c>
-      <c r="E196" t="s">
-        <v>1581</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="G196" s="1" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B197" t="s">
+        <v>931</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="E197" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F197" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="G197" s="1" t="s">
         <v>935</v>
-      </c>
-      <c r="E197" t="s">
-        <v>1551</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="G197" s="1" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B198" t="s">
+        <v>936</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="E198" t="s">
+        <v>1579</v>
+      </c>
+      <c r="F198" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="G198" s="1" t="s">
         <v>940</v>
-      </c>
-      <c r="E198" t="s">
-        <v>1582</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>941</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B199" t="s">
+        <v>941</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="C199" s="1" t="s">
+      <c r="E199" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F199" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="G199" s="1" t="s">
         <v>945</v>
-      </c>
-      <c r="E199" t="s">
-        <v>1583</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>946</v>
-      </c>
-      <c r="G199" s="1" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B200" t="s">
+        <v>946</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="C200" s="1" t="s">
+      <c r="E200" t="s">
+        <v>1581</v>
+      </c>
+      <c r="F200" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="G200" s="1" t="s">
         <v>950</v>
-      </c>
-      <c r="E200" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>951</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B201" t="s">
+        <v>951</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="C201" s="1" t="s">
+      <c r="E201" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F201" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="D201" s="1" t="s">
+      <c r="G201" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="E201" t="s">
-        <v>1559</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B202" t="s">
+        <v>956</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="C202" s="1" t="s">
+      <c r="E202" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F202" s="2" t="s">
         <v>959</v>
       </c>
-      <c r="D202" s="1" t="s">
+      <c r="G202" s="1" t="s">
         <v>960</v>
-      </c>
-      <c r="E202" t="s">
-        <v>1585</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="G202" s="1" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B203" t="s">
+        <v>961</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="E203" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F203" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="G203" s="1" t="s">
         <v>965</v>
-      </c>
-      <c r="E203" t="s">
-        <v>1586</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>966</v>
-      </c>
-      <c r="G203" s="1" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B204" t="s">
+        <v>966</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="C204" s="1" t="s">
+      <c r="E204" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F204" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="D204" s="1" t="s">
+      <c r="G204" s="1" t="s">
         <v>970</v>
-      </c>
-      <c r="E204" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="G204" s="1" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B205" t="s">
+        <v>971</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="C205" s="1" t="s">
+      <c r="E205" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F205" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="G205" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="E205" t="s">
-        <v>1588</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B206" t="s">
+        <v>976</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="C206" s="1" t="s">
+      <c r="E206" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F206" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="G206" s="1" t="s">
         <v>980</v>
-      </c>
-      <c r="E206" t="s">
-        <v>1589</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="G206" s="1" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B207" t="s">
+        <v>981</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="C207" s="1" t="s">
+      <c r="E207" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F207" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="G207" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="E207" t="s">
-        <v>1473</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B208" t="s">
+        <v>986</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="C208" s="1" t="s">
+      <c r="E208" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="G208" s="1" t="s">
         <v>990</v>
-      </c>
-      <c r="E208" t="s">
-        <v>1590</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="G208" s="1" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B209" t="s">
+        <v>991</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="C209" s="1" t="s">
+      <c r="E209" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F209" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="G209" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="E209" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B210" t="s">
+        <v>996</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="C210" s="1" t="s">
+      <c r="E210" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F210" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="G210" s="1" t="s">
         <v>1000</v>
-      </c>
-      <c r="E210" t="s">
-        <v>1592</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G210" s="1" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B211" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="C211" s="1" t="s">
+      <c r="E211" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F211" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="G211" s="1" t="s">
         <v>1005</v>
-      </c>
-      <c r="E211" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B212" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="C212" s="1" t="s">
+      <c r="E212" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F212" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="G212" s="1" t="s">
         <v>1010</v>
-      </c>
-      <c r="E212" t="s">
-        <v>1589</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G212" s="1" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B213" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="C213" s="1" t="s">
+      <c r="E213" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F213" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="G213" s="1" t="s">
         <v>1015</v>
-      </c>
-      <c r="E213" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G213" s="1" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B214" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D214" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="C214" s="1" t="s">
+      <c r="E214" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F214" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="G214" s="1" t="s">
         <v>1020</v>
-      </c>
-      <c r="E214" t="s">
-        <v>1595</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="G214" s="1" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B215" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="C215" s="1" t="s">
+      <c r="E215" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F215" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="G215" s="1" t="s">
         <v>1025</v>
-      </c>
-      <c r="E215" t="s">
-        <v>1521</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G215" s="1" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B216" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>1030</v>
-      </c>
       <c r="E216" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>11</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B217" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="E217" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F217" s="2" t="s">
         <v>1033</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="G217" s="1" t="s">
         <v>1034</v>
-      </c>
-      <c r="E217" t="s">
-        <v>1597</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B218" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D218" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="C218" s="1" t="s">
+      <c r="E218" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F218" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="G218" s="1" t="s">
         <v>1039</v>
-      </c>
-      <c r="E218" t="s">
-        <v>1598</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="G218" s="1" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B219" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="C219" s="1" t="s">
+      <c r="E219" t="s">
+        <v>1596</v>
+      </c>
+      <c r="F219" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="G219" s="1" t="s">
         <v>1044</v>
-      </c>
-      <c r="E219" t="s">
-        <v>1599</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G219" s="1" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B220" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="C220" s="1" t="s">
+      <c r="E220" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F220" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="D220" s="1" t="s">
+      <c r="G220" s="1" t="s">
         <v>1049</v>
-      </c>
-      <c r="E220" t="s">
-        <v>1600</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>1050</v>
-      </c>
-      <c r="G220" s="1" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B221" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="C221" s="1" t="s">
+      <c r="E221" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="D221" s="1" t="s">
+      <c r="G221" s="1" t="s">
         <v>1054</v>
-      </c>
-      <c r="E221" t="s">
-        <v>1601</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B222" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="C222" s="1" t="s">
+      <c r="E222" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="D222" s="1" t="s">
+      <c r="G222" s="1" t="s">
         <v>1059</v>
-      </c>
-      <c r="E222" t="s">
-        <v>1602</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="G222" s="1" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B223" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D223" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>1064</v>
-      </c>
       <c r="E223" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>482</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B224" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D224" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="C224" s="1" t="s">
+      <c r="E224" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="D224" s="1" t="s">
+      <c r="G224" s="1" t="s">
         <v>1068</v>
-      </c>
-      <c r="E224" t="s">
-        <v>1604</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="G224" s="1" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B225" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D225" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="C225" s="1" t="s">
+      <c r="E225" t="s">
+        <v>1602</v>
+      </c>
+      <c r="F225" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="D225" s="1" t="s">
+      <c r="G225" s="1" t="s">
         <v>1073</v>
-      </c>
-      <c r="E225" t="s">
-        <v>1605</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B226" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E226" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B227" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D227" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="C227" s="1" t="s">
+      <c r="E227" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F227" s="2" t="s">
         <v>1081</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="G227" s="1" t="s">
         <v>1082</v>
-      </c>
-      <c r="E227" t="s">
-        <v>1607</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="G227" s="1" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B228" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D228" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="C228" s="1" t="s">
+      <c r="E228" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F228" s="2" t="s">
         <v>1086</v>
       </c>
-      <c r="D228" s="1" t="s">
+      <c r="G228" s="1" t="s">
         <v>1087</v>
-      </c>
-      <c r="E228" t="s">
-        <v>1608</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B229" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>1090</v>
       </c>
-      <c r="C229" s="1" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>1092</v>
-      </c>
       <c r="E229" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>732</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1093</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B230" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E230" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="C230" s="1" t="s">
+      <c r="G230" s="1" t="s">
         <v>1095</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E230" t="s">
-        <v>1610</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>1097</v>
-      </c>
-      <c r="G230" s="1" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B231" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E231" t="s">
+        <v>1608</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="C231" s="1" t="s">
+      <c r="G231" s="1" t="s">
         <v>1100</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E231" t="s">
-        <v>1611</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="G231" s="1" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B232" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>1106</v>
-      </c>
-      <c r="E232" t="s">
-        <v>1612</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G232" s="1" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B233" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
       <c r="E233" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="B234" t="s">
-        <v>1114</v>
+        <v>1106</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="E234" t="s">
-        <v>1614</v>
+        <v>1610</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>1117</v>
+        <v>1109</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>1118</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="B235" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>1122</v>
+        <v>1112</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>1123</v>
+        <v>1113</v>
       </c>
       <c r="E235" t="s">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>1124</v>
+        <v>1114</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1125</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B236" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>1127</v>
+        <v>1119</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
       <c r="E236" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="B237" t="s">
-        <v>1131</v>
+        <v>1123</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
       <c r="E237" t="s">
-        <v>1513</v>
+        <v>1613</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="B238" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
       <c r="E238" t="s">
-        <v>1521</v>
+        <v>1510</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="B239" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>1143</v>
+        <v>1135</v>
       </c>
       <c r="E239" t="s">
-        <v>1617</v>
+        <v>1518</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="B240" t="s">
-        <v>1146</v>
+        <v>1138</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>8</v>
+        <v>1140</v>
       </c>
       <c r="E240" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B241" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>1152</v>
+        <v>8</v>
       </c>
       <c r="E241" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B242" t="s">
-        <v>1155</v>
+        <v>1147</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
       <c r="E242" t="s">
-        <v>1489</v>
+        <v>1616</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B243" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="E243" t="s">
-        <v>1620</v>
+        <v>1486</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B244" t="s">
-        <v>1165</v>
+        <v>1157</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>1166</v>
+        <v>1158</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>1167</v>
+        <v>1159</v>
       </c>
       <c r="E244" t="s">
-        <v>1621</v>
+        <v>1617</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>1168</v>
+        <v>1160</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B245" t="s">
-        <v>1175</v>
+        <v>1162</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>1176</v>
+        <v>1163</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>1177</v>
+        <v>1164</v>
       </c>
       <c r="E245" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1178</v>
+        <v>1165</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1179</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B246" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>1182</v>
+        <v>1174</v>
       </c>
       <c r="E246" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B247" t="s">
-        <v>1185</v>
+        <v>1177</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>1186</v>
+        <v>1178</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>688</v>
+        <v>1179</v>
       </c>
       <c r="E247" t="s">
-        <v>1625</v>
+        <v>1621</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B248" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>1191</v>
+        <v>688</v>
       </c>
       <c r="E248" t="s">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>6</v>
+        <v>1184</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B249" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="E249" t="s">
-        <v>1627</v>
+        <v>1623</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>1196</v>
+        <v>6</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B250" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="E250" t="s">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>1201</v>
+        <v>1193</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1202</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B251" t="s">
-        <v>1203</v>
+        <v>1195</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>1204</v>
+        <v>1196</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
       <c r="E251" t="s">
-        <v>1629</v>
+        <v>1625</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>1206</v>
+        <v>1198</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B252" t="s">
-        <v>1208</v>
+        <v>1200</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>1209</v>
+        <v>1201</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>1210</v>
+        <v>1202</v>
       </c>
       <c r="E252" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>1211</v>
+        <v>1203</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1212</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="B253" t="s">
-        <v>1213</v>
+        <v>1205</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>1214</v>
+        <v>1206</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1215</v>
+        <v>1207</v>
       </c>
       <c r="E253" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>1216</v>
+        <v>1208</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="B254" t="s">
-        <v>1218</v>
+        <v>1210</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>1219</v>
+        <v>1211</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1220</v>
+        <v>1212</v>
       </c>
       <c r="E254" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>7</v>
+        <v>1213</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1221</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B255" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>1223</v>
+        <v>1216</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>3</v>
+        <v>1217</v>
       </c>
       <c r="E255" t="s">
-        <v>1633</v>
+        <v>1629</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>1224</v>
+        <v>7</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1225</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B256" t="s">
-        <v>1226</v>
+        <v>1219</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>1227</v>
+        <v>1220</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>1228</v>
+        <v>3</v>
       </c>
       <c r="E256" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>1106</v>
+        <v>1221</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>1229</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B257" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1232</v>
+        <v>1225</v>
       </c>
       <c r="E257" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>1233</v>
+        <v>1103</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B258" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="E258" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B259" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
       <c r="E259" t="s">
-        <v>1637</v>
+        <v>1633</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B260" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="E260" t="s">
-        <v>1638</v>
+        <v>1634</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B261" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="E261" t="s">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B262" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
       <c r="E262" t="s">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>1259</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B263" t="s">
-        <v>1260</v>
+        <v>1252</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1262</v>
+        <v>1254</v>
       </c>
       <c r="E263" t="s">
-        <v>1641</v>
+        <v>1637</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="B264" t="s">
-        <v>1266</v>
+        <v>1257</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>1267</v>
+        <v>1258</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1268</v>
+        <v>1259</v>
       </c>
       <c r="E264" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>1269</v>
+        <v>1260</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1270</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="B265" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>1409</v>
+        <v>1264</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1272</v>
+        <v>1265</v>
       </c>
       <c r="E265" t="s">
-        <v>1659</v>
+        <v>1639</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>1273</v>
+        <v>1266</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1410</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B266" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>1275</v>
+        <v>1406</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>1276</v>
+        <v>1269</v>
       </c>
       <c r="E266" t="s">
-        <v>1660</v>
+        <v>1656</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>1277</v>
+        <v>1270</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1278</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B267" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1248</v>
+        <v>1273</v>
       </c>
       <c r="E267" t="s">
-        <v>1643</v>
+        <v>1657</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>4</v>
+        <v>1274</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>1407</v>
+        <v>1395</v>
       </c>
       <c r="B268" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1284</v>
+        <v>1245</v>
       </c>
       <c r="E268" t="s">
-        <v>1528</v>
+        <v>1640</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>1285</v>
+        <v>4</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="B269" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>1288</v>
+        <v>1280</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="E269" t="s">
-        <v>1644</v>
+        <v>1525</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1291</v>
-      </c>
-      <c r="L269" t="s">
-        <v>1393</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>1408</v>
+        <v>1395</v>
       </c>
       <c r="B270" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
       <c r="E270" t="s">
-        <v>1645</v>
+        <v>1641</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1296</v>
+        <v>1288</v>
+      </c>
+      <c r="L270" t="s">
+        <v>1390</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="B271" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
       <c r="E271" t="s">
-        <v>1646</v>
+        <v>1642</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="B272" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>1303</v>
+        <v>1295</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1304</v>
+        <v>1296</v>
       </c>
       <c r="E272" t="s">
-        <v>1647</v>
+        <v>1643</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>1305</v>
+        <v>1297</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>1720</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B273" t="s">
-        <v>1306</v>
+        <v>1299</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>1307</v>
+        <v>1300</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>1308</v>
+        <v>1301</v>
       </c>
       <c r="E273" t="s">
-        <v>1648</v>
+        <v>1644</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1309</v>
+        <v>1302</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>1310</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B274" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
       <c r="E274" t="s">
-        <v>1495</v>
+        <v>1645</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B275" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E275" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F275" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G275" s="1" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B276" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E276" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F276" s="2" t="s">
         <v>1316</v>
       </c>
-      <c r="C275" s="1" t="s">
+      <c r="G276" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="D275" s="1" t="s">
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B277" t="s">
         <v>1318</v>
       </c>
-      <c r="E275" t="s">
-        <v>1593</v>
-      </c>
-      <c r="F275" s="2" t="s">
+      <c r="C277" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="G275" s="1" t="s">
+      <c r="D277" s="1" t="s">
         <v>1320</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B276" t="s">
+      <c r="E277" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F277" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G277" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="C276" s="1" t="s">
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B278" t="s">
         <v>1322</v>
       </c>
-      <c r="D276" s="1" t="s">
+      <c r="C278" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="E276" t="s">
-        <v>1649</v>
-      </c>
-      <c r="F276" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="G276" s="1" t="s">
+      <c r="D278" s="1" t="s">
         <v>1324</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
-        <v>1398</v>
-      </c>
-      <c r="B277" t="s">
+      <c r="E278" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>1325</v>
       </c>
-      <c r="C277" s="1" t="s">
+      <c r="G278" s="1" t="s">
         <v>1326</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>1327</v>
-      </c>
-      <c r="E277" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F277" s="2" t="s">
-        <v>1328</v>
-      </c>
-      <c r="G277" s="1" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A278" t="s">
-        <v>1398</v>
-      </c>
-      <c r="B278" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C278" s="1" t="s">
-        <v>1331</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>1332</v>
-      </c>
-      <c r="E278" t="s">
-        <v>1487</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>1333</v>
-      </c>
-      <c r="G278" s="1" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="B279" t="s">
-        <v>1335</v>
+        <v>1327</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
       <c r="E279" t="s">
-        <v>1650</v>
+        <v>1484</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>1339</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B280" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E280" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F280" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G280" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B281" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E281" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F281" s="2" t="s">
         <v>1340</v>
       </c>
-      <c r="C280" s="1" t="s">
+      <c r="G281" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="D280" s="1" t="s">
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B282" t="s">
         <v>1342</v>
       </c>
-      <c r="E280" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F280" s="2" t="s">
+      <c r="C282" s="1" t="s">
         <v>1343</v>
       </c>
-      <c r="G280" s="1" t="s">
+      <c r="D282" s="1" t="s">
         <v>1344</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
-        <v>1396</v>
-      </c>
-      <c r="B281" t="s">
+      <c r="E282" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F282" s="2" t="s">
         <v>1345</v>
       </c>
-      <c r="C281" s="1" t="s">
+      <c r="G282" s="1" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B283" t="s">
         <v>1346</v>
       </c>
-      <c r="D281" s="1" t="s">
+      <c r="C283" s="1" t="s">
         <v>1347</v>
       </c>
-      <c r="E281" t="s">
-        <v>1485</v>
-      </c>
-      <c r="F281" s="2" t="s">
+      <c r="D283" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="G281" s="1" t="s">
-        <v>1719</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A282" t="s">
-        <v>1396</v>
-      </c>
-      <c r="B282" t="s">
+      <c r="E283" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>1349</v>
       </c>
-      <c r="C282" s="1" t="s">
+      <c r="G283" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="D282" s="1" t="s">
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B284" t="s">
         <v>1351</v>
       </c>
-      <c r="E282" t="s">
-        <v>1523</v>
-      </c>
-      <c r="F282" s="2" t="s">
+      <c r="C284" s="1" t="s">
         <v>1352</v>
       </c>
-      <c r="G282" s="1" t="s">
+      <c r="D284" s="1" t="s">
         <v>1353</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
-        <v>1406</v>
-      </c>
-      <c r="B283" t="s">
+      <c r="E284" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F284" s="2" t="s">
         <v>1354</v>
       </c>
-      <c r="C283" s="1" t="s">
+      <c r="G284" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="D283" s="1" t="s">
+    </row>
+    <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B285" t="s">
         <v>1356</v>
       </c>
-      <c r="E283" t="s">
-        <v>1651</v>
-      </c>
-      <c r="F283" s="2" t="s">
+      <c r="C285" s="1" t="s">
         <v>1357</v>
       </c>
-      <c r="G283" s="1" t="s">
+      <c r="D285" s="1" t="s">
         <v>1358</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A284" t="s">
-        <v>1402</v>
-      </c>
-      <c r="B284" t="s">
+      <c r="E285" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F285" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G285" s="1" t="s">
         <v>1359</v>
       </c>
-      <c r="C284" s="1" t="s">
+    </row>
+    <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B286" t="s">
         <v>1360</v>
       </c>
-      <c r="D284" s="1" t="s">
+      <c r="C286" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="E284" t="s">
-        <v>1652</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G284" s="1" t="s">
+      <c r="D286" s="1" t="s">
         <v>1362</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B285" t="s">
+      <c r="E286" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F286" s="2" t="s">
         <v>1363</v>
       </c>
-      <c r="C285" s="1" t="s">
+      <c r="G286" s="1" t="s">
         <v>1364</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="E285" t="s">
-        <v>1653</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>1366</v>
-      </c>
-      <c r="G285" s="1" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A286" t="s">
-        <v>1407</v>
-      </c>
-      <c r="B286" t="s">
-        <v>1368</v>
-      </c>
-      <c r="C286" s="1" t="s">
-        <v>1369</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>1370</v>
-      </c>
-      <c r="E286" t="s">
-        <v>1654</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>1371</v>
-      </c>
-      <c r="G286" s="1" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="287" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="B287" t="s">
-        <v>1119</v>
+        <v>1365</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1120</v>
+        <v>1367</v>
       </c>
       <c r="E287" t="s">
-        <v>1655</v>
+        <v>1651</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1375</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="288" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B288" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E288" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F288" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G288" s="1" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B289" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E289" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F289" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G289" s="1" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B290" t="s">
         <v>1376</v>
       </c>
-      <c r="C288" s="1" t="s">
-        <v>1717</v>
-      </c>
-      <c r="D288" s="1" t="s">
+      <c r="C290" s="1" t="s">
         <v>1377</v>
       </c>
-      <c r="E288" t="s">
-        <v>1507</v>
-      </c>
-      <c r="F288" s="2" t="s">
+      <c r="D290" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="G288" s="1" t="s">
-        <v>1718</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
-        <v>1398</v>
-      </c>
-      <c r="B289" t="s">
+      <c r="E290" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>1379</v>
       </c>
-      <c r="C289" s="1" t="s">
+      <c r="G290" s="1" t="s">
         <v>1380</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>1381</v>
-      </c>
-      <c r="E289" t="s">
-        <v>1656</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>1382</v>
-      </c>
-      <c r="G289" s="1" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A290" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B290" t="s">
-        <v>1384</v>
-      </c>
-      <c r="C290" s="1" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>1386</v>
-      </c>
-      <c r="E290" t="s">
-        <v>1528</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>1387</v>
-      </c>
-      <c r="G290" s="1" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
       <c r="B291" t="s">
-        <v>1213</v>
+        <v>1381</v>
       </c>
       <c r="C291" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E291" t="s">
+        <v>1525</v>
+      </c>
+      <c r="F291" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G291" s="1" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B292" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E292" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F292" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G292" s="1" t="s">
         <v>1389</v>
       </c>
-      <c r="D291" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="E291" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>1391</v>
-      </c>
-      <c r="G291" s="1" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
-        <v>1403</v>
-      </c>
-      <c r="B292" t="s">
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B293" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E293" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F293" s="2" t="s">
         <v>1150</v>
       </c>
-      <c r="C292" s="1" t="s">
+      <c r="G293" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="D292" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="E292" t="s">
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A294" s="5" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D294" s="7" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E294" s="6" t="s">
         <v>1619</v>
       </c>
-      <c r="F292" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G292" s="1" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A293" s="5" t="s">
-        <v>1403</v>
-      </c>
-      <c r="B293" s="6" t="s">
+      <c r="F294" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="C293" s="7" t="s">
+      <c r="G294" s="7" t="s">
         <v>1171</v>
-      </c>
-      <c r="D293" s="7" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E293" s="6" t="s">
-        <v>1622</v>
-      </c>
-      <c r="F293" s="8" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G293" s="7" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>1403</v>
-      </c>
-      <c r="B294" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E294" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>1158</v>
-      </c>
-      <c r="G294" s="1" t="s">
-        <v>1716</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B295" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
       <c r="E295" t="s">
-        <v>1643</v>
+        <v>1486</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>1164</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B296" t="s">
-        <v>1165</v>
+        <v>1157</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>1166</v>
+        <v>1158</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>1167</v>
+        <v>1159</v>
       </c>
       <c r="E296" t="s">
-        <v>1658</v>
+        <v>1640</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>1714</v>
+        <v>1160</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>1715</v>
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B297" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E297" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F297" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E298" s="9" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F298" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="G298" t="s">
+        <v>1724</v>
       </c>
     </row>
   </sheetData>
